--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8601,7 +8601,8 @@
       </c>
       <c r="G339" s="5" t="inlineStr">
         <is>
-          <t>Film - Linda Wilson</t>
+          <t>Film - Linda Wilson
+Film - Linda Wilson</t>
         </is>
       </c>
       <c r="H339" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -10596,11 +10596,7 @@
       <c r="F403" s="4" t="n"/>
       <c r="G403" s="4" t="n"/>
       <c r="H403" s="4" t="n"/>
-      <c r="I403" s="5" t="inlineStr">
-        <is>
-          <t>Film - LGBTQ+</t>
-        </is>
-      </c>
+      <c r="I403" s="4" t="n"/>
       <c r="J403" s="4" t="n"/>
       <c r="K403" s="4" t="n"/>
       <c r="L403" s="4" t="n"/>
@@ -10620,11 +10616,7 @@
       <c r="F404" s="4" t="n"/>
       <c r="G404" s="4" t="n"/>
       <c r="H404" s="4" t="n"/>
-      <c r="I404" s="5" t="inlineStr">
-        <is>
-          <t>Film - LGBTQ+</t>
-        </is>
-      </c>
+      <c r="I404" s="4" t="n"/>
       <c r="J404" s="4" t="n"/>
       <c r="K404" s="4" t="n"/>
       <c r="L404" s="4" t="n"/>
@@ -10652,11 +10644,7 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I405" s="5" t="inlineStr">
-        <is>
-          <t>Film - LGBTQ+</t>
-        </is>
-      </c>
+      <c r="I405" s="4" t="n"/>
       <c r="J405" s="4" t="n"/>
       <c r="K405" s="4" t="n"/>
       <c r="L405" s="4" t="n"/>
@@ -10716,11 +10704,7 @@
       <c r="F408" s="4" t="n"/>
       <c r="G408" s="4" t="n"/>
       <c r="H408" s="4" t="n"/>
-      <c r="I408" s="5" t="inlineStr">
-        <is>
-          <t>Film - LGBTQ+</t>
-        </is>
-      </c>
+      <c r="I408" s="4" t="n"/>
       <c r="J408" s="4" t="n"/>
       <c r="K408" s="4" t="n"/>
       <c r="L408" s="4" t="n"/>
@@ -10740,11 +10724,7 @@
       <c r="F409" s="4" t="n"/>
       <c r="G409" s="4" t="n"/>
       <c r="H409" s="4" t="n"/>
-      <c r="I409" s="5" t="inlineStr">
-        <is>
-          <t>Film - LGBTQ+</t>
-        </is>
-      </c>
+      <c r="I409" s="4" t="n"/>
       <c r="J409" s="4" t="n"/>
       <c r="K409" s="4" t="n"/>
       <c r="L409" s="4" t="n"/>
@@ -10924,11 +10904,7 @@
       <c r="F417" s="4" t="n"/>
       <c r="G417" s="4" t="n"/>
       <c r="H417" s="4" t="n"/>
-      <c r="I417" s="5" t="inlineStr">
-        <is>
-          <t>Film - LGBTQ+</t>
-        </is>
-      </c>
+      <c r="I417" s="4" t="n"/>
       <c r="J417" s="4" t="n"/>
       <c r="K417" s="4" t="n"/>
       <c r="L417" s="4" t="n"/>
@@ -10948,11 +10924,7 @@
       <c r="F418" s="4" t="n"/>
       <c r="G418" s="4" t="n"/>
       <c r="H418" s="4" t="n"/>
-      <c r="I418" s="5" t="inlineStr">
-        <is>
-          <t>Film - LGBTQ+</t>
-        </is>
-      </c>
+      <c r="I418" s="4" t="n"/>
       <c r="J418" s="4" t="n"/>
       <c r="K418" s="4" t="n"/>
       <c r="L418" s="4" t="n"/>
@@ -10972,11 +10944,7 @@
       <c r="F419" s="4" t="n"/>
       <c r="G419" s="4" t="n"/>
       <c r="H419" s="4" t="n"/>
-      <c r="I419" s="5" t="inlineStr">
-        <is>
-          <t>Film - LGBTQ+</t>
-        </is>
-      </c>
+      <c r="I419" s="4" t="n"/>
       <c r="J419" s="4" t="n"/>
       <c r="K419" s="4" t="n"/>
       <c r="L419" s="4" t="n"/>
@@ -11036,11 +11004,7 @@
       <c r="F422" s="4" t="n"/>
       <c r="G422" s="4" t="n"/>
       <c r="H422" s="4" t="n"/>
-      <c r="I422" s="5" t="inlineStr">
-        <is>
-          <t>Film - LGBTQ+</t>
-        </is>
-      </c>
+      <c r="I422" s="4" t="n"/>
       <c r="J422" s="4" t="n"/>
       <c r="K422" s="4" t="n"/>
       <c r="L422" s="4" t="n"/>
@@ -11068,11 +11032,7 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="I423" s="5" t="inlineStr">
-        <is>
-          <t>Film - LGBTQ+</t>
-        </is>
-      </c>
+      <c r="I423" s="4" t="n"/>
       <c r="J423" s="4" t="n"/>
       <c r="K423" s="4" t="n"/>
       <c r="L423" s="4" t="n"/>
@@ -11100,11 +11060,7 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="I424" s="5" t="inlineStr">
-        <is>
-          <t>Film - LGBTQ+</t>
-        </is>
-      </c>
+      <c r="I424" s="4" t="n"/>
       <c r="J424" s="4" t="n"/>
       <c r="K424" s="4" t="n"/>
       <c r="L424" s="4" t="n"/>
@@ -11132,11 +11088,7 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="I425" s="5" t="inlineStr">
-        <is>
-          <t>Film - LGBTQ+</t>
-        </is>
-      </c>
+      <c r="I425" s="4" t="n"/>
       <c r="J425" s="4" t="n"/>
       <c r="K425" s="4" t="n"/>
       <c r="L425" s="4" t="n"/>
@@ -11164,11 +11116,7 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="I426" s="5" t="inlineStr">
-        <is>
-          <t>Film - LGBTQ+</t>
-        </is>
-      </c>
+      <c r="I426" s="4" t="n"/>
       <c r="J426" s="4" t="n"/>
       <c r="K426" s="4" t="n"/>
       <c r="L426" s="4" t="n"/>
@@ -11228,11 +11176,7 @@
       <c r="F429" s="4" t="n"/>
       <c r="G429" s="4" t="n"/>
       <c r="H429" s="4" t="n"/>
-      <c r="I429" s="5" t="inlineStr">
-        <is>
-          <t>Film - LGBTQ+</t>
-        </is>
-      </c>
+      <c r="I429" s="4" t="n"/>
       <c r="J429" s="4" t="n"/>
       <c r="K429" s="4" t="n"/>
       <c r="L429" s="4" t="n"/>
@@ -11252,11 +11196,7 @@
       <c r="F430" s="4" t="n"/>
       <c r="G430" s="4" t="n"/>
       <c r="H430" s="4" t="n"/>
-      <c r="I430" s="5" t="inlineStr">
-        <is>
-          <t>Film - LGBTQ+</t>
-        </is>
-      </c>
+      <c r="I430" s="4" t="n"/>
       <c r="J430" s="4" t="n"/>
       <c r="K430" s="4" t="n"/>
       <c r="L430" s="4" t="n"/>
@@ -11376,11 +11316,7 @@
       <c r="F436" s="4" t="n"/>
       <c r="G436" s="4" t="n"/>
       <c r="H436" s="4" t="n"/>
-      <c r="I436" s="5" t="inlineStr">
-        <is>
-          <t>Film - LGBTQ+</t>
-        </is>
-      </c>
+      <c r="I436" s="4" t="n"/>
       <c r="J436" s="4" t="n"/>
       <c r="K436" s="4" t="n"/>
       <c r="L436" s="4" t="n"/>
@@ -11400,11 +11336,7 @@
       <c r="F437" s="4" t="n"/>
       <c r="G437" s="4" t="n"/>
       <c r="H437" s="4" t="n"/>
-      <c r="I437" s="5" t="inlineStr">
-        <is>
-          <t>Film - LGBTQ+</t>
-        </is>
-      </c>
+      <c r="I437" s="4" t="n"/>
       <c r="J437" s="4" t="n"/>
       <c r="K437" s="4" t="n"/>
       <c r="L437" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -10347,7 +10347,11 @@
       <c r="F394" s="4" t="n"/>
       <c r="G394" s="4" t="n"/>
       <c r="H394" s="4" t="n"/>
-      <c r="I394" s="4" t="n"/>
+      <c r="I394" s="5" t="inlineStr">
+        <is>
+          <t>Dub - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="J394" s="4" t="n"/>
       <c r="K394" s="11" t="inlineStr">
         <is>
@@ -10375,7 +10379,12 @@
       <c r="F395" s="4" t="n"/>
       <c r="G395" s="4" t="n"/>
       <c r="H395" s="4" t="n"/>
-      <c r="I395" s="4" t="n"/>
+      <c r="I395" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Mabli a Ceff Ceff
+Dub - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="J395" s="4" t="n"/>
       <c r="K395" s="11" t="inlineStr">
         <is>
@@ -10406,7 +10415,8 @@
       <c r="I396" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Mabli a Ceff Ceff
-Dub - Mabli a Ceff Ceff</t>
+Dub - Mabli a Ceff Ceff
+Online Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="J396" s="4" t="n"/>
@@ -10473,10 +10483,10 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I398" s="11" t="inlineStr">
-        <is>
-          <t>Online Edit - Mabli a Ceff Ceff
-Dub - Mabli a Ceff Ceff</t>
+      <c r="I398" s="5" t="inlineStr">
+        <is>
+          <t>Dub - Mabli a Ceff Ceff
+Online Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="J398" s="4" t="n"/>
@@ -10542,12 +10552,7 @@
       <c r="F401" s="4" t="n"/>
       <c r="G401" s="4" t="n"/>
       <c r="H401" s="4" t="n"/>
-      <c r="I401" s="11" t="inlineStr">
-        <is>
-          <t>Online Edit - Mabli a Ceff Ceff
-Dub - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="I401" s="4" t="n"/>
       <c r="J401" s="4" t="n"/>
       <c r="K401" s="11" t="inlineStr">
         <is>
@@ -10571,12 +10576,7 @@
       <c r="F402" s="4" t="n"/>
       <c r="G402" s="4" t="n"/>
       <c r="H402" s="4" t="n"/>
-      <c r="I402" s="5" t="inlineStr">
-        <is>
-          <t>Dub - Mabli a Ceff Ceff
-Online Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="I402" s="4" t="n"/>
       <c r="J402" s="4" t="n"/>
       <c r="K402" s="4" t="n"/>
       <c r="L402" s="4" t="n"/>
@@ -11620,9 +11620,10 @@
       <c r="F450" s="4" t="n"/>
       <c r="G450" s="4" t="n"/>
       <c r="H450" s="4" t="n"/>
-      <c r="I450" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
+      <c r="I450" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+Offline Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="J450" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -10347,7 +10347,11 @@
       <c r="F394" s="4" t="n"/>
       <c r="G394" s="4" t="n"/>
       <c r="H394" s="4" t="n"/>
-      <c r="I394" s="4" t="n"/>
+      <c r="I394" s="5" t="inlineStr">
+        <is>
+          <t>Dub - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="J394" s="4" t="n"/>
       <c r="K394" s="11" t="inlineStr">
         <is>
@@ -10375,7 +10379,12 @@
       <c r="F395" s="4" t="n"/>
       <c r="G395" s="4" t="n"/>
       <c r="H395" s="4" t="n"/>
-      <c r="I395" s="4" t="n"/>
+      <c r="I395" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Mabli a Ceff Ceff
+Dub - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="J395" s="4" t="n"/>
       <c r="K395" s="11" t="inlineStr">
         <is>
@@ -10406,7 +10415,8 @@
       <c r="I396" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Mabli a Ceff Ceff
-Dub - Mabli a Ceff Ceff</t>
+Dub - Mabli a Ceff Ceff
+Online Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="J396" s="4" t="n"/>
@@ -10473,10 +10483,10 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I398" s="11" t="inlineStr">
-        <is>
-          <t>Online Edit - Mabli a Ceff Ceff
-Dub - Mabli a Ceff Ceff</t>
+      <c r="I398" s="5" t="inlineStr">
+        <is>
+          <t>Dub - Mabli a Ceff Ceff
+Online Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="J398" s="4" t="n"/>
@@ -10542,12 +10552,7 @@
       <c r="F401" s="4" t="n"/>
       <c r="G401" s="4" t="n"/>
       <c r="H401" s="4" t="n"/>
-      <c r="I401" s="11" t="inlineStr">
-        <is>
-          <t>Online Edit - Mabli a Ceff Ceff
-Dub - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="I401" s="4" t="n"/>
       <c r="J401" s="4" t="n"/>
       <c r="K401" s="11" t="inlineStr">
         <is>
@@ -10571,12 +10576,7 @@
       <c r="F402" s="4" t="n"/>
       <c r="G402" s="4" t="n"/>
       <c r="H402" s="4" t="n"/>
-      <c r="I402" s="5" t="inlineStr">
-        <is>
-          <t>Dub - Mabli a Ceff Ceff
-Online Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="I402" s="4" t="n"/>
       <c r="J402" s="4" t="n"/>
       <c r="K402" s="4" t="n"/>
       <c r="L402" s="4" t="n"/>
@@ -11620,9 +11620,10 @@
       <c r="F450" s="4" t="n"/>
       <c r="G450" s="4" t="n"/>
       <c r="H450" s="4" t="n"/>
-      <c r="I450" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
+      <c r="I450" s="5" t="inlineStr">
+        <is>
+          <t>Film - Y Grŵp Chat
+Offline Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="J450" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -11617,7 +11617,11 @@
       <c r="C450" s="4" t="n"/>
       <c r="D450" s="4" t="n"/>
       <c r="E450" s="4" t="n"/>
-      <c r="F450" s="4" t="n"/>
+      <c r="F450" s="5" t="inlineStr">
+        <is>
+          <t>Film - Y Grŵp Chat</t>
+        </is>
+      </c>
       <c r="G450" s="4" t="n"/>
       <c r="H450" s="4" t="n"/>
       <c r="I450" s="5" t="inlineStr">
@@ -11834,7 +11838,11 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J459" s="4" t="n"/>
+      <c r="J459" s="5" t="inlineStr">
+        <is>
+          <t>Hwyl Fawr Blodwen</t>
+        </is>
+      </c>
       <c r="K459" s="4" t="n"/>
       <c r="L459" s="4" t="n"/>
       <c r="M459" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -11646,7 +11646,11 @@
       <c r="C451" s="4" t="n"/>
       <c r="D451" s="4" t="n"/>
       <c r="E451" s="4" t="n"/>
-      <c r="F451" s="4" t="n"/>
+      <c r="F451" s="5" t="inlineStr">
+        <is>
+          <t>Film - Y Grŵp Chat</t>
+        </is>
+      </c>
       <c r="G451" s="4" t="n"/>
       <c r="H451" s="4" t="n"/>
       <c r="I451" s="11" t="inlineStr">
@@ -11828,19 +11832,28 @@
       </c>
       <c r="B459" s="4" t="n"/>
       <c r="C459" s="4" t="n"/>
-      <c r="D459" s="4" t="n"/>
+      <c r="D459" s="5" t="inlineStr">
+        <is>
+          <t>Film - Hwyl Fawr Blodwen</t>
+        </is>
+      </c>
       <c r="E459" s="4" t="n"/>
-      <c r="F459" s="4" t="n"/>
+      <c r="F459" s="5" t="inlineStr">
+        <is>
+          <t>Film - Hwyl Fawr Blodwen</t>
+        </is>
+      </c>
       <c r="G459" s="4" t="n"/>
       <c r="H459" s="4" t="n"/>
-      <c r="I459" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
+      <c r="I459" s="5" t="inlineStr">
+        <is>
+          <t>Film - Hwyl Fawr Blodwen
+Offline Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="J459" s="5" t="inlineStr">
         <is>
-          <t>Hwyl Fawr Blodwen</t>
+          <t>Film - Hwyl Fawr Blodwen</t>
         </is>
       </c>
       <c r="K459" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -10347,9 +10347,10 @@
       <c r="F394" s="4" t="n"/>
       <c r="G394" s="4" t="n"/>
       <c r="H394" s="4" t="n"/>
-      <c r="I394" s="5" t="inlineStr">
-        <is>
-          <t>Dub - Mabli a Ceff Ceff</t>
+      <c r="I394" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Mabli a Ceff Ceff
+Dub - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="J394" s="4" t="n"/>
@@ -10415,8 +10416,7 @@
       <c r="I396" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Mabli a Ceff Ceff
-Dub - Mabli a Ceff Ceff
-Online Edit - Mabli a Ceff Ceff</t>
+Dub - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="J396" s="4" t="n"/>
@@ -11653,9 +11653,10 @@
       </c>
       <c r="G451" s="4" t="n"/>
       <c r="H451" s="4" t="n"/>
-      <c r="I451" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
+      <c r="I451" s="5" t="inlineStr">
+        <is>
+          <t>Film - Y Grŵp Chat
+Offline Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="J451" s="4" t="n"/>
@@ -11869,17 +11870,30 @@
       </c>
       <c r="B460" s="4" t="n"/>
       <c r="C460" s="4" t="n"/>
-      <c r="D460" s="4" t="n"/>
+      <c r="D460" s="5" t="inlineStr">
+        <is>
+          <t>Film - Hwyl Fawr Blodwen</t>
+        </is>
+      </c>
       <c r="E460" s="4" t="n"/>
-      <c r="F460" s="4" t="n"/>
+      <c r="F460" s="5" t="inlineStr">
+        <is>
+          <t>Film - Hwyl Fawr Blodwen</t>
+        </is>
+      </c>
       <c r="G460" s="4" t="n"/>
       <c r="H460" s="4" t="n"/>
-      <c r="I460" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
-      <c r="J460" s="4" t="n"/>
+      <c r="I460" s="5" t="inlineStr">
+        <is>
+          <t>Film - Hwyl Fawr Blodwen
+Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="J460" s="5" t="inlineStr">
+        <is>
+          <t>Film - Hwyl Fawr Blodwen</t>
+        </is>
+      </c>
       <c r="K460" s="4" t="n"/>
       <c r="L460" s="4" t="n"/>
       <c r="M460" s="4" t="n"/>
@@ -11893,17 +11907,30 @@
       </c>
       <c r="B461" s="4" t="n"/>
       <c r="C461" s="4" t="n"/>
-      <c r="D461" s="4" t="n"/>
+      <c r="D461" s="5" t="inlineStr">
+        <is>
+          <t>Film - Hwyl Fawr Blodwen</t>
+        </is>
+      </c>
       <c r="E461" s="4" t="n"/>
-      <c r="F461" s="4" t="n"/>
+      <c r="F461" s="5" t="inlineStr">
+        <is>
+          <t>Film - Hwyl Fawr Blodwen</t>
+        </is>
+      </c>
       <c r="G461" s="4" t="n"/>
       <c r="H461" s="4" t="n"/>
-      <c r="I461" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
-      <c r="J461" s="4" t="n"/>
+      <c r="I461" s="5" t="inlineStr">
+        <is>
+          <t>Film - Hwyl Fawr Blodwen
+Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="J461" s="5" t="inlineStr">
+        <is>
+          <t>Film - Hwyl Fawr Blodwen</t>
+        </is>
+      </c>
       <c r="K461" s="4" t="n"/>
       <c r="L461" s="4" t="n"/>
       <c r="M461" s="4" t="n"/>
@@ -13267,7 +13294,11 @@
       <c r="C520" s="4" t="n"/>
       <c r="D520" s="4" t="n"/>
       <c r="E520" s="4" t="n"/>
-      <c r="F520" s="4" t="n"/>
+      <c r="F520" s="5" t="inlineStr">
+        <is>
+          <t>Film - Cogydd</t>
+        </is>
+      </c>
       <c r="G520" s="4" t="n"/>
       <c r="H520" s="4" t="n"/>
       <c r="I520" s="5" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -13322,7 +13322,11 @@
       <c r="C521" s="4" t="n"/>
       <c r="D521" s="4" t="n"/>
       <c r="E521" s="4" t="n"/>
-      <c r="F521" s="4" t="n"/>
+      <c r="F521" s="5" t="inlineStr">
+        <is>
+          <t>Film - Cogydd</t>
+        </is>
+      </c>
       <c r="G521" s="4" t="n"/>
       <c r="H521" s="4" t="n"/>
       <c r="I521" s="5" t="inlineStr">
@@ -13346,7 +13350,11 @@
       <c r="C522" s="4" t="n"/>
       <c r="D522" s="4" t="n"/>
       <c r="E522" s="4" t="n"/>
-      <c r="F522" s="4" t="n"/>
+      <c r="F522" s="5" t="inlineStr">
+        <is>
+          <t>Film - Cogydd</t>
+        </is>
+      </c>
       <c r="G522" s="4" t="n"/>
       <c r="H522" s="4" t="n"/>
       <c r="I522" s="5" t="inlineStr">
@@ -13370,7 +13378,11 @@
       <c r="C523" s="4" t="n"/>
       <c r="D523" s="4" t="n"/>
       <c r="E523" s="4" t="n"/>
-      <c r="F523" s="4" t="n"/>
+      <c r="F523" s="5" t="inlineStr">
+        <is>
+          <t>Film - Cogydd</t>
+        </is>
+      </c>
       <c r="G523" s="4" t="n"/>
       <c r="H523" s="4" t="n"/>
       <c r="I523" s="5" t="inlineStr">
@@ -13394,7 +13406,11 @@
       <c r="C524" s="4" t="n"/>
       <c r="D524" s="4" t="n"/>
       <c r="E524" s="4" t="n"/>
-      <c r="F524" s="4" t="n"/>
+      <c r="F524" s="5" t="inlineStr">
+        <is>
+          <t>Film - Cogydd</t>
+        </is>
+      </c>
       <c r="G524" s="4" t="n"/>
       <c r="H524" s="4" t="n"/>
       <c r="I524" s="5" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8349,7 +8349,11 @@
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="M331" s="4" t="n"/>
+      <c r="M331" s="5" t="inlineStr">
+        <is>
+          <t>Sick</t>
+        </is>
+      </c>
       <c r="N331" s="10" t="inlineStr">
         <is>
           <t>TOIL - Darts 6 G</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8605,8 +8605,7 @@
       </c>
       <c r="G339" s="5" t="inlineStr">
         <is>
-          <t>Film - Linda Wilson
-Film - Linda Wilson</t>
+          <t>Film - Linda Wilson</t>
         </is>
       </c>
       <c r="H339" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8385,7 +8385,7 @@
       <c r="J332" s="4" t="n"/>
       <c r="K332" s="5" t="inlineStr">
         <is>
-          <t>Rhwym Galon</t>
+          <t>Rhedeg Rhacs</t>
         </is>
       </c>
       <c r="L332" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N535"/>
+  <dimension ref="A1:O535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -513,6 +513,7 @@
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -538,50 +539,55 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>Dan Rees</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>Derwena Burt</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Elin Jones</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Euros Llyr Morgan</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Iestyn O'Leary</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Jason Lye-Phillips</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Lara Hughes</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Osian Lewis</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Owain Jones</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Rhodri Lewis</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Wil Williams</t>
         </is>
@@ -604,12 +610,13 @@
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>Sick - Sick</t>
         </is>
       </c>
-      <c r="N2" s="4" t="n"/>
+      <c r="O2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -628,12 +635,13 @@
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
       <c r="L3" s="4" t="n"/>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>Sick - Sick</t>
         </is>
       </c>
-      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -652,12 +660,13 @@
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>Sick - Sick</t>
         </is>
       </c>
-      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -676,12 +685,13 @@
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>Sick - Sick</t>
         </is>
       </c>
-      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -700,12 +710,13 @@
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>Sick - Sick</t>
         </is>
       </c>
-      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -726,6 +737,7 @@
       <c r="L7" s="7" t="n"/>
       <c r="M7" s="7" t="n"/>
       <c r="N7" s="7" t="n"/>
+      <c r="O7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -746,6 +758,7 @@
       <c r="L8" s="7" t="n"/>
       <c r="M8" s="7" t="n"/>
       <c r="N8" s="7" t="n"/>
+      <c r="O8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -766,6 +779,7 @@
       <c r="L9" s="4" t="n"/>
       <c r="M9" s="4" t="n"/>
       <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -786,6 +800,7 @@
       <c r="L10" s="4" t="n"/>
       <c r="M10" s="4" t="n"/>
       <c r="N10" s="4" t="n"/>
+      <c r="O10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -806,6 +821,7 @@
       <c r="L11" s="4" t="n"/>
       <c r="M11" s="4" t="n"/>
       <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -826,6 +842,7 @@
       <c r="L12" s="4" t="n"/>
       <c r="M12" s="4" t="n"/>
       <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -846,6 +863,7 @@
       <c r="L13" s="4" t="n"/>
       <c r="M13" s="4" t="n"/>
       <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -866,6 +884,7 @@
       <c r="L14" s="7" t="n"/>
       <c r="M14" s="7" t="n"/>
       <c r="N14" s="7" t="n"/>
+      <c r="O14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -886,6 +905,7 @@
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="7" t="n"/>
       <c r="N15" s="7" t="n"/>
+      <c r="O15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -906,6 +926,7 @@
       <c r="L16" s="4" t="n"/>
       <c r="M16" s="4" t="n"/>
       <c r="N16" s="4" t="n"/>
+      <c r="O16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -926,6 +947,7 @@
       <c r="L17" s="4" t="n"/>
       <c r="M17" s="4" t="n"/>
       <c r="N17" s="4" t="n"/>
+      <c r="O17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -946,6 +968,7 @@
       <c r="L18" s="4" t="n"/>
       <c r="M18" s="4" t="n"/>
       <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -966,6 +989,7 @@
       <c r="L19" s="4" t="n"/>
       <c r="M19" s="4" t="n"/>
       <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -986,6 +1010,7 @@
       <c r="L20" s="4" t="n"/>
       <c r="M20" s="4" t="n"/>
       <c r="N20" s="4" t="n"/>
+      <c r="O20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -1006,6 +1031,7 @@
       <c r="L21" s="7" t="n"/>
       <c r="M21" s="7" t="n"/>
       <c r="N21" s="7" t="n"/>
+      <c r="O21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -1026,6 +1052,7 @@
       <c r="L22" s="7" t="n"/>
       <c r="M22" s="7" t="n"/>
       <c r="N22" s="7" t="n"/>
+      <c r="O22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1046,6 +1073,7 @@
       <c r="L23" s="4" t="n"/>
       <c r="M23" s="4" t="n"/>
       <c r="N23" s="4" t="n"/>
+      <c r="O23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1066,6 +1094,7 @@
       <c r="L24" s="4" t="n"/>
       <c r="M24" s="4" t="n"/>
       <c r="N24" s="4" t="n"/>
+      <c r="O24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1086,6 +1115,7 @@
       <c r="L25" s="4" t="n"/>
       <c r="M25" s="4" t="n"/>
       <c r="N25" s="4" t="n"/>
+      <c r="O25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1106,6 +1136,7 @@
       <c r="L26" s="4" t="n"/>
       <c r="M26" s="4" t="n"/>
       <c r="N26" s="4" t="n"/>
+      <c r="O26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1126,6 +1157,7 @@
       <c r="L27" s="4" t="n"/>
       <c r="M27" s="4" t="n"/>
       <c r="N27" s="4" t="n"/>
+      <c r="O27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -1146,6 +1178,7 @@
       <c r="L28" s="7" t="n"/>
       <c r="M28" s="7" t="n"/>
       <c r="N28" s="7" t="n"/>
+      <c r="O28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -1166,6 +1199,7 @@
       <c r="L29" s="7" t="n"/>
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="7" t="n"/>
+      <c r="O29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -1186,6 +1220,7 @@
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
       <c r="N30" s="4" t="n"/>
+      <c r="O30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1206,6 +1241,7 @@
       <c r="L31" s="4" t="n"/>
       <c r="M31" s="4" t="n"/>
       <c r="N31" s="4" t="n"/>
+      <c r="O31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -1230,6 +1266,7 @@
       <c r="L32" s="4" t="n"/>
       <c r="M32" s="4" t="n"/>
       <c r="N32" s="4" t="n"/>
+      <c r="O32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -1254,6 +1291,7 @@
       <c r="L33" s="4" t="n"/>
       <c r="M33" s="4" t="n"/>
       <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -1278,6 +1316,7 @@
       <c r="L34" s="4" t="n"/>
       <c r="M34" s="4" t="n"/>
       <c r="N34" s="4" t="n"/>
+      <c r="O34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -1298,6 +1337,7 @@
       <c r="L35" s="7" t="n"/>
       <c r="M35" s="7" t="n"/>
       <c r="N35" s="7" t="n"/>
+      <c r="O35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -1318,6 +1358,7 @@
       <c r="L36" s="7" t="n"/>
       <c r="M36" s="7" t="n"/>
       <c r="N36" s="7" t="n"/>
+      <c r="O36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1342,6 +1383,7 @@
       <c r="L37" s="4" t="n"/>
       <c r="M37" s="4" t="n"/>
       <c r="N37" s="4" t="n"/>
+      <c r="O37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -1366,6 +1408,7 @@
       <c r="L38" s="4" t="n"/>
       <c r="M38" s="4" t="n"/>
       <c r="N38" s="4" t="n"/>
+      <c r="O38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -1386,14 +1429,15 @@
       <c r="H39" s="4" t="n"/>
       <c r="I39" s="4" t="n"/>
       <c r="J39" s="4" t="n"/>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="K39" s="4" t="n"/>
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>Sick - Sick</t>
         </is>
       </c>
-      <c r="L39" s="4" t="n"/>
       <c r="M39" s="4" t="n"/>
       <c r="N39" s="4" t="n"/>
+      <c r="O39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -1410,14 +1454,15 @@
       <c r="H40" s="4" t="n"/>
       <c r="I40" s="4" t="n"/>
       <c r="J40" s="4" t="n"/>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="K40" s="4" t="n"/>
+      <c r="L40" s="5" t="inlineStr">
         <is>
           <t>Sick - Sick</t>
         </is>
       </c>
-      <c r="L40" s="4" t="n"/>
       <c r="M40" s="4" t="n"/>
       <c r="N40" s="4" t="n"/>
+      <c r="O40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -1438,6 +1483,7 @@
       <c r="L41" s="4" t="n"/>
       <c r="M41" s="4" t="n"/>
       <c r="N41" s="4" t="n"/>
+      <c r="O41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -1458,6 +1504,7 @@
       <c r="L42" s="7" t="n"/>
       <c r="M42" s="7" t="n"/>
       <c r="N42" s="7" t="n"/>
+      <c r="O42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -1478,6 +1525,7 @@
       <c r="L43" s="7" t="n"/>
       <c r="M43" s="7" t="n"/>
       <c r="N43" s="7" t="n"/>
+      <c r="O43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -1498,6 +1546,7 @@
       <c r="L44" s="4" t="n"/>
       <c r="M44" s="4" t="n"/>
       <c r="N44" s="4" t="n"/>
+      <c r="O44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -1518,6 +1567,7 @@
       <c r="L45" s="4" t="n"/>
       <c r="M45" s="4" t="n"/>
       <c r="N45" s="4" t="n"/>
+      <c r="O45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -1538,6 +1588,7 @@
       <c r="L46" s="4" t="n"/>
       <c r="M46" s="4" t="n"/>
       <c r="N46" s="4" t="n"/>
+      <c r="O46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -1558,6 +1609,7 @@
       <c r="L47" s="4" t="n"/>
       <c r="M47" s="4" t="n"/>
       <c r="N47" s="4" t="n"/>
+      <c r="O47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -1578,6 +1630,7 @@
       <c r="L48" s="4" t="n"/>
       <c r="M48" s="4" t="n"/>
       <c r="N48" s="4" t="n"/>
+      <c r="O48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -1598,6 +1651,7 @@
       <c r="L49" s="7" t="n"/>
       <c r="M49" s="7" t="n"/>
       <c r="N49" s="7" t="n"/>
+      <c r="O49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -1618,6 +1672,7 @@
       <c r="L50" s="7" t="n"/>
       <c r="M50" s="7" t="n"/>
       <c r="N50" s="7" t="n"/>
+      <c r="O50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -1638,6 +1693,7 @@
       <c r="L51" s="4" t="n"/>
       <c r="M51" s="4" t="n"/>
       <c r="N51" s="4" t="n"/>
+      <c r="O51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -1658,6 +1714,7 @@
       <c r="L52" s="4" t="n"/>
       <c r="M52" s="4" t="n"/>
       <c r="N52" s="4" t="n"/>
+      <c r="O52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -1678,6 +1735,7 @@
       <c r="L53" s="4" t="n"/>
       <c r="M53" s="4" t="n"/>
       <c r="N53" s="4" t="n"/>
+      <c r="O53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -1698,6 +1756,7 @@
       <c r="L54" s="4" t="n"/>
       <c r="M54" s="4" t="n"/>
       <c r="N54" s="4" t="n"/>
+      <c r="O54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -1718,6 +1777,7 @@
       <c r="L55" s="4" t="n"/>
       <c r="M55" s="4" t="n"/>
       <c r="N55" s="4" t="n"/>
+      <c r="O55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -1738,6 +1798,7 @@
       <c r="L56" s="7" t="n"/>
       <c r="M56" s="7" t="n"/>
       <c r="N56" s="7" t="n"/>
+      <c r="O56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -1758,6 +1819,7 @@
       <c r="L57" s="7" t="n"/>
       <c r="M57" s="7" t="n"/>
       <c r="N57" s="7" t="n"/>
+      <c r="O57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -1774,14 +1836,15 @@
       <c r="H58" s="4" t="n"/>
       <c r="I58" s="4" t="n"/>
       <c r="J58" s="4" t="n"/>
-      <c r="K58" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L58" s="4" t="n"/>
+      <c r="K58" s="4" t="n"/>
+      <c r="L58" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M58" s="4" t="n"/>
       <c r="N58" s="4" t="n"/>
+      <c r="O58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -1798,14 +1861,15 @@
       <c r="H59" s="4" t="n"/>
       <c r="I59" s="4" t="n"/>
       <c r="J59" s="4" t="n"/>
-      <c r="K59" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L59" s="4" t="n"/>
+      <c r="K59" s="4" t="n"/>
+      <c r="L59" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M59" s="4" t="n"/>
       <c r="N59" s="4" t="n"/>
+      <c r="O59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -1826,6 +1890,7 @@
       <c r="L60" s="4" t="n"/>
       <c r="M60" s="4" t="n"/>
       <c r="N60" s="4" t="n"/>
+      <c r="O60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -1846,6 +1911,7 @@
       <c r="L61" s="4" t="n"/>
       <c r="M61" s="4" t="n"/>
       <c r="N61" s="4" t="n"/>
+      <c r="O61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -1866,6 +1932,7 @@
       <c r="L62" s="4" t="n"/>
       <c r="M62" s="4" t="n"/>
       <c r="N62" s="4" t="n"/>
+      <c r="O62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -1886,6 +1953,7 @@
       <c r="L63" s="7" t="n"/>
       <c r="M63" s="7" t="n"/>
       <c r="N63" s="7" t="n"/>
+      <c r="O63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
@@ -1906,6 +1974,7 @@
       <c r="L64" s="7" t="n"/>
       <c r="M64" s="7" t="n"/>
       <c r="N64" s="7" t="n"/>
+      <c r="O64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -1923,25 +1992,26 @@
       <c r="E65" s="4" t="n"/>
       <c r="F65" s="4" t="n"/>
       <c r="G65" s="4" t="n"/>
-      <c r="H65" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="H65" s="4" t="n"/>
       <c r="I65" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="J65" s="4" t="n"/>
-      <c r="K65" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L65" s="4" t="n"/>
+      <c r="J65" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="K65" s="4" t="n"/>
+      <c r="L65" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M65" s="4" t="n"/>
       <c r="N65" s="4" t="n"/>
+      <c r="O65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -1959,25 +2029,26 @@
       <c r="E66" s="4" t="n"/>
       <c r="F66" s="4" t="n"/>
       <c r="G66" s="4" t="n"/>
-      <c r="H66" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="H66" s="4" t="n"/>
       <c r="I66" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="J66" s="4" t="n"/>
-      <c r="K66" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L66" s="4" t="n"/>
+      <c r="J66" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="n"/>
+      <c r="L66" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M66" s="4" t="n"/>
       <c r="N66" s="4" t="n"/>
+      <c r="O66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -1995,25 +2066,26 @@
       <c r="E67" s="4" t="n"/>
       <c r="F67" s="4" t="n"/>
       <c r="G67" s="4" t="n"/>
-      <c r="H67" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="H67" s="4" t="n"/>
       <c r="I67" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="J67" s="4" t="n"/>
-      <c r="K67" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L67" s="4" t="n"/>
+      <c r="J67" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="n"/>
+      <c r="L67" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M67" s="4" t="n"/>
       <c r="N67" s="4" t="n"/>
+      <c r="O67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -2034,6 +2106,7 @@
       <c r="L68" s="4" t="n"/>
       <c r="M68" s="4" t="n"/>
       <c r="N68" s="4" t="n"/>
+      <c r="O68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -2051,25 +2124,26 @@
       <c r="E69" s="4" t="n"/>
       <c r="F69" s="4" t="n"/>
       <c r="G69" s="4" t="n"/>
-      <c r="H69" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="H69" s="4" t="n"/>
       <c r="I69" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="J69" s="4" t="n"/>
-      <c r="K69" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L69" s="4" t="n"/>
+      <c r="J69" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="n"/>
+      <c r="L69" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M69" s="4" t="n"/>
       <c r="N69" s="4" t="n"/>
+      <c r="O69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -2090,6 +2164,7 @@
       <c r="L70" s="7" t="n"/>
       <c r="M70" s="7" t="n"/>
       <c r="N70" s="7" t="n"/>
+      <c r="O70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -2110,6 +2185,7 @@
       <c r="L71" s="7" t="n"/>
       <c r="M71" s="7" t="n"/>
       <c r="N71" s="7" t="n"/>
+      <c r="O71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -2128,16 +2204,17 @@
       <c r="F72" s="4" t="n"/>
       <c r="G72" s="4" t="n"/>
       <c r="H72" s="4" t="n"/>
-      <c r="I72" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J72" s="4" t="n"/>
+      <c r="I72" s="4" t="n"/>
+      <c r="J72" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="K72" s="4" t="n"/>
       <c r="L72" s="4" t="n"/>
       <c r="M72" s="4" t="n"/>
       <c r="N72" s="4" t="n"/>
+      <c r="O72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -2156,20 +2233,21 @@
       <c r="F73" s="4" t="n"/>
       <c r="G73" s="4" t="n"/>
       <c r="H73" s="4" t="n"/>
-      <c r="I73" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J73" s="4" t="n"/>
-      <c r="K73" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L73" s="4" t="n"/>
+      <c r="I73" s="4" t="n"/>
+      <c r="J73" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="n"/>
+      <c r="L73" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M73" s="4" t="n"/>
       <c r="N73" s="4" t="n"/>
+      <c r="O73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -2188,16 +2266,17 @@
       <c r="F74" s="4" t="n"/>
       <c r="G74" s="4" t="n"/>
       <c r="H74" s="4" t="n"/>
-      <c r="I74" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J74" s="4" t="n"/>
+      <c r="I74" s="4" t="n"/>
+      <c r="J74" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="K74" s="4" t="n"/>
       <c r="L74" s="4" t="n"/>
       <c r="M74" s="4" t="n"/>
       <c r="N74" s="4" t="n"/>
+      <c r="O74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -2216,20 +2295,21 @@
       <c r="F75" s="4" t="n"/>
       <c r="G75" s="4" t="n"/>
       <c r="H75" s="4" t="n"/>
-      <c r="I75" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J75" s="4" t="n"/>
-      <c r="K75" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L75" s="4" t="n"/>
+      <c r="I75" s="4" t="n"/>
+      <c r="J75" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="n"/>
+      <c r="L75" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M75" s="4" t="n"/>
       <c r="N75" s="4" t="n"/>
+      <c r="O75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -2248,20 +2328,21 @@
       <c r="F76" s="4" t="n"/>
       <c r="G76" s="4" t="n"/>
       <c r="H76" s="4" t="n"/>
-      <c r="I76" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J76" s="4" t="n"/>
-      <c r="K76" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L76" s="4" t="n"/>
+      <c r="I76" s="4" t="n"/>
+      <c r="J76" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="K76" s="4" t="n"/>
+      <c r="L76" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M76" s="4" t="n"/>
       <c r="N76" s="4" t="n"/>
+      <c r="O76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
@@ -2282,6 +2363,7 @@
       <c r="L77" s="7" t="n"/>
       <c r="M77" s="7" t="n"/>
       <c r="N77" s="7" t="n"/>
+      <c r="O77" s="7" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
@@ -2302,6 +2384,7 @@
       <c r="L78" s="7" t="n"/>
       <c r="M78" s="7" t="n"/>
       <c r="N78" s="7" t="n"/>
+      <c r="O78" s="7" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -2322,6 +2405,7 @@
       <c r="L79" s="4" t="n"/>
       <c r="M79" s="4" t="n"/>
       <c r="N79" s="4" t="n"/>
+      <c r="O79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -2342,6 +2426,7 @@
       <c r="L80" s="4" t="n"/>
       <c r="M80" s="4" t="n"/>
       <c r="N80" s="4" t="n"/>
+      <c r="O80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -2362,6 +2447,7 @@
       <c r="L81" s="4" t="n"/>
       <c r="M81" s="4" t="n"/>
       <c r="N81" s="4" t="n"/>
+      <c r="O81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -2382,6 +2468,7 @@
       <c r="L82" s="4" t="n"/>
       <c r="M82" s="4" t="n"/>
       <c r="N82" s="4" t="n"/>
+      <c r="O82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -2402,6 +2489,7 @@
       <c r="L83" s="4" t="n"/>
       <c r="M83" s="4" t="n"/>
       <c r="N83" s="4" t="n"/>
+      <c r="O83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
@@ -2422,6 +2510,7 @@
       <c r="L84" s="7" t="n"/>
       <c r="M84" s="7" t="n"/>
       <c r="N84" s="7" t="n"/>
+      <c r="O84" s="7" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
@@ -2442,6 +2531,7 @@
       <c r="L85" s="7" t="n"/>
       <c r="M85" s="7" t="n"/>
       <c r="N85" s="7" t="n"/>
+      <c r="O85" s="7" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -2460,12 +2550,13 @@
       <c r="J86" s="4" t="n"/>
       <c r="K86" s="4" t="n"/>
       <c r="L86" s="4" t="n"/>
-      <c r="M86" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N86" s="4" t="n"/>
+      <c r="M86" s="4" t="n"/>
+      <c r="N86" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -2484,12 +2575,13 @@
       <c r="J87" s="4" t="n"/>
       <c r="K87" s="4" t="n"/>
       <c r="L87" s="4" t="n"/>
-      <c r="M87" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N87" s="4" t="n"/>
+      <c r="M87" s="4" t="n"/>
+      <c r="N87" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -2508,12 +2600,13 @@
       <c r="J88" s="4" t="n"/>
       <c r="K88" s="4" t="n"/>
       <c r="L88" s="4" t="n"/>
-      <c r="M88" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N88" s="4" t="n"/>
+      <c r="M88" s="4" t="n"/>
+      <c r="N88" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -2532,12 +2625,13 @@
       <c r="J89" s="4" t="n"/>
       <c r="K89" s="4" t="n"/>
       <c r="L89" s="4" t="n"/>
-      <c r="M89" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N89" s="4" t="n"/>
+      <c r="M89" s="4" t="n"/>
+      <c r="N89" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
@@ -2556,12 +2650,13 @@
       <c r="J90" s="4" t="n"/>
       <c r="K90" s="4" t="n"/>
       <c r="L90" s="4" t="n"/>
-      <c r="M90" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N90" s="4" t="n"/>
+      <c r="M90" s="4" t="n"/>
+      <c r="N90" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
@@ -2582,6 +2677,7 @@
       <c r="L91" s="7" t="n"/>
       <c r="M91" s="7" t="n"/>
       <c r="N91" s="7" t="n"/>
+      <c r="O91" s="7" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
@@ -2602,6 +2698,7 @@
       <c r="L92" s="7" t="n"/>
       <c r="M92" s="7" t="n"/>
       <c r="N92" s="7" t="n"/>
+      <c r="O92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -2622,6 +2719,7 @@
       <c r="L93" s="4" t="n"/>
       <c r="M93" s="4" t="n"/>
       <c r="N93" s="4" t="n"/>
+      <c r="O93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -2642,6 +2740,7 @@
       <c r="L94" s="4" t="n"/>
       <c r="M94" s="4" t="n"/>
       <c r="N94" s="4" t="n"/>
+      <c r="O94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -2662,6 +2761,7 @@
       <c r="L95" s="4" t="n"/>
       <c r="M95" s="4" t="n"/>
       <c r="N95" s="4" t="n"/>
+      <c r="O95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
@@ -2682,6 +2782,7 @@
       <c r="L96" s="4" t="n"/>
       <c r="M96" s="4" t="n"/>
       <c r="N96" s="4" t="n"/>
+      <c r="O96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -2702,6 +2803,7 @@
       <c r="L97" s="4" t="n"/>
       <c r="M97" s="4" t="n"/>
       <c r="N97" s="4" t="n"/>
+      <c r="O97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
@@ -2722,6 +2824,7 @@
       <c r="L98" s="7" t="n"/>
       <c r="M98" s="7" t="n"/>
       <c r="N98" s="7" t="n"/>
+      <c r="O98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
@@ -2742,6 +2845,7 @@
       <c r="L99" s="7" t="n"/>
       <c r="M99" s="7" t="n"/>
       <c r="N99" s="7" t="n"/>
+      <c r="O99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -2762,6 +2866,7 @@
       <c r="L100" s="4" t="n"/>
       <c r="M100" s="4" t="n"/>
       <c r="N100" s="4" t="n"/>
+      <c r="O100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -2782,6 +2887,7 @@
       <c r="L101" s="4" t="n"/>
       <c r="M101" s="4" t="n"/>
       <c r="N101" s="4" t="n"/>
+      <c r="O101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -2802,6 +2908,7 @@
       <c r="L102" s="4" t="n"/>
       <c r="M102" s="4" t="n"/>
       <c r="N102" s="4" t="n"/>
+      <c r="O102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -2822,6 +2929,7 @@
       <c r="L103" s="4" t="n"/>
       <c r="M103" s="4" t="n"/>
       <c r="N103" s="4" t="n"/>
+      <c r="O103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -2842,6 +2950,7 @@
       <c r="L104" s="4" t="n"/>
       <c r="M104" s="4" t="n"/>
       <c r="N104" s="4" t="n"/>
+      <c r="O104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
@@ -2862,6 +2971,7 @@
       <c r="L105" s="7" t="n"/>
       <c r="M105" s="7" t="n"/>
       <c r="N105" s="7" t="n"/>
+      <c r="O105" s="7" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
@@ -2882,6 +2992,7 @@
       <c r="L106" s="7" t="n"/>
       <c r="M106" s="7" t="n"/>
       <c r="N106" s="7" t="n"/>
+      <c r="O106" s="7" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -2902,6 +3013,7 @@
       <c r="L107" s="4" t="n"/>
       <c r="M107" s="4" t="n"/>
       <c r="N107" s="4" t="n"/>
+      <c r="O107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -2922,6 +3034,7 @@
       <c r="L108" s="4" t="n"/>
       <c r="M108" s="4" t="n"/>
       <c r="N108" s="4" t="n"/>
+      <c r="O108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -2942,6 +3055,7 @@
       <c r="L109" s="4" t="n"/>
       <c r="M109" s="4" t="n"/>
       <c r="N109" s="4" t="n"/>
+      <c r="O109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
@@ -2962,6 +3076,7 @@
       <c r="L110" s="4" t="n"/>
       <c r="M110" s="4" t="n"/>
       <c r="N110" s="4" t="n"/>
+      <c r="O110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -2982,6 +3097,7 @@
       <c r="L111" s="4" t="n"/>
       <c r="M111" s="4" t="n"/>
       <c r="N111" s="4" t="n"/>
+      <c r="O111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
@@ -3002,6 +3118,7 @@
       <c r="L112" s="7" t="n"/>
       <c r="M112" s="7" t="n"/>
       <c r="N112" s="7" t="n"/>
+      <c r="O112" s="7" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
@@ -3022,6 +3139,7 @@
       <c r="L113" s="7" t="n"/>
       <c r="M113" s="7" t="n"/>
       <c r="N113" s="7" t="n"/>
+      <c r="O113" s="7" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -3042,6 +3160,7 @@
       <c r="L114" s="4" t="n"/>
       <c r="M114" s="4" t="n"/>
       <c r="N114" s="4" t="n"/>
+      <c r="O114" s="4" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -3062,6 +3181,7 @@
       <c r="L115" s="4" t="n"/>
       <c r="M115" s="4" t="n"/>
       <c r="N115" s="4" t="n"/>
+      <c r="O115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -3082,6 +3202,7 @@
       <c r="L116" s="4" t="n"/>
       <c r="M116" s="4" t="n"/>
       <c r="N116" s="4" t="n"/>
+      <c r="O116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -3102,6 +3223,7 @@
       <c r="L117" s="4" t="n"/>
       <c r="M117" s="4" t="n"/>
       <c r="N117" s="4" t="n"/>
+      <c r="O117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
@@ -3122,6 +3244,7 @@
       <c r="L118" s="4" t="n"/>
       <c r="M118" s="4" t="n"/>
       <c r="N118" s="4" t="n"/>
+      <c r="O118" s="4" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
@@ -3142,6 +3265,7 @@
       <c r="L119" s="7" t="n"/>
       <c r="M119" s="7" t="n"/>
       <c r="N119" s="7" t="n"/>
+      <c r="O119" s="7" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
@@ -3162,6 +3286,7 @@
       <c r="L120" s="7" t="n"/>
       <c r="M120" s="7" t="n"/>
       <c r="N120" s="7" t="n"/>
+      <c r="O120" s="7" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -3182,6 +3307,7 @@
       <c r="L121" s="4" t="n"/>
       <c r="M121" s="4" t="n"/>
       <c r="N121" s="4" t="n"/>
+      <c r="O121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -3196,16 +3322,17 @@
       <c r="F122" s="4" t="n"/>
       <c r="G122" s="4" t="n"/>
       <c r="H122" s="4" t="n"/>
-      <c r="I122" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J122" s="4" t="n"/>
+      <c r="I122" s="4" t="n"/>
+      <c r="J122" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="K122" s="4" t="n"/>
       <c r="L122" s="4" t="n"/>
       <c r="M122" s="4" t="n"/>
       <c r="N122" s="4" t="n"/>
+      <c r="O122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -3220,16 +3347,17 @@
       <c r="F123" s="4" t="n"/>
       <c r="G123" s="4" t="n"/>
       <c r="H123" s="4" t="n"/>
-      <c r="I123" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J123" s="4" t="n"/>
+      <c r="I123" s="4" t="n"/>
+      <c r="J123" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="K123" s="4" t="n"/>
       <c r="L123" s="4" t="n"/>
       <c r="M123" s="4" t="n"/>
       <c r="N123" s="4" t="n"/>
+      <c r="O123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -3250,6 +3378,7 @@
       <c r="L124" s="4" t="n"/>
       <c r="M124" s="4" t="n"/>
       <c r="N124" s="4" t="n"/>
+      <c r="O124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -3270,6 +3399,7 @@
       <c r="L125" s="4" t="n"/>
       <c r="M125" s="4" t="n"/>
       <c r="N125" s="4" t="n"/>
+      <c r="O125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
@@ -3290,6 +3420,7 @@
       <c r="L126" s="7" t="n"/>
       <c r="M126" s="7" t="n"/>
       <c r="N126" s="7" t="n"/>
+      <c r="O126" s="7" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
@@ -3310,6 +3441,7 @@
       <c r="L127" s="7" t="n"/>
       <c r="M127" s="7" t="n"/>
       <c r="N127" s="7" t="n"/>
+      <c r="O127" s="7" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
@@ -3330,6 +3462,7 @@
       <c r="L128" s="4" t="n"/>
       <c r="M128" s="4" t="n"/>
       <c r="N128" s="4" t="n"/>
+      <c r="O128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -3350,6 +3483,7 @@
       <c r="L129" s="4" t="n"/>
       <c r="M129" s="4" t="n"/>
       <c r="N129" s="4" t="n"/>
+      <c r="O129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
@@ -3370,6 +3504,7 @@
       <c r="L130" s="4" t="n"/>
       <c r="M130" s="4" t="n"/>
       <c r="N130" s="4" t="n"/>
+      <c r="O130" s="4" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
@@ -3390,6 +3525,7 @@
       <c r="L131" s="4" t="n"/>
       <c r="M131" s="4" t="n"/>
       <c r="N131" s="4" t="n"/>
+      <c r="O131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -3410,6 +3546,7 @@
       <c r="L132" s="4" t="n"/>
       <c r="M132" s="4" t="n"/>
       <c r="N132" s="4" t="n"/>
+      <c r="O132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
@@ -3430,6 +3567,7 @@
       <c r="L133" s="7" t="n"/>
       <c r="M133" s="7" t="n"/>
       <c r="N133" s="7" t="n"/>
+      <c r="O133" s="7" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
@@ -3450,6 +3588,7 @@
       <c r="L134" s="7" t="n"/>
       <c r="M134" s="7" t="n"/>
       <c r="N134" s="7" t="n"/>
+      <c r="O134" s="7" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -3470,6 +3609,7 @@
       <c r="L135" s="4" t="n"/>
       <c r="M135" s="4" t="n"/>
       <c r="N135" s="4" t="n"/>
+      <c r="O135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
@@ -3490,6 +3630,7 @@
       <c r="L136" s="4" t="n"/>
       <c r="M136" s="4" t="n"/>
       <c r="N136" s="4" t="n"/>
+      <c r="O136" s="4" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -3510,6 +3651,7 @@
       <c r="L137" s="4" t="n"/>
       <c r="M137" s="4" t="n"/>
       <c r="N137" s="4" t="n"/>
+      <c r="O137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
@@ -3528,12 +3670,13 @@
       <c r="J138" s="4" t="n"/>
       <c r="K138" s="4" t="n"/>
       <c r="L138" s="4" t="n"/>
-      <c r="M138" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N138" s="4" t="n"/>
+      <c r="M138" s="4" t="n"/>
+      <c r="N138" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O138" s="4" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
@@ -3552,12 +3695,13 @@
       <c r="J139" s="4" t="n"/>
       <c r="K139" s="4" t="n"/>
       <c r="L139" s="4" t="n"/>
-      <c r="M139" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N139" s="4" t="n"/>
+      <c r="M139" s="4" t="n"/>
+      <c r="N139" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
@@ -3578,6 +3722,7 @@
       <c r="L140" s="7" t="n"/>
       <c r="M140" s="7" t="n"/>
       <c r="N140" s="7" t="n"/>
+      <c r="O140" s="7" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
@@ -3598,6 +3743,7 @@
       <c r="L141" s="7" t="n"/>
       <c r="M141" s="7" t="n"/>
       <c r="N141" s="7" t="n"/>
+      <c r="O141" s="7" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
@@ -3616,12 +3762,13 @@
       <c r="J142" s="4" t="n"/>
       <c r="K142" s="4" t="n"/>
       <c r="L142" s="4" t="n"/>
-      <c r="M142" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N142" s="4" t="n"/>
+      <c r="M142" s="4" t="n"/>
+      <c r="N142" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O142" s="4" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -3642,6 +3789,7 @@
       <c r="L143" s="4" t="n"/>
       <c r="M143" s="4" t="n"/>
       <c r="N143" s="4" t="n"/>
+      <c r="O143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
@@ -3662,6 +3810,7 @@
       <c r="L144" s="4" t="n"/>
       <c r="M144" s="4" t="n"/>
       <c r="N144" s="4" t="n"/>
+      <c r="O144" s="4" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -3682,6 +3831,7 @@
       <c r="L145" s="4" t="n"/>
       <c r="M145" s="4" t="n"/>
       <c r="N145" s="4" t="n"/>
+      <c r="O145" s="4" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
@@ -3695,17 +3845,18 @@
       <c r="E146" s="4" t="n"/>
       <c r="F146" s="4" t="n"/>
       <c r="G146" s="4" t="n"/>
-      <c r="H146" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="I146" s="4" t="n"/>
+      <c r="H146" s="4" t="n"/>
+      <c r="I146" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J146" s="4" t="n"/>
       <c r="K146" s="4" t="n"/>
       <c r="L146" s="4" t="n"/>
       <c r="M146" s="4" t="n"/>
       <c r="N146" s="4" t="n"/>
+      <c r="O146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
@@ -3726,6 +3877,7 @@
       <c r="L147" s="7" t="n"/>
       <c r="M147" s="7" t="n"/>
       <c r="N147" s="7" t="n"/>
+      <c r="O147" s="7" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
@@ -3746,6 +3898,7 @@
       <c r="L148" s="7" t="n"/>
       <c r="M148" s="7" t="n"/>
       <c r="N148" s="7" t="n"/>
+      <c r="O148" s="7" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
@@ -3759,17 +3912,18 @@
       <c r="E149" s="4" t="n"/>
       <c r="F149" s="4" t="n"/>
       <c r="G149" s="4" t="n"/>
-      <c r="H149" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="I149" s="4" t="n"/>
+      <c r="H149" s="4" t="n"/>
+      <c r="I149" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J149" s="4" t="n"/>
       <c r="K149" s="4" t="n"/>
       <c r="L149" s="4" t="n"/>
       <c r="M149" s="4" t="n"/>
       <c r="N149" s="4" t="n"/>
+      <c r="O149" s="4" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
@@ -3783,17 +3937,18 @@
       <c r="E150" s="4" t="n"/>
       <c r="F150" s="4" t="n"/>
       <c r="G150" s="4" t="n"/>
-      <c r="H150" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="I150" s="4" t="n"/>
+      <c r="H150" s="4" t="n"/>
+      <c r="I150" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J150" s="4" t="n"/>
       <c r="K150" s="4" t="n"/>
       <c r="L150" s="4" t="n"/>
       <c r="M150" s="4" t="n"/>
       <c r="N150" s="4" t="n"/>
+      <c r="O150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -3814,6 +3969,7 @@
       <c r="L151" s="4" t="n"/>
       <c r="M151" s="4" t="n"/>
       <c r="N151" s="4" t="n"/>
+      <c r="O151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
@@ -3834,6 +3990,7 @@
       <c r="L152" s="4" t="n"/>
       <c r="M152" s="4" t="n"/>
       <c r="N152" s="4" t="n"/>
+      <c r="O152" s="4" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -3854,6 +4011,7 @@
       <c r="L153" s="4" t="n"/>
       <c r="M153" s="4" t="n"/>
       <c r="N153" s="4" t="n"/>
+      <c r="O153" s="4" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
@@ -3874,6 +4032,7 @@
       <c r="L154" s="7" t="n"/>
       <c r="M154" s="7" t="n"/>
       <c r="N154" s="7" t="n"/>
+      <c r="O154" s="7" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
@@ -3894,6 +4053,7 @@
       <c r="L155" s="7" t="n"/>
       <c r="M155" s="7" t="n"/>
       <c r="N155" s="7" t="n"/>
+      <c r="O155" s="7" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
@@ -3914,6 +4074,7 @@
       <c r="L156" s="4" t="n"/>
       <c r="M156" s="4" t="n"/>
       <c r="N156" s="4" t="n"/>
+      <c r="O156" s="4" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
@@ -3934,6 +4095,7 @@
       <c r="L157" s="4" t="n"/>
       <c r="M157" s="4" t="n"/>
       <c r="N157" s="4" t="n"/>
+      <c r="O157" s="4" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
@@ -3954,6 +4116,7 @@
       <c r="L158" s="4" t="n"/>
       <c r="M158" s="4" t="n"/>
       <c r="N158" s="4" t="n"/>
+      <c r="O158" s="4" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -3974,6 +4137,7 @@
       <c r="L159" s="4" t="n"/>
       <c r="M159" s="4" t="n"/>
       <c r="N159" s="4" t="n"/>
+      <c r="O159" s="4" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
@@ -3994,6 +4158,7 @@
       <c r="L160" s="4" t="n"/>
       <c r="M160" s="4" t="n"/>
       <c r="N160" s="4" t="n"/>
+      <c r="O160" s="4" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
@@ -4014,6 +4179,7 @@
       <c r="L161" s="7" t="n"/>
       <c r="M161" s="7" t="n"/>
       <c r="N161" s="7" t="n"/>
+      <c r="O161" s="7" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
@@ -4034,6 +4200,7 @@
       <c r="L162" s="7" t="n"/>
       <c r="M162" s="7" t="n"/>
       <c r="N162" s="7" t="n"/>
+      <c r="O162" s="7" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -4058,6 +4225,7 @@
       <c r="L163" s="4" t="n"/>
       <c r="M163" s="4" t="n"/>
       <c r="N163" s="4" t="n"/>
+      <c r="O163" s="4" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
@@ -4078,6 +4246,7 @@
       <c r="L164" s="4" t="n"/>
       <c r="M164" s="4" t="n"/>
       <c r="N164" s="4" t="n"/>
+      <c r="O164" s="4" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -4093,12 +4262,12 @@
       <c r="C165" s="4" t="n"/>
       <c r="D165" s="4" t="n"/>
       <c r="E165" s="4" t="n"/>
-      <c r="F165" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="G165" s="4" t="n"/>
+      <c r="F165" s="4" t="n"/>
+      <c r="G165" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="H165" s="4" t="n"/>
       <c r="I165" s="4" t="n"/>
       <c r="J165" s="4" t="n"/>
@@ -4106,6 +4275,7 @@
       <c r="L165" s="4" t="n"/>
       <c r="M165" s="4" t="n"/>
       <c r="N165" s="4" t="n"/>
+      <c r="O165" s="4" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
@@ -4121,12 +4291,12 @@
       <c r="C166" s="4" t="n"/>
       <c r="D166" s="4" t="n"/>
       <c r="E166" s="4" t="n"/>
-      <c r="F166" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="G166" s="4" t="n"/>
+      <c r="F166" s="4" t="n"/>
+      <c r="G166" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="H166" s="4" t="n"/>
       <c r="I166" s="4" t="n"/>
       <c r="J166" s="4" t="n"/>
@@ -4134,6 +4304,7 @@
       <c r="L166" s="4" t="n"/>
       <c r="M166" s="4" t="n"/>
       <c r="N166" s="4" t="n"/>
+      <c r="O166" s="4" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
@@ -4149,23 +4320,24 @@
       <c r="C167" s="4" t="n"/>
       <c r="D167" s="4" t="n"/>
       <c r="E167" s="4" t="n"/>
-      <c r="F167" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="G167" s="4" t="n"/>
+      <c r="F167" s="4" t="n"/>
+      <c r="G167" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="H167" s="4" t="n"/>
       <c r="I167" s="4" t="n"/>
-      <c r="J167" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="K167" s="4" t="n"/>
+      <c r="J167" s="4" t="n"/>
+      <c r="K167" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L167" s="4" t="n"/>
       <c r="M167" s="4" t="n"/>
-      <c r="N167" s="8" t="inlineStr">
+      <c r="N167" s="4" t="n"/>
+      <c r="O167" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -4190,6 +4362,7 @@
       <c r="L168" s="7" t="n"/>
       <c r="M168" s="7" t="n"/>
       <c r="N168" s="7" t="n"/>
+      <c r="O168" s="7" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
@@ -4210,6 +4383,7 @@
       <c r="L169" s="7" t="n"/>
       <c r="M169" s="7" t="n"/>
       <c r="N169" s="7" t="n"/>
+      <c r="O169" s="7" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
@@ -4221,19 +4395,20 @@
       <c r="C170" s="4" t="n"/>
       <c r="D170" s="4" t="n"/>
       <c r="E170" s="4" t="n"/>
-      <c r="F170" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="G170" s="4" t="n"/>
+      <c r="F170" s="4" t="n"/>
+      <c r="G170" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="H170" s="4" t="n"/>
       <c r="I170" s="4" t="n"/>
       <c r="J170" s="4" t="n"/>
       <c r="K170" s="4" t="n"/>
       <c r="L170" s="4" t="n"/>
       <c r="M170" s="4" t="n"/>
-      <c r="N170" s="8" t="inlineStr">
+      <c r="N170" s="4" t="n"/>
+      <c r="O170" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -4249,12 +4424,12 @@
       <c r="C171" s="4" t="n"/>
       <c r="D171" s="4" t="n"/>
       <c r="E171" s="4" t="n"/>
-      <c r="F171" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="G171" s="4" t="n"/>
+      <c r="F171" s="4" t="n"/>
+      <c r="G171" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="H171" s="4" t="n"/>
       <c r="I171" s="4" t="n"/>
       <c r="J171" s="4" t="n"/>
@@ -4262,6 +4437,7 @@
       <c r="L171" s="4" t="n"/>
       <c r="M171" s="4" t="n"/>
       <c r="N171" s="4" t="n"/>
+      <c r="O171" s="4" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
@@ -4273,12 +4449,12 @@
       <c r="C172" s="4" t="n"/>
       <c r="D172" s="4" t="n"/>
       <c r="E172" s="4" t="n"/>
-      <c r="F172" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="G172" s="4" t="n"/>
+      <c r="F172" s="4" t="n"/>
+      <c r="G172" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="H172" s="4" t="n"/>
       <c r="I172" s="4" t="n"/>
       <c r="J172" s="4" t="n"/>
@@ -4286,6 +4462,7 @@
       <c r="L172" s="4" t="n"/>
       <c r="M172" s="4" t="n"/>
       <c r="N172" s="4" t="n"/>
+      <c r="O172" s="4" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -4297,12 +4474,12 @@
       <c r="C173" s="4" t="n"/>
       <c r="D173" s="4" t="n"/>
       <c r="E173" s="4" t="n"/>
-      <c r="F173" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="G173" s="4" t="n"/>
+      <c r="F173" s="4" t="n"/>
+      <c r="G173" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="H173" s="4" t="n"/>
       <c r="I173" s="4" t="n"/>
       <c r="J173" s="4" t="n"/>
@@ -4310,6 +4487,7 @@
       <c r="L173" s="4" t="n"/>
       <c r="M173" s="4" t="n"/>
       <c r="N173" s="4" t="n"/>
+      <c r="O173" s="4" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
@@ -4321,12 +4499,12 @@
       <c r="C174" s="4" t="n"/>
       <c r="D174" s="4" t="n"/>
       <c r="E174" s="4" t="n"/>
-      <c r="F174" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="G174" s="4" t="n"/>
+      <c r="F174" s="4" t="n"/>
+      <c r="G174" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="H174" s="4" t="n"/>
       <c r="I174" s="4" t="n"/>
       <c r="J174" s="4" t="n"/>
@@ -4334,6 +4512,7 @@
       <c r="L174" s="4" t="n"/>
       <c r="M174" s="4" t="n"/>
       <c r="N174" s="4" t="n"/>
+      <c r="O174" s="4" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
@@ -4354,6 +4533,7 @@
       <c r="L175" s="7" t="n"/>
       <c r="M175" s="7" t="n"/>
       <c r="N175" s="7" t="n"/>
+      <c r="O175" s="7" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="6" t="inlineStr">
@@ -4374,6 +4554,7 @@
       <c r="L176" s="7" t="n"/>
       <c r="M176" s="7" t="n"/>
       <c r="N176" s="7" t="n"/>
+      <c r="O176" s="7" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
@@ -4394,6 +4575,7 @@
       <c r="L177" s="4" t="n"/>
       <c r="M177" s="4" t="n"/>
       <c r="N177" s="4" t="n"/>
+      <c r="O177" s="4" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
@@ -4414,6 +4596,7 @@
       <c r="L178" s="4" t="n"/>
       <c r="M178" s="4" t="n"/>
       <c r="N178" s="4" t="n"/>
+      <c r="O178" s="4" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
@@ -4434,6 +4617,7 @@
       <c r="L179" s="4" t="n"/>
       <c r="M179" s="4" t="n"/>
       <c r="N179" s="4" t="n"/>
+      <c r="O179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
@@ -4454,6 +4638,7 @@
       <c r="L180" s="4" t="n"/>
       <c r="M180" s="4" t="n"/>
       <c r="N180" s="4" t="n"/>
+      <c r="O180" s="4" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -4474,6 +4659,7 @@
       <c r="L181" s="4" t="n"/>
       <c r="M181" s="4" t="n"/>
       <c r="N181" s="4" t="n"/>
+      <c r="O181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="6" t="inlineStr">
@@ -4494,6 +4680,7 @@
       <c r="L182" s="7" t="n"/>
       <c r="M182" s="7" t="n"/>
       <c r="N182" s="7" t="n"/>
+      <c r="O182" s="7" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
@@ -4514,6 +4701,7 @@
       <c r="L183" s="7" t="n"/>
       <c r="M183" s="7" t="n"/>
       <c r="N183" s="7" t="n"/>
+      <c r="O183" s="7" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
@@ -4534,6 +4722,7 @@
       <c r="L184" s="4" t="n"/>
       <c r="M184" s="4" t="n"/>
       <c r="N184" s="4" t="n"/>
+      <c r="O184" s="4" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -4554,6 +4743,7 @@
       <c r="L185" s="4" t="n"/>
       <c r="M185" s="4" t="n"/>
       <c r="N185" s="4" t="n"/>
+      <c r="O185" s="4" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
@@ -4574,6 +4764,7 @@
       <c r="L186" s="4" t="n"/>
       <c r="M186" s="4" t="n"/>
       <c r="N186" s="4" t="n"/>
+      <c r="O186" s="4" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -4594,6 +4785,7 @@
       <c r="L187" s="4" t="n"/>
       <c r="M187" s="4" t="n"/>
       <c r="N187" s="4" t="n"/>
+      <c r="O187" s="4" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
@@ -4614,6 +4806,7 @@
       <c r="L188" s="4" t="n"/>
       <c r="M188" s="4" t="n"/>
       <c r="N188" s="4" t="n"/>
+      <c r="O188" s="4" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
@@ -4634,6 +4827,7 @@
       <c r="L189" s="7" t="n"/>
       <c r="M189" s="7" t="n"/>
       <c r="N189" s="7" t="n"/>
+      <c r="O189" s="7" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="6" t="inlineStr">
@@ -4654,6 +4848,7 @@
       <c r="L190" s="7" t="n"/>
       <c r="M190" s="7" t="n"/>
       <c r="N190" s="7" t="n"/>
+      <c r="O190" s="7" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
@@ -4674,6 +4869,7 @@
       <c r="L191" s="4" t="n"/>
       <c r="M191" s="4" t="n"/>
       <c r="N191" s="4" t="n"/>
+      <c r="O191" s="4" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
@@ -4694,6 +4890,7 @@
       <c r="L192" s="4" t="n"/>
       <c r="M192" s="4" t="n"/>
       <c r="N192" s="4" t="n"/>
+      <c r="O192" s="4" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
@@ -4714,6 +4911,7 @@
       <c r="L193" s="4" t="n"/>
       <c r="M193" s="4" t="n"/>
       <c r="N193" s="4" t="n"/>
+      <c r="O193" s="4" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
@@ -4734,6 +4932,7 @@
       <c r="L194" s="4" t="n"/>
       <c r="M194" s="4" t="n"/>
       <c r="N194" s="4" t="n"/>
+      <c r="O194" s="4" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -4745,12 +4944,12 @@
       <c r="C195" s="4" t="n"/>
       <c r="D195" s="4" t="n"/>
       <c r="E195" s="4" t="n"/>
-      <c r="F195" s="5" t="inlineStr">
+      <c r="F195" s="4" t="n"/>
+      <c r="G195" s="5" t="inlineStr">
         <is>
           <t>A/L (Half Day) - Annual Leave</t>
         </is>
       </c>
-      <c r="G195" s="4" t="n"/>
       <c r="H195" s="4" t="n"/>
       <c r="I195" s="4" t="n"/>
       <c r="J195" s="4" t="n"/>
@@ -4758,6 +4957,7 @@
       <c r="L195" s="4" t="n"/>
       <c r="M195" s="4" t="n"/>
       <c r="N195" s="4" t="n"/>
+      <c r="O195" s="4" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="6" t="inlineStr">
@@ -4778,6 +4978,7 @@
       <c r="L196" s="7" t="n"/>
       <c r="M196" s="7" t="n"/>
       <c r="N196" s="7" t="n"/>
+      <c r="O196" s="7" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
@@ -4798,6 +4999,7 @@
       <c r="L197" s="7" t="n"/>
       <c r="M197" s="7" t="n"/>
       <c r="N197" s="7" t="n"/>
+      <c r="O197" s="7" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
@@ -4809,12 +5011,12 @@
       <c r="C198" s="4" t="n"/>
       <c r="D198" s="4" t="n"/>
       <c r="E198" s="4" t="n"/>
-      <c r="F198" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="G198" s="4" t="n"/>
+      <c r="F198" s="4" t="n"/>
+      <c r="G198" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="H198" s="4" t="n"/>
       <c r="I198" s="4" t="n"/>
       <c r="J198" s="4" t="n"/>
@@ -4822,6 +5024,7 @@
       <c r="L198" s="4" t="n"/>
       <c r="M198" s="4" t="n"/>
       <c r="N198" s="4" t="n"/>
+      <c r="O198" s="4" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -4846,6 +5049,7 @@
       <c r="L199" s="4" t="n"/>
       <c r="M199" s="4" t="n"/>
       <c r="N199" s="4" t="n"/>
+      <c r="O199" s="4" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
@@ -4866,6 +5070,7 @@
       <c r="L200" s="4" t="n"/>
       <c r="M200" s="4" t="n"/>
       <c r="N200" s="4" t="n"/>
+      <c r="O200" s="4" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
@@ -4886,6 +5091,7 @@
       <c r="L201" s="4" t="n"/>
       <c r="M201" s="4" t="n"/>
       <c r="N201" s="4" t="n"/>
+      <c r="O201" s="4" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
@@ -4906,6 +5112,7 @@
       <c r="L202" s="4" t="n"/>
       <c r="M202" s="4" t="n"/>
       <c r="N202" s="4" t="n"/>
+      <c r="O202" s="4" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
@@ -4926,6 +5133,7 @@
       <c r="L203" s="7" t="n"/>
       <c r="M203" s="7" t="n"/>
       <c r="N203" s="7" t="n"/>
+      <c r="O203" s="7" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="6" t="inlineStr">
@@ -4946,6 +5154,7 @@
       <c r="L204" s="7" t="n"/>
       <c r="M204" s="7" t="n"/>
       <c r="N204" s="7" t="n"/>
+      <c r="O204" s="7" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
@@ -4966,6 +5175,7 @@
       <c r="L205" s="4" t="n"/>
       <c r="M205" s="4" t="n"/>
       <c r="N205" s="4" t="n"/>
+      <c r="O205" s="4" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
@@ -4986,6 +5196,7 @@
       <c r="L206" s="4" t="n"/>
       <c r="M206" s="4" t="n"/>
       <c r="N206" s="4" t="n"/>
+      <c r="O206" s="4" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
@@ -5006,6 +5217,7 @@
       <c r="L207" s="4" t="n"/>
       <c r="M207" s="4" t="n"/>
       <c r="N207" s="4" t="n"/>
+      <c r="O207" s="4" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
@@ -5026,6 +5238,7 @@
       <c r="L208" s="4" t="n"/>
       <c r="M208" s="4" t="n"/>
       <c r="N208" s="4" t="n"/>
+      <c r="O208" s="4" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
@@ -5046,6 +5259,7 @@
       <c r="L209" s="4" t="n"/>
       <c r="M209" s="4" t="n"/>
       <c r="N209" s="4" t="n"/>
+      <c r="O209" s="4" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="6" t="inlineStr">
@@ -5066,6 +5280,7 @@
       <c r="L210" s="7" t="n"/>
       <c r="M210" s="7" t="n"/>
       <c r="N210" s="7" t="n"/>
+      <c r="O210" s="7" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
@@ -5086,6 +5301,7 @@
       <c r="L211" s="7" t="n"/>
       <c r="M211" s="7" t="n"/>
       <c r="N211" s="7" t="n"/>
+      <c r="O211" s="7" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
@@ -5106,6 +5322,7 @@
       <c r="L212" s="4" t="n"/>
       <c r="M212" s="4" t="n"/>
       <c r="N212" s="4" t="n"/>
+      <c r="O212" s="4" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
@@ -5126,6 +5343,7 @@
       <c r="L213" s="4" t="n"/>
       <c r="M213" s="4" t="n"/>
       <c r="N213" s="4" t="n"/>
+      <c r="O213" s="4" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
@@ -5146,6 +5364,7 @@
       <c r="L214" s="4" t="n"/>
       <c r="M214" s="4" t="n"/>
       <c r="N214" s="4" t="n"/>
+      <c r="O214" s="4" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
@@ -5166,6 +5385,7 @@
       <c r="L215" s="4" t="n"/>
       <c r="M215" s="4" t="n"/>
       <c r="N215" s="4" t="n"/>
+      <c r="O215" s="4" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
@@ -5186,6 +5406,7 @@
       <c r="L216" s="4" t="n"/>
       <c r="M216" s="4" t="n"/>
       <c r="N216" s="4" t="n"/>
+      <c r="O216" s="4" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
@@ -5206,6 +5427,7 @@
       <c r="L217" s="7" t="n"/>
       <c r="M217" s="7" t="n"/>
       <c r="N217" s="7" t="n"/>
+      <c r="O217" s="7" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="6" t="inlineStr">
@@ -5226,6 +5448,7 @@
       <c r="L218" s="7" t="n"/>
       <c r="M218" s="7" t="n"/>
       <c r="N218" s="7" t="n"/>
+      <c r="O218" s="7" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
@@ -5237,23 +5460,24 @@
       <c r="C219" s="4" t="n"/>
       <c r="D219" s="4" t="n"/>
       <c r="E219" s="4" t="n"/>
-      <c r="F219" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="G219" s="4" t="n"/>
+      <c r="F219" s="4" t="n"/>
+      <c r="G219" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="H219" s="4" t="n"/>
-      <c r="I219" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J219" s="4" t="n"/>
+      <c r="I219" s="4" t="n"/>
+      <c r="J219" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="K219" s="4" t="n"/>
       <c r="L219" s="4" t="n"/>
       <c r="M219" s="4" t="n"/>
       <c r="N219" s="4" t="n"/>
+      <c r="O219" s="4" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
@@ -5265,23 +5489,24 @@
       <c r="C220" s="4" t="n"/>
       <c r="D220" s="4" t="n"/>
       <c r="E220" s="4" t="n"/>
-      <c r="F220" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="G220" s="4" t="n"/>
+      <c r="F220" s="4" t="n"/>
+      <c r="G220" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="H220" s="4" t="n"/>
-      <c r="I220" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J220" s="4" t="n"/>
+      <c r="I220" s="4" t="n"/>
+      <c r="J220" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="K220" s="4" t="n"/>
       <c r="L220" s="4" t="n"/>
       <c r="M220" s="4" t="n"/>
       <c r="N220" s="4" t="n"/>
+      <c r="O220" s="4" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
@@ -5293,23 +5518,24 @@
       <c r="C221" s="4" t="n"/>
       <c r="D221" s="4" t="n"/>
       <c r="E221" s="4" t="n"/>
-      <c r="F221" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="G221" s="4" t="n"/>
+      <c r="F221" s="4" t="n"/>
+      <c r="G221" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="H221" s="4" t="n"/>
-      <c r="I221" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J221" s="4" t="n"/>
+      <c r="I221" s="4" t="n"/>
+      <c r="J221" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="K221" s="4" t="n"/>
       <c r="L221" s="4" t="n"/>
       <c r="M221" s="4" t="n"/>
       <c r="N221" s="4" t="n"/>
+      <c r="O221" s="4" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
@@ -5324,16 +5550,17 @@
       <c r="F222" s="4" t="n"/>
       <c r="G222" s="4" t="n"/>
       <c r="H222" s="4" t="n"/>
-      <c r="I222" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J222" s="4" t="n"/>
+      <c r="I222" s="4" t="n"/>
+      <c r="J222" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="K222" s="4" t="n"/>
       <c r="L222" s="4" t="n"/>
       <c r="M222" s="4" t="n"/>
       <c r="N222" s="4" t="n"/>
+      <c r="O222" s="4" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
@@ -5348,16 +5575,17 @@
       <c r="F223" s="4" t="n"/>
       <c r="G223" s="4" t="n"/>
       <c r="H223" s="4" t="n"/>
-      <c r="I223" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J223" s="4" t="n"/>
+      <c r="I223" s="4" t="n"/>
+      <c r="J223" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="K223" s="4" t="n"/>
       <c r="L223" s="4" t="n"/>
       <c r="M223" s="4" t="n"/>
       <c r="N223" s="4" t="n"/>
+      <c r="O223" s="4" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="6" t="inlineStr">
@@ -5378,6 +5606,7 @@
       <c r="L224" s="7" t="n"/>
       <c r="M224" s="7" t="n"/>
       <c r="N224" s="7" t="n"/>
+      <c r="O224" s="7" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
@@ -5398,6 +5627,7 @@
       <c r="L225" s="7" t="n"/>
       <c r="M225" s="7" t="n"/>
       <c r="N225" s="7" t="n"/>
+      <c r="O225" s="7" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
@@ -5418,6 +5648,7 @@
       <c r="L226" s="4" t="n"/>
       <c r="M226" s="4" t="n"/>
       <c r="N226" s="4" t="n"/>
+      <c r="O226" s="4" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
@@ -5438,6 +5669,7 @@
       <c r="L227" s="4" t="n"/>
       <c r="M227" s="4" t="n"/>
       <c r="N227" s="4" t="n"/>
+      <c r="O227" s="4" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
@@ -5451,21 +5683,22 @@
       <c r="E228" s="4" t="n"/>
       <c r="F228" s="4" t="n"/>
       <c r="G228" s="4" t="n"/>
-      <c r="H228" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="I228" s="4" t="n"/>
+      <c r="H228" s="4" t="n"/>
+      <c r="I228" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J228" s="4" t="n"/>
-      <c r="K228" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L228" s="4" t="n"/>
+      <c r="K228" s="4" t="n"/>
+      <c r="L228" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M228" s="4" t="n"/>
       <c r="N228" s="4" t="n"/>
+      <c r="O228" s="4" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
@@ -5483,17 +5716,18 @@
       <c r="E229" s="4" t="n"/>
       <c r="F229" s="4" t="n"/>
       <c r="G229" s="4" t="n"/>
-      <c r="H229" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="I229" s="4" t="n"/>
+      <c r="H229" s="4" t="n"/>
+      <c r="I229" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J229" s="4" t="n"/>
       <c r="K229" s="4" t="n"/>
       <c r="L229" s="4" t="n"/>
       <c r="M229" s="4" t="n"/>
       <c r="N229" s="4" t="n"/>
+      <c r="O229" s="4" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
@@ -5507,17 +5741,18 @@
       <c r="E230" s="4" t="n"/>
       <c r="F230" s="4" t="n"/>
       <c r="G230" s="4" t="n"/>
-      <c r="H230" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="I230" s="4" t="n"/>
+      <c r="H230" s="4" t="n"/>
+      <c r="I230" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J230" s="4" t="n"/>
       <c r="K230" s="4" t="n"/>
       <c r="L230" s="4" t="n"/>
       <c r="M230" s="4" t="n"/>
       <c r="N230" s="4" t="n"/>
+      <c r="O230" s="4" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
@@ -5538,6 +5773,7 @@
       <c r="L231" s="7" t="n"/>
       <c r="M231" s="7" t="n"/>
       <c r="N231" s="7" t="n"/>
+      <c r="O231" s="7" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="6" t="inlineStr">
@@ -5558,6 +5794,7 @@
       <c r="L232" s="7" t="n"/>
       <c r="M232" s="7" t="n"/>
       <c r="N232" s="7" t="n"/>
+      <c r="O232" s="7" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
@@ -5571,25 +5808,26 @@
       <c r="E233" s="4" t="n"/>
       <c r="F233" s="4" t="n"/>
       <c r="G233" s="4" t="n"/>
-      <c r="H233" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="I233" s="4" t="n"/>
-      <c r="J233" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="H233" s="4" t="n"/>
+      <c r="I233" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="J233" s="4" t="n"/>
       <c r="K233" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L233" s="4" t="n"/>
+      <c r="L233" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M233" s="4" t="n"/>
       <c r="N233" s="4" t="n"/>
+      <c r="O233" s="4" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
@@ -5603,21 +5841,22 @@
       <c r="E234" s="4" t="n"/>
       <c r="F234" s="4" t="n"/>
       <c r="G234" s="4" t="n"/>
-      <c r="H234" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="I234" s="4" t="n"/>
+      <c r="H234" s="4" t="n"/>
+      <c r="I234" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J234" s="4" t="n"/>
-      <c r="K234" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L234" s="4" t="n"/>
+      <c r="K234" s="4" t="n"/>
+      <c r="L234" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M234" s="4" t="n"/>
       <c r="N234" s="4" t="n"/>
+      <c r="O234" s="4" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
@@ -5631,21 +5870,22 @@
       <c r="E235" s="4" t="n"/>
       <c r="F235" s="4" t="n"/>
       <c r="G235" s="4" t="n"/>
-      <c r="H235" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="I235" s="4" t="n"/>
+      <c r="H235" s="4" t="n"/>
+      <c r="I235" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J235" s="4" t="n"/>
-      <c r="K235" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L235" s="4" t="n"/>
+      <c r="K235" s="4" t="n"/>
+      <c r="L235" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M235" s="4" t="n"/>
       <c r="N235" s="4" t="n"/>
+      <c r="O235" s="4" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
@@ -5662,14 +5902,15 @@
       <c r="H236" s="4" t="n"/>
       <c r="I236" s="4" t="n"/>
       <c r="J236" s="4" t="n"/>
-      <c r="K236" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L236" s="4" t="n"/>
+      <c r="K236" s="4" t="n"/>
+      <c r="L236" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M236" s="4" t="n"/>
       <c r="N236" s="4" t="n"/>
+      <c r="O236" s="4" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
@@ -5686,14 +5927,15 @@
       <c r="H237" s="4" t="n"/>
       <c r="I237" s="4" t="n"/>
       <c r="J237" s="4" t="n"/>
-      <c r="K237" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L237" s="4" t="n"/>
+      <c r="K237" s="4" t="n"/>
+      <c r="L237" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M237" s="4" t="n"/>
       <c r="N237" s="4" t="n"/>
+      <c r="O237" s="4" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="6" t="inlineStr">
@@ -5714,6 +5956,7 @@
       <c r="L238" s="7" t="n"/>
       <c r="M238" s="7" t="n"/>
       <c r="N238" s="7" t="n"/>
+      <c r="O238" s="7" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
@@ -5734,6 +5977,7 @@
       <c r="L239" s="7" t="n"/>
       <c r="M239" s="7" t="n"/>
       <c r="N239" s="7" t="n"/>
+      <c r="O239" s="7" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
@@ -5750,18 +5994,19 @@
       <c r="H240" s="4" t="n"/>
       <c r="I240" s="4" t="n"/>
       <c r="J240" s="4" t="n"/>
-      <c r="K240" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="K240" s="4" t="n"/>
       <c r="L240" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="M240" s="4" t="n"/>
+      <c r="M240" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N240" s="4" t="n"/>
+      <c r="O240" s="4" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
@@ -5775,25 +6020,26 @@
       <c r="E241" s="4" t="n"/>
       <c r="F241" s="4" t="n"/>
       <c r="G241" s="4" t="n"/>
-      <c r="H241" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="I241" s="4" t="n"/>
+      <c r="H241" s="4" t="n"/>
+      <c r="I241" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J241" s="4" t="n"/>
-      <c r="K241" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="K241" s="4" t="n"/>
       <c r="L241" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="M241" s="4" t="n"/>
+      <c r="M241" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N241" s="4" t="n"/>
+      <c r="O241" s="4" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
@@ -5807,21 +6053,22 @@
       <c r="E242" s="4" t="n"/>
       <c r="F242" s="4" t="n"/>
       <c r="G242" s="4" t="n"/>
-      <c r="H242" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="I242" s="4" t="n"/>
+      <c r="H242" s="4" t="n"/>
+      <c r="I242" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J242" s="4" t="n"/>
       <c r="K242" s="4" t="n"/>
-      <c r="L242" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M242" s="4" t="n"/>
+      <c r="L242" s="4" t="n"/>
+      <c r="M242" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N242" s="4" t="n"/>
+      <c r="O242" s="4" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
@@ -5835,17 +6082,18 @@
       <c r="E243" s="4" t="n"/>
       <c r="F243" s="4" t="n"/>
       <c r="G243" s="4" t="n"/>
-      <c r="H243" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="I243" s="4" t="n"/>
+      <c r="H243" s="4" t="n"/>
+      <c r="I243" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J243" s="4" t="n"/>
       <c r="K243" s="4" t="n"/>
       <c r="L243" s="4" t="n"/>
       <c r="M243" s="4" t="n"/>
-      <c r="N243" s="8" t="inlineStr">
+      <c r="N243" s="4" t="n"/>
+      <c r="O243" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5863,17 +6111,18 @@
       <c r="E244" s="4" t="n"/>
       <c r="F244" s="4" t="n"/>
       <c r="G244" s="4" t="n"/>
-      <c r="H244" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="I244" s="4" t="n"/>
+      <c r="H244" s="4" t="n"/>
+      <c r="I244" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J244" s="4" t="n"/>
       <c r="K244" s="4" t="n"/>
       <c r="L244" s="4" t="n"/>
       <c r="M244" s="4" t="n"/>
-      <c r="N244" s="8" t="inlineStr">
+      <c r="N244" s="4" t="n"/>
+      <c r="O244" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5898,6 +6147,7 @@
       <c r="L245" s="7" t="n"/>
       <c r="M245" s="7" t="n"/>
       <c r="N245" s="7" t="n"/>
+      <c r="O245" s="7" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="6" t="inlineStr">
@@ -5918,6 +6168,7 @@
       <c r="L246" s="7" t="n"/>
       <c r="M246" s="7" t="n"/>
       <c r="N246" s="7" t="n"/>
+      <c r="O246" s="7" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
@@ -5931,17 +6182,18 @@
       <c r="E247" s="4" t="n"/>
       <c r="F247" s="4" t="n"/>
       <c r="G247" s="4" t="n"/>
-      <c r="H247" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="I247" s="4" t="n"/>
+      <c r="H247" s="4" t="n"/>
+      <c r="I247" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J247" s="4" t="n"/>
       <c r="K247" s="4" t="n"/>
       <c r="L247" s="4" t="n"/>
       <c r="M247" s="4" t="n"/>
-      <c r="N247" s="8" t="inlineStr">
+      <c r="N247" s="4" t="n"/>
+      <c r="O247" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5959,17 +6211,18 @@
       <c r="E248" s="4" t="n"/>
       <c r="F248" s="4" t="n"/>
       <c r="G248" s="4" t="n"/>
-      <c r="H248" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="I248" s="4" t="n"/>
+      <c r="H248" s="4" t="n"/>
+      <c r="I248" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J248" s="4" t="n"/>
       <c r="K248" s="4" t="n"/>
       <c r="L248" s="4" t="n"/>
       <c r="M248" s="4" t="n"/>
-      <c r="N248" s="8" t="inlineStr">
+      <c r="N248" s="4" t="n"/>
+      <c r="O248" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5993,7 +6246,8 @@
       <c r="K249" s="4" t="n"/>
       <c r="L249" s="4" t="n"/>
       <c r="M249" s="4" t="n"/>
-      <c r="N249" s="8" t="inlineStr">
+      <c r="N249" s="4" t="n"/>
+      <c r="O249" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6018,6 +6272,7 @@
       <c r="L250" s="4" t="n"/>
       <c r="M250" s="4" t="n"/>
       <c r="N250" s="4" t="n"/>
+      <c r="O250" s="4" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
@@ -6038,6 +6293,7 @@
       <c r="L251" s="4" t="n"/>
       <c r="M251" s="4" t="n"/>
       <c r="N251" s="4" t="n"/>
+      <c r="O251" s="4" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="6" t="inlineStr">
@@ -6058,6 +6314,7 @@
       <c r="L252" s="7" t="n"/>
       <c r="M252" s="7" t="n"/>
       <c r="N252" s="7" t="n"/>
+      <c r="O252" s="7" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="6" t="inlineStr">
@@ -6078,6 +6335,7 @@
       <c r="L253" s="7" t="n"/>
       <c r="M253" s="7" t="n"/>
       <c r="N253" s="7" t="n"/>
+      <c r="O253" s="7" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
@@ -6098,6 +6356,7 @@
       <c r="L254" s="4" t="n"/>
       <c r="M254" s="4" t="n"/>
       <c r="N254" s="4" t="n"/>
+      <c r="O254" s="4" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
@@ -6118,6 +6377,7 @@
       <c r="L255" s="4" t="n"/>
       <c r="M255" s="4" t="n"/>
       <c r="N255" s="4" t="n"/>
+      <c r="O255" s="4" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
@@ -6138,6 +6398,7 @@
       <c r="L256" s="4" t="n"/>
       <c r="M256" s="4" t="n"/>
       <c r="N256" s="4" t="n"/>
+      <c r="O256" s="4" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
@@ -6154,14 +6415,15 @@
       <c r="H257" s="4" t="n"/>
       <c r="I257" s="4" t="n"/>
       <c r="J257" s="4" t="n"/>
-      <c r="K257" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L257" s="4" t="n"/>
+      <c r="K257" s="4" t="n"/>
+      <c r="L257" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M257" s="4" t="n"/>
       <c r="N257" s="4" t="n"/>
+      <c r="O257" s="4" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
@@ -6175,25 +6437,26 @@
       <c r="E258" s="4" t="n"/>
       <c r="F258" s="4" t="n"/>
       <c r="G258" s="4" t="n"/>
-      <c r="H258" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="I258" s="4" t="n"/>
+      <c r="H258" s="4" t="n"/>
+      <c r="I258" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J258" s="4" t="n"/>
-      <c r="K258" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L258" s="4" t="n"/>
-      <c r="M258" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N258" s="4" t="n"/>
+      <c r="K258" s="4" t="n"/>
+      <c r="L258" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="M258" s="4" t="n"/>
+      <c r="N258" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O258" s="4" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
@@ -6214,6 +6477,7 @@
       <c r="L259" s="7" t="n"/>
       <c r="M259" s="7" t="n"/>
       <c r="N259" s="7" t="n"/>
+      <c r="O259" s="7" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="6" t="inlineStr">
@@ -6234,6 +6498,7 @@
       <c r="L260" s="7" t="n"/>
       <c r="M260" s="7" t="n"/>
       <c r="N260" s="7" t="n"/>
+      <c r="O260" s="7" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
@@ -6247,25 +6512,26 @@
       <c r="E261" s="4" t="n"/>
       <c r="F261" s="4" t="n"/>
       <c r="G261" s="4" t="n"/>
-      <c r="H261" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="I261" s="4" t="n"/>
+      <c r="H261" s="4" t="n"/>
+      <c r="I261" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J261" s="4" t="n"/>
-      <c r="K261" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L261" s="4" t="n"/>
-      <c r="M261" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N261" s="4" t="n"/>
+      <c r="K261" s="4" t="n"/>
+      <c r="L261" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="M261" s="4" t="n"/>
+      <c r="N261" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O261" s="4" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
@@ -6282,14 +6548,15 @@
       <c r="H262" s="4" t="n"/>
       <c r="I262" s="4" t="n"/>
       <c r="J262" s="4" t="n"/>
-      <c r="K262" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L262" s="4" t="n"/>
+      <c r="K262" s="4" t="n"/>
+      <c r="L262" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M262" s="4" t="n"/>
       <c r="N262" s="4" t="n"/>
+      <c r="O262" s="4" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
@@ -6310,6 +6577,7 @@
       <c r="L263" s="4" t="n"/>
       <c r="M263" s="4" t="n"/>
       <c r="N263" s="4" t="n"/>
+      <c r="O263" s="4" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
@@ -6330,6 +6598,7 @@
       <c r="L264" s="4" t="n"/>
       <c r="M264" s="4" t="n"/>
       <c r="N264" s="4" t="n"/>
+      <c r="O264" s="4" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
@@ -6347,13 +6616,14 @@
       <c r="I265" s="4" t="n"/>
       <c r="J265" s="4" t="n"/>
       <c r="K265" s="4" t="n"/>
-      <c r="L265" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M265" s="4" t="n"/>
+      <c r="L265" s="4" t="n"/>
+      <c r="M265" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N265" s="4" t="n"/>
+      <c r="O265" s="4" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="6" t="inlineStr">
@@ -6374,6 +6644,7 @@
       <c r="L266" s="7" t="n"/>
       <c r="M266" s="7" t="n"/>
       <c r="N266" s="7" t="n"/>
+      <c r="O266" s="7" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
@@ -6394,6 +6665,7 @@
       <c r="L267" s="7" t="n"/>
       <c r="M267" s="7" t="n"/>
       <c r="N267" s="7" t="n"/>
+      <c r="O267" s="7" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
@@ -6414,6 +6686,7 @@
       <c r="L268" s="4" t="n"/>
       <c r="M268" s="4" t="n"/>
       <c r="N268" s="4" t="n"/>
+      <c r="O268" s="4" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
@@ -6433,7 +6706,8 @@
       <c r="K269" s="4" t="n"/>
       <c r="L269" s="4" t="n"/>
       <c r="M269" s="4" t="n"/>
-      <c r="N269" s="8" t="inlineStr">
+      <c r="N269" s="4" t="n"/>
+      <c r="O269" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6453,15 +6727,16 @@
       <c r="G270" s="4" t="n"/>
       <c r="H270" s="4" t="n"/>
       <c r="I270" s="4" t="n"/>
-      <c r="J270" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="K270" s="4" t="n"/>
+      <c r="J270" s="4" t="n"/>
+      <c r="K270" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L270" s="4" t="n"/>
       <c r="M270" s="4" t="n"/>
-      <c r="N270" s="8" t="inlineStr">
+      <c r="N270" s="4" t="n"/>
+      <c r="O270" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6485,7 +6760,8 @@
       <c r="K271" s="4" t="n"/>
       <c r="L271" s="4" t="n"/>
       <c r="M271" s="4" t="n"/>
-      <c r="N271" s="8" t="inlineStr">
+      <c r="N271" s="4" t="n"/>
+      <c r="O271" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6509,7 +6785,8 @@
       <c r="K272" s="4" t="n"/>
       <c r="L272" s="4" t="n"/>
       <c r="M272" s="4" t="n"/>
-      <c r="N272" s="8" t="inlineStr">
+      <c r="N272" s="4" t="n"/>
+      <c r="O272" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6534,6 +6811,7 @@
       <c r="L273" s="7" t="n"/>
       <c r="M273" s="7" t="n"/>
       <c r="N273" s="7" t="n"/>
+      <c r="O273" s="7" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="6" t="inlineStr">
@@ -6554,6 +6832,7 @@
       <c r="L274" s="7" t="n"/>
       <c r="M274" s="7" t="n"/>
       <c r="N274" s="7" t="n"/>
+      <c r="O274" s="7" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
@@ -6569,19 +6848,20 @@
       <c r="G275" s="4" t="n"/>
       <c r="H275" s="4" t="n"/>
       <c r="I275" s="4" t="n"/>
-      <c r="J275" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="K275" s="4" t="n"/>
+      <c r="J275" s="4" t="n"/>
+      <c r="K275" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L275" s="4" t="n"/>
-      <c r="M275" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="M275" s="4" t="n"/>
       <c r="N275" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O275" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6604,12 +6884,13 @@
       <c r="J276" s="4" t="n"/>
       <c r="K276" s="4" t="n"/>
       <c r="L276" s="4" t="n"/>
-      <c r="M276" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="M276" s="4" t="n"/>
       <c r="N276" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O276" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6632,12 +6913,13 @@
       <c r="J277" s="4" t="n"/>
       <c r="K277" s="4" t="n"/>
       <c r="L277" s="4" t="n"/>
-      <c r="M277" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="M277" s="4" t="n"/>
       <c r="N277" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O277" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6660,12 +6942,13 @@
       <c r="J278" s="4" t="n"/>
       <c r="K278" s="4" t="n"/>
       <c r="L278" s="4" t="n"/>
-      <c r="M278" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N278" s="4" t="n"/>
+      <c r="M278" s="4" t="n"/>
+      <c r="N278" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O278" s="4" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
@@ -6686,6 +6969,7 @@
       <c r="L279" s="4" t="n"/>
       <c r="M279" s="4" t="n"/>
       <c r="N279" s="4" t="n"/>
+      <c r="O279" s="4" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="6" t="inlineStr">
@@ -6706,6 +6990,7 @@
       <c r="L280" s="7" t="n"/>
       <c r="M280" s="7" t="n"/>
       <c r="N280" s="7" t="n"/>
+      <c r="O280" s="7" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
@@ -6726,6 +7011,7 @@
       <c r="L281" s="7" t="n"/>
       <c r="M281" s="7" t="n"/>
       <c r="N281" s="7" t="n"/>
+      <c r="O281" s="7" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
@@ -6750,6 +7036,7 @@
       <c r="L282" s="4" t="n"/>
       <c r="M282" s="4" t="n"/>
       <c r="N282" s="4" t="n"/>
+      <c r="O282" s="4" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
@@ -6774,6 +7061,7 @@
       <c r="L283" s="4" t="n"/>
       <c r="M283" s="4" t="n"/>
       <c r="N283" s="4" t="n"/>
+      <c r="O283" s="4" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
@@ -6798,6 +7086,7 @@
       <c r="L284" s="4" t="n"/>
       <c r="M284" s="4" t="n"/>
       <c r="N284" s="4" t="n"/>
+      <c r="O284" s="4" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
@@ -6822,6 +7111,7 @@
       <c r="L285" s="4" t="n"/>
       <c r="M285" s="4" t="n"/>
       <c r="N285" s="4" t="n"/>
+      <c r="O285" s="4" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
@@ -6842,14 +7132,15 @@
       <c r="H286" s="4" t="n"/>
       <c r="I286" s="4" t="n"/>
       <c r="J286" s="4" t="n"/>
-      <c r="K286" s="5" t="inlineStr">
+      <c r="K286" s="4" t="n"/>
+      <c r="L286" s="5" t="inlineStr">
         <is>
           <t>Sick - Sick</t>
         </is>
       </c>
-      <c r="L286" s="4" t="n"/>
       <c r="M286" s="4" t="n"/>
       <c r="N286" s="4" t="n"/>
+      <c r="O286" s="4" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="6" t="inlineStr">
@@ -6870,6 +7161,7 @@
       <c r="L287" s="7" t="n"/>
       <c r="M287" s="7" t="n"/>
       <c r="N287" s="7" t="n"/>
+      <c r="O287" s="7" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="6" t="inlineStr">
@@ -6890,6 +7182,7 @@
       <c r="L288" s="7" t="n"/>
       <c r="M288" s="7" t="n"/>
       <c r="N288" s="7" t="n"/>
+      <c r="O288" s="7" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
@@ -6905,27 +7198,28 @@
       <c r="C289" s="4" t="n"/>
       <c r="D289" s="4" t="n"/>
       <c r="E289" s="4" t="n"/>
-      <c r="F289" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="G289" s="4" t="n"/>
-      <c r="H289" s="9" t="inlineStr">
+      <c r="F289" s="4" t="n"/>
+      <c r="G289" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="H289" s="4" t="n"/>
+      <c r="I289" s="9" t="inlineStr">
         <is>
           <t>Delivery - Rhwym Galon</t>
         </is>
       </c>
-      <c r="I289" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J289" s="4" t="n"/>
+      <c r="J289" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="K289" s="4" t="n"/>
       <c r="L289" s="4" t="n"/>
       <c r="M289" s="4" t="n"/>
       <c r="N289" s="4" t="n"/>
+      <c r="O289" s="4" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
@@ -6941,27 +7235,28 @@
       <c r="C290" s="4" t="n"/>
       <c r="D290" s="4" t="n"/>
       <c r="E290" s="4" t="n"/>
-      <c r="F290" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="G290" s="4" t="n"/>
-      <c r="H290" s="10" t="inlineStr">
+      <c r="F290" s="4" t="n"/>
+      <c r="G290" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="H290" s="4" t="n"/>
+      <c r="I290" s="10" t="inlineStr">
         <is>
           <t>TOIL - Rhwym Galon</t>
         </is>
       </c>
-      <c r="I290" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J290" s="4" t="n"/>
+      <c r="J290" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="K290" s="4" t="n"/>
       <c r="L290" s="4" t="n"/>
       <c r="M290" s="4" t="n"/>
       <c r="N290" s="4" t="n"/>
+      <c r="O290" s="4" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
@@ -6973,23 +7268,24 @@
       <c r="C291" s="4" t="n"/>
       <c r="D291" s="4" t="n"/>
       <c r="E291" s="4" t="n"/>
-      <c r="F291" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="G291" s="4" t="n"/>
+      <c r="F291" s="4" t="n"/>
+      <c r="G291" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="H291" s="4" t="n"/>
-      <c r="I291" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J291" s="4" t="n"/>
+      <c r="I291" s="4" t="n"/>
+      <c r="J291" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="K291" s="4" t="n"/>
       <c r="L291" s="4" t="n"/>
       <c r="M291" s="4" t="n"/>
       <c r="N291" s="4" t="n"/>
+      <c r="O291" s="4" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
@@ -7001,23 +7297,24 @@
       <c r="C292" s="4" t="n"/>
       <c r="D292" s="4" t="n"/>
       <c r="E292" s="4" t="n"/>
-      <c r="F292" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="G292" s="4" t="n"/>
+      <c r="F292" s="4" t="n"/>
+      <c r="G292" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="H292" s="4" t="n"/>
-      <c r="I292" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J292" s="4" t="n"/>
+      <c r="I292" s="4" t="n"/>
+      <c r="J292" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="K292" s="4" t="n"/>
       <c r="L292" s="4" t="n"/>
       <c r="M292" s="4" t="n"/>
       <c r="N292" s="4" t="n"/>
+      <c r="O292" s="4" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
@@ -7029,27 +7326,28 @@
       <c r="C293" s="4" t="n"/>
       <c r="D293" s="4" t="n"/>
       <c r="E293" s="4" t="n"/>
-      <c r="F293" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="G293" s="4" t="n"/>
-      <c r="H293" s="9" t="inlineStr">
+      <c r="F293" s="4" t="n"/>
+      <c r="G293" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="H293" s="4" t="n"/>
+      <c r="I293" s="9" t="inlineStr">
         <is>
           <t>Delivery - Rhwym Galon</t>
         </is>
       </c>
-      <c r="I293" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J293" s="4" t="n"/>
+      <c r="J293" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="K293" s="4" t="n"/>
       <c r="L293" s="4" t="n"/>
       <c r="M293" s="4" t="n"/>
       <c r="N293" s="4" t="n"/>
+      <c r="O293" s="4" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="6" t="inlineStr">
@@ -7070,6 +7368,7 @@
       <c r="L294" s="7" t="n"/>
       <c r="M294" s="7" t="n"/>
       <c r="N294" s="7" t="n"/>
+      <c r="O294" s="7" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
@@ -7090,6 +7389,7 @@
       <c r="L295" s="7" t="n"/>
       <c r="M295" s="7" t="n"/>
       <c r="N295" s="7" t="n"/>
+      <c r="O295" s="7" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
@@ -7112,16 +7412,17 @@
       <c r="F296" s="4" t="n"/>
       <c r="G296" s="4" t="n"/>
       <c r="H296" s="4" t="n"/>
-      <c r="I296" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J296" s="4" t="n"/>
+      <c r="I296" s="4" t="n"/>
+      <c r="J296" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="K296" s="4" t="n"/>
       <c r="L296" s="4" t="n"/>
       <c r="M296" s="4" t="n"/>
       <c r="N296" s="4" t="n"/>
+      <c r="O296" s="4" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
@@ -7141,27 +7442,28 @@
         </is>
       </c>
       <c r="E297" s="4" t="n"/>
-      <c r="F297" s="5" t="inlineStr">
+      <c r="F297" s="4" t="n"/>
+      <c r="G297" s="5" t="inlineStr">
         <is>
           <t>A/L (Half Day) - Annual Leave</t>
         </is>
       </c>
-      <c r="G297" s="4" t="n"/>
       <c r="H297" s="4" t="n"/>
-      <c r="I297" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J297" s="4" t="n"/>
-      <c r="K297" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L297" s="4" t="n"/>
+      <c r="I297" s="4" t="n"/>
+      <c r="J297" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="K297" s="4" t="n"/>
+      <c r="L297" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M297" s="4" t="n"/>
       <c r="N297" s="4" t="n"/>
+      <c r="O297" s="4" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
@@ -7184,20 +7486,21 @@
       <c r="F298" s="4" t="n"/>
       <c r="G298" s="4" t="n"/>
       <c r="H298" s="4" t="n"/>
-      <c r="I298" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J298" s="4" t="n"/>
-      <c r="K298" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L298" s="4" t="n"/>
+      <c r="I298" s="4" t="n"/>
+      <c r="J298" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="K298" s="4" t="n"/>
+      <c r="L298" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M298" s="4" t="n"/>
       <c r="N298" s="4" t="n"/>
+      <c r="O298" s="4" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
@@ -7221,16 +7524,17 @@
       <c r="F299" s="4" t="n"/>
       <c r="G299" s="4" t="n"/>
       <c r="H299" s="4" t="n"/>
-      <c r="I299" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J299" s="4" t="n"/>
+      <c r="I299" s="4" t="n"/>
+      <c r="J299" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="K299" s="4" t="n"/>
       <c r="L299" s="4" t="n"/>
       <c r="M299" s="4" t="n"/>
       <c r="N299" s="4" t="n"/>
+      <c r="O299" s="4" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
@@ -7248,25 +7552,26 @@
       <c r="E300" s="4" t="n"/>
       <c r="F300" s="4" t="n"/>
       <c r="G300" s="4" t="n"/>
-      <c r="H300" s="9" t="inlineStr">
+      <c r="H300" s="4" t="n"/>
+      <c r="I300" s="9" t="inlineStr">
         <is>
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="I300" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J300" s="4" t="n"/>
+      <c r="J300" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="K300" s="4" t="n"/>
-      <c r="L300" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M300" s="4" t="n"/>
+      <c r="L300" s="4" t="n"/>
+      <c r="M300" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N300" s="4" t="n"/>
+      <c r="O300" s="4" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="6" t="inlineStr">
@@ -7287,6 +7592,7 @@
       <c r="L301" s="7" t="n"/>
       <c r="M301" s="7" t="n"/>
       <c r="N301" s="7" t="n"/>
+      <c r="O301" s="7" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="6" t="inlineStr">
@@ -7307,6 +7613,7 @@
       <c r="L302" s="7" t="n"/>
       <c r="M302" s="7" t="n"/>
       <c r="N302" s="7" t="n"/>
+      <c r="O302" s="7" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
@@ -7324,13 +7631,14 @@
       <c r="I303" s="4" t="n"/>
       <c r="J303" s="4" t="n"/>
       <c r="K303" s="4" t="n"/>
-      <c r="L303" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M303" s="4" t="n"/>
+      <c r="L303" s="4" t="n"/>
+      <c r="M303" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N303" s="4" t="n"/>
+      <c r="O303" s="4" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
@@ -7348,13 +7656,14 @@
       <c r="I304" s="4" t="n"/>
       <c r="J304" s="4" t="n"/>
       <c r="K304" s="4" t="n"/>
-      <c r="L304" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M304" s="4" t="n"/>
+      <c r="L304" s="4" t="n"/>
+      <c r="M304" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N304" s="4" t="n"/>
+      <c r="O304" s="4" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
@@ -7372,13 +7681,14 @@
       <c r="I305" s="4" t="n"/>
       <c r="J305" s="4" t="n"/>
       <c r="K305" s="4" t="n"/>
-      <c r="L305" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M305" s="4" t="n"/>
+      <c r="L305" s="4" t="n"/>
+      <c r="M305" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N305" s="4" t="n"/>
+      <c r="O305" s="4" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
@@ -7396,13 +7706,14 @@
       <c r="I306" s="4" t="n"/>
       <c r="J306" s="4" t="n"/>
       <c r="K306" s="4" t="n"/>
-      <c r="L306" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M306" s="4" t="n"/>
+      <c r="L306" s="4" t="n"/>
+      <c r="M306" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N306" s="4" t="n"/>
+      <c r="O306" s="4" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
@@ -7420,17 +7731,18 @@
       <c r="I307" s="4" t="n"/>
       <c r="J307" s="4" t="n"/>
       <c r="K307" s="4" t="n"/>
-      <c r="L307" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="L307" s="4" t="n"/>
       <c r="M307" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N307" s="4" t="n"/>
+      <c r="N307" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O307" s="4" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="6" t="inlineStr">
@@ -7451,6 +7763,7 @@
       <c r="L308" s="7" t="n"/>
       <c r="M308" s="7" t="n"/>
       <c r="N308" s="7" t="n"/>
+      <c r="O308" s="7" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="6" t="inlineStr">
@@ -7471,6 +7784,7 @@
       <c r="L309" s="7" t="n"/>
       <c r="M309" s="7" t="n"/>
       <c r="N309" s="7" t="n"/>
+      <c r="O309" s="7" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
@@ -7489,28 +7803,29 @@
       <c r="F310" s="4" t="n"/>
       <c r="G310" s="4" t="n"/>
       <c r="H310" s="4" t="n"/>
-      <c r="I310" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J310" s="5" t="inlineStr">
+      <c r="I310" s="4" t="n"/>
+      <c r="J310" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="K310" s="5" t="inlineStr">
         <is>
           <t>Pre-Production - Mabli</t>
         </is>
       </c>
-      <c r="K310" s="5" t="inlineStr">
+      <c r="L310" s="5" t="inlineStr">
         <is>
           <t>Edit - Socials</t>
         </is>
       </c>
-      <c r="L310" s="4" t="n"/>
-      <c r="M310" s="5" t="inlineStr">
+      <c r="M310" s="4" t="n"/>
+      <c r="N310" s="5" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="N310" s="5" t="inlineStr">
+      <c r="O310" s="5" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -7541,28 +7856,29 @@
       <c r="F311" s="4" t="n"/>
       <c r="G311" s="4" t="n"/>
       <c r="H311" s="4" t="n"/>
-      <c r="I311" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J311" s="5" t="inlineStr">
+      <c r="I311" s="4" t="n"/>
+      <c r="J311" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="K311" s="5" t="inlineStr">
         <is>
           <t>Datblygu</t>
         </is>
       </c>
-      <c r="K311" s="10" t="inlineStr">
+      <c r="L311" s="10" t="inlineStr">
         <is>
           <t>TOIL - Hansh Socials</t>
         </is>
       </c>
-      <c r="L311" s="4" t="n"/>
-      <c r="M311" s="5" t="inlineStr">
+      <c r="M311" s="4" t="n"/>
+      <c r="N311" s="5" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="N311" s="5" t="inlineStr">
+      <c r="O311" s="5" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -7593,32 +7909,33 @@
       <c r="F312" s="4" t="n"/>
       <c r="G312" s="4" t="n"/>
       <c r="H312" s="4" t="n"/>
-      <c r="I312" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J312" s="5" t="inlineStr">
+      <c r="I312" s="4" t="n"/>
+      <c r="J312" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="K312" s="5" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="K312" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L312" s="5" t="inlineStr">
+      <c r="L312" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="M312" s="5" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="M312" s="5" t="inlineStr">
+      <c r="N312" s="5" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="N312" s="5" t="inlineStr">
+      <c r="O312" s="5" t="inlineStr">
         <is>
           <t>Edit Annibynwyr</t>
         </is>
@@ -7646,39 +7963,40 @@
         </is>
       </c>
       <c r="E313" s="4" t="n"/>
-      <c r="F313" s="5" t="inlineStr">
+      <c r="F313" s="4" t="n"/>
+      <c r="G313" s="5" t="inlineStr">
         <is>
           <t>A/L (Half Day) - 1/2 Day Annual Leave</t>
         </is>
       </c>
-      <c r="G313" s="4" t="n"/>
       <c r="H313" s="4" t="n"/>
-      <c r="I313" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J313" s="5" t="inlineStr">
+      <c r="I313" s="4" t="n"/>
+      <c r="J313" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="K313" s="5" t="inlineStr">
         <is>
           <t>Datblygu</t>
         </is>
       </c>
-      <c r="K313" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L313" s="5" t="inlineStr">
+      <c r="L313" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="M313" s="5" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="M313" s="5" t="inlineStr">
+      <c r="N313" s="5" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="N313" s="5" t="inlineStr">
+      <c r="O313" s="5" t="inlineStr">
         <is>
           <t>Edit Annibynwyr</t>
         </is>
@@ -7702,39 +8020,40 @@
         </is>
       </c>
       <c r="E314" s="4" t="n"/>
-      <c r="F314" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="G314" s="4" t="n"/>
+      <c r="F314" s="4" t="n"/>
+      <c r="G314" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="H314" s="4" t="n"/>
-      <c r="I314" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J314" s="5" t="inlineStr">
+      <c r="I314" s="4" t="n"/>
+      <c r="J314" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="K314" s="5" t="inlineStr">
         <is>
           <t>Datblygu</t>
         </is>
       </c>
-      <c r="K314" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L314" s="5" t="inlineStr">
+      <c r="L314" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="M314" s="5" t="inlineStr">
         <is>
           <t>Black History 2026</t>
         </is>
       </c>
-      <c r="M314" s="10" t="inlineStr">
+      <c r="N314" s="10" t="inlineStr">
         <is>
           <t>TOIL - Darts</t>
         </is>
       </c>
-      <c r="N314" s="5" t="inlineStr">
+      <c r="O314" s="5" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -7751,22 +8070,23 @@
       <c r="D315" s="7" t="n"/>
       <c r="E315" s="7" t="n"/>
       <c r="F315" s="7" t="n"/>
-      <c r="G315" s="5" t="inlineStr">
+      <c r="G315" s="7" t="n"/>
+      <c r="H315" s="5" t="inlineStr">
         <is>
           <t>Film - Linda Wilson</t>
         </is>
       </c>
-      <c r="H315" s="7" t="n"/>
       <c r="I315" s="7" t="n"/>
       <c r="J315" s="7" t="n"/>
       <c r="K315" s="7" t="n"/>
       <c r="L315" s="7" t="n"/>
-      <c r="M315" s="5" t="inlineStr">
+      <c r="M315" s="7" t="n"/>
+      <c r="N315" s="5" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
       </c>
-      <c r="N315" s="5" t="inlineStr">
+      <c r="O315" s="5" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -7789,12 +8109,13 @@
       <c r="J316" s="7" t="n"/>
       <c r="K316" s="7" t="n"/>
       <c r="L316" s="7" t="n"/>
-      <c r="M316" s="5" t="inlineStr">
+      <c r="M316" s="7" t="n"/>
+      <c r="N316" s="5" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
       </c>
-      <c r="N316" s="5" t="inlineStr">
+      <c r="O316" s="5" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -7818,39 +8139,40 @@
       </c>
       <c r="D317" s="4" t="n"/>
       <c r="E317" s="4" t="n"/>
-      <c r="F317" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="F317" s="4" t="n"/>
       <c r="G317" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="H317" s="4" t="n"/>
-      <c r="I317" s="11" t="inlineStr">
+      <c r="H317" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="I317" s="4" t="n"/>
+      <c r="J317" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J317" s="4" t="n"/>
-      <c r="K317" s="5" t="inlineStr">
+      <c r="K317" s="4" t="n"/>
+      <c r="L317" s="5" t="inlineStr">
         <is>
           <t>Socials - Rookie Teachers</t>
         </is>
       </c>
-      <c r="L317" s="5" t="inlineStr">
+      <c r="M317" s="5" t="inlineStr">
         <is>
           <t>Film - Hansh Socials</t>
         </is>
       </c>
-      <c r="M317" s="10" t="inlineStr">
+      <c r="N317" s="10" t="inlineStr">
         <is>
           <t>TOIL - Darts 6 G</t>
         </is>
       </c>
-      <c r="N317" s="5" t="inlineStr">
+      <c r="O317" s="5" t="inlineStr">
         <is>
           <t>External - Darts 6 G</t>
         </is>
@@ -7869,28 +8191,29 @@
       <c r="F318" s="4" t="n"/>
       <c r="G318" s="4" t="n"/>
       <c r="H318" s="4" t="n"/>
-      <c r="I318" s="11" t="inlineStr">
+      <c r="I318" s="4" t="n"/>
+      <c r="J318" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J318" s="4" t="n"/>
-      <c r="K318" s="5" t="inlineStr">
+      <c r="K318" s="4" t="n"/>
+      <c r="L318" s="5" t="inlineStr">
         <is>
           <t>Socials - Rookie Teachers</t>
         </is>
       </c>
-      <c r="L318" s="5" t="inlineStr">
+      <c r="M318" s="5" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="M318" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N318" s="5" t="inlineStr">
+      <c r="N318" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O318" s="5" t="inlineStr">
         <is>
           <t>Edit - Hansh Socials</t>
         </is>
@@ -7909,28 +8232,29 @@
       <c r="F319" s="4" t="n"/>
       <c r="G319" s="4" t="n"/>
       <c r="H319" s="4" t="n"/>
-      <c r="I319" s="11" t="inlineStr">
+      <c r="I319" s="4" t="n"/>
+      <c r="J319" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J319" s="4" t="n"/>
-      <c r="K319" s="5" t="inlineStr">
+      <c r="K319" s="4" t="n"/>
+      <c r="L319" s="5" t="inlineStr">
         <is>
           <t>Socials - Rookie Teachers</t>
         </is>
       </c>
-      <c r="L319" s="5" t="inlineStr">
+      <c r="M319" s="5" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="M319" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N319" s="5" t="inlineStr">
+      <c r="N319" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O319" s="5" t="inlineStr">
         <is>
           <t>Edit - Hansh Socials</t>
         </is>
@@ -7951,38 +8275,39 @@
       <c r="D320" s="4" t="n"/>
       <c r="E320" s="4" t="n"/>
       <c r="F320" s="4" t="n"/>
-      <c r="G320" s="5" t="inlineStr">
+      <c r="G320" s="4" t="n"/>
+      <c r="H320" s="5" t="inlineStr">
         <is>
           <t>Film - Linda Wilson</t>
         </is>
       </c>
-      <c r="H320" s="5" t="inlineStr">
+      <c r="I320" s="5" t="inlineStr">
         <is>
           <t>Film - Rhedeg Rhacs - Aberteifi</t>
         </is>
       </c>
-      <c r="I320" s="5" t="inlineStr">
+      <c r="J320" s="5" t="inlineStr">
         <is>
           <t>Record VO &amp; Title Song</t>
         </is>
       </c>
-      <c r="J320" s="4" t="n"/>
-      <c r="K320" s="5" t="inlineStr">
+      <c r="K320" s="4" t="n"/>
+      <c r="L320" s="5" t="inlineStr">
         <is>
           <t>Socials - Rookie Teachers</t>
         </is>
       </c>
-      <c r="L320" s="5" t="inlineStr">
+      <c r="M320" s="5" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="M320" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N320" s="5" t="inlineStr">
+      <c r="N320" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O320" s="5" t="inlineStr">
         <is>
           <t>Film - Rhedeg Rhacs - Aberteifi</t>
         </is>
@@ -8004,33 +8329,34 @@
       <c r="E321" s="4" t="n"/>
       <c r="F321" s="4" t="n"/>
       <c r="G321" s="4" t="n"/>
-      <c r="H321" s="5" t="inlineStr">
+      <c r="H321" s="4" t="n"/>
+      <c r="I321" s="5" t="inlineStr">
         <is>
           <t>Sick</t>
         </is>
       </c>
-      <c r="I321" s="11" t="inlineStr">
+      <c r="J321" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J321" s="4" t="n"/>
-      <c r="K321" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L321" s="5" t="inlineStr">
+      <c r="K321" s="4" t="n"/>
+      <c r="L321" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="M321" s="5" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="M321" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N321" s="5" t="inlineStr">
+      <c r="N321" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O321" s="5" t="inlineStr">
         <is>
           <t>Edit - Fresh From Wales</t>
         </is>
@@ -8055,6 +8381,7 @@
       <c r="L322" s="7" t="n"/>
       <c r="M322" s="7" t="n"/>
       <c r="N322" s="7" t="n"/>
+      <c r="O322" s="7" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="6" t="inlineStr">
@@ -8075,6 +8402,7 @@
       <c r="L323" s="7" t="n"/>
       <c r="M323" s="7" t="n"/>
       <c r="N323" s="7" t="n"/>
+      <c r="O323" s="7" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="3" t="inlineStr">
@@ -8089,28 +8417,29 @@
       <c r="F324" s="4" t="n"/>
       <c r="G324" s="4" t="n"/>
       <c r="H324" s="4" t="n"/>
-      <c r="I324" s="5" t="inlineStr">
+      <c r="I324" s="4" t="n"/>
+      <c r="J324" s="5" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J324" s="4" t="n"/>
-      <c r="K324" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L324" s="5" t="inlineStr">
+      <c r="K324" s="4" t="n"/>
+      <c r="L324" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="M324" s="5" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="M324" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N324" s="4" t="n"/>
+      <c r="N324" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O324" s="4" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
@@ -8125,28 +8454,29 @@
       <c r="F325" s="4" t="n"/>
       <c r="G325" s="4" t="n"/>
       <c r="H325" s="4" t="n"/>
-      <c r="I325" s="5" t="inlineStr">
+      <c r="I325" s="4" t="n"/>
+      <c r="J325" s="5" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J325" s="4" t="n"/>
-      <c r="K325" s="5" t="inlineStr">
+      <c r="K325" s="4" t="n"/>
+      <c r="L325" s="5" t="inlineStr">
         <is>
           <t>Edit - Rookie Teachers</t>
         </is>
       </c>
-      <c r="L325" s="5" t="inlineStr">
+      <c r="M325" s="5" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="M325" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N325" s="4" t="n"/>
+      <c r="N325" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O325" s="4" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="3" t="inlineStr">
@@ -8161,28 +8491,29 @@
       <c r="F326" s="4" t="n"/>
       <c r="G326" s="4" t="n"/>
       <c r="H326" s="4" t="n"/>
-      <c r="I326" s="5" t="inlineStr">
+      <c r="I326" s="4" t="n"/>
+      <c r="J326" s="5" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J326" s="4" t="n"/>
-      <c r="K326" s="5" t="inlineStr">
+      <c r="K326" s="4" t="n"/>
+      <c r="L326" s="5" t="inlineStr">
         <is>
           <t>Edit - Rookie Teachers</t>
         </is>
       </c>
-      <c r="L326" s="5" t="inlineStr">
+      <c r="M326" s="5" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="M326" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N326" s="4" t="n"/>
+      <c r="N326" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O326" s="4" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="3" t="inlineStr">
@@ -8201,28 +8532,29 @@
       <c r="F327" s="4" t="n"/>
       <c r="G327" s="4" t="n"/>
       <c r="H327" s="4" t="n"/>
-      <c r="I327" s="5" t="inlineStr">
+      <c r="I327" s="4" t="n"/>
+      <c r="J327" s="5" t="inlineStr">
         <is>
           <t>Sŵ Ni</t>
         </is>
       </c>
-      <c r="J327" s="4" t="n"/>
-      <c r="K327" s="5" t="inlineStr">
+      <c r="K327" s="4" t="n"/>
+      <c r="L327" s="5" t="inlineStr">
         <is>
           <t>Rookie Teachers</t>
         </is>
       </c>
-      <c r="L327" s="5" t="inlineStr">
+      <c r="M327" s="5" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="M327" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N327" s="5" t="inlineStr">
+      <c r="N327" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O327" s="5" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -8242,35 +8574,36 @@
       <c r="C328" s="4" t="n"/>
       <c r="D328" s="4" t="n"/>
       <c r="E328" s="4" t="n"/>
-      <c r="F328" s="5" t="inlineStr">
+      <c r="F328" s="4" t="n"/>
+      <c r="G328" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Lleisio Sw Ni </t>
         </is>
       </c>
-      <c r="G328" s="4" t="n"/>
       <c r="H328" s="4" t="n"/>
-      <c r="I328" s="5" t="inlineStr">
+      <c r="I328" s="4" t="n"/>
+      <c r="J328" s="5" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J328" s="4" t="n"/>
-      <c r="K328" s="5" t="inlineStr">
+      <c r="K328" s="4" t="n"/>
+      <c r="L328" s="5" t="inlineStr">
         <is>
           <t>Rookie Teachers</t>
         </is>
       </c>
-      <c r="L328" s="5" t="inlineStr">
+      <c r="M328" s="5" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="M328" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N328" s="5" t="inlineStr">
+      <c r="N328" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O328" s="5" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -8295,6 +8628,7 @@
       <c r="L329" s="7" t="n"/>
       <c r="M329" s="7" t="n"/>
       <c r="N329" s="7" t="n"/>
+      <c r="O329" s="7" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="6" t="inlineStr">
@@ -8315,6 +8649,7 @@
       <c r="L330" s="7" t="n"/>
       <c r="M330" s="7" t="n"/>
       <c r="N330" s="7" t="n"/>
+      <c r="O330" s="7" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="3" t="inlineStr">
@@ -8325,36 +8660,41 @@
       <c r="B331" s="4" t="n"/>
       <c r="C331" s="4" t="n"/>
       <c r="D331" s="4" t="n"/>
-      <c r="E331" s="4" t="n"/>
+      <c r="E331" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Rookie Teachers</t>
+        </is>
+      </c>
       <c r="F331" s="4" t="n"/>
       <c r="G331" s="4" t="n"/>
-      <c r="H331" s="9" t="inlineStr">
+      <c r="H331" s="4" t="n"/>
+      <c r="I331" s="9" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I331" s="5" t="inlineStr">
+      <c r="J331" s="5" t="inlineStr">
         <is>
           <t>Sŵ Ni</t>
         </is>
       </c>
-      <c r="J331" s="4" t="n"/>
-      <c r="K331" s="5" t="inlineStr">
+      <c r="K331" s="4" t="n"/>
+      <c r="L331" s="5" t="inlineStr">
         <is>
           <t>Rhwym Galon</t>
         </is>
       </c>
-      <c r="L331" s="5" t="inlineStr">
+      <c r="M331" s="5" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="M331" s="5" t="inlineStr">
+      <c r="N331" s="5" t="inlineStr">
         <is>
           <t>Sick</t>
         </is>
       </c>
-      <c r="N331" s="10" t="inlineStr">
+      <c r="O331" s="10" t="inlineStr">
         <is>
           <t>TOIL - Darts 6 G</t>
         </is>
@@ -8372,25 +8712,26 @@
       <c r="E332" s="4" t="n"/>
       <c r="F332" s="4" t="n"/>
       <c r="G332" s="4" t="n"/>
-      <c r="H332" s="9" t="inlineStr">
+      <c r="H332" s="4" t="n"/>
+      <c r="I332" s="9" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I332" s="5" t="inlineStr">
+      <c r="J332" s="5" t="inlineStr">
         <is>
           <t>Sŵ Ni</t>
         </is>
       </c>
-      <c r="J332" s="4" t="n"/>
-      <c r="K332" s="5" t="inlineStr">
+      <c r="K332" s="4" t="n"/>
+      <c r="L332" s="5" t="inlineStr">
         <is>
           <t>Rhedeg Rhacs</t>
         </is>
       </c>
-      <c r="L332" s="4" t="n"/>
       <c r="M332" s="4" t="n"/>
       <c r="N332" s="4" t="n"/>
+      <c r="O332" s="4" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="3" t="inlineStr">
@@ -8404,25 +8745,26 @@
       <c r="E333" s="4" t="n"/>
       <c r="F333" s="4" t="n"/>
       <c r="G333" s="4" t="n"/>
-      <c r="H333" s="9" t="inlineStr">
+      <c r="H333" s="4" t="n"/>
+      <c r="I333" s="9" t="inlineStr">
         <is>
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="I333" s="5" t="inlineStr">
+      <c r="J333" s="5" t="inlineStr">
         <is>
           <t>Sŵ Ni</t>
         </is>
       </c>
-      <c r="J333" s="4" t="n"/>
-      <c r="K333" s="5" t="inlineStr">
+      <c r="K333" s="4" t="n"/>
+      <c r="L333" s="5" t="inlineStr">
         <is>
           <t>Rhwym Galon</t>
         </is>
       </c>
-      <c r="L333" s="4" t="n"/>
       <c r="M333" s="4" t="n"/>
       <c r="N333" s="4" t="n"/>
+      <c r="O333" s="4" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="3" t="inlineStr">
@@ -8438,31 +8780,32 @@
         </is>
       </c>
       <c r="E334" s="4" t="n"/>
-      <c r="F334" s="5" t="inlineStr">
+      <c r="F334" s="4" t="n"/>
+      <c r="G334" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="G334" s="4" t="n"/>
       <c r="H334" s="4" t="n"/>
-      <c r="I334" s="5" t="inlineStr">
+      <c r="I334" s="4" t="n"/>
+      <c r="J334" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J334" s="4" t="n"/>
-      <c r="K334" s="5" t="inlineStr">
+      <c r="K334" s="4" t="n"/>
+      <c r="L334" s="5" t="inlineStr">
         <is>
           <t>Rhwym Galon</t>
         </is>
       </c>
-      <c r="L334" s="4" t="n"/>
-      <c r="M334" s="5" t="inlineStr">
+      <c r="M334" s="4" t="n"/>
+      <c r="N334" s="5" t="inlineStr">
         <is>
           <t>Rhodri p/up Cyfranwyr</t>
         </is>
       </c>
-      <c r="N334" s="5" t="inlineStr">
+      <c r="O334" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -8482,27 +8825,28 @@
         </is>
       </c>
       <c r="E335" s="4" t="n"/>
-      <c r="F335" s="5" t="inlineStr">
+      <c r="F335" s="4" t="n"/>
+      <c r="G335" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="G335" s="4" t="n"/>
       <c r="H335" s="4" t="n"/>
-      <c r="I335" s="5" t="inlineStr">
+      <c r="I335" s="4" t="n"/>
+      <c r="J335" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J335" s="4" t="n"/>
-      <c r="K335" s="5" t="inlineStr">
+      <c r="K335" s="4" t="n"/>
+      <c r="L335" s="5" t="inlineStr">
         <is>
           <t>Rhwym Galon</t>
         </is>
       </c>
-      <c r="L335" s="4" t="n"/>
       <c r="M335" s="4" t="n"/>
-      <c r="N335" s="5" t="inlineStr">
+      <c r="N335" s="4" t="n"/>
+      <c r="O335" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -8527,6 +8871,7 @@
       <c r="L336" s="7" t="n"/>
       <c r="M336" s="7" t="n"/>
       <c r="N336" s="7" t="n"/>
+      <c r="O336" s="7" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="6" t="inlineStr">
@@ -8547,6 +8892,7 @@
       <c r="L337" s="7" t="n"/>
       <c r="M337" s="7" t="n"/>
       <c r="N337" s="7" t="n"/>
+      <c r="O337" s="7" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="3" t="inlineStr">
@@ -8562,23 +8908,24 @@
         </is>
       </c>
       <c r="E338" s="4" t="n"/>
-      <c r="F338" s="5" t="inlineStr">
+      <c r="F338" s="4" t="n"/>
+      <c r="G338" s="5" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="G338" s="4" t="n"/>
       <c r="H338" s="4" t="n"/>
-      <c r="I338" s="5" t="inlineStr">
+      <c r="I338" s="4" t="n"/>
+      <c r="J338" s="5" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="J338" s="4" t="n"/>
       <c r="K338" s="4" t="n"/>
       <c r="L338" s="4" t="n"/>
       <c r="M338" s="4" t="n"/>
-      <c r="N338" s="5" t="inlineStr">
+      <c r="N338" s="4" t="n"/>
+      <c r="O338" s="5" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -8598,31 +8945,32 @@
         </is>
       </c>
       <c r="E339" s="4" t="n"/>
-      <c r="F339" s="5" t="inlineStr">
+      <c r="F339" s="4" t="n"/>
+      <c r="G339" s="5" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="G339" s="5" t="inlineStr">
+      <c r="H339" s="5" t="inlineStr">
         <is>
           <t>Film - Linda Wilson</t>
         </is>
       </c>
-      <c r="H339" s="4" t="n"/>
-      <c r="I339" s="5" t="inlineStr">
+      <c r="I339" s="4" t="n"/>
+      <c r="J339" s="5" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="J339" s="4" t="n"/>
       <c r="K339" s="4" t="n"/>
       <c r="L339" s="4" t="n"/>
-      <c r="M339" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N339" s="5" t="inlineStr">
+      <c r="M339" s="4" t="n"/>
+      <c r="N339" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O339" s="5" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -8642,35 +8990,36 @@
         </is>
       </c>
       <c r="E340" s="4" t="n"/>
-      <c r="F340" s="5" t="inlineStr">
+      <c r="F340" s="4" t="n"/>
+      <c r="G340" s="5" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="G340" s="5" t="inlineStr">
+      <c r="H340" s="5" t="inlineStr">
         <is>
           <t>Ffilmio Mabli - AM</t>
         </is>
       </c>
-      <c r="H340" s="4" t="n"/>
-      <c r="I340" s="5" t="inlineStr">
+      <c r="I340" s="4" t="n"/>
+      <c r="J340" s="5" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="J340" s="4" t="n"/>
-      <c r="K340" s="5" t="inlineStr">
+      <c r="K340" s="4" t="n"/>
+      <c r="L340" s="5" t="inlineStr">
         <is>
           <t>Socials - Sŵ Ni</t>
         </is>
       </c>
-      <c r="L340" s="4" t="n"/>
-      <c r="M340" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N340" s="5" t="inlineStr">
+      <c r="M340" s="4" t="n"/>
+      <c r="N340" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O340" s="5" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -8693,20 +9042,21 @@
       <c r="F341" s="4" t="n"/>
       <c r="G341" s="4" t="n"/>
       <c r="H341" s="4" t="n"/>
-      <c r="I341" s="5" t="inlineStr">
+      <c r="I341" s="4" t="n"/>
+      <c r="J341" s="5" t="inlineStr">
         <is>
           <t>Prep Sw Ni MP</t>
         </is>
       </c>
-      <c r="J341" s="4" t="n"/>
       <c r="K341" s="4" t="n"/>
       <c r="L341" s="4" t="n"/>
-      <c r="M341" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N341" s="4" t="n"/>
+      <c r="M341" s="4" t="n"/>
+      <c r="N341" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O341" s="4" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="3" t="inlineStr">
@@ -8723,30 +9073,31 @@
       </c>
       <c r="E342" s="4" t="n"/>
       <c r="F342" s="4" t="n"/>
-      <c r="G342" s="5" t="inlineStr">
+      <c r="G342" s="4" t="n"/>
+      <c r="H342" s="5" t="inlineStr">
         <is>
           <t>Film - Linda Wilson</t>
         </is>
       </c>
-      <c r="H342" s="9" t="inlineStr">
+      <c r="I342" s="9" t="inlineStr">
         <is>
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="I342" s="5" t="inlineStr">
+      <c r="J342" s="5" t="inlineStr">
         <is>
           <t>Film - Prep Sw Ni MP</t>
         </is>
       </c>
-      <c r="J342" s="4" t="n"/>
       <c r="K342" s="4" t="n"/>
       <c r="L342" s="4" t="n"/>
-      <c r="M342" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N342" s="4" t="n"/>
+      <c r="M342" s="4" t="n"/>
+      <c r="N342" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O342" s="4" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="6" t="inlineStr">
@@ -8767,6 +9118,7 @@
       <c r="L343" s="7" t="n"/>
       <c r="M343" s="7" t="n"/>
       <c r="N343" s="7" t="n"/>
+      <c r="O343" s="7" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="6" t="inlineStr">
@@ -8787,6 +9139,7 @@
       <c r="L344" s="7" t="n"/>
       <c r="M344" s="7" t="n"/>
       <c r="N344" s="7" t="n"/>
+      <c r="O344" s="7" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="3" t="inlineStr">
@@ -8802,31 +9155,32 @@
         </is>
       </c>
       <c r="E345" s="4" t="n"/>
-      <c r="F345" s="5" t="inlineStr">
+      <c r="F345" s="4" t="n"/>
+      <c r="G345" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="G345" s="4" t="n"/>
       <c r="H345" s="4" t="n"/>
-      <c r="I345" s="5" t="inlineStr">
+      <c r="I345" s="4" t="n"/>
+      <c r="J345" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J345" s="4" t="n"/>
-      <c r="K345" s="5" t="inlineStr">
+      <c r="K345" s="4" t="n"/>
+      <c r="L345" s="5" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="L345" s="4" t="n"/>
-      <c r="M345" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N345" s="5" t="inlineStr">
+      <c r="M345" s="4" t="n"/>
+      <c r="N345" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O345" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -8846,31 +9200,32 @@
         </is>
       </c>
       <c r="E346" s="4" t="n"/>
-      <c r="F346" s="5" t="inlineStr">
+      <c r="F346" s="4" t="n"/>
+      <c r="G346" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="G346" s="4" t="n"/>
       <c r="H346" s="4" t="n"/>
-      <c r="I346" s="5" t="inlineStr">
+      <c r="I346" s="4" t="n"/>
+      <c r="J346" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J346" s="4" t="n"/>
-      <c r="K346" s="5" t="inlineStr">
+      <c r="K346" s="4" t="n"/>
+      <c r="L346" s="5" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="L346" s="4" t="n"/>
-      <c r="M346" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N346" s="5" t="inlineStr">
+      <c r="M346" s="4" t="n"/>
+      <c r="N346" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O346" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -8890,35 +9245,36 @@
         </is>
       </c>
       <c r="E347" s="4" t="n"/>
-      <c r="F347" s="5" t="inlineStr">
+      <c r="F347" s="4" t="n"/>
+      <c r="G347" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="G347" s="4" t="n"/>
       <c r="H347" s="4" t="n"/>
-      <c r="I347" s="5" t="inlineStr">
+      <c r="I347" s="4" t="n"/>
+      <c r="J347" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J347" s="5" t="inlineStr">
+      <c r="K347" s="5" t="inlineStr">
         <is>
           <t>SOCIAL MEDIA CONFERENCE</t>
         </is>
       </c>
-      <c r="K347" s="5" t="inlineStr">
+      <c r="L347" s="5" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="L347" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M347" s="4" t="n"/>
-      <c r="N347" s="5" t="inlineStr">
+      <c r="M347" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N347" s="4" t="n"/>
+      <c r="O347" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -8938,31 +9294,32 @@
         </is>
       </c>
       <c r="E348" s="4" t="n"/>
-      <c r="F348" s="5" t="inlineStr">
+      <c r="F348" s="4" t="n"/>
+      <c r="G348" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="G348" s="4" t="n"/>
       <c r="H348" s="4" t="n"/>
-      <c r="I348" s="5" t="inlineStr">
+      <c r="I348" s="4" t="n"/>
+      <c r="J348" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J348" s="4" t="n"/>
-      <c r="K348" s="5" t="inlineStr">
+      <c r="K348" s="4" t="n"/>
+      <c r="L348" s="5" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="L348" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M348" s="4" t="n"/>
-      <c r="N348" s="5" t="inlineStr">
+      <c r="M348" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N348" s="4" t="n"/>
+      <c r="O348" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -8982,48 +9339,49 @@
         </is>
       </c>
       <c r="E349" s="4" t="n"/>
-      <c r="F349" s="5" t="inlineStr">
+      <c r="F349" s="4" t="n"/>
+      <c r="G349" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="G349" s="5" t="inlineStr">
+      <c r="H349" s="5" t="inlineStr">
         <is>
           <t>Urban Cowboys</t>
         </is>
       </c>
-      <c r="H349" s="5" t="inlineStr">
+      <c r="I349" s="5" t="inlineStr">
         <is>
           <t>Urban Cowboys</t>
         </is>
       </c>
-      <c r="I349" s="5" t="inlineStr">
+      <c r="J349" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J349" s="5" t="inlineStr">
+      <c r="K349" s="5" t="inlineStr">
         <is>
           <t>Urban Cowboys</t>
         </is>
       </c>
-      <c r="K349" s="5" t="inlineStr">
+      <c r="L349" s="5" t="inlineStr">
         <is>
           <t>Urban Cowboys
 Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="L349" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M349" s="5" t="inlineStr">
+      <c r="M349" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N349" s="5" t="inlineStr">
         <is>
           <t>Urban Cowboys</t>
         </is>
       </c>
-      <c r="N349" s="5" t="inlineStr">
+      <c r="O349" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -9048,42 +9406,43 @@
       </c>
       <c r="E350" s="7" t="n"/>
       <c r="F350" s="7" t="n"/>
-      <c r="G350" s="5" t="inlineStr">
+      <c r="G350" s="7" t="n"/>
+      <c r="H350" s="5" t="inlineStr">
         <is>
           <t>Urban Cowboys</t>
         </is>
       </c>
-      <c r="H350" s="5" t="inlineStr">
+      <c r="I350" s="5" t="inlineStr">
         <is>
           <t>Urban Cowboys</t>
         </is>
       </c>
-      <c r="I350" s="5" t="inlineStr">
+      <c r="J350" s="5" t="inlineStr">
         <is>
           <t>Urban Cowboys</t>
         </is>
       </c>
-      <c r="J350" s="5" t="inlineStr">
+      <c r="K350" s="5" t="inlineStr">
         <is>
           <t>Urban Cowboys</t>
         </is>
       </c>
-      <c r="K350" s="5" t="inlineStr">
+      <c r="L350" s="5" t="inlineStr">
         <is>
           <t>Urban Cowboys</t>
         </is>
       </c>
-      <c r="L350" s="5" t="inlineStr">
+      <c r="M350" s="5" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="M350" s="5" t="inlineStr">
+      <c r="N350" s="5" t="inlineStr">
         <is>
           <t>Urban Cowboys</t>
         </is>
       </c>
-      <c r="N350" s="5" t="inlineStr">
+      <c r="O350" s="5" t="inlineStr">
         <is>
           <t>Urban Cowboys</t>
         </is>
@@ -9108,42 +9467,43 @@
       </c>
       <c r="E351" s="7" t="n"/>
       <c r="F351" s="7" t="n"/>
-      <c r="G351" s="5" t="inlineStr">
+      <c r="G351" s="7" t="n"/>
+      <c r="H351" s="5" t="inlineStr">
         <is>
           <t>Urban Cowboys</t>
         </is>
       </c>
-      <c r="H351" s="5" t="inlineStr">
+      <c r="I351" s="5" t="inlineStr">
         <is>
           <t>Urban Cowboys</t>
         </is>
       </c>
-      <c r="I351" s="5" t="inlineStr">
+      <c r="J351" s="5" t="inlineStr">
         <is>
           <t>Urban Cowboys</t>
         </is>
       </c>
-      <c r="J351" s="5" t="inlineStr">
+      <c r="K351" s="5" t="inlineStr">
         <is>
           <t>Urban Cowboys</t>
         </is>
       </c>
-      <c r="K351" s="5" t="inlineStr">
+      <c r="L351" s="5" t="inlineStr">
         <is>
           <t>Urban Cowboys</t>
         </is>
       </c>
-      <c r="L351" s="5" t="inlineStr">
+      <c r="M351" s="5" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="M351" s="5" t="inlineStr">
+      <c r="N351" s="5" t="inlineStr">
         <is>
           <t>Urban Cowboys</t>
         </is>
       </c>
-      <c r="N351" s="5" t="inlineStr">
+      <c r="O351" s="5" t="inlineStr">
         <is>
           <t>Urban Cowboys</t>
         </is>
@@ -9161,25 +9521,26 @@
       <c r="E352" s="4" t="n"/>
       <c r="F352" s="4" t="n"/>
       <c r="G352" s="4" t="n"/>
-      <c r="H352" s="9" t="inlineStr">
+      <c r="H352" s="4" t="n"/>
+      <c r="I352" s="9" t="inlineStr">
         <is>
           <t>Delivery - Black History 2026</t>
         </is>
       </c>
-      <c r="I352" s="4" t="n"/>
       <c r="J352" s="4" t="n"/>
-      <c r="K352" s="5" t="inlineStr">
+      <c r="K352" s="4" t="n"/>
+      <c r="L352" s="5" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="L352" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M352" s="4" t="n"/>
+      <c r="M352" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N352" s="4" t="n"/>
+      <c r="O352" s="4" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="3" t="inlineStr">
@@ -9197,13 +9558,14 @@
       <c r="I353" s="4" t="n"/>
       <c r="J353" s="4" t="n"/>
       <c r="K353" s="4" t="n"/>
-      <c r="L353" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M353" s="4" t="n"/>
+      <c r="L353" s="4" t="n"/>
+      <c r="M353" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N353" s="4" t="n"/>
+      <c r="O353" s="4" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="3" t="inlineStr">
@@ -9218,20 +9580,21 @@
       <c r="F354" s="4" t="n"/>
       <c r="G354" s="4" t="n"/>
       <c r="H354" s="4" t="n"/>
-      <c r="I354" s="11" t="inlineStr">
+      <c r="I354" s="4" t="n"/>
+      <c r="J354" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J354" s="4" t="n"/>
       <c r="K354" s="4" t="n"/>
-      <c r="L354" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M354" s="4" t="n"/>
+      <c r="L354" s="4" t="n"/>
+      <c r="M354" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N354" s="4" t="n"/>
+      <c r="O354" s="4" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="3" t="inlineStr">
@@ -9246,20 +9609,21 @@
       <c r="F355" s="4" t="n"/>
       <c r="G355" s="4" t="n"/>
       <c r="H355" s="4" t="n"/>
-      <c r="I355" s="11" t="inlineStr">
+      <c r="I355" s="4" t="n"/>
+      <c r="J355" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J355" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="K355" s="4" t="n"/>
+      <c r="K355" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L355" s="4" t="n"/>
       <c r="M355" s="4" t="n"/>
       <c r="N355" s="4" t="n"/>
+      <c r="O355" s="4" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="3" t="inlineStr">
@@ -9274,20 +9638,21 @@
       <c r="F356" s="4" t="n"/>
       <c r="G356" s="4" t="n"/>
       <c r="H356" s="4" t="n"/>
-      <c r="I356" s="11" t="inlineStr">
+      <c r="I356" s="4" t="n"/>
+      <c r="J356" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J356" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="K356" s="4" t="n"/>
+      <c r="K356" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L356" s="4" t="n"/>
       <c r="M356" s="4" t="n"/>
       <c r="N356" s="4" t="n"/>
+      <c r="O356" s="4" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="6" t="inlineStr">
@@ -9298,12 +9663,12 @@
       <c r="B357" s="7" t="n"/>
       <c r="C357" s="7" t="n"/>
       <c r="D357" s="7" t="n"/>
-      <c r="E357" s="10" t="inlineStr">
+      <c r="E357" s="7" t="n"/>
+      <c r="F357" s="10" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F357" s="7" t="n"/>
       <c r="G357" s="7" t="n"/>
       <c r="H357" s="7" t="n"/>
       <c r="I357" s="7" t="n"/>
@@ -9312,6 +9677,7 @@
       <c r="L357" s="7" t="n"/>
       <c r="M357" s="7" t="n"/>
       <c r="N357" s="7" t="n"/>
+      <c r="O357" s="7" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="6" t="inlineStr">
@@ -9322,12 +9688,12 @@
       <c r="B358" s="7" t="n"/>
       <c r="C358" s="7" t="n"/>
       <c r="D358" s="7" t="n"/>
-      <c r="E358" s="10" t="inlineStr">
+      <c r="E358" s="7" t="n"/>
+      <c r="F358" s="10" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F358" s="7" t="n"/>
       <c r="G358" s="7" t="n"/>
       <c r="H358" s="7" t="n"/>
       <c r="I358" s="7" t="n"/>
@@ -9336,6 +9702,7 @@
       <c r="L358" s="7" t="n"/>
       <c r="M358" s="7" t="n"/>
       <c r="N358" s="7" t="n"/>
+      <c r="O358" s="7" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="3" t="inlineStr">
@@ -9350,28 +9717,29 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E359" s="10" t="inlineStr">
+      <c r="E359" s="4" t="n"/>
+      <c r="F359" s="10" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F359" s="4" t="n"/>
       <c r="G359" s="4" t="n"/>
       <c r="H359" s="4" t="n"/>
-      <c r="I359" s="11" t="inlineStr">
+      <c r="I359" s="4" t="n"/>
+      <c r="J359" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J359" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="K359" s="4" t="n"/>
+      <c r="K359" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L359" s="4" t="n"/>
       <c r="M359" s="4" t="n"/>
       <c r="N359" s="4" t="n"/>
+      <c r="O359" s="4" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="3" t="inlineStr">
@@ -9386,28 +9754,29 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E360" s="10" t="inlineStr">
+      <c r="E360" s="4" t="n"/>
+      <c r="F360" s="10" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F360" s="4" t="n"/>
       <c r="G360" s="4" t="n"/>
       <c r="H360" s="4" t="n"/>
-      <c r="I360" s="11" t="inlineStr">
+      <c r="I360" s="4" t="n"/>
+      <c r="J360" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J360" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="K360" s="4" t="n"/>
+      <c r="K360" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L360" s="4" t="n"/>
       <c r="M360" s="4" t="n"/>
       <c r="N360" s="4" t="n"/>
+      <c r="O360" s="4" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="3" t="inlineStr">
@@ -9422,32 +9791,33 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E361" s="10" t="inlineStr">
+      <c r="E361" s="4" t="n"/>
+      <c r="F361" s="10" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F361" s="4" t="n"/>
       <c r="G361" s="4" t="n"/>
       <c r="H361" s="4" t="n"/>
-      <c r="I361" s="11" t="inlineStr">
+      <c r="I361" s="4" t="n"/>
+      <c r="J361" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J361" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="K361" s="11" t="inlineStr">
+      <c r="K361" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="L361" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L361" s="4" t="n"/>
       <c r="M361" s="4" t="n"/>
       <c r="N361" s="4" t="n"/>
+      <c r="O361" s="4" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="3" t="inlineStr">
@@ -9462,32 +9832,33 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E362" s="10" t="inlineStr">
+      <c r="E362" s="4" t="n"/>
+      <c r="F362" s="10" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F362" s="4" t="n"/>
       <c r="G362" s="4" t="n"/>
       <c r="H362" s="4" t="n"/>
-      <c r="I362" s="11" t="inlineStr">
+      <c r="I362" s="4" t="n"/>
+      <c r="J362" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J362" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="K362" s="11" t="inlineStr">
+      <c r="K362" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="L362" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L362" s="4" t="n"/>
       <c r="M362" s="4" t="n"/>
       <c r="N362" s="4" t="n"/>
+      <c r="O362" s="4" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="3" t="inlineStr">
@@ -9498,32 +9869,33 @@
       <c r="B363" s="4" t="n"/>
       <c r="C363" s="4" t="n"/>
       <c r="D363" s="4" t="n"/>
-      <c r="E363" s="10" t="inlineStr">
+      <c r="E363" s="4" t="n"/>
+      <c r="F363" s="10" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F363" s="4" t="n"/>
       <c r="G363" s="4" t="n"/>
       <c r="H363" s="4" t="n"/>
-      <c r="I363" s="11" t="inlineStr">
+      <c r="I363" s="4" t="n"/>
+      <c r="J363" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J363" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="K363" s="11" t="inlineStr">
+      <c r="K363" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="L363" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L363" s="4" t="n"/>
       <c r="M363" s="4" t="n"/>
       <c r="N363" s="4" t="n"/>
+      <c r="O363" s="4" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="6" t="inlineStr">
@@ -9534,12 +9906,12 @@
       <c r="B364" s="7" t="n"/>
       <c r="C364" s="7" t="n"/>
       <c r="D364" s="7" t="n"/>
-      <c r="E364" s="10" t="inlineStr">
+      <c r="E364" s="7" t="n"/>
+      <c r="F364" s="10" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F364" s="7" t="n"/>
       <c r="G364" s="7" t="n"/>
       <c r="H364" s="7" t="n"/>
       <c r="I364" s="7" t="n"/>
@@ -9548,6 +9920,7 @@
       <c r="L364" s="7" t="n"/>
       <c r="M364" s="7" t="n"/>
       <c r="N364" s="7" t="n"/>
+      <c r="O364" s="7" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="6" t="inlineStr">
@@ -9558,12 +9931,12 @@
       <c r="B365" s="7" t="n"/>
       <c r="C365" s="7" t="n"/>
       <c r="D365" s="7" t="n"/>
-      <c r="E365" s="10" t="inlineStr">
+      <c r="E365" s="7" t="n"/>
+      <c r="F365" s="10" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F365" s="7" t="n"/>
       <c r="G365" s="7" t="n"/>
       <c r="H365" s="7" t="n"/>
       <c r="I365" s="7" t="n"/>
@@ -9572,6 +9945,7 @@
       <c r="L365" s="7" t="n"/>
       <c r="M365" s="7" t="n"/>
       <c r="N365" s="7" t="n"/>
+      <c r="O365" s="7" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="3" t="inlineStr">
@@ -9582,32 +9956,33 @@
       <c r="B366" s="4" t="n"/>
       <c r="C366" s="4" t="n"/>
       <c r="D366" s="4" t="n"/>
-      <c r="E366" s="10" t="inlineStr">
+      <c r="E366" s="4" t="n"/>
+      <c r="F366" s="10" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F366" s="4" t="n"/>
       <c r="G366" s="4" t="n"/>
       <c r="H366" s="4" t="n"/>
-      <c r="I366" s="11" t="inlineStr">
+      <c r="I366" s="4" t="n"/>
+      <c r="J366" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J366" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="K366" s="11" t="inlineStr">
+      <c r="K366" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="L366" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L366" s="4" t="n"/>
       <c r="M366" s="4" t="n"/>
       <c r="N366" s="4" t="n"/>
+      <c r="O366" s="4" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="3" t="inlineStr">
@@ -9622,24 +9997,25 @@
       <c r="F367" s="4" t="n"/>
       <c r="G367" s="4" t="n"/>
       <c r="H367" s="4" t="n"/>
-      <c r="I367" s="11" t="inlineStr">
+      <c r="I367" s="4" t="n"/>
+      <c r="J367" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J367" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="K367" s="11" t="inlineStr">
+      <c r="K367" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="L367" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L367" s="4" t="n"/>
       <c r="M367" s="4" t="n"/>
       <c r="N367" s="4" t="n"/>
+      <c r="O367" s="4" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="3" t="inlineStr">
@@ -9654,20 +10030,21 @@
       <c r="F368" s="4" t="n"/>
       <c r="G368" s="4" t="n"/>
       <c r="H368" s="4" t="n"/>
-      <c r="I368" s="11" t="inlineStr">
+      <c r="I368" s="4" t="n"/>
+      <c r="J368" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J368" s="4" t="n"/>
-      <c r="K368" s="11" t="inlineStr">
+      <c r="K368" s="4" t="n"/>
+      <c r="L368" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L368" s="4" t="n"/>
       <c r="M368" s="4" t="n"/>
       <c r="N368" s="4" t="n"/>
+      <c r="O368" s="4" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="3" t="inlineStr">
@@ -9682,20 +10059,21 @@
       <c r="F369" s="4" t="n"/>
       <c r="G369" s="4" t="n"/>
       <c r="H369" s="4" t="n"/>
-      <c r="I369" s="11" t="inlineStr">
+      <c r="I369" s="4" t="n"/>
+      <c r="J369" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J369" s="4" t="n"/>
-      <c r="K369" s="11" t="inlineStr">
+      <c r="K369" s="4" t="n"/>
+      <c r="L369" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L369" s="4" t="n"/>
       <c r="M369" s="4" t="n"/>
       <c r="N369" s="4" t="n"/>
+      <c r="O369" s="4" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="3" t="inlineStr">
@@ -9710,20 +10088,21 @@
       <c r="F370" s="4" t="n"/>
       <c r="G370" s="4" t="n"/>
       <c r="H370" s="4" t="n"/>
-      <c r="I370" s="11" t="inlineStr">
+      <c r="I370" s="4" t="n"/>
+      <c r="J370" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J370" s="4" t="n"/>
-      <c r="K370" s="11" t="inlineStr">
+      <c r="K370" s="4" t="n"/>
+      <c r="L370" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L370" s="4" t="n"/>
       <c r="M370" s="4" t="n"/>
       <c r="N370" s="4" t="n"/>
+      <c r="O370" s="4" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="6" t="inlineStr">
@@ -9744,6 +10123,7 @@
       <c r="L371" s="7" t="n"/>
       <c r="M371" s="7" t="n"/>
       <c r="N371" s="7" t="n"/>
+      <c r="O371" s="7" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="6" t="inlineStr">
@@ -9764,6 +10144,7 @@
       <c r="L372" s="7" t="n"/>
       <c r="M372" s="7" t="n"/>
       <c r="N372" s="7" t="n"/>
+      <c r="O372" s="7" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="3" t="inlineStr">
@@ -9778,20 +10159,21 @@
       <c r="F373" s="4" t="n"/>
       <c r="G373" s="4" t="n"/>
       <c r="H373" s="4" t="n"/>
-      <c r="I373" s="11" t="inlineStr">
+      <c r="I373" s="4" t="n"/>
+      <c r="J373" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J373" s="4" t="n"/>
-      <c r="K373" s="11" t="inlineStr">
+      <c r="K373" s="4" t="n"/>
+      <c r="L373" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L373" s="4" t="n"/>
       <c r="M373" s="4" t="n"/>
       <c r="N373" s="4" t="n"/>
+      <c r="O373" s="4" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="3" t="inlineStr">
@@ -9806,20 +10188,21 @@
       <c r="F374" s="4" t="n"/>
       <c r="G374" s="4" t="n"/>
       <c r="H374" s="4" t="n"/>
-      <c r="I374" s="11" t="inlineStr">
+      <c r="I374" s="4" t="n"/>
+      <c r="J374" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J374" s="4" t="n"/>
-      <c r="K374" s="11" t="inlineStr">
+      <c r="K374" s="4" t="n"/>
+      <c r="L374" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L374" s="4" t="n"/>
       <c r="M374" s="4" t="n"/>
       <c r="N374" s="4" t="n"/>
+      <c r="O374" s="4" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="3" t="inlineStr">
@@ -9834,20 +10217,21 @@
       <c r="F375" s="4" t="n"/>
       <c r="G375" s="4" t="n"/>
       <c r="H375" s="4" t="n"/>
-      <c r="I375" s="11" t="inlineStr">
+      <c r="I375" s="4" t="n"/>
+      <c r="J375" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J375" s="4" t="n"/>
-      <c r="K375" s="11" t="inlineStr">
+      <c r="K375" s="4" t="n"/>
+      <c r="L375" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L375" s="4" t="n"/>
       <c r="M375" s="4" t="n"/>
       <c r="N375" s="4" t="n"/>
+      <c r="O375" s="4" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="3" t="inlineStr">
@@ -9862,20 +10246,21 @@
       <c r="F376" s="4" t="n"/>
       <c r="G376" s="4" t="n"/>
       <c r="H376" s="4" t="n"/>
-      <c r="I376" s="11" t="inlineStr">
+      <c r="I376" s="4" t="n"/>
+      <c r="J376" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J376" s="4" t="n"/>
-      <c r="K376" s="11" t="inlineStr">
+      <c r="K376" s="4" t="n"/>
+      <c r="L376" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L376" s="4" t="n"/>
       <c r="M376" s="4" t="n"/>
       <c r="N376" s="4" t="n"/>
+      <c r="O376" s="4" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="3" t="inlineStr">
@@ -9890,20 +10275,21 @@
       <c r="F377" s="4" t="n"/>
       <c r="G377" s="4" t="n"/>
       <c r="H377" s="4" t="n"/>
-      <c r="I377" s="11" t="inlineStr">
+      <c r="I377" s="4" t="n"/>
+      <c r="J377" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J377" s="4" t="n"/>
-      <c r="K377" s="11" t="inlineStr">
+      <c r="K377" s="4" t="n"/>
+      <c r="L377" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L377" s="4" t="n"/>
       <c r="M377" s="4" t="n"/>
       <c r="N377" s="4" t="n"/>
+      <c r="O377" s="4" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="6" t="inlineStr">
@@ -9915,12 +10301,12 @@
       <c r="C378" s="7" t="n"/>
       <c r="D378" s="7" t="n"/>
       <c r="E378" s="7" t="n"/>
-      <c r="F378" s="5" t="inlineStr">
+      <c r="F378" s="7" t="n"/>
+      <c r="G378" s="5" t="inlineStr">
         <is>
           <t>NORTHERN STAR DEADLINE</t>
         </is>
       </c>
-      <c r="G378" s="7" t="n"/>
       <c r="H378" s="7" t="n"/>
       <c r="I378" s="7" t="n"/>
       <c r="J378" s="7" t="n"/>
@@ -9928,6 +10314,7 @@
       <c r="L378" s="7" t="n"/>
       <c r="M378" s="7" t="n"/>
       <c r="N378" s="7" t="n"/>
+      <c r="O378" s="7" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="6" t="inlineStr">
@@ -9948,6 +10335,7 @@
       <c r="L379" s="7" t="n"/>
       <c r="M379" s="7" t="n"/>
       <c r="N379" s="7" t="n"/>
+      <c r="O379" s="7" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="3" t="inlineStr">
@@ -9962,20 +10350,21 @@
       <c r="F380" s="4" t="n"/>
       <c r="G380" s="4" t="n"/>
       <c r="H380" s="4" t="n"/>
-      <c r="I380" s="11" t="inlineStr">
+      <c r="I380" s="4" t="n"/>
+      <c r="J380" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J380" s="4" t="n"/>
-      <c r="K380" s="11" t="inlineStr">
+      <c r="K380" s="4" t="n"/>
+      <c r="L380" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L380" s="4" t="n"/>
       <c r="M380" s="4" t="n"/>
       <c r="N380" s="4" t="n"/>
+      <c r="O380" s="4" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="3" t="inlineStr">
@@ -9990,20 +10379,21 @@
       <c r="F381" s="4" t="n"/>
       <c r="G381" s="4" t="n"/>
       <c r="H381" s="4" t="n"/>
-      <c r="I381" s="11" t="inlineStr">
+      <c r="I381" s="4" t="n"/>
+      <c r="J381" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J381" s="4" t="n"/>
-      <c r="K381" s="11" t="inlineStr">
+      <c r="K381" s="4" t="n"/>
+      <c r="L381" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L381" s="4" t="n"/>
       <c r="M381" s="4" t="n"/>
       <c r="N381" s="4" t="n"/>
+      <c r="O381" s="4" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="3" t="inlineStr">
@@ -10018,20 +10408,21 @@
       <c r="F382" s="4" t="n"/>
       <c r="G382" s="4" t="n"/>
       <c r="H382" s="4" t="n"/>
-      <c r="I382" s="8" t="inlineStr">
+      <c r="I382" s="4" t="n"/>
+      <c r="J382" s="8" t="inlineStr">
         <is>
           <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J382" s="4" t="n"/>
-      <c r="K382" s="11" t="inlineStr">
+      <c r="K382" s="4" t="n"/>
+      <c r="L382" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L382" s="4" t="n"/>
       <c r="M382" s="4" t="n"/>
       <c r="N382" s="4" t="n"/>
+      <c r="O382" s="4" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="3" t="inlineStr">
@@ -10046,20 +10437,21 @@
       <c r="F383" s="4" t="n"/>
       <c r="G383" s="4" t="n"/>
       <c r="H383" s="4" t="n"/>
-      <c r="I383" s="8" t="inlineStr">
+      <c r="I383" s="4" t="n"/>
+      <c r="J383" s="8" t="inlineStr">
         <is>
           <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J383" s="4" t="n"/>
-      <c r="K383" s="11" t="inlineStr">
+      <c r="K383" s="4" t="n"/>
+      <c r="L383" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L383" s="4" t="n"/>
       <c r="M383" s="4" t="n"/>
       <c r="N383" s="4" t="n"/>
+      <c r="O383" s="4" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="3" t="inlineStr">
@@ -10074,24 +10466,25 @@
       <c r="F384" s="4" t="n"/>
       <c r="G384" s="4" t="n"/>
       <c r="H384" s="4" t="n"/>
-      <c r="I384" s="5" t="inlineStr">
+      <c r="I384" s="4" t="n"/>
+      <c r="J384" s="5" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J384" s="4" t="n"/>
-      <c r="K384" s="11" t="inlineStr">
+      <c r="K384" s="4" t="n"/>
+      <c r="L384" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L384" s="4" t="n"/>
-      <c r="M384" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N384" s="4" t="n"/>
+      <c r="M384" s="4" t="n"/>
+      <c r="N384" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O384" s="4" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="6" t="inlineStr">
@@ -10112,6 +10505,7 @@
       <c r="L385" s="7" t="n"/>
       <c r="M385" s="7" t="n"/>
       <c r="N385" s="7" t="n"/>
+      <c r="O385" s="7" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="6" t="inlineStr">
@@ -10132,6 +10526,7 @@
       <c r="L386" s="7" t="n"/>
       <c r="M386" s="7" t="n"/>
       <c r="N386" s="7" t="n"/>
+      <c r="O386" s="7" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="3" t="inlineStr">
@@ -10150,20 +10545,21 @@
       <c r="F387" s="4" t="n"/>
       <c r="G387" s="4" t="n"/>
       <c r="H387" s="4" t="n"/>
-      <c r="I387" s="5" t="inlineStr">
+      <c r="I387" s="4" t="n"/>
+      <c r="J387" s="5" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J387" s="4" t="n"/>
-      <c r="K387" s="11" t="inlineStr">
+      <c r="K387" s="4" t="n"/>
+      <c r="L387" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L387" s="4" t="n"/>
       <c r="M387" s="4" t="n"/>
       <c r="N387" s="4" t="n"/>
+      <c r="O387" s="4" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="3" t="inlineStr">
@@ -10182,20 +10578,21 @@
       <c r="F388" s="4" t="n"/>
       <c r="G388" s="4" t="n"/>
       <c r="H388" s="4" t="n"/>
-      <c r="I388" s="11" t="inlineStr">
+      <c r="I388" s="4" t="n"/>
+      <c r="J388" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J388" s="4" t="n"/>
-      <c r="K388" s="11" t="inlineStr">
+      <c r="K388" s="4" t="n"/>
+      <c r="L388" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L388" s="4" t="n"/>
       <c r="M388" s="4" t="n"/>
       <c r="N388" s="4" t="n"/>
+      <c r="O388" s="4" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="3" t="inlineStr">
@@ -10214,20 +10611,21 @@
       <c r="F389" s="4" t="n"/>
       <c r="G389" s="4" t="n"/>
       <c r="H389" s="4" t="n"/>
-      <c r="I389" s="11" t="inlineStr">
+      <c r="I389" s="4" t="n"/>
+      <c r="J389" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J389" s="4" t="n"/>
-      <c r="K389" s="11" t="inlineStr">
+      <c r="K389" s="4" t="n"/>
+      <c r="L389" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L389" s="4" t="n"/>
       <c r="M389" s="4" t="n"/>
       <c r="N389" s="4" t="n"/>
+      <c r="O389" s="4" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="3" t="inlineStr">
@@ -10246,20 +10644,21 @@
       <c r="F390" s="4" t="n"/>
       <c r="G390" s="4" t="n"/>
       <c r="H390" s="4" t="n"/>
-      <c r="I390" s="5" t="inlineStr">
+      <c r="I390" s="4" t="n"/>
+      <c r="J390" s="5" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J390" s="4" t="n"/>
-      <c r="K390" s="11" t="inlineStr">
+      <c r="K390" s="4" t="n"/>
+      <c r="L390" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L390" s="4" t="n"/>
       <c r="M390" s="4" t="n"/>
       <c r="N390" s="4" t="n"/>
+      <c r="O390" s="4" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="3" t="inlineStr">
@@ -10278,20 +10677,21 @@
       <c r="F391" s="4" t="n"/>
       <c r="G391" s="4" t="n"/>
       <c r="H391" s="4" t="n"/>
-      <c r="I391" s="11" t="inlineStr">
+      <c r="I391" s="4" t="n"/>
+      <c r="J391" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J391" s="4" t="n"/>
-      <c r="K391" s="11" t="inlineStr">
+      <c r="K391" s="4" t="n"/>
+      <c r="L391" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L391" s="4" t="n"/>
       <c r="M391" s="4" t="n"/>
       <c r="N391" s="4" t="n"/>
+      <c r="O391" s="4" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="6" t="inlineStr">
@@ -10312,6 +10712,7 @@
       <c r="L392" s="7" t="n"/>
       <c r="M392" s="7" t="n"/>
       <c r="N392" s="7" t="n"/>
+      <c r="O392" s="7" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="6" t="inlineStr">
@@ -10332,6 +10733,7 @@
       <c r="L393" s="7" t="n"/>
       <c r="M393" s="7" t="n"/>
       <c r="N393" s="7" t="n"/>
+      <c r="O393" s="7" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="3" t="inlineStr">
@@ -10350,21 +10752,22 @@
       <c r="F394" s="4" t="n"/>
       <c r="G394" s="4" t="n"/>
       <c r="H394" s="4" t="n"/>
-      <c r="I394" s="11" t="inlineStr">
+      <c r="I394" s="4" t="n"/>
+      <c r="J394" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Mabli a Ceff Ceff
 Dub - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="J394" s="4" t="n"/>
-      <c r="K394" s="11" t="inlineStr">
+      <c r="K394" s="4" t="n"/>
+      <c r="L394" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L394" s="4" t="n"/>
       <c r="M394" s="4" t="n"/>
       <c r="N394" s="4" t="n"/>
+      <c r="O394" s="4" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="3" t="inlineStr">
@@ -10383,21 +10786,22 @@
       <c r="F395" s="4" t="n"/>
       <c r="G395" s="4" t="n"/>
       <c r="H395" s="4" t="n"/>
-      <c r="I395" s="11" t="inlineStr">
+      <c r="I395" s="4" t="n"/>
+      <c r="J395" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Mabli a Ceff Ceff
 Dub - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="J395" s="4" t="n"/>
-      <c r="K395" s="11" t="inlineStr">
+      <c r="K395" s="4" t="n"/>
+      <c r="L395" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L395" s="4" t="n"/>
       <c r="M395" s="4" t="n"/>
       <c r="N395" s="4" t="n"/>
+      <c r="O395" s="4" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="3" t="inlineStr">
@@ -10416,21 +10820,22 @@
       <c r="F396" s="4" t="n"/>
       <c r="G396" s="4" t="n"/>
       <c r="H396" s="4" t="n"/>
-      <c r="I396" s="11" t="inlineStr">
+      <c r="I396" s="4" t="n"/>
+      <c r="J396" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Mabli a Ceff Ceff
 Dub - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="J396" s="4" t="n"/>
-      <c r="K396" s="11" t="inlineStr">
+      <c r="K396" s="4" t="n"/>
+      <c r="L396" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L396" s="4" t="n"/>
       <c r="M396" s="4" t="n"/>
       <c r="N396" s="4" t="n"/>
+      <c r="O396" s="4" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="3" t="inlineStr">
@@ -10449,21 +10854,22 @@
       <c r="F397" s="4" t="n"/>
       <c r="G397" s="4" t="n"/>
       <c r="H397" s="4" t="n"/>
-      <c r="I397" s="11" t="inlineStr">
+      <c r="I397" s="4" t="n"/>
+      <c r="J397" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Mabli a Ceff Ceff
 Dub - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="J397" s="4" t="n"/>
-      <c r="K397" s="11" t="inlineStr">
+      <c r="K397" s="4" t="n"/>
+      <c r="L397" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L397" s="4" t="n"/>
       <c r="M397" s="4" t="n"/>
       <c r="N397" s="4" t="n"/>
+      <c r="O397" s="4" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="3" t="inlineStr">
@@ -10475,32 +10881,33 @@
       <c r="C398" s="4" t="n"/>
       <c r="D398" s="4" t="n"/>
       <c r="E398" s="4" t="n"/>
-      <c r="F398" s="9" t="inlineStr">
+      <c r="F398" s="4" t="n"/>
+      <c r="G398" s="9" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="G398" s="4" t="n"/>
-      <c r="H398" s="9" t="inlineStr">
+      <c r="H398" s="4" t="n"/>
+      <c r="I398" s="9" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I398" s="5" t="inlineStr">
+      <c r="J398" s="5" t="inlineStr">
         <is>
           <t>Dub - Mabli a Ceff Ceff
 Online Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="J398" s="4" t="n"/>
-      <c r="K398" s="11" t="inlineStr">
+      <c r="K398" s="4" t="n"/>
+      <c r="L398" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L398" s="4" t="n"/>
       <c r="M398" s="4" t="n"/>
       <c r="N398" s="4" t="n"/>
+      <c r="O398" s="4" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="6" t="inlineStr">
@@ -10521,6 +10928,7 @@
       <c r="L399" s="7" t="n"/>
       <c r="M399" s="7" t="n"/>
       <c r="N399" s="7" t="n"/>
+      <c r="O399" s="7" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="6" t="inlineStr">
@@ -10541,6 +10949,7 @@
       <c r="L400" s="7" t="n"/>
       <c r="M400" s="7" t="n"/>
       <c r="N400" s="7" t="n"/>
+      <c r="O400" s="7" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="3" t="inlineStr">
@@ -10557,14 +10966,15 @@
       <c r="H401" s="4" t="n"/>
       <c r="I401" s="4" t="n"/>
       <c r="J401" s="4" t="n"/>
-      <c r="K401" s="11" t="inlineStr">
+      <c r="K401" s="4" t="n"/>
+      <c r="L401" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="L401" s="4" t="n"/>
       <c r="M401" s="4" t="n"/>
       <c r="N401" s="4" t="n"/>
+      <c r="O401" s="4" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="3" t="inlineStr">
@@ -10585,6 +10995,7 @@
       <c r="L402" s="4" t="n"/>
       <c r="M402" s="4" t="n"/>
       <c r="N402" s="4" t="n"/>
+      <c r="O402" s="4" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="3" t="inlineStr">
@@ -10605,6 +11016,7 @@
       <c r="L403" s="4" t="n"/>
       <c r="M403" s="4" t="n"/>
       <c r="N403" s="4" t="n"/>
+      <c r="O403" s="4" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="3" t="inlineStr">
@@ -10625,6 +11037,7 @@
       <c r="L404" s="4" t="n"/>
       <c r="M404" s="4" t="n"/>
       <c r="N404" s="4" t="n"/>
+      <c r="O404" s="4" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="3" t="inlineStr">
@@ -10636,23 +11049,24 @@
       <c r="C405" s="4" t="n"/>
       <c r="D405" s="4" t="n"/>
       <c r="E405" s="4" t="n"/>
-      <c r="F405" s="9" t="inlineStr">
+      <c r="F405" s="4" t="n"/>
+      <c r="G405" s="9" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="G405" s="4" t="n"/>
-      <c r="H405" s="9" t="inlineStr">
+      <c r="H405" s="4" t="n"/>
+      <c r="I405" s="9" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I405" s="4" t="n"/>
       <c r="J405" s="4" t="n"/>
       <c r="K405" s="4" t="n"/>
       <c r="L405" s="4" t="n"/>
       <c r="M405" s="4" t="n"/>
       <c r="N405" s="4" t="n"/>
+      <c r="O405" s="4" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="6" t="inlineStr">
@@ -10673,6 +11087,7 @@
       <c r="L406" s="7" t="n"/>
       <c r="M406" s="7" t="n"/>
       <c r="N406" s="7" t="n"/>
+      <c r="O406" s="7" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="6" t="inlineStr">
@@ -10693,6 +11108,7 @@
       <c r="L407" s="7" t="n"/>
       <c r="M407" s="7" t="n"/>
       <c r="N407" s="7" t="n"/>
+      <c r="O407" s="7" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="3" t="inlineStr">
@@ -10713,6 +11129,7 @@
       <c r="L408" s="4" t="n"/>
       <c r="M408" s="4" t="n"/>
       <c r="N408" s="4" t="n"/>
+      <c r="O408" s="4" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="3" t="inlineStr">
@@ -10733,6 +11150,7 @@
       <c r="L409" s="4" t="n"/>
       <c r="M409" s="4" t="n"/>
       <c r="N409" s="4" t="n"/>
+      <c r="O409" s="4" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="3" t="inlineStr">
@@ -10747,16 +11165,17 @@
       <c r="F410" s="4" t="n"/>
       <c r="G410" s="4" t="n"/>
       <c r="H410" s="4" t="n"/>
-      <c r="I410" s="11" t="inlineStr">
+      <c r="I410" s="4" t="n"/>
+      <c r="J410" s="11" t="inlineStr">
         <is>
           <t>Online Edit - External</t>
         </is>
       </c>
-      <c r="J410" s="4" t="n"/>
       <c r="K410" s="4" t="n"/>
       <c r="L410" s="4" t="n"/>
       <c r="M410" s="4" t="n"/>
       <c r="N410" s="4" t="n"/>
+      <c r="O410" s="4" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="3" t="inlineStr">
@@ -10771,16 +11190,17 @@
       <c r="F411" s="4" t="n"/>
       <c r="G411" s="4" t="n"/>
       <c r="H411" s="4" t="n"/>
-      <c r="I411" s="11" t="inlineStr">
+      <c r="I411" s="4" t="n"/>
+      <c r="J411" s="11" t="inlineStr">
         <is>
           <t>Online Edit - External</t>
         </is>
       </c>
-      <c r="J411" s="4" t="n"/>
       <c r="K411" s="4" t="n"/>
       <c r="L411" s="4" t="n"/>
       <c r="M411" s="4" t="n"/>
       <c r="N411" s="4" t="n"/>
+      <c r="O411" s="4" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="3" t="inlineStr">
@@ -10795,16 +11215,17 @@
       <c r="F412" s="4" t="n"/>
       <c r="G412" s="4" t="n"/>
       <c r="H412" s="4" t="n"/>
-      <c r="I412" s="11" t="inlineStr">
+      <c r="I412" s="4" t="n"/>
+      <c r="J412" s="11" t="inlineStr">
         <is>
           <t>Online Edit - External</t>
         </is>
       </c>
-      <c r="J412" s="4" t="n"/>
       <c r="K412" s="4" t="n"/>
       <c r="L412" s="4" t="n"/>
       <c r="M412" s="4" t="n"/>
       <c r="N412" s="4" t="n"/>
+      <c r="O412" s="4" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="6" t="inlineStr">
@@ -10825,6 +11246,7 @@
       <c r="L413" s="7" t="n"/>
       <c r="M413" s="7" t="n"/>
       <c r="N413" s="7" t="n"/>
+      <c r="O413" s="7" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="6" t="inlineStr">
@@ -10845,6 +11267,7 @@
       <c r="L414" s="7" t="n"/>
       <c r="M414" s="7" t="n"/>
       <c r="N414" s="7" t="n"/>
+      <c r="O414" s="7" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="3" t="inlineStr">
@@ -10859,16 +11282,17 @@
       <c r="F415" s="4" t="n"/>
       <c r="G415" s="4" t="n"/>
       <c r="H415" s="4" t="n"/>
-      <c r="I415" s="11" t="inlineStr">
+      <c r="I415" s="4" t="n"/>
+      <c r="J415" s="11" t="inlineStr">
         <is>
           <t>Online Edit - External</t>
         </is>
       </c>
-      <c r="J415" s="4" t="n"/>
       <c r="K415" s="4" t="n"/>
       <c r="L415" s="4" t="n"/>
       <c r="M415" s="4" t="n"/>
       <c r="N415" s="4" t="n"/>
+      <c r="O415" s="4" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="3" t="inlineStr">
@@ -10883,16 +11307,17 @@
       <c r="F416" s="4" t="n"/>
       <c r="G416" s="4" t="n"/>
       <c r="H416" s="4" t="n"/>
-      <c r="I416" s="11" t="inlineStr">
+      <c r="I416" s="4" t="n"/>
+      <c r="J416" s="11" t="inlineStr">
         <is>
           <t>Online Edit - External</t>
         </is>
       </c>
-      <c r="J416" s="4" t="n"/>
       <c r="K416" s="4" t="n"/>
       <c r="L416" s="4" t="n"/>
       <c r="M416" s="4" t="n"/>
       <c r="N416" s="4" t="n"/>
+      <c r="O416" s="4" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="3" t="inlineStr">
@@ -10913,6 +11338,7 @@
       <c r="L417" s="4" t="n"/>
       <c r="M417" s="4" t="n"/>
       <c r="N417" s="4" t="n"/>
+      <c r="O417" s="4" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="3" t="inlineStr">
@@ -10933,6 +11359,7 @@
       <c r="L418" s="4" t="n"/>
       <c r="M418" s="4" t="n"/>
       <c r="N418" s="4" t="n"/>
+      <c r="O418" s="4" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="3" t="inlineStr">
@@ -10953,6 +11380,7 @@
       <c r="L419" s="4" t="n"/>
       <c r="M419" s="4" t="n"/>
       <c r="N419" s="4" t="n"/>
+      <c r="O419" s="4" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="6" t="inlineStr">
@@ -10973,6 +11401,7 @@
       <c r="L420" s="7" t="n"/>
       <c r="M420" s="7" t="n"/>
       <c r="N420" s="7" t="n"/>
+      <c r="O420" s="7" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="6" t="inlineStr">
@@ -10993,6 +11422,7 @@
       <c r="L421" s="7" t="n"/>
       <c r="M421" s="7" t="n"/>
       <c r="N421" s="7" t="n"/>
+      <c r="O421" s="7" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="3" t="inlineStr">
@@ -11013,6 +11443,7 @@
       <c r="L422" s="4" t="n"/>
       <c r="M422" s="4" t="n"/>
       <c r="N422" s="4" t="n"/>
+      <c r="O422" s="4" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="3" t="inlineStr">
@@ -11024,23 +11455,24 @@
       <c r="C423" s="4" t="n"/>
       <c r="D423" s="4" t="n"/>
       <c r="E423" s="4" t="n"/>
-      <c r="F423" s="9" t="inlineStr">
+      <c r="F423" s="4" t="n"/>
+      <c r="G423" s="9" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="G423" s="4" t="n"/>
-      <c r="H423" s="9" t="inlineStr">
+      <c r="H423" s="4" t="n"/>
+      <c r="I423" s="9" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="I423" s="4" t="n"/>
       <c r="J423" s="4" t="n"/>
       <c r="K423" s="4" t="n"/>
       <c r="L423" s="4" t="n"/>
       <c r="M423" s="4" t="n"/>
       <c r="N423" s="4" t="n"/>
+      <c r="O423" s="4" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="3" t="inlineStr">
@@ -11052,23 +11484,24 @@
       <c r="C424" s="4" t="n"/>
       <c r="D424" s="4" t="n"/>
       <c r="E424" s="4" t="n"/>
-      <c r="F424" s="9" t="inlineStr">
+      <c r="F424" s="4" t="n"/>
+      <c r="G424" s="9" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="G424" s="4" t="n"/>
-      <c r="H424" s="9" t="inlineStr">
+      <c r="H424" s="4" t="n"/>
+      <c r="I424" s="9" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="I424" s="4" t="n"/>
       <c r="J424" s="4" t="n"/>
       <c r="K424" s="4" t="n"/>
       <c r="L424" s="4" t="n"/>
       <c r="M424" s="4" t="n"/>
       <c r="N424" s="4" t="n"/>
+      <c r="O424" s="4" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="3" t="inlineStr">
@@ -11080,23 +11513,24 @@
       <c r="C425" s="4" t="n"/>
       <c r="D425" s="4" t="n"/>
       <c r="E425" s="4" t="n"/>
-      <c r="F425" s="9" t="inlineStr">
+      <c r="F425" s="4" t="n"/>
+      <c r="G425" s="9" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="G425" s="4" t="n"/>
-      <c r="H425" s="9" t="inlineStr">
+      <c r="H425" s="4" t="n"/>
+      <c r="I425" s="9" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="I425" s="4" t="n"/>
       <c r="J425" s="4" t="n"/>
       <c r="K425" s="4" t="n"/>
       <c r="L425" s="4" t="n"/>
       <c r="M425" s="4" t="n"/>
       <c r="N425" s="4" t="n"/>
+      <c r="O425" s="4" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="3" t="inlineStr">
@@ -11108,23 +11542,24 @@
       <c r="C426" s="4" t="n"/>
       <c r="D426" s="4" t="n"/>
       <c r="E426" s="4" t="n"/>
-      <c r="F426" s="9" t="inlineStr">
+      <c r="F426" s="4" t="n"/>
+      <c r="G426" s="9" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="G426" s="4" t="n"/>
-      <c r="H426" s="9" t="inlineStr">
+      <c r="H426" s="4" t="n"/>
+      <c r="I426" s="9" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="I426" s="4" t="n"/>
       <c r="J426" s="4" t="n"/>
       <c r="K426" s="4" t="n"/>
       <c r="L426" s="4" t="n"/>
       <c r="M426" s="4" t="n"/>
       <c r="N426" s="4" t="n"/>
+      <c r="O426" s="4" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="6" t="inlineStr">
@@ -11145,6 +11580,7 @@
       <c r="L427" s="7" t="n"/>
       <c r="M427" s="7" t="n"/>
       <c r="N427" s="7" t="n"/>
+      <c r="O427" s="7" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="6" t="inlineStr">
@@ -11165,6 +11601,7 @@
       <c r="L428" s="7" t="n"/>
       <c r="M428" s="7" t="n"/>
       <c r="N428" s="7" t="n"/>
+      <c r="O428" s="7" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="3" t="inlineStr">
@@ -11185,6 +11622,7 @@
       <c r="L429" s="4" t="n"/>
       <c r="M429" s="4" t="n"/>
       <c r="N429" s="4" t="n"/>
+      <c r="O429" s="4" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="3" t="inlineStr">
@@ -11205,6 +11643,7 @@
       <c r="L430" s="4" t="n"/>
       <c r="M430" s="4" t="n"/>
       <c r="N430" s="4" t="n"/>
+      <c r="O430" s="4" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="3" t="inlineStr">
@@ -11225,6 +11664,7 @@
       <c r="L431" s="4" t="n"/>
       <c r="M431" s="4" t="n"/>
       <c r="N431" s="4" t="n"/>
+      <c r="O431" s="4" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="3" t="inlineStr">
@@ -11245,6 +11685,7 @@
       <c r="L432" s="4" t="n"/>
       <c r="M432" s="4" t="n"/>
       <c r="N432" s="4" t="n"/>
+      <c r="O432" s="4" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="3" t="inlineStr">
@@ -11265,6 +11706,7 @@
       <c r="L433" s="4" t="n"/>
       <c r="M433" s="4" t="n"/>
       <c r="N433" s="4" t="n"/>
+      <c r="O433" s="4" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="6" t="inlineStr">
@@ -11285,6 +11727,7 @@
       <c r="L434" s="7" t="n"/>
       <c r="M434" s="7" t="n"/>
       <c r="N434" s="7" t="n"/>
+      <c r="O434" s="7" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="6" t="inlineStr">
@@ -11305,6 +11748,7 @@
       <c r="L435" s="7" t="n"/>
       <c r="M435" s="7" t="n"/>
       <c r="N435" s="7" t="n"/>
+      <c r="O435" s="7" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="3" t="inlineStr">
@@ -11325,6 +11769,7 @@
       <c r="L436" s="4" t="n"/>
       <c r="M436" s="4" t="n"/>
       <c r="N436" s="4" t="n"/>
+      <c r="O436" s="4" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="3" t="inlineStr">
@@ -11345,6 +11790,7 @@
       <c r="L437" s="4" t="n"/>
       <c r="M437" s="4" t="n"/>
       <c r="N437" s="4" t="n"/>
+      <c r="O437" s="4" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="3" t="inlineStr">
@@ -11365,6 +11811,7 @@
       <c r="L438" s="4" t="n"/>
       <c r="M438" s="4" t="n"/>
       <c r="N438" s="4" t="n"/>
+      <c r="O438" s="4" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="3" t="inlineStr">
@@ -11385,6 +11832,7 @@
       <c r="L439" s="4" t="n"/>
       <c r="M439" s="4" t="n"/>
       <c r="N439" s="4" t="n"/>
+      <c r="O439" s="4" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="3" t="inlineStr">
@@ -11405,6 +11853,7 @@
       <c r="L440" s="4" t="n"/>
       <c r="M440" s="4" t="n"/>
       <c r="N440" s="4" t="n"/>
+      <c r="O440" s="4" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="6" t="inlineStr">
@@ -11425,6 +11874,7 @@
       <c r="L441" s="7" t="n"/>
       <c r="M441" s="7" t="n"/>
       <c r="N441" s="7" t="n"/>
+      <c r="O441" s="7" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="6" t="inlineStr">
@@ -11445,6 +11895,7 @@
       <c r="L442" s="7" t="n"/>
       <c r="M442" s="7" t="n"/>
       <c r="N442" s="7" t="n"/>
+      <c r="O442" s="7" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="3" t="inlineStr">
@@ -11459,16 +11910,17 @@
       <c r="F443" s="4" t="n"/>
       <c r="G443" s="4" t="n"/>
       <c r="H443" s="4" t="n"/>
-      <c r="I443" s="11" t="inlineStr">
+      <c r="I443" s="4" t="n"/>
+      <c r="J443" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J443" s="4" t="n"/>
       <c r="K443" s="4" t="n"/>
       <c r="L443" s="4" t="n"/>
       <c r="M443" s="4" t="n"/>
       <c r="N443" s="4" t="n"/>
+      <c r="O443" s="4" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="3" t="inlineStr">
@@ -11483,16 +11935,17 @@
       <c r="F444" s="4" t="n"/>
       <c r="G444" s="4" t="n"/>
       <c r="H444" s="4" t="n"/>
-      <c r="I444" s="11" t="inlineStr">
+      <c r="I444" s="4" t="n"/>
+      <c r="J444" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J444" s="4" t="n"/>
       <c r="K444" s="4" t="n"/>
       <c r="L444" s="4" t="n"/>
       <c r="M444" s="4" t="n"/>
       <c r="N444" s="4" t="n"/>
+      <c r="O444" s="4" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="3" t="inlineStr">
@@ -11506,21 +11959,22 @@
       <c r="E445" s="4" t="n"/>
       <c r="F445" s="4" t="n"/>
       <c r="G445" s="4" t="n"/>
-      <c r="H445" s="9" t="inlineStr">
+      <c r="H445" s="4" t="n"/>
+      <c r="I445" s="9" t="inlineStr">
         <is>
           <t>Delivery - LGBTQ+</t>
         </is>
       </c>
-      <c r="I445" s="11" t="inlineStr">
+      <c r="J445" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J445" s="4" t="n"/>
       <c r="K445" s="4" t="n"/>
       <c r="L445" s="4" t="n"/>
       <c r="M445" s="4" t="n"/>
       <c r="N445" s="4" t="n"/>
+      <c r="O445" s="4" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="3" t="inlineStr">
@@ -11535,16 +11989,17 @@
       <c r="F446" s="4" t="n"/>
       <c r="G446" s="4" t="n"/>
       <c r="H446" s="4" t="n"/>
-      <c r="I446" s="11" t="inlineStr">
+      <c r="I446" s="4" t="n"/>
+      <c r="J446" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J446" s="4" t="n"/>
       <c r="K446" s="4" t="n"/>
       <c r="L446" s="4" t="n"/>
       <c r="M446" s="4" t="n"/>
       <c r="N446" s="4" t="n"/>
+      <c r="O446" s="4" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="3" t="inlineStr">
@@ -11559,16 +12014,17 @@
       <c r="F447" s="4" t="n"/>
       <c r="G447" s="4" t="n"/>
       <c r="H447" s="4" t="n"/>
-      <c r="I447" s="11" t="inlineStr">
+      <c r="I447" s="4" t="n"/>
+      <c r="J447" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J447" s="4" t="n"/>
       <c r="K447" s="4" t="n"/>
       <c r="L447" s="4" t="n"/>
       <c r="M447" s="4" t="n"/>
       <c r="N447" s="4" t="n"/>
+      <c r="O447" s="4" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="6" t="inlineStr">
@@ -11589,6 +12045,7 @@
       <c r="L448" s="7" t="n"/>
       <c r="M448" s="7" t="n"/>
       <c r="N448" s="7" t="n"/>
+      <c r="O448" s="7" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="6" t="inlineStr">
@@ -11609,6 +12066,7 @@
       <c r="L449" s="7" t="n"/>
       <c r="M449" s="7" t="n"/>
       <c r="N449" s="7" t="n"/>
+      <c r="O449" s="7" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="3" t="inlineStr">
@@ -11620,24 +12078,25 @@
       <c r="C450" s="4" t="n"/>
       <c r="D450" s="4" t="n"/>
       <c r="E450" s="4" t="n"/>
-      <c r="F450" s="5" t="inlineStr">
+      <c r="F450" s="4" t="n"/>
+      <c r="G450" s="5" t="inlineStr">
         <is>
           <t>Film - Y Grŵp Chat</t>
         </is>
       </c>
-      <c r="G450" s="4" t="n"/>
       <c r="H450" s="4" t="n"/>
-      <c r="I450" s="5" t="inlineStr">
+      <c r="I450" s="4" t="n"/>
+      <c r="J450" s="5" t="inlineStr">
         <is>
           <t>Film - Y Grŵp Chat
 Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J450" s="4" t="n"/>
       <c r="K450" s="4" t="n"/>
       <c r="L450" s="4" t="n"/>
       <c r="M450" s="4" t="n"/>
       <c r="N450" s="4" t="n"/>
+      <c r="O450" s="4" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="3" t="inlineStr">
@@ -11649,24 +12108,25 @@
       <c r="C451" s="4" t="n"/>
       <c r="D451" s="4" t="n"/>
       <c r="E451" s="4" t="n"/>
-      <c r="F451" s="5" t="inlineStr">
+      <c r="F451" s="4" t="n"/>
+      <c r="G451" s="5" t="inlineStr">
         <is>
           <t>Film - Y Grŵp Chat</t>
         </is>
       </c>
-      <c r="G451" s="4" t="n"/>
       <c r="H451" s="4" t="n"/>
-      <c r="I451" s="5" t="inlineStr">
+      <c r="I451" s="4" t="n"/>
+      <c r="J451" s="5" t="inlineStr">
         <is>
           <t>Film - Y Grŵp Chat
 Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J451" s="4" t="n"/>
       <c r="K451" s="4" t="n"/>
       <c r="L451" s="4" t="n"/>
       <c r="M451" s="4" t="n"/>
       <c r="N451" s="4" t="n"/>
+      <c r="O451" s="4" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="3" t="inlineStr">
@@ -11681,16 +12141,17 @@
       <c r="F452" s="4" t="n"/>
       <c r="G452" s="4" t="n"/>
       <c r="H452" s="4" t="n"/>
-      <c r="I452" s="11" t="inlineStr">
+      <c r="I452" s="4" t="n"/>
+      <c r="J452" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J452" s="4" t="n"/>
       <c r="K452" s="4" t="n"/>
       <c r="L452" s="4" t="n"/>
       <c r="M452" s="4" t="n"/>
       <c r="N452" s="4" t="n"/>
+      <c r="O452" s="4" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="3" t="inlineStr">
@@ -11705,16 +12166,17 @@
       <c r="F453" s="4" t="n"/>
       <c r="G453" s="4" t="n"/>
       <c r="H453" s="4" t="n"/>
-      <c r="I453" s="11" t="inlineStr">
+      <c r="I453" s="4" t="n"/>
+      <c r="J453" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J453" s="4" t="n"/>
       <c r="K453" s="4" t="n"/>
       <c r="L453" s="4" t="n"/>
       <c r="M453" s="4" t="n"/>
       <c r="N453" s="4" t="n"/>
+      <c r="O453" s="4" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="3" t="inlineStr">
@@ -11729,16 +12191,17 @@
       <c r="F454" s="4" t="n"/>
       <c r="G454" s="4" t="n"/>
       <c r="H454" s="4" t="n"/>
-      <c r="I454" s="11" t="inlineStr">
+      <c r="I454" s="4" t="n"/>
+      <c r="J454" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J454" s="4" t="n"/>
       <c r="K454" s="4" t="n"/>
       <c r="L454" s="4" t="n"/>
       <c r="M454" s="4" t="n"/>
       <c r="N454" s="4" t="n"/>
+      <c r="O454" s="4" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="6" t="inlineStr">
@@ -11759,6 +12222,7 @@
       <c r="L455" s="7" t="n"/>
       <c r="M455" s="7" t="n"/>
       <c r="N455" s="7" t="n"/>
+      <c r="O455" s="7" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="6" t="inlineStr">
@@ -11779,6 +12243,7 @@
       <c r="L456" s="7" t="n"/>
       <c r="M456" s="7" t="n"/>
       <c r="N456" s="7" t="n"/>
+      <c r="O456" s="7" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="3" t="inlineStr">
@@ -11793,16 +12258,17 @@
       <c r="F457" s="4" t="n"/>
       <c r="G457" s="4" t="n"/>
       <c r="H457" s="4" t="n"/>
-      <c r="I457" s="11" t="inlineStr">
+      <c r="I457" s="4" t="n"/>
+      <c r="J457" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J457" s="4" t="n"/>
       <c r="K457" s="4" t="n"/>
       <c r="L457" s="4" t="n"/>
       <c r="M457" s="4" t="n"/>
       <c r="N457" s="4" t="n"/>
+      <c r="O457" s="4" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="3" t="inlineStr">
@@ -11817,16 +12283,17 @@
       <c r="F458" s="4" t="n"/>
       <c r="G458" s="4" t="n"/>
       <c r="H458" s="4" t="n"/>
-      <c r="I458" s="11" t="inlineStr">
+      <c r="I458" s="4" t="n"/>
+      <c r="J458" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J458" s="4" t="n"/>
       <c r="K458" s="4" t="n"/>
       <c r="L458" s="4" t="n"/>
       <c r="M458" s="4" t="n"/>
       <c r="N458" s="4" t="n"/>
+      <c r="O458" s="4" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="3" t="inlineStr">
@@ -11842,28 +12309,29 @@
         </is>
       </c>
       <c r="E459" s="4" t="n"/>
-      <c r="F459" s="5" t="inlineStr">
+      <c r="F459" s="4" t="n"/>
+      <c r="G459" s="5" t="inlineStr">
         <is>
           <t>Film - Hwyl Fawr Blodwen</t>
         </is>
       </c>
-      <c r="G459" s="4" t="n"/>
       <c r="H459" s="4" t="n"/>
-      <c r="I459" s="5" t="inlineStr">
+      <c r="I459" s="4" t="n"/>
+      <c r="J459" s="5" t="inlineStr">
         <is>
           <t>Film - Hwyl Fawr Blodwen
 Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J459" s="5" t="inlineStr">
+      <c r="K459" s="5" t="inlineStr">
         <is>
           <t>Film - Hwyl Fawr Blodwen</t>
         </is>
       </c>
-      <c r="K459" s="4" t="n"/>
       <c r="L459" s="4" t="n"/>
       <c r="M459" s="4" t="n"/>
       <c r="N459" s="4" t="n"/>
+      <c r="O459" s="4" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="3" t="inlineStr">
@@ -11879,28 +12347,29 @@
         </is>
       </c>
       <c r="E460" s="4" t="n"/>
-      <c r="F460" s="5" t="inlineStr">
+      <c r="F460" s="4" t="n"/>
+      <c r="G460" s="5" t="inlineStr">
         <is>
           <t>Film - Hwyl Fawr Blodwen</t>
         </is>
       </c>
-      <c r="G460" s="4" t="n"/>
       <c r="H460" s="4" t="n"/>
-      <c r="I460" s="5" t="inlineStr">
+      <c r="I460" s="4" t="n"/>
+      <c r="J460" s="5" t="inlineStr">
         <is>
           <t>Film - Hwyl Fawr Blodwen
 Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J460" s="5" t="inlineStr">
+      <c r="K460" s="5" t="inlineStr">
         <is>
           <t>Film - Hwyl Fawr Blodwen</t>
         </is>
       </c>
-      <c r="K460" s="4" t="n"/>
       <c r="L460" s="4" t="n"/>
       <c r="M460" s="4" t="n"/>
       <c r="N460" s="4" t="n"/>
+      <c r="O460" s="4" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="3" t="inlineStr">
@@ -11916,28 +12385,29 @@
         </is>
       </c>
       <c r="E461" s="4" t="n"/>
-      <c r="F461" s="5" t="inlineStr">
+      <c r="F461" s="4" t="n"/>
+      <c r="G461" s="5" t="inlineStr">
         <is>
           <t>Film - Hwyl Fawr Blodwen</t>
         </is>
       </c>
-      <c r="G461" s="4" t="n"/>
       <c r="H461" s="4" t="n"/>
-      <c r="I461" s="5" t="inlineStr">
+      <c r="I461" s="4" t="n"/>
+      <c r="J461" s="5" t="inlineStr">
         <is>
           <t>Film - Hwyl Fawr Blodwen
 Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J461" s="5" t="inlineStr">
+      <c r="K461" s="5" t="inlineStr">
         <is>
           <t>Film - Hwyl Fawr Blodwen</t>
         </is>
       </c>
-      <c r="K461" s="4" t="n"/>
       <c r="L461" s="4" t="n"/>
       <c r="M461" s="4" t="n"/>
       <c r="N461" s="4" t="n"/>
+      <c r="O461" s="4" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="6" t="inlineStr">
@@ -11958,6 +12428,7 @@
       <c r="L462" s="7" t="n"/>
       <c r="M462" s="7" t="n"/>
       <c r="N462" s="7" t="n"/>
+      <c r="O462" s="7" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="6" t="inlineStr">
@@ -11978,6 +12449,7 @@
       <c r="L463" s="7" t="n"/>
       <c r="M463" s="7" t="n"/>
       <c r="N463" s="7" t="n"/>
+      <c r="O463" s="7" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="3" t="inlineStr">
@@ -11992,16 +12464,17 @@
       <c r="F464" s="4" t="n"/>
       <c r="G464" s="4" t="n"/>
       <c r="H464" s="4" t="n"/>
-      <c r="I464" s="11" t="inlineStr">
+      <c r="I464" s="4" t="n"/>
+      <c r="J464" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J464" s="4" t="n"/>
       <c r="K464" s="4" t="n"/>
       <c r="L464" s="4" t="n"/>
       <c r="M464" s="4" t="n"/>
       <c r="N464" s="4" t="n"/>
+      <c r="O464" s="4" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="3" t="inlineStr">
@@ -12016,16 +12489,17 @@
       <c r="F465" s="4" t="n"/>
       <c r="G465" s="4" t="n"/>
       <c r="H465" s="4" t="n"/>
-      <c r="I465" s="11" t="inlineStr">
+      <c r="I465" s="4" t="n"/>
+      <c r="J465" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J465" s="4" t="n"/>
       <c r="K465" s="4" t="n"/>
       <c r="L465" s="4" t="n"/>
       <c r="M465" s="4" t="n"/>
       <c r="N465" s="4" t="n"/>
+      <c r="O465" s="4" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="3" t="inlineStr">
@@ -12040,16 +12514,17 @@
       <c r="F466" s="4" t="n"/>
       <c r="G466" s="4" t="n"/>
       <c r="H466" s="4" t="n"/>
-      <c r="I466" s="11" t="inlineStr">
+      <c r="I466" s="4" t="n"/>
+      <c r="J466" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J466" s="4" t="n"/>
       <c r="K466" s="4" t="n"/>
       <c r="L466" s="4" t="n"/>
       <c r="M466" s="4" t="n"/>
       <c r="N466" s="4" t="n"/>
+      <c r="O466" s="4" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="3" t="inlineStr">
@@ -12064,16 +12539,17 @@
       <c r="F467" s="4" t="n"/>
       <c r="G467" s="4" t="n"/>
       <c r="H467" s="4" t="n"/>
-      <c r="I467" s="11" t="inlineStr">
+      <c r="I467" s="4" t="n"/>
+      <c r="J467" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J467" s="4" t="n"/>
       <c r="K467" s="4" t="n"/>
       <c r="L467" s="4" t="n"/>
       <c r="M467" s="4" t="n"/>
       <c r="N467" s="4" t="n"/>
+      <c r="O467" s="4" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="3" t="inlineStr">
@@ -12088,16 +12564,17 @@
       <c r="F468" s="4" t="n"/>
       <c r="G468" s="4" t="n"/>
       <c r="H468" s="4" t="n"/>
-      <c r="I468" s="11" t="inlineStr">
+      <c r="I468" s="4" t="n"/>
+      <c r="J468" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J468" s="4" t="n"/>
       <c r="K468" s="4" t="n"/>
       <c r="L468" s="4" t="n"/>
       <c r="M468" s="4" t="n"/>
       <c r="N468" s="4" t="n"/>
+      <c r="O468" s="4" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="6" t="inlineStr">
@@ -12118,6 +12595,7 @@
       <c r="L469" s="7" t="n"/>
       <c r="M469" s="7" t="n"/>
       <c r="N469" s="7" t="n"/>
+      <c r="O469" s="7" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="6" t="inlineStr">
@@ -12138,6 +12616,7 @@
       <c r="L470" s="7" t="n"/>
       <c r="M470" s="7" t="n"/>
       <c r="N470" s="7" t="n"/>
+      <c r="O470" s="7" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="3" t="inlineStr">
@@ -12152,16 +12631,17 @@
       <c r="F471" s="4" t="n"/>
       <c r="G471" s="4" t="n"/>
       <c r="H471" s="4" t="n"/>
-      <c r="I471" s="11" t="inlineStr">
+      <c r="I471" s="4" t="n"/>
+      <c r="J471" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J471" s="4" t="n"/>
       <c r="K471" s="4" t="n"/>
       <c r="L471" s="4" t="n"/>
       <c r="M471" s="4" t="n"/>
       <c r="N471" s="4" t="n"/>
+      <c r="O471" s="4" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="3" t="inlineStr">
@@ -12176,16 +12656,17 @@
       <c r="F472" s="4" t="n"/>
       <c r="G472" s="4" t="n"/>
       <c r="H472" s="4" t="n"/>
-      <c r="I472" s="11" t="inlineStr">
+      <c r="I472" s="4" t="n"/>
+      <c r="J472" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J472" s="4" t="n"/>
       <c r="K472" s="4" t="n"/>
       <c r="L472" s="4" t="n"/>
       <c r="M472" s="4" t="n"/>
       <c r="N472" s="4" t="n"/>
+      <c r="O472" s="4" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="3" t="inlineStr">
@@ -12200,16 +12681,17 @@
       <c r="F473" s="4" t="n"/>
       <c r="G473" s="4" t="n"/>
       <c r="H473" s="4" t="n"/>
-      <c r="I473" s="11" t="inlineStr">
+      <c r="I473" s="4" t="n"/>
+      <c r="J473" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J473" s="4" t="n"/>
       <c r="K473" s="4" t="n"/>
       <c r="L473" s="4" t="n"/>
       <c r="M473" s="4" t="n"/>
       <c r="N473" s="4" t="n"/>
+      <c r="O473" s="4" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="3" t="inlineStr">
@@ -12224,16 +12706,17 @@
       <c r="F474" s="4" t="n"/>
       <c r="G474" s="4" t="n"/>
       <c r="H474" s="4" t="n"/>
-      <c r="I474" s="11" t="inlineStr">
+      <c r="I474" s="4" t="n"/>
+      <c r="J474" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J474" s="4" t="n"/>
       <c r="K474" s="4" t="n"/>
       <c r="L474" s="4" t="n"/>
       <c r="M474" s="4" t="n"/>
       <c r="N474" s="4" t="n"/>
+      <c r="O474" s="4" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="3" t="inlineStr">
@@ -12248,16 +12731,17 @@
       <c r="F475" s="4" t="n"/>
       <c r="G475" s="4" t="n"/>
       <c r="H475" s="4" t="n"/>
-      <c r="I475" s="11" t="inlineStr">
+      <c r="I475" s="4" t="n"/>
+      <c r="J475" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J475" s="4" t="n"/>
       <c r="K475" s="4" t="n"/>
       <c r="L475" s="4" t="n"/>
       <c r="M475" s="4" t="n"/>
       <c r="N475" s="4" t="n"/>
+      <c r="O475" s="4" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="6" t="inlineStr">
@@ -12278,6 +12762,7 @@
       <c r="L476" s="7" t="n"/>
       <c r="M476" s="7" t="n"/>
       <c r="N476" s="7" t="n"/>
+      <c r="O476" s="7" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="6" t="inlineStr">
@@ -12298,6 +12783,7 @@
       <c r="L477" s="7" t="n"/>
       <c r="M477" s="7" t="n"/>
       <c r="N477" s="7" t="n"/>
+      <c r="O477" s="7" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="3" t="inlineStr">
@@ -12309,23 +12795,24 @@
       <c r="C478" s="4" t="n"/>
       <c r="D478" s="4" t="n"/>
       <c r="E478" s="4" t="n"/>
-      <c r="F478" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="G478" s="4" t="n"/>
+      <c r="F478" s="4" t="n"/>
+      <c r="G478" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="H478" s="4" t="n"/>
-      <c r="I478" s="11" t="inlineStr">
+      <c r="I478" s="4" t="n"/>
+      <c r="J478" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J478" s="4" t="n"/>
       <c r="K478" s="4" t="n"/>
       <c r="L478" s="4" t="n"/>
       <c r="M478" s="4" t="n"/>
       <c r="N478" s="4" t="n"/>
+      <c r="O478" s="4" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="3" t="inlineStr">
@@ -12337,23 +12824,24 @@
       <c r="C479" s="4" t="n"/>
       <c r="D479" s="4" t="n"/>
       <c r="E479" s="4" t="n"/>
-      <c r="F479" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="G479" s="4" t="n"/>
+      <c r="F479" s="4" t="n"/>
+      <c r="G479" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="H479" s="4" t="n"/>
-      <c r="I479" s="11" t="inlineStr">
+      <c r="I479" s="4" t="n"/>
+      <c r="J479" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J479" s="4" t="n"/>
       <c r="K479" s="4" t="n"/>
       <c r="L479" s="4" t="n"/>
       <c r="M479" s="4" t="n"/>
       <c r="N479" s="4" t="n"/>
+      <c r="O479" s="4" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="3" t="inlineStr">
@@ -12365,23 +12853,24 @@
       <c r="C480" s="4" t="n"/>
       <c r="D480" s="4" t="n"/>
       <c r="E480" s="4" t="n"/>
-      <c r="F480" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="G480" s="4" t="n"/>
+      <c r="F480" s="4" t="n"/>
+      <c r="G480" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="H480" s="4" t="n"/>
-      <c r="I480" s="11" t="inlineStr">
+      <c r="I480" s="4" t="n"/>
+      <c r="J480" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J480" s="4" t="n"/>
       <c r="K480" s="4" t="n"/>
       <c r="L480" s="4" t="n"/>
       <c r="M480" s="4" t="n"/>
       <c r="N480" s="4" t="n"/>
+      <c r="O480" s="4" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="3" t="inlineStr">
@@ -12393,27 +12882,28 @@
       <c r="C481" s="4" t="n"/>
       <c r="D481" s="4" t="n"/>
       <c r="E481" s="4" t="n"/>
-      <c r="F481" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="G481" s="4" t="n"/>
+      <c r="F481" s="4" t="n"/>
+      <c r="G481" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="H481" s="4" t="n"/>
-      <c r="I481" s="11" t="inlineStr">
+      <c r="I481" s="4" t="n"/>
+      <c r="J481" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J481" s="4" t="n"/>
       <c r="K481" s="4" t="n"/>
       <c r="L481" s="4" t="n"/>
-      <c r="M481" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N481" s="4" t="n"/>
+      <c r="M481" s="4" t="n"/>
+      <c r="N481" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O481" s="4" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="3" t="inlineStr">
@@ -12425,27 +12915,28 @@
       <c r="C482" s="4" t="n"/>
       <c r="D482" s="4" t="n"/>
       <c r="E482" s="4" t="n"/>
-      <c r="F482" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="G482" s="4" t="n"/>
+      <c r="F482" s="4" t="n"/>
+      <c r="G482" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="H482" s="4" t="n"/>
-      <c r="I482" s="11" t="inlineStr">
+      <c r="I482" s="4" t="n"/>
+      <c r="J482" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J482" s="4" t="n"/>
       <c r="K482" s="4" t="n"/>
       <c r="L482" s="4" t="n"/>
-      <c r="M482" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N482" s="4" t="n"/>
+      <c r="M482" s="4" t="n"/>
+      <c r="N482" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O482" s="4" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="6" t="inlineStr">
@@ -12466,6 +12957,7 @@
       <c r="L483" s="7" t="n"/>
       <c r="M483" s="7" t="n"/>
       <c r="N483" s="7" t="n"/>
+      <c r="O483" s="7" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="6" t="inlineStr">
@@ -12486,6 +12978,7 @@
       <c r="L484" s="7" t="n"/>
       <c r="M484" s="7" t="n"/>
       <c r="N484" s="7" t="n"/>
+      <c r="O484" s="7" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="3" t="inlineStr">
@@ -12500,16 +12993,17 @@
       <c r="F485" s="4" t="n"/>
       <c r="G485" s="4" t="n"/>
       <c r="H485" s="4" t="n"/>
-      <c r="I485" s="11" t="inlineStr">
+      <c r="I485" s="4" t="n"/>
+      <c r="J485" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J485" s="4" t="n"/>
       <c r="K485" s="4" t="n"/>
       <c r="L485" s="4" t="n"/>
       <c r="M485" s="4" t="n"/>
       <c r="N485" s="4" t="n"/>
+      <c r="O485" s="4" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="3" t="inlineStr">
@@ -12524,16 +13018,17 @@
       <c r="F486" s="4" t="n"/>
       <c r="G486" s="4" t="n"/>
       <c r="H486" s="4" t="n"/>
-      <c r="I486" s="11" t="inlineStr">
+      <c r="I486" s="4" t="n"/>
+      <c r="J486" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J486" s="4" t="n"/>
       <c r="K486" s="4" t="n"/>
       <c r="L486" s="4" t="n"/>
       <c r="M486" s="4" t="n"/>
       <c r="N486" s="4" t="n"/>
+      <c r="O486" s="4" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="3" t="inlineStr">
@@ -12548,16 +13043,17 @@
       <c r="F487" s="4" t="n"/>
       <c r="G487" s="4" t="n"/>
       <c r="H487" s="4" t="n"/>
-      <c r="I487" s="11" t="inlineStr">
+      <c r="I487" s="4" t="n"/>
+      <c r="J487" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J487" s="4" t="n"/>
       <c r="K487" s="4" t="n"/>
       <c r="L487" s="4" t="n"/>
       <c r="M487" s="4" t="n"/>
       <c r="N487" s="4" t="n"/>
+      <c r="O487" s="4" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="3" t="inlineStr">
@@ -12572,16 +13068,17 @@
       <c r="F488" s="4" t="n"/>
       <c r="G488" s="4" t="n"/>
       <c r="H488" s="4" t="n"/>
-      <c r="I488" s="11" t="inlineStr">
+      <c r="I488" s="4" t="n"/>
+      <c r="J488" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J488" s="4" t="n"/>
       <c r="K488" s="4" t="n"/>
       <c r="L488" s="4" t="n"/>
       <c r="M488" s="4" t="n"/>
       <c r="N488" s="4" t="n"/>
+      <c r="O488" s="4" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="3" t="inlineStr">
@@ -12596,16 +13093,17 @@
       <c r="F489" s="4" t="n"/>
       <c r="G489" s="4" t="n"/>
       <c r="H489" s="4" t="n"/>
-      <c r="I489" s="11" t="inlineStr">
+      <c r="I489" s="4" t="n"/>
+      <c r="J489" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J489" s="4" t="n"/>
       <c r="K489" s="4" t="n"/>
       <c r="L489" s="4" t="n"/>
       <c r="M489" s="4" t="n"/>
       <c r="N489" s="4" t="n"/>
+      <c r="O489" s="4" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="6" t="inlineStr">
@@ -12626,6 +13124,7 @@
       <c r="L490" s="7" t="n"/>
       <c r="M490" s="7" t="n"/>
       <c r="N490" s="7" t="n"/>
+      <c r="O490" s="7" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="6" t="inlineStr">
@@ -12646,6 +13145,7 @@
       <c r="L491" s="7" t="n"/>
       <c r="M491" s="7" t="n"/>
       <c r="N491" s="7" t="n"/>
+      <c r="O491" s="7" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="3" t="inlineStr">
@@ -12660,16 +13160,17 @@
       <c r="F492" s="4" t="n"/>
       <c r="G492" s="4" t="n"/>
       <c r="H492" s="4" t="n"/>
-      <c r="I492" s="11" t="inlineStr">
+      <c r="I492" s="4" t="n"/>
+      <c r="J492" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J492" s="4" t="n"/>
       <c r="K492" s="4" t="n"/>
       <c r="L492" s="4" t="n"/>
       <c r="M492" s="4" t="n"/>
       <c r="N492" s="4" t="n"/>
+      <c r="O492" s="4" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="3" t="inlineStr">
@@ -12684,16 +13185,17 @@
       <c r="F493" s="4" t="n"/>
       <c r="G493" s="4" t="n"/>
       <c r="H493" s="4" t="n"/>
-      <c r="I493" s="11" t="inlineStr">
+      <c r="I493" s="4" t="n"/>
+      <c r="J493" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J493" s="4" t="n"/>
       <c r="K493" s="4" t="n"/>
       <c r="L493" s="4" t="n"/>
       <c r="M493" s="4" t="n"/>
       <c r="N493" s="4" t="n"/>
+      <c r="O493" s="4" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="3" t="inlineStr">
@@ -12708,16 +13210,17 @@
       <c r="F494" s="4" t="n"/>
       <c r="G494" s="4" t="n"/>
       <c r="H494" s="4" t="n"/>
-      <c r="I494" s="11" t="inlineStr">
+      <c r="I494" s="4" t="n"/>
+      <c r="J494" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J494" s="4" t="n"/>
       <c r="K494" s="4" t="n"/>
       <c r="L494" s="4" t="n"/>
       <c r="M494" s="4" t="n"/>
       <c r="N494" s="4" t="n"/>
+      <c r="O494" s="4" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="3" t="inlineStr">
@@ -12732,16 +13235,17 @@
       <c r="F495" s="4" t="n"/>
       <c r="G495" s="4" t="n"/>
       <c r="H495" s="4" t="n"/>
-      <c r="I495" s="11" t="inlineStr">
+      <c r="I495" s="4" t="n"/>
+      <c r="J495" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J495" s="4" t="n"/>
       <c r="K495" s="4" t="n"/>
       <c r="L495" s="4" t="n"/>
       <c r="M495" s="4" t="n"/>
       <c r="N495" s="4" t="n"/>
+      <c r="O495" s="4" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="3" t="inlineStr">
@@ -12756,16 +13260,17 @@
       <c r="F496" s="4" t="n"/>
       <c r="G496" s="4" t="n"/>
       <c r="H496" s="4" t="n"/>
-      <c r="I496" s="11" t="inlineStr">
+      <c r="I496" s="4" t="n"/>
+      <c r="J496" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J496" s="4" t="n"/>
       <c r="K496" s="4" t="n"/>
       <c r="L496" s="4" t="n"/>
       <c r="M496" s="4" t="n"/>
       <c r="N496" s="4" t="n"/>
+      <c r="O496" s="4" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="6" t="inlineStr">
@@ -12786,6 +13291,7 @@
       <c r="L497" s="7" t="n"/>
       <c r="M497" s="7" t="n"/>
       <c r="N497" s="7" t="n"/>
+      <c r="O497" s="7" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="6" t="inlineStr">
@@ -12806,6 +13312,7 @@
       <c r="L498" s="7" t="n"/>
       <c r="M498" s="7" t="n"/>
       <c r="N498" s="7" t="n"/>
+      <c r="O498" s="7" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="3" t="inlineStr">
@@ -12820,16 +13327,17 @@
       <c r="F499" s="4" t="n"/>
       <c r="G499" s="4" t="n"/>
       <c r="H499" s="4" t="n"/>
-      <c r="I499" s="11" t="inlineStr">
+      <c r="I499" s="4" t="n"/>
+      <c r="J499" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J499" s="4" t="n"/>
       <c r="K499" s="4" t="n"/>
       <c r="L499" s="4" t="n"/>
       <c r="M499" s="4" t="n"/>
       <c r="N499" s="4" t="n"/>
+      <c r="O499" s="4" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="3" t="inlineStr">
@@ -12844,16 +13352,17 @@
       <c r="F500" s="4" t="n"/>
       <c r="G500" s="4" t="n"/>
       <c r="H500" s="4" t="n"/>
-      <c r="I500" s="11" t="inlineStr">
+      <c r="I500" s="4" t="n"/>
+      <c r="J500" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J500" s="4" t="n"/>
       <c r="K500" s="4" t="n"/>
       <c r="L500" s="4" t="n"/>
       <c r="M500" s="4" t="n"/>
       <c r="N500" s="4" t="n"/>
+      <c r="O500" s="4" t="n"/>
     </row>
     <row r="501">
       <c r="A501" s="3" t="inlineStr">
@@ -12868,16 +13377,17 @@
       <c r="F501" s="4" t="n"/>
       <c r="G501" s="4" t="n"/>
       <c r="H501" s="4" t="n"/>
-      <c r="I501" s="11" t="inlineStr">
+      <c r="I501" s="4" t="n"/>
+      <c r="J501" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J501" s="4" t="n"/>
       <c r="K501" s="4" t="n"/>
       <c r="L501" s="4" t="n"/>
       <c r="M501" s="4" t="n"/>
       <c r="N501" s="4" t="n"/>
+      <c r="O501" s="4" t="n"/>
     </row>
     <row r="502">
       <c r="A502" s="3" t="inlineStr">
@@ -12892,16 +13402,17 @@
       <c r="F502" s="4" t="n"/>
       <c r="G502" s="4" t="n"/>
       <c r="H502" s="4" t="n"/>
-      <c r="I502" s="11" t="inlineStr">
+      <c r="I502" s="4" t="n"/>
+      <c r="J502" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J502" s="4" t="n"/>
       <c r="K502" s="4" t="n"/>
       <c r="L502" s="4" t="n"/>
       <c r="M502" s="4" t="n"/>
       <c r="N502" s="4" t="n"/>
+      <c r="O502" s="4" t="n"/>
     </row>
     <row r="503">
       <c r="A503" s="3" t="inlineStr">
@@ -12916,16 +13427,17 @@
       <c r="F503" s="4" t="n"/>
       <c r="G503" s="4" t="n"/>
       <c r="H503" s="4" t="n"/>
-      <c r="I503" s="11" t="inlineStr">
+      <c r="I503" s="4" t="n"/>
+      <c r="J503" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J503" s="4" t="n"/>
       <c r="K503" s="4" t="n"/>
       <c r="L503" s="4" t="n"/>
       <c r="M503" s="4" t="n"/>
       <c r="N503" s="4" t="n"/>
+      <c r="O503" s="4" t="n"/>
     </row>
     <row r="504">
       <c r="A504" s="6" t="inlineStr">
@@ -12946,6 +13458,7 @@
       <c r="L504" s="7" t="n"/>
       <c r="M504" s="7" t="n"/>
       <c r="N504" s="7" t="n"/>
+      <c r="O504" s="7" t="n"/>
     </row>
     <row r="505">
       <c r="A505" s="6" t="inlineStr">
@@ -12966,6 +13479,7 @@
       <c r="L505" s="7" t="n"/>
       <c r="M505" s="7" t="n"/>
       <c r="N505" s="7" t="n"/>
+      <c r="O505" s="7" t="n"/>
     </row>
     <row r="506">
       <c r="A506" s="3" t="inlineStr">
@@ -12980,16 +13494,17 @@
       <c r="F506" s="4" t="n"/>
       <c r="G506" s="4" t="n"/>
       <c r="H506" s="4" t="n"/>
-      <c r="I506" s="11" t="inlineStr">
+      <c r="I506" s="4" t="n"/>
+      <c r="J506" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J506" s="4" t="n"/>
       <c r="K506" s="4" t="n"/>
       <c r="L506" s="4" t="n"/>
       <c r="M506" s="4" t="n"/>
       <c r="N506" s="4" t="n"/>
+      <c r="O506" s="4" t="n"/>
     </row>
     <row r="507">
       <c r="A507" s="3" t="inlineStr">
@@ -13004,16 +13519,17 @@
       <c r="F507" s="4" t="n"/>
       <c r="G507" s="4" t="n"/>
       <c r="H507" s="4" t="n"/>
-      <c r="I507" s="11" t="inlineStr">
+      <c r="I507" s="4" t="n"/>
+      <c r="J507" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J507" s="4" t="n"/>
       <c r="K507" s="4" t="n"/>
       <c r="L507" s="4" t="n"/>
       <c r="M507" s="4" t="n"/>
       <c r="N507" s="4" t="n"/>
+      <c r="O507" s="4" t="n"/>
     </row>
     <row r="508">
       <c r="A508" s="3" t="inlineStr">
@@ -13028,16 +13544,17 @@
       <c r="F508" s="4" t="n"/>
       <c r="G508" s="4" t="n"/>
       <c r="H508" s="4" t="n"/>
-      <c r="I508" s="11" t="inlineStr">
+      <c r="I508" s="4" t="n"/>
+      <c r="J508" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J508" s="4" t="n"/>
       <c r="K508" s="4" t="n"/>
       <c r="L508" s="4" t="n"/>
       <c r="M508" s="4" t="n"/>
       <c r="N508" s="4" t="n"/>
+      <c r="O508" s="4" t="n"/>
     </row>
     <row r="509">
       <c r="A509" s="3" t="inlineStr">
@@ -13052,16 +13569,17 @@
       <c r="F509" s="4" t="n"/>
       <c r="G509" s="4" t="n"/>
       <c r="H509" s="4" t="n"/>
-      <c r="I509" s="11" t="inlineStr">
+      <c r="I509" s="4" t="n"/>
+      <c r="J509" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J509" s="4" t="n"/>
       <c r="K509" s="4" t="n"/>
       <c r="L509" s="4" t="n"/>
       <c r="M509" s="4" t="n"/>
       <c r="N509" s="4" t="n"/>
+      <c r="O509" s="4" t="n"/>
     </row>
     <row r="510">
       <c r="A510" s="3" t="inlineStr">
@@ -13076,16 +13594,17 @@
       <c r="F510" s="4" t="n"/>
       <c r="G510" s="4" t="n"/>
       <c r="H510" s="4" t="n"/>
-      <c r="I510" s="11" t="inlineStr">
+      <c r="I510" s="4" t="n"/>
+      <c r="J510" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J510" s="4" t="n"/>
       <c r="K510" s="4" t="n"/>
       <c r="L510" s="4" t="n"/>
       <c r="M510" s="4" t="n"/>
       <c r="N510" s="4" t="n"/>
+      <c r="O510" s="4" t="n"/>
     </row>
     <row r="511">
       <c r="A511" s="6" t="inlineStr">
@@ -13106,6 +13625,7 @@
       <c r="L511" s="7" t="n"/>
       <c r="M511" s="7" t="n"/>
       <c r="N511" s="7" t="n"/>
+      <c r="O511" s="7" t="n"/>
     </row>
     <row r="512">
       <c r="A512" s="6" t="inlineStr">
@@ -13126,6 +13646,7 @@
       <c r="L512" s="7" t="n"/>
       <c r="M512" s="7" t="n"/>
       <c r="N512" s="7" t="n"/>
+      <c r="O512" s="7" t="n"/>
     </row>
     <row r="513">
       <c r="A513" s="3" t="inlineStr">
@@ -13140,16 +13661,17 @@
       <c r="F513" s="4" t="n"/>
       <c r="G513" s="4" t="n"/>
       <c r="H513" s="4" t="n"/>
-      <c r="I513" s="8" t="inlineStr">
+      <c r="I513" s="4" t="n"/>
+      <c r="J513" s="8" t="inlineStr">
         <is>
           <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J513" s="4" t="n"/>
       <c r="K513" s="4" t="n"/>
       <c r="L513" s="4" t="n"/>
       <c r="M513" s="4" t="n"/>
       <c r="N513" s="4" t="n"/>
+      <c r="O513" s="4" t="n"/>
     </row>
     <row r="514">
       <c r="A514" s="3" t="inlineStr">
@@ -13164,16 +13686,17 @@
       <c r="F514" s="4" t="n"/>
       <c r="G514" s="4" t="n"/>
       <c r="H514" s="4" t="n"/>
-      <c r="I514" s="8" t="inlineStr">
+      <c r="I514" s="4" t="n"/>
+      <c r="J514" s="8" t="inlineStr">
         <is>
           <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J514" s="4" t="n"/>
       <c r="K514" s="4" t="n"/>
       <c r="L514" s="4" t="n"/>
       <c r="M514" s="4" t="n"/>
       <c r="N514" s="4" t="n"/>
+      <c r="O514" s="4" t="n"/>
     </row>
     <row r="515">
       <c r="A515" s="3" t="inlineStr">
@@ -13188,16 +13711,17 @@
       <c r="F515" s="4" t="n"/>
       <c r="G515" s="4" t="n"/>
       <c r="H515" s="4" t="n"/>
-      <c r="I515" s="8" t="inlineStr">
+      <c r="I515" s="4" t="n"/>
+      <c r="J515" s="8" t="inlineStr">
         <is>
           <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J515" s="4" t="n"/>
       <c r="K515" s="4" t="n"/>
       <c r="L515" s="4" t="n"/>
       <c r="M515" s="4" t="n"/>
       <c r="N515" s="4" t="n"/>
+      <c r="O515" s="4" t="n"/>
     </row>
     <row r="516">
       <c r="A516" s="3" t="inlineStr">
@@ -13212,16 +13736,17 @@
       <c r="F516" s="4" t="n"/>
       <c r="G516" s="4" t="n"/>
       <c r="H516" s="4" t="n"/>
-      <c r="I516" s="8" t="inlineStr">
+      <c r="I516" s="4" t="n"/>
+      <c r="J516" s="8" t="inlineStr">
         <is>
           <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J516" s="4" t="n"/>
       <c r="K516" s="4" t="n"/>
       <c r="L516" s="4" t="n"/>
       <c r="M516" s="4" t="n"/>
       <c r="N516" s="4" t="n"/>
+      <c r="O516" s="4" t="n"/>
     </row>
     <row r="517">
       <c r="A517" s="3" t="inlineStr">
@@ -13236,16 +13761,17 @@
       <c r="F517" s="4" t="n"/>
       <c r="G517" s="4" t="n"/>
       <c r="H517" s="4" t="n"/>
-      <c r="I517" s="8" t="inlineStr">
+      <c r="I517" s="4" t="n"/>
+      <c r="J517" s="8" t="inlineStr">
         <is>
           <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J517" s="4" t="n"/>
       <c r="K517" s="4" t="n"/>
       <c r="L517" s="4" t="n"/>
       <c r="M517" s="4" t="n"/>
       <c r="N517" s="4" t="n"/>
+      <c r="O517" s="4" t="n"/>
     </row>
     <row r="518">
       <c r="A518" s="6" t="inlineStr">
@@ -13266,6 +13792,7 @@
       <c r="L518" s="7" t="n"/>
       <c r="M518" s="7" t="n"/>
       <c r="N518" s="7" t="n"/>
+      <c r="O518" s="7" t="n"/>
     </row>
     <row r="519">
       <c r="A519" s="6" t="inlineStr">
@@ -13286,6 +13813,7 @@
       <c r="L519" s="7" t="n"/>
       <c r="M519" s="7" t="n"/>
       <c r="N519" s="7" t="n"/>
+      <c r="O519" s="7" t="n"/>
     </row>
     <row r="520">
       <c r="A520" s="3" t="inlineStr">
@@ -13297,23 +13825,24 @@
       <c r="C520" s="4" t="n"/>
       <c r="D520" s="4" t="n"/>
       <c r="E520" s="4" t="n"/>
-      <c r="F520" s="5" t="inlineStr">
+      <c r="F520" s="4" t="n"/>
+      <c r="G520" s="5" t="inlineStr">
         <is>
           <t>Film - Cogydd</t>
         </is>
       </c>
-      <c r="G520" s="4" t="n"/>
       <c r="H520" s="4" t="n"/>
-      <c r="I520" s="5" t="inlineStr">
+      <c r="I520" s="4" t="n"/>
+      <c r="J520" s="5" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J520" s="4" t="n"/>
       <c r="K520" s="4" t="n"/>
       <c r="L520" s="4" t="n"/>
       <c r="M520" s="4" t="n"/>
       <c r="N520" s="4" t="n"/>
+      <c r="O520" s="4" t="n"/>
     </row>
     <row r="521">
       <c r="A521" s="3" t="inlineStr">
@@ -13325,23 +13854,24 @@
       <c r="C521" s="4" t="n"/>
       <c r="D521" s="4" t="n"/>
       <c r="E521" s="4" t="n"/>
-      <c r="F521" s="5" t="inlineStr">
+      <c r="F521" s="4" t="n"/>
+      <c r="G521" s="5" t="inlineStr">
         <is>
           <t>Film - Cogydd</t>
         </is>
       </c>
-      <c r="G521" s="4" t="n"/>
       <c r="H521" s="4" t="n"/>
-      <c r="I521" s="5" t="inlineStr">
+      <c r="I521" s="4" t="n"/>
+      <c r="J521" s="5" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J521" s="4" t="n"/>
       <c r="K521" s="4" t="n"/>
       <c r="L521" s="4" t="n"/>
       <c r="M521" s="4" t="n"/>
       <c r="N521" s="4" t="n"/>
+      <c r="O521" s="4" t="n"/>
     </row>
     <row r="522">
       <c r="A522" s="3" t="inlineStr">
@@ -13353,23 +13883,24 @@
       <c r="C522" s="4" t="n"/>
       <c r="D522" s="4" t="n"/>
       <c r="E522" s="4" t="n"/>
-      <c r="F522" s="5" t="inlineStr">
+      <c r="F522" s="4" t="n"/>
+      <c r="G522" s="5" t="inlineStr">
         <is>
           <t>Film - Cogydd</t>
         </is>
       </c>
-      <c r="G522" s="4" t="n"/>
       <c r="H522" s="4" t="n"/>
-      <c r="I522" s="5" t="inlineStr">
+      <c r="I522" s="4" t="n"/>
+      <c r="J522" s="5" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J522" s="4" t="n"/>
       <c r="K522" s="4" t="n"/>
       <c r="L522" s="4" t="n"/>
       <c r="M522" s="4" t="n"/>
       <c r="N522" s="4" t="n"/>
+      <c r="O522" s="4" t="n"/>
     </row>
     <row r="523">
       <c r="A523" s="3" t="inlineStr">
@@ -13381,23 +13912,24 @@
       <c r="C523" s="4" t="n"/>
       <c r="D523" s="4" t="n"/>
       <c r="E523" s="4" t="n"/>
-      <c r="F523" s="5" t="inlineStr">
+      <c r="F523" s="4" t="n"/>
+      <c r="G523" s="5" t="inlineStr">
         <is>
           <t>Film - Cogydd</t>
         </is>
       </c>
-      <c r="G523" s="4" t="n"/>
       <c r="H523" s="4" t="n"/>
-      <c r="I523" s="5" t="inlineStr">
+      <c r="I523" s="4" t="n"/>
+      <c r="J523" s="5" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J523" s="4" t="n"/>
       <c r="K523" s="4" t="n"/>
       <c r="L523" s="4" t="n"/>
       <c r="M523" s="4" t="n"/>
       <c r="N523" s="4" t="n"/>
+      <c r="O523" s="4" t="n"/>
     </row>
     <row r="524">
       <c r="A524" s="3" t="inlineStr">
@@ -13409,23 +13941,24 @@
       <c r="C524" s="4" t="n"/>
       <c r="D524" s="4" t="n"/>
       <c r="E524" s="4" t="n"/>
-      <c r="F524" s="5" t="inlineStr">
+      <c r="F524" s="4" t="n"/>
+      <c r="G524" s="5" t="inlineStr">
         <is>
           <t>Film - Cogydd</t>
         </is>
       </c>
-      <c r="G524" s="4" t="n"/>
       <c r="H524" s="4" t="n"/>
-      <c r="I524" s="5" t="inlineStr">
+      <c r="I524" s="4" t="n"/>
+      <c r="J524" s="5" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J524" s="4" t="n"/>
       <c r="K524" s="4" t="n"/>
       <c r="L524" s="4" t="n"/>
       <c r="M524" s="4" t="n"/>
       <c r="N524" s="4" t="n"/>
+      <c r="O524" s="4" t="n"/>
     </row>
     <row r="525">
       <c r="A525" s="6" t="inlineStr">
@@ -13446,6 +13979,7 @@
       <c r="L525" s="7" t="n"/>
       <c r="M525" s="7" t="n"/>
       <c r="N525" s="7" t="n"/>
+      <c r="O525" s="7" t="n"/>
     </row>
     <row r="526">
       <c r="A526" s="6" t="inlineStr">
@@ -13466,6 +14000,7 @@
       <c r="L526" s="7" t="n"/>
       <c r="M526" s="7" t="n"/>
       <c r="N526" s="7" t="n"/>
+      <c r="O526" s="7" t="n"/>
     </row>
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
@@ -13480,16 +14015,17 @@
       <c r="F527" s="4" t="n"/>
       <c r="G527" s="4" t="n"/>
       <c r="H527" s="4" t="n"/>
-      <c r="I527" s="11" t="inlineStr">
+      <c r="I527" s="4" t="n"/>
+      <c r="J527" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J527" s="4" t="n"/>
       <c r="K527" s="4" t="n"/>
       <c r="L527" s="4" t="n"/>
       <c r="M527" s="4" t="n"/>
       <c r="N527" s="4" t="n"/>
+      <c r="O527" s="4" t="n"/>
     </row>
     <row r="528">
       <c r="A528" s="3" t="inlineStr">
@@ -13504,16 +14040,17 @@
       <c r="F528" s="4" t="n"/>
       <c r="G528" s="4" t="n"/>
       <c r="H528" s="4" t="n"/>
-      <c r="I528" s="11" t="inlineStr">
+      <c r="I528" s="4" t="n"/>
+      <c r="J528" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J528" s="4" t="n"/>
       <c r="K528" s="4" t="n"/>
       <c r="L528" s="4" t="n"/>
       <c r="M528" s="4" t="n"/>
       <c r="N528" s="4" t="n"/>
+      <c r="O528" s="4" t="n"/>
     </row>
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
@@ -13527,21 +14064,22 @@
       <c r="E529" s="4" t="n"/>
       <c r="F529" s="4" t="n"/>
       <c r="G529" s="4" t="n"/>
-      <c r="H529" s="9" t="inlineStr">
+      <c r="H529" s="4" t="n"/>
+      <c r="I529" s="9" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I529" s="11" t="inlineStr">
+      <c r="J529" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J529" s="4" t="n"/>
       <c r="K529" s="4" t="n"/>
       <c r="L529" s="4" t="n"/>
       <c r="M529" s="4" t="n"/>
       <c r="N529" s="4" t="n"/>
+      <c r="O529" s="4" t="n"/>
     </row>
     <row r="530">
       <c r="A530" s="3" t="inlineStr">
@@ -13555,21 +14093,22 @@
       <c r="E530" s="4" t="n"/>
       <c r="F530" s="4" t="n"/>
       <c r="G530" s="4" t="n"/>
-      <c r="H530" s="9" t="inlineStr">
+      <c r="H530" s="4" t="n"/>
+      <c r="I530" s="9" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I530" s="11" t="inlineStr">
+      <c r="J530" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J530" s="4" t="n"/>
       <c r="K530" s="4" t="n"/>
       <c r="L530" s="4" t="n"/>
       <c r="M530" s="4" t="n"/>
       <c r="N530" s="4" t="n"/>
+      <c r="O530" s="4" t="n"/>
     </row>
     <row r="531">
       <c r="A531" s="3" t="inlineStr">
@@ -13583,21 +14122,22 @@
       <c r="E531" s="4" t="n"/>
       <c r="F531" s="4" t="n"/>
       <c r="G531" s="4" t="n"/>
-      <c r="H531" s="9" t="inlineStr">
+      <c r="H531" s="4" t="n"/>
+      <c r="I531" s="9" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I531" s="11" t="inlineStr">
+      <c r="J531" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J531" s="4" t="n"/>
       <c r="K531" s="4" t="n"/>
       <c r="L531" s="4" t="n"/>
       <c r="M531" s="4" t="n"/>
       <c r="N531" s="4" t="n"/>
+      <c r="O531" s="4" t="n"/>
     </row>
     <row r="532">
       <c r="A532" s="6" t="inlineStr">
@@ -13618,6 +14158,7 @@
       <c r="L532" s="7" t="n"/>
       <c r="M532" s="7" t="n"/>
       <c r="N532" s="7" t="n"/>
+      <c r="O532" s="7" t="n"/>
     </row>
     <row r="533">
       <c r="A533" s="6" t="inlineStr">
@@ -13638,6 +14179,7 @@
       <c r="L533" s="7" t="n"/>
       <c r="M533" s="7" t="n"/>
       <c r="N533" s="7" t="n"/>
+      <c r="O533" s="7" t="n"/>
     </row>
     <row r="534">
       <c r="A534" s="3" t="inlineStr">
@@ -13651,17 +14193,18 @@
       <c r="E534" s="4" t="n"/>
       <c r="F534" s="4" t="n"/>
       <c r="G534" s="4" t="n"/>
-      <c r="H534" s="9" t="inlineStr">
+      <c r="H534" s="4" t="n"/>
+      <c r="I534" s="9" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I534" s="4" t="n"/>
       <c r="J534" s="4" t="n"/>
       <c r="K534" s="4" t="n"/>
       <c r="L534" s="4" t="n"/>
       <c r="M534" s="4" t="n"/>
       <c r="N534" s="4" t="n"/>
+      <c r="O534" s="4" t="n"/>
     </row>
     <row r="535">
       <c r="A535" s="3" t="inlineStr">
@@ -13675,17 +14218,18 @@
       <c r="E535" s="4" t="n"/>
       <c r="F535" s="4" t="n"/>
       <c r="G535" s="4" t="n"/>
-      <c r="H535" s="9" t="inlineStr">
+      <c r="H535" s="4" t="n"/>
+      <c r="I535" s="9" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I535" s="4" t="n"/>
       <c r="J535" s="4" t="n"/>
       <c r="K535" s="4" t="n"/>
       <c r="L535" s="4" t="n"/>
       <c r="M535" s="4" t="n"/>
       <c r="N535" s="4" t="n"/>
+      <c r="O535" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9518,7 +9518,11 @@
       <c r="B352" s="4" t="n"/>
       <c r="C352" s="4" t="n"/>
       <c r="D352" s="4" t="n"/>
-      <c r="E352" s="4" t="n"/>
+      <c r="E352" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F352" s="4" t="n"/>
       <c r="G352" s="4" t="n"/>
       <c r="H352" s="4" t="n"/>
@@ -9551,7 +9555,11 @@
       <c r="B353" s="4" t="n"/>
       <c r="C353" s="4" t="n"/>
       <c r="D353" s="4" t="n"/>
-      <c r="E353" s="4" t="n"/>
+      <c r="E353" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F353" s="4" t="n"/>
       <c r="G353" s="4" t="n"/>
       <c r="H353" s="4" t="n"/>
@@ -10409,9 +10417,9 @@
       <c r="G382" s="4" t="n"/>
       <c r="H382" s="4" t="n"/>
       <c r="I382" s="4" t="n"/>
-      <c r="J382" s="8" t="inlineStr">
-        <is>
-          <t>Notes / Changes - Sŵ Ni</t>
+      <c r="J382" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K382" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8668,11 +8668,7 @@
       <c r="F331" s="4" t="n"/>
       <c r="G331" s="4" t="n"/>
       <c r="H331" s="4" t="n"/>
-      <c r="I331" s="9" t="inlineStr">
-        <is>
-          <t>Delivery - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="I331" s="4" t="n"/>
       <c r="J331" s="5" t="inlineStr">
         <is>
           <t>Sŵ Ni</t>
@@ -8713,11 +8709,7 @@
       <c r="F332" s="4" t="n"/>
       <c r="G332" s="4" t="n"/>
       <c r="H332" s="4" t="n"/>
-      <c r="I332" s="9" t="inlineStr">
-        <is>
-          <t>Delivery - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="I332" s="4" t="n"/>
       <c r="J332" s="5" t="inlineStr">
         <is>
           <t>Sŵ Ni</t>
@@ -8730,7 +8722,12 @@
         </is>
       </c>
       <c r="M332" s="4" t="n"/>
-      <c r="N332" s="4" t="n"/>
+      <c r="N332" s="5" t="inlineStr">
+        <is>
+          <t>Sick
+Sick</t>
+        </is>
+      </c>
       <c r="O332" s="4" t="n"/>
     </row>
     <row r="333">
@@ -8746,11 +8743,7 @@
       <c r="F333" s="4" t="n"/>
       <c r="G333" s="4" t="n"/>
       <c r="H333" s="4" t="n"/>
-      <c r="I333" s="9" t="inlineStr">
-        <is>
-          <t>Delivery - Rookie Teachers</t>
-        </is>
-      </c>
+      <c r="I333" s="4" t="n"/>
       <c r="J333" s="5" t="inlineStr">
         <is>
           <t>Sŵ Ni</t>
@@ -8832,7 +8825,11 @@
         </is>
       </c>
       <c r="H335" s="4" t="n"/>
-      <c r="I335" s="4" t="n"/>
+      <c r="I335" s="9" t="inlineStr">
+        <is>
+          <t>Delivery - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="J335" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9414,11 +9414,7 @@
           <t>Urban Cowboys</t>
         </is>
       </c>
-      <c r="J350" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
+      <c r="J350" s="7" t="n"/>
       <c r="K350" s="5" t="inlineStr">
         <is>
           <t>Urban Cowboys</t>
@@ -9475,11 +9471,7 @@
           <t>Urban Cowboys</t>
         </is>
       </c>
-      <c r="J351" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
+      <c r="J351" s="7" t="n"/>
       <c r="K351" s="5" t="inlineStr">
         <is>
           <t>Urban Cowboys</t>
@@ -9528,7 +9520,11 @@
           <t>Delivery - Black History 2026</t>
         </is>
       </c>
-      <c r="J352" s="4" t="n"/>
+      <c r="J352" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="K352" s="4" t="n"/>
       <c r="L352" s="5" t="inlineStr">
         <is>
@@ -9561,7 +9557,11 @@
       <c r="G353" s="4" t="n"/>
       <c r="H353" s="4" t="n"/>
       <c r="I353" s="4" t="n"/>
-      <c r="J353" s="4" t="n"/>
+      <c r="J353" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="K353" s="4" t="n"/>
       <c r="L353" s="4" t="n"/>
       <c r="M353" s="8" t="inlineStr">
@@ -9586,9 +9586,9 @@
       <c r="G354" s="4" t="n"/>
       <c r="H354" s="4" t="n"/>
       <c r="I354" s="4" t="n"/>
-      <c r="J354" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
+      <c r="J354" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="K354" s="4" t="n"/>
@@ -10443,9 +10443,9 @@
       <c r="G383" s="4" t="n"/>
       <c r="H383" s="4" t="n"/>
       <c r="I383" s="4" t="n"/>
-      <c r="J383" s="8" t="inlineStr">
-        <is>
-          <t>Notes / Changes - Sŵ Ni</t>
+      <c r="J383" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K383" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8705,7 +8705,11 @@
       <c r="B332" s="4" t="n"/>
       <c r="C332" s="4" t="n"/>
       <c r="D332" s="4" t="n"/>
-      <c r="E332" s="4" t="n"/>
+      <c r="E332" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Rookie Teachers</t>
+        </is>
+      </c>
       <c r="F332" s="4" t="n"/>
       <c r="G332" s="4" t="n"/>
       <c r="H332" s="4" t="n"/>
@@ -8724,8 +8728,7 @@
       <c r="M332" s="4" t="n"/>
       <c r="N332" s="5" t="inlineStr">
         <is>
-          <t>Sick
-Sick</t>
+          <t>Sick</t>
         </is>
       </c>
       <c r="O332" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9584,7 +9584,11 @@
       <c r="B354" s="4" t="n"/>
       <c r="C354" s="4" t="n"/>
       <c r="D354" s="4" t="n"/>
-      <c r="E354" s="4" t="n"/>
+      <c r="E354" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F354" s="4" t="n"/>
       <c r="G354" s="4" t="n"/>
       <c r="H354" s="4" t="n"/>
@@ -9613,7 +9617,11 @@
       <c r="B355" s="4" t="n"/>
       <c r="C355" s="4" t="n"/>
       <c r="D355" s="4" t="n"/>
-      <c r="E355" s="4" t="n"/>
+      <c r="E355" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F355" s="4" t="n"/>
       <c r="G355" s="4" t="n"/>
       <c r="H355" s="4" t="n"/>
@@ -9642,7 +9650,11 @@
       <c r="B356" s="4" t="n"/>
       <c r="C356" s="4" t="n"/>
       <c r="D356" s="4" t="n"/>
-      <c r="E356" s="4" t="n"/>
+      <c r="E356" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="F356" s="4" t="n"/>
       <c r="G356" s="4" t="n"/>
       <c r="H356" s="4" t="n"/>
@@ -9725,7 +9737,11 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E359" s="4" t="n"/>
+      <c r="E359" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="F359" s="10" t="inlineStr">
         <is>
           <t>OFF</t>
@@ -9762,7 +9778,11 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E360" s="4" t="n"/>
+      <c r="E360" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="F360" s="10" t="inlineStr">
         <is>
           <t>OFF</t>
@@ -9799,7 +9819,11 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E361" s="4" t="n"/>
+      <c r="E361" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F361" s="10" t="inlineStr">
         <is>
           <t>OFF</t>
@@ -9818,11 +9842,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L361" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L361" s="4" t="n"/>
       <c r="M361" s="4" t="n"/>
       <c r="N361" s="4" t="n"/>
       <c r="O361" s="4" t="n"/>
@@ -9840,7 +9860,11 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E362" s="4" t="n"/>
+      <c r="E362" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F362" s="10" t="inlineStr">
         <is>
           <t>OFF</t>
@@ -9859,11 +9883,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L362" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L362" s="4" t="n"/>
       <c r="M362" s="4" t="n"/>
       <c r="N362" s="4" t="n"/>
       <c r="O362" s="4" t="n"/>
@@ -9896,11 +9916,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L363" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L363" s="4" t="n"/>
       <c r="M363" s="4" t="n"/>
       <c r="N363" s="4" t="n"/>
       <c r="O363" s="4" t="n"/>
@@ -9983,11 +9999,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L366" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L366" s="4" t="n"/>
       <c r="M366" s="4" t="n"/>
       <c r="N366" s="4" t="n"/>
       <c r="O366" s="4" t="n"/>
@@ -10016,11 +10028,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L367" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L367" s="4" t="n"/>
       <c r="M367" s="4" t="n"/>
       <c r="N367" s="4" t="n"/>
       <c r="O367" s="4" t="n"/>
@@ -10045,11 +10053,7 @@
         </is>
       </c>
       <c r="K368" s="4" t="n"/>
-      <c r="L368" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L368" s="4" t="n"/>
       <c r="M368" s="4" t="n"/>
       <c r="N368" s="4" t="n"/>
       <c r="O368" s="4" t="n"/>
@@ -10074,11 +10078,7 @@
         </is>
       </c>
       <c r="K369" s="4" t="n"/>
-      <c r="L369" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L369" s="4" t="n"/>
       <c r="M369" s="4" t="n"/>
       <c r="N369" s="4" t="n"/>
       <c r="O369" s="4" t="n"/>
@@ -10103,11 +10103,7 @@
         </is>
       </c>
       <c r="K370" s="4" t="n"/>
-      <c r="L370" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L370" s="4" t="n"/>
       <c r="M370" s="4" t="n"/>
       <c r="N370" s="4" t="n"/>
       <c r="O370" s="4" t="n"/>
@@ -10174,11 +10170,7 @@
         </is>
       </c>
       <c r="K373" s="4" t="n"/>
-      <c r="L373" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L373" s="4" t="n"/>
       <c r="M373" s="4" t="n"/>
       <c r="N373" s="4" t="n"/>
       <c r="O373" s="4" t="n"/>
@@ -10203,11 +10195,7 @@
         </is>
       </c>
       <c r="K374" s="4" t="n"/>
-      <c r="L374" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L374" s="4" t="n"/>
       <c r="M374" s="4" t="n"/>
       <c r="N374" s="4" t="n"/>
       <c r="O374" s="4" t="n"/>
@@ -10232,11 +10220,7 @@
         </is>
       </c>
       <c r="K375" s="4" t="n"/>
-      <c r="L375" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L375" s="4" t="n"/>
       <c r="M375" s="4" t="n"/>
       <c r="N375" s="4" t="n"/>
       <c r="O375" s="4" t="n"/>
@@ -10261,11 +10245,7 @@
         </is>
       </c>
       <c r="K376" s="4" t="n"/>
-      <c r="L376" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L376" s="4" t="n"/>
       <c r="M376" s="4" t="n"/>
       <c r="N376" s="4" t="n"/>
       <c r="O376" s="4" t="n"/>
@@ -10290,11 +10270,7 @@
         </is>
       </c>
       <c r="K377" s="4" t="n"/>
-      <c r="L377" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L377" s="4" t="n"/>
       <c r="M377" s="4" t="n"/>
       <c r="N377" s="4" t="n"/>
       <c r="O377" s="4" t="n"/>
@@ -10365,11 +10341,7 @@
         </is>
       </c>
       <c r="K380" s="4" t="n"/>
-      <c r="L380" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L380" s="4" t="n"/>
       <c r="M380" s="4" t="n"/>
       <c r="N380" s="4" t="n"/>
       <c r="O380" s="4" t="n"/>
@@ -10394,11 +10366,7 @@
         </is>
       </c>
       <c r="K381" s="4" t="n"/>
-      <c r="L381" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L381" s="4" t="n"/>
       <c r="M381" s="4" t="n"/>
       <c r="N381" s="4" t="n"/>
       <c r="O381" s="4" t="n"/>
@@ -10423,11 +10391,7 @@
         </is>
       </c>
       <c r="K382" s="4" t="n"/>
-      <c r="L382" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L382" s="4" t="n"/>
       <c r="M382" s="4" t="n"/>
       <c r="N382" s="4" t="n"/>
       <c r="O382" s="4" t="n"/>
@@ -10452,11 +10416,7 @@
         </is>
       </c>
       <c r="K383" s="4" t="n"/>
-      <c r="L383" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L383" s="4" t="n"/>
       <c r="M383" s="4" t="n"/>
       <c r="N383" s="4" t="n"/>
       <c r="O383" s="4" t="n"/>
@@ -10481,11 +10441,7 @@
         </is>
       </c>
       <c r="K384" s="4" t="n"/>
-      <c r="L384" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L384" s="4" t="n"/>
       <c r="M384" s="4" t="n"/>
       <c r="N384" s="8" t="inlineStr">
         <is>
@@ -10560,11 +10516,7 @@
         </is>
       </c>
       <c r="K387" s="4" t="n"/>
-      <c r="L387" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L387" s="4" t="n"/>
       <c r="M387" s="4" t="n"/>
       <c r="N387" s="4" t="n"/>
       <c r="O387" s="4" t="n"/>
@@ -10593,11 +10545,7 @@
         </is>
       </c>
       <c r="K388" s="4" t="n"/>
-      <c r="L388" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L388" s="4" t="n"/>
       <c r="M388" s="4" t="n"/>
       <c r="N388" s="4" t="n"/>
       <c r="O388" s="4" t="n"/>
@@ -10626,11 +10574,7 @@
         </is>
       </c>
       <c r="K389" s="4" t="n"/>
-      <c r="L389" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L389" s="4" t="n"/>
       <c r="M389" s="4" t="n"/>
       <c r="N389" s="4" t="n"/>
       <c r="O389" s="4" t="n"/>
@@ -10659,11 +10603,7 @@
         </is>
       </c>
       <c r="K390" s="4" t="n"/>
-      <c r="L390" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L390" s="4" t="n"/>
       <c r="M390" s="4" t="n"/>
       <c r="N390" s="4" t="n"/>
       <c r="O390" s="4" t="n"/>
@@ -10692,11 +10632,7 @@
         </is>
       </c>
       <c r="K391" s="4" t="n"/>
-      <c r="L391" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L391" s="4" t="n"/>
       <c r="M391" s="4" t="n"/>
       <c r="N391" s="4" t="n"/>
       <c r="O391" s="4" t="n"/>
@@ -10768,11 +10704,7 @@
         </is>
       </c>
       <c r="K394" s="4" t="n"/>
-      <c r="L394" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L394" s="4" t="n"/>
       <c r="M394" s="4" t="n"/>
       <c r="N394" s="4" t="n"/>
       <c r="O394" s="4" t="n"/>
@@ -10802,11 +10734,7 @@
         </is>
       </c>
       <c r="K395" s="4" t="n"/>
-      <c r="L395" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L395" s="4" t="n"/>
       <c r="M395" s="4" t="n"/>
       <c r="N395" s="4" t="n"/>
       <c r="O395" s="4" t="n"/>
@@ -10836,11 +10764,7 @@
         </is>
       </c>
       <c r="K396" s="4" t="n"/>
-      <c r="L396" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L396" s="4" t="n"/>
       <c r="M396" s="4" t="n"/>
       <c r="N396" s="4" t="n"/>
       <c r="O396" s="4" t="n"/>
@@ -10870,11 +10794,7 @@
         </is>
       </c>
       <c r="K397" s="4" t="n"/>
-      <c r="L397" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L397" s="4" t="n"/>
       <c r="M397" s="4" t="n"/>
       <c r="N397" s="4" t="n"/>
       <c r="O397" s="4" t="n"/>
@@ -10908,11 +10828,7 @@
         </is>
       </c>
       <c r="K398" s="4" t="n"/>
-      <c r="L398" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L398" s="4" t="n"/>
       <c r="M398" s="4" t="n"/>
       <c r="N398" s="4" t="n"/>
       <c r="O398" s="4" t="n"/>
@@ -10975,11 +10891,7 @@
       <c r="I401" s="4" t="n"/>
       <c r="J401" s="4" t="n"/>
       <c r="K401" s="4" t="n"/>
-      <c r="L401" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="L401" s="4" t="n"/>
       <c r="M401" s="4" t="n"/>
       <c r="N401" s="4" t="n"/>
       <c r="O401" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9652,7 +9652,7 @@
       <c r="D356" s="4" t="n"/>
       <c r="E356" s="5" t="inlineStr">
         <is>
-          <t>Edit - Mabli a Ceff Ceff</t>
+          <t>Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="F356" s="4" t="n"/>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="E361" s="5" t="inlineStr">
         <is>
-          <t>Edit - Sŵ Ni</t>
+          <t>Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="F361" s="10" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9862,7 +9862,7 @@
       </c>
       <c r="E362" s="5" t="inlineStr">
         <is>
-          <t>Edit - Sŵ Ni</t>
+          <t>Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="F362" s="10" t="inlineStr">
@@ -9897,7 +9897,11 @@
       <c r="B363" s="4" t="n"/>
       <c r="C363" s="4" t="n"/>
       <c r="D363" s="4" t="n"/>
-      <c r="E363" s="4" t="n"/>
+      <c r="E363" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="F363" s="10" t="inlineStr">
         <is>
           <t>OFF</t>
@@ -9980,7 +9984,11 @@
       <c r="B366" s="4" t="n"/>
       <c r="C366" s="4" t="n"/>
       <c r="D366" s="4" t="n"/>
-      <c r="E366" s="4" t="n"/>
+      <c r="E366" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F366" s="10" t="inlineStr">
         <is>
           <t>OFF</t>
@@ -10013,7 +10021,11 @@
       <c r="B367" s="4" t="n"/>
       <c r="C367" s="4" t="n"/>
       <c r="D367" s="4" t="n"/>
-      <c r="E367" s="4" t="n"/>
+      <c r="E367" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F367" s="4" t="n"/>
       <c r="G367" s="4" t="n"/>
       <c r="H367" s="4" t="n"/>
@@ -10042,7 +10054,11 @@
       <c r="B368" s="4" t="n"/>
       <c r="C368" s="4" t="n"/>
       <c r="D368" s="4" t="n"/>
-      <c r="E368" s="4" t="n"/>
+      <c r="E368" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F368" s="4" t="n"/>
       <c r="G368" s="4" t="n"/>
       <c r="H368" s="4" t="n"/>
@@ -10067,7 +10083,11 @@
       <c r="B369" s="4" t="n"/>
       <c r="C369" s="4" t="n"/>
       <c r="D369" s="4" t="n"/>
-      <c r="E369" s="4" t="n"/>
+      <c r="E369" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F369" s="4" t="n"/>
       <c r="G369" s="4" t="n"/>
       <c r="H369" s="4" t="n"/>
@@ -10092,7 +10112,11 @@
       <c r="B370" s="4" t="n"/>
       <c r="C370" s="4" t="n"/>
       <c r="D370" s="4" t="n"/>
-      <c r="E370" s="4" t="n"/>
+      <c r="E370" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F370" s="4" t="n"/>
       <c r="G370" s="4" t="n"/>
       <c r="H370" s="4" t="n"/>
@@ -10159,7 +10183,11 @@
       <c r="B373" s="4" t="n"/>
       <c r="C373" s="4" t="n"/>
       <c r="D373" s="4" t="n"/>
-      <c r="E373" s="4" t="n"/>
+      <c r="E373" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="F373" s="4" t="n"/>
       <c r="G373" s="4" t="n"/>
       <c r="H373" s="4" t="n"/>
@@ -10184,7 +10212,11 @@
       <c r="B374" s="4" t="n"/>
       <c r="C374" s="4" t="n"/>
       <c r="D374" s="4" t="n"/>
-      <c r="E374" s="4" t="n"/>
+      <c r="E374" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="F374" s="4" t="n"/>
       <c r="G374" s="4" t="n"/>
       <c r="H374" s="4" t="n"/>
@@ -10209,7 +10241,11 @@
       <c r="B375" s="4" t="n"/>
       <c r="C375" s="4" t="n"/>
       <c r="D375" s="4" t="n"/>
-      <c r="E375" s="4" t="n"/>
+      <c r="E375" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="F375" s="4" t="n"/>
       <c r="G375" s="4" t="n"/>
       <c r="H375" s="4" t="n"/>
@@ -10234,7 +10270,11 @@
       <c r="B376" s="4" t="n"/>
       <c r="C376" s="4" t="n"/>
       <c r="D376" s="4" t="n"/>
-      <c r="E376" s="4" t="n"/>
+      <c r="E376" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="F376" s="4" t="n"/>
       <c r="G376" s="4" t="n"/>
       <c r="H376" s="4" t="n"/>
@@ -10259,7 +10299,11 @@
       <c r="B377" s="4" t="n"/>
       <c r="C377" s="4" t="n"/>
       <c r="D377" s="4" t="n"/>
-      <c r="E377" s="4" t="n"/>
+      <c r="E377" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="F377" s="4" t="n"/>
       <c r="G377" s="4" t="n"/>
       <c r="H377" s="4" t="n"/>
@@ -10330,7 +10374,11 @@
       <c r="B380" s="4" t="n"/>
       <c r="C380" s="4" t="n"/>
       <c r="D380" s="4" t="n"/>
-      <c r="E380" s="4" t="n"/>
+      <c r="E380" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F380" s="4" t="n"/>
       <c r="G380" s="4" t="n"/>
       <c r="H380" s="4" t="n"/>
@@ -10355,7 +10403,11 @@
       <c r="B381" s="4" t="n"/>
       <c r="C381" s="4" t="n"/>
       <c r="D381" s="4" t="n"/>
-      <c r="E381" s="4" t="n"/>
+      <c r="E381" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F381" s="4" t="n"/>
       <c r="G381" s="4" t="n"/>
       <c r="H381" s="4" t="n"/>
@@ -10380,7 +10432,11 @@
       <c r="B382" s="4" t="n"/>
       <c r="C382" s="4" t="n"/>
       <c r="D382" s="4" t="n"/>
-      <c r="E382" s="4" t="n"/>
+      <c r="E382" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F382" s="4" t="n"/>
       <c r="G382" s="4" t="n"/>
       <c r="H382" s="4" t="n"/>
@@ -10405,7 +10461,11 @@
       <c r="B383" s="4" t="n"/>
       <c r="C383" s="4" t="n"/>
       <c r="D383" s="4" t="n"/>
-      <c r="E383" s="4" t="n"/>
+      <c r="E383" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F383" s="4" t="n"/>
       <c r="G383" s="4" t="n"/>
       <c r="H383" s="4" t="n"/>
@@ -10430,7 +10490,11 @@
       <c r="B384" s="4" t="n"/>
       <c r="C384" s="4" t="n"/>
       <c r="D384" s="4" t="n"/>
-      <c r="E384" s="4" t="n"/>
+      <c r="E384" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F384" s="4" t="n"/>
       <c r="G384" s="4" t="n"/>
       <c r="H384" s="4" t="n"/>
@@ -10505,7 +10569,11 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E387" s="4" t="n"/>
+      <c r="E387" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="F387" s="4" t="n"/>
       <c r="G387" s="4" t="n"/>
       <c r="H387" s="4" t="n"/>
@@ -10534,7 +10602,11 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E388" s="4" t="n"/>
+      <c r="E388" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="F388" s="4" t="n"/>
       <c r="G388" s="4" t="n"/>
       <c r="H388" s="4" t="n"/>
@@ -10563,7 +10635,11 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E389" s="4" t="n"/>
+      <c r="E389" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="F389" s="4" t="n"/>
       <c r="G389" s="4" t="n"/>
       <c r="H389" s="4" t="n"/>
@@ -10592,7 +10668,11 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E390" s="4" t="n"/>
+      <c r="E390" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="F390" s="4" t="n"/>
       <c r="G390" s="4" t="n"/>
       <c r="H390" s="4" t="n"/>
@@ -10621,7 +10701,11 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E391" s="4" t="n"/>
+      <c r="E391" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="F391" s="4" t="n"/>
       <c r="G391" s="4" t="n"/>
       <c r="H391" s="4" t="n"/>
@@ -10692,7 +10776,11 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E394" s="4" t="n"/>
+      <c r="E394" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="F394" s="4" t="n"/>
       <c r="G394" s="4" t="n"/>
       <c r="H394" s="4" t="n"/>
@@ -10722,7 +10810,11 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E395" s="4" t="n"/>
+      <c r="E395" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="F395" s="4" t="n"/>
       <c r="G395" s="4" t="n"/>
       <c r="H395" s="4" t="n"/>
@@ -10752,7 +10844,11 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E396" s="4" t="n"/>
+      <c r="E396" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="F396" s="4" t="n"/>
       <c r="G396" s="4" t="n"/>
       <c r="H396" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -10846,7 +10846,8 @@
       </c>
       <c r="E396" s="5" t="inlineStr">
         <is>
-          <t>Edit - Mabli a Ceff Ceff</t>
+          <t>Edit - Sŵ Ni
+Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="F396" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -10879,7 +10879,11 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E397" s="4" t="n"/>
+      <c r="E397" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F397" s="4" t="n"/>
       <c r="G397" s="4" t="n"/>
       <c r="H397" s="4" t="n"/>
@@ -10905,7 +10909,11 @@
       <c r="B398" s="4" t="n"/>
       <c r="C398" s="4" t="n"/>
       <c r="D398" s="4" t="n"/>
-      <c r="E398" s="4" t="n"/>
+      <c r="E398" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F398" s="4" t="n"/>
       <c r="G398" s="9" t="inlineStr">
         <is>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -10994,7 +10994,11 @@
       <c r="G401" s="4" t="n"/>
       <c r="H401" s="4" t="n"/>
       <c r="I401" s="4" t="n"/>
-      <c r="J401" s="4" t="n"/>
+      <c r="J401" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K401" s="4" t="n"/>
       <c r="L401" s="4" t="n"/>
       <c r="M401" s="4" t="n"/>
@@ -11015,7 +11019,11 @@
       <c r="G402" s="4" t="n"/>
       <c r="H402" s="4" t="n"/>
       <c r="I402" s="4" t="n"/>
-      <c r="J402" s="4" t="n"/>
+      <c r="J402" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K402" s="4" t="n"/>
       <c r="L402" s="4" t="n"/>
       <c r="M402" s="4" t="n"/>
@@ -11036,7 +11044,11 @@
       <c r="G403" s="4" t="n"/>
       <c r="H403" s="4" t="n"/>
       <c r="I403" s="4" t="n"/>
-      <c r="J403" s="4" t="n"/>
+      <c r="J403" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K403" s="4" t="n"/>
       <c r="L403" s="4" t="n"/>
       <c r="M403" s="4" t="n"/>
@@ -11057,7 +11069,11 @@
       <c r="G404" s="4" t="n"/>
       <c r="H404" s="4" t="n"/>
       <c r="I404" s="4" t="n"/>
-      <c r="J404" s="4" t="n"/>
+      <c r="J404" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K404" s="4" t="n"/>
       <c r="L404" s="4" t="n"/>
       <c r="M404" s="4" t="n"/>
@@ -11086,7 +11102,11 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J405" s="4" t="n"/>
+      <c r="J405" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K405" s="4" t="n"/>
       <c r="L405" s="4" t="n"/>
       <c r="M405" s="4" t="n"/>
@@ -12113,8 +12133,7 @@
       <c r="I450" s="4" t="n"/>
       <c r="J450" s="5" t="inlineStr">
         <is>
-          <t>Film - Y Grŵp Chat
-Offline Edit - Sŵ Ni</t>
+          <t>Film - Y Grŵp Chat</t>
         </is>
       </c>
       <c r="K450" s="4" t="n"/>
@@ -12143,8 +12162,7 @@
       <c r="I451" s="4" t="n"/>
       <c r="J451" s="5" t="inlineStr">
         <is>
-          <t>Film - Y Grŵp Chat
-Offline Edit - Sŵ Ni</t>
+          <t>Film - Y Grŵp Chat</t>
         </is>
       </c>
       <c r="K451" s="4" t="n"/>
@@ -12167,11 +12185,7 @@
       <c r="G452" s="4" t="n"/>
       <c r="H452" s="4" t="n"/>
       <c r="I452" s="4" t="n"/>
-      <c r="J452" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J452" s="4" t="n"/>
       <c r="K452" s="4" t="n"/>
       <c r="L452" s="4" t="n"/>
       <c r="M452" s="4" t="n"/>
@@ -12192,11 +12206,7 @@
       <c r="G453" s="4" t="n"/>
       <c r="H453" s="4" t="n"/>
       <c r="I453" s="4" t="n"/>
-      <c r="J453" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J453" s="4" t="n"/>
       <c r="K453" s="4" t="n"/>
       <c r="L453" s="4" t="n"/>
       <c r="M453" s="4" t="n"/>
@@ -12217,11 +12227,7 @@
       <c r="G454" s="4" t="n"/>
       <c r="H454" s="4" t="n"/>
       <c r="I454" s="4" t="n"/>
-      <c r="J454" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J454" s="4" t="n"/>
       <c r="K454" s="4" t="n"/>
       <c r="L454" s="4" t="n"/>
       <c r="M454" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -11169,7 +11169,11 @@
       <c r="G408" s="4" t="n"/>
       <c r="H408" s="4" t="n"/>
       <c r="I408" s="4" t="n"/>
-      <c r="J408" s="4" t="n"/>
+      <c r="J408" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K408" s="4" t="n"/>
       <c r="L408" s="4" t="n"/>
       <c r="M408" s="4" t="n"/>
@@ -11378,7 +11382,11 @@
       <c r="G417" s="4" t="n"/>
       <c r="H417" s="4" t="n"/>
       <c r="I417" s="4" t="n"/>
-      <c r="J417" s="4" t="n"/>
+      <c r="J417" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K417" s="4" t="n"/>
       <c r="L417" s="4" t="n"/>
       <c r="M417" s="4" t="n"/>
@@ -11399,7 +11407,11 @@
       <c r="G418" s="4" t="n"/>
       <c r="H418" s="4" t="n"/>
       <c r="I418" s="4" t="n"/>
-      <c r="J418" s="4" t="n"/>
+      <c r="J418" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K418" s="4" t="n"/>
       <c r="L418" s="4" t="n"/>
       <c r="M418" s="4" t="n"/>
@@ -11420,7 +11432,11 @@
       <c r="G419" s="4" t="n"/>
       <c r="H419" s="4" t="n"/>
       <c r="I419" s="4" t="n"/>
-      <c r="J419" s="4" t="n"/>
+      <c r="J419" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K419" s="4" t="n"/>
       <c r="L419" s="4" t="n"/>
       <c r="M419" s="4" t="n"/>
@@ -12290,11 +12306,7 @@
       <c r="G457" s="4" t="n"/>
       <c r="H457" s="4" t="n"/>
       <c r="I457" s="4" t="n"/>
-      <c r="J457" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J457" s="4" t="n"/>
       <c r="K457" s="4" t="n"/>
       <c r="L457" s="4" t="n"/>
       <c r="M457" s="4" t="n"/>
@@ -12315,11 +12327,7 @@
       <c r="G458" s="4" t="n"/>
       <c r="H458" s="4" t="n"/>
       <c r="I458" s="4" t="n"/>
-      <c r="J458" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J458" s="4" t="n"/>
       <c r="K458" s="4" t="n"/>
       <c r="L458" s="4" t="n"/>
       <c r="M458" s="4" t="n"/>
@@ -12350,8 +12358,7 @@
       <c r="I459" s="4" t="n"/>
       <c r="J459" s="5" t="inlineStr">
         <is>
-          <t>Film - Hwyl Fawr Blodwen
-Offline Edit - Sŵ Ni</t>
+          <t>Film - Hwyl Fawr Blodwen</t>
         </is>
       </c>
       <c r="K459" s="5" t="inlineStr">
@@ -12388,8 +12395,7 @@
       <c r="I460" s="4" t="n"/>
       <c r="J460" s="5" t="inlineStr">
         <is>
-          <t>Film - Hwyl Fawr Blodwen
-Offline Edit - Sŵ Ni</t>
+          <t>Film - Hwyl Fawr Blodwen</t>
         </is>
       </c>
       <c r="K460" s="5" t="inlineStr">
@@ -12426,8 +12432,7 @@
       <c r="I461" s="4" t="n"/>
       <c r="J461" s="5" t="inlineStr">
         <is>
-          <t>Film - Hwyl Fawr Blodwen
-Offline Edit - Sŵ Ni</t>
+          <t>Film - Hwyl Fawr Blodwen</t>
         </is>
       </c>
       <c r="K461" s="5" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -12076,9 +12076,9 @@
       <c r="G447" s="4" t="n"/>
       <c r="H447" s="4" t="n"/>
       <c r="I447" s="4" t="n"/>
-      <c r="J447" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
+      <c r="J447" s="5" t="inlineStr">
+        <is>
+          <t>Film - Y Grŵp Chat</t>
         </is>
       </c>
       <c r="K447" s="4" t="n"/>
@@ -12201,7 +12201,11 @@
       <c r="G452" s="4" t="n"/>
       <c r="H452" s="4" t="n"/>
       <c r="I452" s="4" t="n"/>
-      <c r="J452" s="4" t="n"/>
+      <c r="J452" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K452" s="4" t="n"/>
       <c r="L452" s="4" t="n"/>
       <c r="M452" s="4" t="n"/>
@@ -12222,7 +12226,11 @@
       <c r="G453" s="4" t="n"/>
       <c r="H453" s="4" t="n"/>
       <c r="I453" s="4" t="n"/>
-      <c r="J453" s="4" t="n"/>
+      <c r="J453" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K453" s="4" t="n"/>
       <c r="L453" s="4" t="n"/>
       <c r="M453" s="4" t="n"/>
@@ -12243,7 +12251,11 @@
       <c r="G454" s="4" t="n"/>
       <c r="H454" s="4" t="n"/>
       <c r="I454" s="4" t="n"/>
-      <c r="J454" s="4" t="n"/>
+      <c r="J454" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K454" s="4" t="n"/>
       <c r="L454" s="4" t="n"/>
       <c r="M454" s="4" t="n"/>
@@ -12306,7 +12318,11 @@
       <c r="G457" s="4" t="n"/>
       <c r="H457" s="4" t="n"/>
       <c r="I457" s="4" t="n"/>
-      <c r="J457" s="4" t="n"/>
+      <c r="J457" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K457" s="4" t="n"/>
       <c r="L457" s="4" t="n"/>
       <c r="M457" s="4" t="n"/>
@@ -12327,7 +12343,11 @@
       <c r="G458" s="4" t="n"/>
       <c r="H458" s="4" t="n"/>
       <c r="I458" s="4" t="n"/>
-      <c r="J458" s="4" t="n"/>
+      <c r="J458" s="5" t="inlineStr">
+        <is>
+          <t>Film - Hwyl Fawr Blodwen</t>
+        </is>
+      </c>
       <c r="K458" s="4" t="n"/>
       <c r="L458" s="4" t="n"/>
       <c r="M458" s="4" t="n"/>
@@ -12601,11 +12621,7 @@
       <c r="G468" s="4" t="n"/>
       <c r="H468" s="4" t="n"/>
       <c r="I468" s="4" t="n"/>
-      <c r="J468" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J468" s="4" t="n"/>
       <c r="K468" s="4" t="n"/>
       <c r="L468" s="4" t="n"/>
       <c r="M468" s="4" t="n"/>
@@ -12693,11 +12709,7 @@
       <c r="G472" s="4" t="n"/>
       <c r="H472" s="4" t="n"/>
       <c r="I472" s="4" t="n"/>
-      <c r="J472" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J472" s="4" t="n"/>
       <c r="K472" s="4" t="n"/>
       <c r="L472" s="4" t="n"/>
       <c r="M472" s="4" t="n"/>
@@ -12718,11 +12730,7 @@
       <c r="G473" s="4" t="n"/>
       <c r="H473" s="4" t="n"/>
       <c r="I473" s="4" t="n"/>
-      <c r="J473" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J473" s="4" t="n"/>
       <c r="K473" s="4" t="n"/>
       <c r="L473" s="4" t="n"/>
       <c r="M473" s="4" t="n"/>
@@ -12743,11 +12751,7 @@
       <c r="G474" s="4" t="n"/>
       <c r="H474" s="4" t="n"/>
       <c r="I474" s="4" t="n"/>
-      <c r="J474" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J474" s="4" t="n"/>
       <c r="K474" s="4" t="n"/>
       <c r="L474" s="4" t="n"/>
       <c r="M474" s="4" t="n"/>
@@ -12768,11 +12772,7 @@
       <c r="G475" s="4" t="n"/>
       <c r="H475" s="4" t="n"/>
       <c r="I475" s="4" t="n"/>
-      <c r="J475" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J475" s="4" t="n"/>
       <c r="K475" s="4" t="n"/>
       <c r="L475" s="4" t="n"/>
       <c r="M475" s="4" t="n"/>
@@ -12839,11 +12839,7 @@
       </c>
       <c r="H478" s="4" t="n"/>
       <c r="I478" s="4" t="n"/>
-      <c r="J478" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J478" s="4" t="n"/>
       <c r="K478" s="4" t="n"/>
       <c r="L478" s="4" t="n"/>
       <c r="M478" s="4" t="n"/>
@@ -12868,11 +12864,7 @@
       </c>
       <c r="H479" s="4" t="n"/>
       <c r="I479" s="4" t="n"/>
-      <c r="J479" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J479" s="4" t="n"/>
       <c r="K479" s="4" t="n"/>
       <c r="L479" s="4" t="n"/>
       <c r="M479" s="4" t="n"/>
@@ -12897,11 +12889,7 @@
       </c>
       <c r="H480" s="4" t="n"/>
       <c r="I480" s="4" t="n"/>
-      <c r="J480" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J480" s="4" t="n"/>
       <c r="K480" s="4" t="n"/>
       <c r="L480" s="4" t="n"/>
       <c r="M480" s="4" t="n"/>
@@ -12926,11 +12914,7 @@
       </c>
       <c r="H481" s="4" t="n"/>
       <c r="I481" s="4" t="n"/>
-      <c r="J481" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J481" s="4" t="n"/>
       <c r="K481" s="4" t="n"/>
       <c r="L481" s="4" t="n"/>
       <c r="M481" s="4" t="n"/>
@@ -12959,11 +12943,7 @@
       </c>
       <c r="H482" s="4" t="n"/>
       <c r="I482" s="4" t="n"/>
-      <c r="J482" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J482" s="4" t="n"/>
       <c r="K482" s="4" t="n"/>
       <c r="L482" s="4" t="n"/>
       <c r="M482" s="4" t="n"/>
@@ -13030,11 +13010,7 @@
       <c r="G485" s="4" t="n"/>
       <c r="H485" s="4" t="n"/>
       <c r="I485" s="4" t="n"/>
-      <c r="J485" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J485" s="4" t="n"/>
       <c r="K485" s="4" t="n"/>
       <c r="L485" s="4" t="n"/>
       <c r="M485" s="4" t="n"/>
@@ -13055,11 +13031,7 @@
       <c r="G486" s="4" t="n"/>
       <c r="H486" s="4" t="n"/>
       <c r="I486" s="4" t="n"/>
-      <c r="J486" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J486" s="4" t="n"/>
       <c r="K486" s="4" t="n"/>
       <c r="L486" s="4" t="n"/>
       <c r="M486" s="4" t="n"/>
@@ -13080,11 +13052,7 @@
       <c r="G487" s="4" t="n"/>
       <c r="H487" s="4" t="n"/>
       <c r="I487" s="4" t="n"/>
-      <c r="J487" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J487" s="4" t="n"/>
       <c r="K487" s="4" t="n"/>
       <c r="L487" s="4" t="n"/>
       <c r="M487" s="4" t="n"/>
@@ -13105,11 +13073,7 @@
       <c r="G488" s="4" t="n"/>
       <c r="H488" s="4" t="n"/>
       <c r="I488" s="4" t="n"/>
-      <c r="J488" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J488" s="4" t="n"/>
       <c r="K488" s="4" t="n"/>
       <c r="L488" s="4" t="n"/>
       <c r="M488" s="4" t="n"/>
@@ -13130,11 +13094,7 @@
       <c r="G489" s="4" t="n"/>
       <c r="H489" s="4" t="n"/>
       <c r="I489" s="4" t="n"/>
-      <c r="J489" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J489" s="4" t="n"/>
       <c r="K489" s="4" t="n"/>
       <c r="L489" s="4" t="n"/>
       <c r="M489" s="4" t="n"/>
@@ -13197,11 +13157,7 @@
       <c r="G492" s="4" t="n"/>
       <c r="H492" s="4" t="n"/>
       <c r="I492" s="4" t="n"/>
-      <c r="J492" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J492" s="4" t="n"/>
       <c r="K492" s="4" t="n"/>
       <c r="L492" s="4" t="n"/>
       <c r="M492" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -12621,7 +12621,11 @@
       <c r="G468" s="4" t="n"/>
       <c r="H468" s="4" t="n"/>
       <c r="I468" s="4" t="n"/>
-      <c r="J468" s="4" t="n"/>
+      <c r="J468" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K468" s="4" t="n"/>
       <c r="L468" s="4" t="n"/>
       <c r="M468" s="4" t="n"/>
@@ -12709,7 +12713,11 @@
       <c r="G472" s="4" t="n"/>
       <c r="H472" s="4" t="n"/>
       <c r="I472" s="4" t="n"/>
-      <c r="J472" s="4" t="n"/>
+      <c r="J472" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K472" s="4" t="n"/>
       <c r="L472" s="4" t="n"/>
       <c r="M472" s="4" t="n"/>
@@ -12730,7 +12738,11 @@
       <c r="G473" s="4" t="n"/>
       <c r="H473" s="4" t="n"/>
       <c r="I473" s="4" t="n"/>
-      <c r="J473" s="4" t="n"/>
+      <c r="J473" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K473" s="4" t="n"/>
       <c r="L473" s="4" t="n"/>
       <c r="M473" s="4" t="n"/>
@@ -12751,7 +12763,11 @@
       <c r="G474" s="4" t="n"/>
       <c r="H474" s="4" t="n"/>
       <c r="I474" s="4" t="n"/>
-      <c r="J474" s="4" t="n"/>
+      <c r="J474" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K474" s="4" t="n"/>
       <c r="L474" s="4" t="n"/>
       <c r="M474" s="4" t="n"/>
@@ -12772,7 +12788,11 @@
       <c r="G475" s="4" t="n"/>
       <c r="H475" s="4" t="n"/>
       <c r="I475" s="4" t="n"/>
-      <c r="J475" s="4" t="n"/>
+      <c r="J475" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K475" s="4" t="n"/>
       <c r="L475" s="4" t="n"/>
       <c r="M475" s="4" t="n"/>
@@ -12839,7 +12859,11 @@
       </c>
       <c r="H478" s="4" t="n"/>
       <c r="I478" s="4" t="n"/>
-      <c r="J478" s="4" t="n"/>
+      <c r="J478" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K478" s="4" t="n"/>
       <c r="L478" s="4" t="n"/>
       <c r="M478" s="4" t="n"/>
@@ -12864,7 +12888,11 @@
       </c>
       <c r="H479" s="4" t="n"/>
       <c r="I479" s="4" t="n"/>
-      <c r="J479" s="4" t="n"/>
+      <c r="J479" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K479" s="4" t="n"/>
       <c r="L479" s="4" t="n"/>
       <c r="M479" s="4" t="n"/>
@@ -12889,7 +12917,11 @@
       </c>
       <c r="H480" s="4" t="n"/>
       <c r="I480" s="4" t="n"/>
-      <c r="J480" s="4" t="n"/>
+      <c r="J480" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K480" s="4" t="n"/>
       <c r="L480" s="4" t="n"/>
       <c r="M480" s="4" t="n"/>
@@ -13178,11 +13210,7 @@
       <c r="G493" s="4" t="n"/>
       <c r="H493" s="4" t="n"/>
       <c r="I493" s="4" t="n"/>
-      <c r="J493" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J493" s="4" t="n"/>
       <c r="K493" s="4" t="n"/>
       <c r="L493" s="4" t="n"/>
       <c r="M493" s="4" t="n"/>
@@ -13203,11 +13231,7 @@
       <c r="G494" s="4" t="n"/>
       <c r="H494" s="4" t="n"/>
       <c r="I494" s="4" t="n"/>
-      <c r="J494" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J494" s="4" t="n"/>
       <c r="K494" s="4" t="n"/>
       <c r="L494" s="4" t="n"/>
       <c r="M494" s="4" t="n"/>
@@ -13228,11 +13252,7 @@
       <c r="G495" s="4" t="n"/>
       <c r="H495" s="4" t="n"/>
       <c r="I495" s="4" t="n"/>
-      <c r="J495" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J495" s="4" t="n"/>
       <c r="K495" s="4" t="n"/>
       <c r="L495" s="4" t="n"/>
       <c r="M495" s="4" t="n"/>
@@ -13253,11 +13273,7 @@
       <c r="G496" s="4" t="n"/>
       <c r="H496" s="4" t="n"/>
       <c r="I496" s="4" t="n"/>
-      <c r="J496" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J496" s="4" t="n"/>
       <c r="K496" s="4" t="n"/>
       <c r="L496" s="4" t="n"/>
       <c r="M496" s="4" t="n"/>
@@ -13320,11 +13336,7 @@
       <c r="G499" s="4" t="n"/>
       <c r="H499" s="4" t="n"/>
       <c r="I499" s="4" t="n"/>
-      <c r="J499" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J499" s="4" t="n"/>
       <c r="K499" s="4" t="n"/>
       <c r="L499" s="4" t="n"/>
       <c r="M499" s="4" t="n"/>
@@ -13345,11 +13357,7 @@
       <c r="G500" s="4" t="n"/>
       <c r="H500" s="4" t="n"/>
       <c r="I500" s="4" t="n"/>
-      <c r="J500" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J500" s="4" t="n"/>
       <c r="K500" s="4" t="n"/>
       <c r="L500" s="4" t="n"/>
       <c r="M500" s="4" t="n"/>
@@ -13370,11 +13378,7 @@
       <c r="G501" s="4" t="n"/>
       <c r="H501" s="4" t="n"/>
       <c r="I501" s="4" t="n"/>
-      <c r="J501" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J501" s="4" t="n"/>
       <c r="K501" s="4" t="n"/>
       <c r="L501" s="4" t="n"/>
       <c r="M501" s="4" t="n"/>
@@ -13395,11 +13399,7 @@
       <c r="G502" s="4" t="n"/>
       <c r="H502" s="4" t="n"/>
       <c r="I502" s="4" t="n"/>
-      <c r="J502" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J502" s="4" t="n"/>
       <c r="K502" s="4" t="n"/>
       <c r="L502" s="4" t="n"/>
       <c r="M502" s="4" t="n"/>
@@ -13420,11 +13420,7 @@
       <c r="G503" s="4" t="n"/>
       <c r="H503" s="4" t="n"/>
       <c r="I503" s="4" t="n"/>
-      <c r="J503" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J503" s="4" t="n"/>
       <c r="K503" s="4" t="n"/>
       <c r="L503" s="4" t="n"/>
       <c r="M503" s="4" t="n"/>
@@ -13487,11 +13483,7 @@
       <c r="G506" s="4" t="n"/>
       <c r="H506" s="4" t="n"/>
       <c r="I506" s="4" t="n"/>
-      <c r="J506" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J506" s="4" t="n"/>
       <c r="K506" s="4" t="n"/>
       <c r="L506" s="4" t="n"/>
       <c r="M506" s="4" t="n"/>
@@ -13512,11 +13504,7 @@
       <c r="G507" s="4" t="n"/>
       <c r="H507" s="4" t="n"/>
       <c r="I507" s="4" t="n"/>
-      <c r="J507" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J507" s="4" t="n"/>
       <c r="K507" s="4" t="n"/>
       <c r="L507" s="4" t="n"/>
       <c r="M507" s="4" t="n"/>
@@ -13537,11 +13525,7 @@
       <c r="G508" s="4" t="n"/>
       <c r="H508" s="4" t="n"/>
       <c r="I508" s="4" t="n"/>
-      <c r="J508" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J508" s="4" t="n"/>
       <c r="K508" s="4" t="n"/>
       <c r="L508" s="4" t="n"/>
       <c r="M508" s="4" t="n"/>
@@ -13562,11 +13546,7 @@
       <c r="G509" s="4" t="n"/>
       <c r="H509" s="4" t="n"/>
       <c r="I509" s="4" t="n"/>
-      <c r="J509" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J509" s="4" t="n"/>
       <c r="K509" s="4" t="n"/>
       <c r="L509" s="4" t="n"/>
       <c r="M509" s="4" t="n"/>
@@ -13587,11 +13567,7 @@
       <c r="G510" s="4" t="n"/>
       <c r="H510" s="4" t="n"/>
       <c r="I510" s="4" t="n"/>
-      <c r="J510" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J510" s="4" t="n"/>
       <c r="K510" s="4" t="n"/>
       <c r="L510" s="4" t="n"/>
       <c r="M510" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -11499,7 +11499,11 @@
       <c r="G422" s="4" t="n"/>
       <c r="H422" s="4" t="n"/>
       <c r="I422" s="4" t="n"/>
-      <c r="J422" s="4" t="n"/>
+      <c r="J422" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K422" s="4" t="n"/>
       <c r="L422" s="4" t="n"/>
       <c r="M422" s="4" t="n"/>
@@ -11528,7 +11532,11 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="J423" s="4" t="n"/>
+      <c r="J423" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K423" s="4" t="n"/>
       <c r="L423" s="4" t="n"/>
       <c r="M423" s="4" t="n"/>
@@ -11557,7 +11565,11 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="J424" s="4" t="n"/>
+      <c r="J424" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K424" s="4" t="n"/>
       <c r="L424" s="4" t="n"/>
       <c r="M424" s="4" t="n"/>
@@ -11586,7 +11598,11 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="J425" s="4" t="n"/>
+      <c r="J425" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K425" s="4" t="n"/>
       <c r="L425" s="4" t="n"/>
       <c r="M425" s="4" t="n"/>
@@ -11615,7 +11631,11 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="J426" s="4" t="n"/>
+      <c r="J426" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K426" s="4" t="n"/>
       <c r="L426" s="4" t="n"/>
       <c r="M426" s="4" t="n"/>
@@ -12318,11 +12338,7 @@
       <c r="G457" s="4" t="n"/>
       <c r="H457" s="4" t="n"/>
       <c r="I457" s="4" t="n"/>
-      <c r="J457" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J457" s="4" t="n"/>
       <c r="K457" s="4" t="n"/>
       <c r="L457" s="4" t="n"/>
       <c r="M457" s="4" t="n"/>
@@ -12788,11 +12804,7 @@
       <c r="G475" s="4" t="n"/>
       <c r="H475" s="4" t="n"/>
       <c r="I475" s="4" t="n"/>
-      <c r="J475" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J475" s="4" t="n"/>
       <c r="K475" s="4" t="n"/>
       <c r="L475" s="4" t="n"/>
       <c r="M475" s="4" t="n"/>
@@ -12859,11 +12871,7 @@
       </c>
       <c r="H478" s="4" t="n"/>
       <c r="I478" s="4" t="n"/>
-      <c r="J478" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J478" s="4" t="n"/>
       <c r="K478" s="4" t="n"/>
       <c r="L478" s="4" t="n"/>
       <c r="M478" s="4" t="n"/>
@@ -12888,11 +12896,7 @@
       </c>
       <c r="H479" s="4" t="n"/>
       <c r="I479" s="4" t="n"/>
-      <c r="J479" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J479" s="4" t="n"/>
       <c r="K479" s="4" t="n"/>
       <c r="L479" s="4" t="n"/>
       <c r="M479" s="4" t="n"/>
@@ -12917,11 +12921,7 @@
       </c>
       <c r="H480" s="4" t="n"/>
       <c r="I480" s="4" t="n"/>
-      <c r="J480" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J480" s="4" t="n"/>
       <c r="K480" s="4" t="n"/>
       <c r="L480" s="4" t="n"/>
       <c r="M480" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -12537,11 +12537,7 @@
       <c r="G464" s="4" t="n"/>
       <c r="H464" s="4" t="n"/>
       <c r="I464" s="4" t="n"/>
-      <c r="J464" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J464" s="4" t="n"/>
       <c r="K464" s="4" t="n"/>
       <c r="L464" s="4" t="n"/>
       <c r="M464" s="4" t="n"/>
@@ -12562,11 +12558,7 @@
       <c r="G465" s="4" t="n"/>
       <c r="H465" s="4" t="n"/>
       <c r="I465" s="4" t="n"/>
-      <c r="J465" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J465" s="4" t="n"/>
       <c r="K465" s="4" t="n"/>
       <c r="L465" s="4" t="n"/>
       <c r="M465" s="4" t="n"/>
@@ -12587,11 +12579,7 @@
       <c r="G466" s="4" t="n"/>
       <c r="H466" s="4" t="n"/>
       <c r="I466" s="4" t="n"/>
-      <c r="J466" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J466" s="4" t="n"/>
       <c r="K466" s="4" t="n"/>
       <c r="L466" s="4" t="n"/>
       <c r="M466" s="4" t="n"/>
@@ -12612,11 +12600,7 @@
       <c r="G467" s="4" t="n"/>
       <c r="H467" s="4" t="n"/>
       <c r="I467" s="4" t="n"/>
-      <c r="J467" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J467" s="4" t="n"/>
       <c r="K467" s="4" t="n"/>
       <c r="L467" s="4" t="n"/>
       <c r="M467" s="4" t="n"/>
@@ -12637,11 +12621,7 @@
       <c r="G468" s="4" t="n"/>
       <c r="H468" s="4" t="n"/>
       <c r="I468" s="4" t="n"/>
-      <c r="J468" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J468" s="4" t="n"/>
       <c r="K468" s="4" t="n"/>
       <c r="L468" s="4" t="n"/>
       <c r="M468" s="4" t="n"/>
@@ -12704,11 +12684,7 @@
       <c r="G471" s="4" t="n"/>
       <c r="H471" s="4" t="n"/>
       <c r="I471" s="4" t="n"/>
-      <c r="J471" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J471" s="4" t="n"/>
       <c r="K471" s="4" t="n"/>
       <c r="L471" s="4" t="n"/>
       <c r="M471" s="4" t="n"/>
@@ -12729,11 +12705,7 @@
       <c r="G472" s="4" t="n"/>
       <c r="H472" s="4" t="n"/>
       <c r="I472" s="4" t="n"/>
-      <c r="J472" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J472" s="4" t="n"/>
       <c r="K472" s="4" t="n"/>
       <c r="L472" s="4" t="n"/>
       <c r="M472" s="4" t="n"/>
@@ -12754,11 +12726,7 @@
       <c r="G473" s="4" t="n"/>
       <c r="H473" s="4" t="n"/>
       <c r="I473" s="4" t="n"/>
-      <c r="J473" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J473" s="4" t="n"/>
       <c r="K473" s="4" t="n"/>
       <c r="L473" s="4" t="n"/>
       <c r="M473" s="4" t="n"/>
@@ -12779,11 +12747,7 @@
       <c r="G474" s="4" t="n"/>
       <c r="H474" s="4" t="n"/>
       <c r="I474" s="4" t="n"/>
-      <c r="J474" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J474" s="4" t="n"/>
       <c r="K474" s="4" t="n"/>
       <c r="L474" s="4" t="n"/>
       <c r="M474" s="4" t="n"/>
@@ -13336,7 +13300,11 @@
       <c r="G499" s="4" t="n"/>
       <c r="H499" s="4" t="n"/>
       <c r="I499" s="4" t="n"/>
-      <c r="J499" s="4" t="n"/>
+      <c r="J499" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K499" s="4" t="n"/>
       <c r="L499" s="4" t="n"/>
       <c r="M499" s="4" t="n"/>
@@ -13357,7 +13325,11 @@
       <c r="G500" s="4" t="n"/>
       <c r="H500" s="4" t="n"/>
       <c r="I500" s="4" t="n"/>
-      <c r="J500" s="4" t="n"/>
+      <c r="J500" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K500" s="4" t="n"/>
       <c r="L500" s="4" t="n"/>
       <c r="M500" s="4" t="n"/>
@@ -13378,7 +13350,11 @@
       <c r="G501" s="4" t="n"/>
       <c r="H501" s="4" t="n"/>
       <c r="I501" s="4" t="n"/>
-      <c r="J501" s="4" t="n"/>
+      <c r="J501" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K501" s="4" t="n"/>
       <c r="L501" s="4" t="n"/>
       <c r="M501" s="4" t="n"/>
@@ -13399,7 +13375,11 @@
       <c r="G502" s="4" t="n"/>
       <c r="H502" s="4" t="n"/>
       <c r="I502" s="4" t="n"/>
-      <c r="J502" s="4" t="n"/>
+      <c r="J502" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K502" s="4" t="n"/>
       <c r="L502" s="4" t="n"/>
       <c r="M502" s="4" t="n"/>
@@ -13420,7 +13400,11 @@
       <c r="G503" s="4" t="n"/>
       <c r="H503" s="4" t="n"/>
       <c r="I503" s="4" t="n"/>
-      <c r="J503" s="4" t="n"/>
+      <c r="J503" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K503" s="4" t="n"/>
       <c r="L503" s="4" t="n"/>
       <c r="M503" s="4" t="n"/>
@@ -13483,7 +13467,11 @@
       <c r="G506" s="4" t="n"/>
       <c r="H506" s="4" t="n"/>
       <c r="I506" s="4" t="n"/>
-      <c r="J506" s="4" t="n"/>
+      <c r="J506" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K506" s="4" t="n"/>
       <c r="L506" s="4" t="n"/>
       <c r="M506" s="4" t="n"/>
@@ -13504,7 +13492,11 @@
       <c r="G507" s="4" t="n"/>
       <c r="H507" s="4" t="n"/>
       <c r="I507" s="4" t="n"/>
-      <c r="J507" s="4" t="n"/>
+      <c r="J507" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K507" s="4" t="n"/>
       <c r="L507" s="4" t="n"/>
       <c r="M507" s="4" t="n"/>
@@ -13525,7 +13517,11 @@
       <c r="G508" s="4" t="n"/>
       <c r="H508" s="4" t="n"/>
       <c r="I508" s="4" t="n"/>
-      <c r="J508" s="4" t="n"/>
+      <c r="J508" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K508" s="4" t="n"/>
       <c r="L508" s="4" t="n"/>
       <c r="M508" s="4" t="n"/>
@@ -13546,7 +13542,11 @@
       <c r="G509" s="4" t="n"/>
       <c r="H509" s="4" t="n"/>
       <c r="I509" s="4" t="n"/>
-      <c r="J509" s="4" t="n"/>
+      <c r="J509" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K509" s="4" t="n"/>
       <c r="L509" s="4" t="n"/>
       <c r="M509" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -13194,7 +13194,12 @@
       <c r="F494" s="4" t="n"/>
       <c r="G494" s="4" t="n"/>
       <c r="H494" s="4" t="n"/>
-      <c r="I494" s="4" t="n"/>
+      <c r="I494" s="9" t="inlineStr">
+        <is>
+          <t>Delivery - Hwyl Fawr Blodwen
+Delivery - Y Grŵp Chat</t>
+        </is>
+      </c>
       <c r="J494" s="4" t="n"/>
       <c r="K494" s="4" t="n"/>
       <c r="L494" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8907,7 +8907,11 @@
           <t>Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="E338" s="4" t="n"/>
+      <c r="E338" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Welsh Music Prize</t>
+        </is>
+      </c>
       <c r="F338" s="4" t="n"/>
       <c r="G338" s="5" t="inlineStr">
         <is>
@@ -8944,7 +8948,11 @@
           <t>Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="E339" s="4" t="n"/>
+      <c r="E339" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Welsh Music Prize</t>
+        </is>
+      </c>
       <c r="F339" s="4" t="n"/>
       <c r="G339" s="5" t="inlineStr">
         <is>
@@ -8989,7 +8997,11 @@
           <t>Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="E340" s="4" t="n"/>
+      <c r="E340" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Welsh Music Prize</t>
+        </is>
+      </c>
       <c r="F340" s="4" t="n"/>
       <c r="G340" s="5" t="inlineStr">
         <is>
@@ -9393,56 +9405,24 @@
           <t>Sat 03 Oct 2026</t>
         </is>
       </c>
-      <c r="B350" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
+      <c r="B350" s="7" t="n"/>
       <c r="C350" s="7" t="n"/>
-      <c r="D350" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
+      <c r="D350" s="7" t="n"/>
       <c r="E350" s="7" t="n"/>
       <c r="F350" s="7" t="n"/>
       <c r="G350" s="7" t="n"/>
-      <c r="H350" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
-      <c r="I350" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
+      <c r="H350" s="7" t="n"/>
+      <c r="I350" s="7" t="n"/>
       <c r="J350" s="7" t="n"/>
-      <c r="K350" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
-      <c r="L350" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
+      <c r="K350" s="7" t="n"/>
+      <c r="L350" s="7" t="n"/>
       <c r="M350" s="5" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="N350" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
-      <c r="O350" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
+      <c r="N350" s="7" t="n"/>
+      <c r="O350" s="7" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="6" t="inlineStr">
@@ -9450,56 +9430,24 @@
           <t>Sun 04 Oct 2026</t>
         </is>
       </c>
-      <c r="B351" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
+      <c r="B351" s="7" t="n"/>
       <c r="C351" s="7" t="n"/>
-      <c r="D351" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
+      <c r="D351" s="7" t="n"/>
       <c r="E351" s="7" t="n"/>
       <c r="F351" s="7" t="n"/>
       <c r="G351" s="7" t="n"/>
-      <c r="H351" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
-      <c r="I351" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
+      <c r="H351" s="7" t="n"/>
+      <c r="I351" s="7" t="n"/>
       <c r="J351" s="7" t="n"/>
-      <c r="K351" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
-      <c r="L351" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
+      <c r="K351" s="7" t="n"/>
+      <c r="L351" s="7" t="n"/>
       <c r="M351" s="5" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="N351" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
-      <c r="O351" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
+      <c r="N351" s="7" t="n"/>
+      <c r="O351" s="7" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="3" t="inlineStr">
@@ -12270,7 +12218,11 @@
       <c r="F454" s="4" t="n"/>
       <c r="G454" s="4" t="n"/>
       <c r="H454" s="4" t="n"/>
-      <c r="I454" s="4" t="n"/>
+      <c r="I454" s="9" t="inlineStr">
+        <is>
+          <t>Delivery - Deep Watch</t>
+        </is>
+      </c>
       <c r="J454" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9256,7 +9256,11 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E347" s="4" t="n"/>
+      <c r="E347" s="5" t="inlineStr">
+        <is>
+          <t>Edit - HOYS</t>
+        </is>
+      </c>
       <c r="F347" s="4" t="n"/>
       <c r="G347" s="5" t="inlineStr">
         <is>
@@ -9305,7 +9309,11 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E348" s="4" t="n"/>
+      <c r="E348" s="5" t="inlineStr">
+        <is>
+          <t>Edit - HOYS</t>
+        </is>
+      </c>
       <c r="F348" s="4" t="n"/>
       <c r="G348" s="5" t="inlineStr">
         <is>
@@ -9350,7 +9358,11 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E349" s="4" t="n"/>
+      <c r="E349" s="5" t="inlineStr">
+        <is>
+          <t>Edit - HOYS</t>
+        </is>
+      </c>
       <c r="F349" s="4" t="n"/>
       <c r="G349" s="5" t="inlineStr">
         <is>
@@ -10936,7 +10948,11 @@
       </c>
       <c r="B401" s="4" t="n"/>
       <c r="C401" s="4" t="n"/>
-      <c r="D401" s="4" t="n"/>
+      <c r="D401" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="E401" s="4" t="n"/>
       <c r="F401" s="4" t="n"/>
       <c r="G401" s="4" t="n"/>
@@ -10961,7 +10977,12 @@
       </c>
       <c r="B402" s="4" t="n"/>
       <c r="C402" s="4" t="n"/>
-      <c r="D402" s="4" t="n"/>
+      <c r="D402" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+
+Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="E402" s="4" t="n"/>
       <c r="F402" s="4" t="n"/>
       <c r="G402" s="4" t="n"/>
@@ -12789,8 +12810,16 @@
       <c r="I478" s="4" t="n"/>
       <c r="J478" s="4" t="n"/>
       <c r="K478" s="4" t="n"/>
-      <c r="L478" s="4" t="n"/>
-      <c r="M478" s="4" t="n"/>
+      <c r="L478" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Dewi Mockumentary</t>
+        </is>
+      </c>
+      <c r="M478" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Dewi Mockumentary</t>
+        </is>
+      </c>
       <c r="N478" s="4" t="n"/>
       <c r="O478" s="4" t="n"/>
     </row>
@@ -12814,8 +12843,16 @@
       <c r="I479" s="4" t="n"/>
       <c r="J479" s="4" t="n"/>
       <c r="K479" s="4" t="n"/>
-      <c r="L479" s="4" t="n"/>
-      <c r="M479" s="4" t="n"/>
+      <c r="L479" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Dewi Mockumentary</t>
+        </is>
+      </c>
+      <c r="M479" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Dewi Mockumentary</t>
+        </is>
+      </c>
       <c r="N479" s="4" t="n"/>
       <c r="O479" s="4" t="n"/>
     </row>
@@ -12839,8 +12876,16 @@
       <c r="I480" s="4" t="n"/>
       <c r="J480" s="4" t="n"/>
       <c r="K480" s="4" t="n"/>
-      <c r="L480" s="4" t="n"/>
-      <c r="M480" s="4" t="n"/>
+      <c r="L480" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Dewi Mockumentary</t>
+        </is>
+      </c>
+      <c r="M480" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Dewi Mockumentary</t>
+        </is>
+      </c>
       <c r="N480" s="4" t="n"/>
       <c r="O480" s="4" t="n"/>
     </row>
@@ -12864,8 +12909,16 @@
       <c r="I481" s="4" t="n"/>
       <c r="J481" s="4" t="n"/>
       <c r="K481" s="4" t="n"/>
-      <c r="L481" s="4" t="n"/>
-      <c r="M481" s="4" t="n"/>
+      <c r="L481" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Dewi Mockumentary</t>
+        </is>
+      </c>
+      <c r="M481" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Dewi Mockumentary</t>
+        </is>
+      </c>
       <c r="N481" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -12893,8 +12946,16 @@
       <c r="I482" s="4" t="n"/>
       <c r="J482" s="4" t="n"/>
       <c r="K482" s="4" t="n"/>
-      <c r="L482" s="4" t="n"/>
-      <c r="M482" s="4" t="n"/>
+      <c r="L482" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Dewi Mockumentary</t>
+        </is>
+      </c>
+      <c r="M482" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Dewi Mockumentary</t>
+        </is>
+      </c>
       <c r="N482" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -12958,7 +13019,11 @@
       <c r="G485" s="4" t="n"/>
       <c r="H485" s="4" t="n"/>
       <c r="I485" s="4" t="n"/>
-      <c r="J485" s="4" t="n"/>
+      <c r="J485" s="5" t="inlineStr">
+        <is>
+          <t>Dub - Dewi Mockumentary</t>
+        </is>
+      </c>
       <c r="K485" s="4" t="n"/>
       <c r="L485" s="4" t="n"/>
       <c r="M485" s="4" t="n"/>
@@ -12979,7 +13044,11 @@
       <c r="G486" s="4" t="n"/>
       <c r="H486" s="4" t="n"/>
       <c r="I486" s="4" t="n"/>
-      <c r="J486" s="4" t="n"/>
+      <c r="J486" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Dewi Mockumentary</t>
+        </is>
+      </c>
       <c r="K486" s="4" t="n"/>
       <c r="L486" s="4" t="n"/>
       <c r="M486" s="4" t="n"/>
@@ -13000,7 +13069,11 @@
       <c r="G487" s="4" t="n"/>
       <c r="H487" s="4" t="n"/>
       <c r="I487" s="4" t="n"/>
-      <c r="J487" s="4" t="n"/>
+      <c r="J487" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Dewi Mockumentary</t>
+        </is>
+      </c>
       <c r="K487" s="4" t="n"/>
       <c r="L487" s="4" t="n"/>
       <c r="M487" s="4" t="n"/>
@@ -13125,7 +13198,11 @@
       <c r="F493" s="4" t="n"/>
       <c r="G493" s="4" t="n"/>
       <c r="H493" s="4" t="n"/>
-      <c r="I493" s="4" t="n"/>
+      <c r="I493" s="9" t="inlineStr">
+        <is>
+          <t>Delivery - Dewi Mockumentary</t>
+        </is>
+      </c>
       <c r="J493" s="4" t="n"/>
       <c r="K493" s="4" t="n"/>
       <c r="L493" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8742,7 +8742,11 @@
       <c r="B333" s="4" t="n"/>
       <c r="C333" s="4" t="n"/>
       <c r="D333" s="4" t="n"/>
-      <c r="E333" s="4" t="n"/>
+      <c r="E333" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Rookie Teachers</t>
+        </is>
+      </c>
       <c r="F333" s="4" t="n"/>
       <c r="G333" s="4" t="n"/>
       <c r="H333" s="4" t="n"/>
@@ -8775,7 +8779,11 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E334" s="4" t="n"/>
+      <c r="E334" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Rookie Teachers</t>
+        </is>
+      </c>
       <c r="F334" s="4" t="n"/>
       <c r="G334" s="5" t="inlineStr">
         <is>
@@ -9369,30 +9377,17 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="H349" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
-      <c r="I349" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
+      <c r="H349" s="4" t="n"/>
+      <c r="I349" s="4" t="n"/>
       <c r="J349" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K349" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
+      <c r="K349" s="4" t="n"/>
       <c r="L349" s="5" t="inlineStr">
         <is>
-          <t>Urban Cowboys
-Edit - Black History 2026</t>
+          <t>Edit - Black History 2026</t>
         </is>
       </c>
       <c r="M349" s="8" t="inlineStr">
@@ -9400,11 +9395,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N349" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
+      <c r="N349" s="4" t="n"/>
       <c r="O349" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
@@ -10963,9 +10954,21 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K401" s="4" t="n"/>
-      <c r="L401" s="4" t="n"/>
-      <c r="M401" s="4" t="n"/>
+      <c r="K401" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="L401" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M401" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N401" s="4" t="n"/>
       <c r="O401" s="4" t="n"/>
     </row>
@@ -10979,8 +10982,7 @@
       <c r="C402" s="4" t="n"/>
       <c r="D402" s="5" t="inlineStr">
         <is>
-          <t>Film - LGBTQ+
-Film - LGBTQ+</t>
+          <t>Film - LGBTQ+</t>
         </is>
       </c>
       <c r="E402" s="4" t="n"/>
@@ -10993,9 +10995,21 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K402" s="4" t="n"/>
-      <c r="L402" s="4" t="n"/>
-      <c r="M402" s="4" t="n"/>
+      <c r="K402" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="L402" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M402" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N402" s="4" t="n"/>
       <c r="O402" s="4" t="n"/>
     </row>
@@ -11007,7 +11021,11 @@
       </c>
       <c r="B403" s="4" t="n"/>
       <c r="C403" s="4" t="n"/>
-      <c r="D403" s="4" t="n"/>
+      <c r="D403" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="E403" s="4" t="n"/>
       <c r="F403" s="4" t="n"/>
       <c r="G403" s="4" t="n"/>
@@ -11018,9 +11036,21 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K403" s="4" t="n"/>
-      <c r="L403" s="4" t="n"/>
-      <c r="M403" s="4" t="n"/>
+      <c r="K403" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="L403" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M403" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N403" s="4" t="n"/>
       <c r="O403" s="4" t="n"/>
     </row>
@@ -11032,7 +11062,11 @@
       </c>
       <c r="B404" s="4" t="n"/>
       <c r="C404" s="4" t="n"/>
-      <c r="D404" s="4" t="n"/>
+      <c r="D404" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="E404" s="4" t="n"/>
       <c r="F404" s="4" t="n"/>
       <c r="G404" s="4" t="n"/>
@@ -11043,9 +11077,21 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K404" s="4" t="n"/>
-      <c r="L404" s="4" t="n"/>
-      <c r="M404" s="4" t="n"/>
+      <c r="K404" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="L404" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M404" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N404" s="4" t="n"/>
       <c r="O404" s="4" t="n"/>
     </row>
@@ -11057,7 +11103,11 @@
       </c>
       <c r="B405" s="4" t="n"/>
       <c r="C405" s="4" t="n"/>
-      <c r="D405" s="4" t="n"/>
+      <c r="D405" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="E405" s="4" t="n"/>
       <c r="F405" s="4" t="n"/>
       <c r="G405" s="9" t="inlineStr">
@@ -11076,9 +11126,21 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K405" s="4" t="n"/>
-      <c r="L405" s="4" t="n"/>
-      <c r="M405" s="4" t="n"/>
+      <c r="K405" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="L405" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M405" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N405" s="4" t="n"/>
       <c r="O405" s="4" t="n"/>
     </row>
@@ -11144,8 +11206,16 @@
         </is>
       </c>
       <c r="K408" s="4" t="n"/>
-      <c r="L408" s="4" t="n"/>
-      <c r="M408" s="4" t="n"/>
+      <c r="L408" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M408" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N408" s="4" t="n"/>
       <c r="O408" s="4" t="n"/>
     </row>
@@ -11165,8 +11235,16 @@
       <c r="I409" s="4" t="n"/>
       <c r="J409" s="4" t="n"/>
       <c r="K409" s="4" t="n"/>
-      <c r="L409" s="4" t="n"/>
-      <c r="M409" s="4" t="n"/>
+      <c r="L409" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M409" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N409" s="4" t="n"/>
       <c r="O409" s="4" t="n"/>
     </row>
@@ -11190,8 +11268,16 @@
         </is>
       </c>
       <c r="K410" s="4" t="n"/>
-      <c r="L410" s="4" t="n"/>
-      <c r="M410" s="4" t="n"/>
+      <c r="L410" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M410" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N410" s="4" t="n"/>
       <c r="O410" s="4" t="n"/>
     </row>
@@ -11215,8 +11301,16 @@
         </is>
       </c>
       <c r="K411" s="4" t="n"/>
-      <c r="L411" s="4" t="n"/>
-      <c r="M411" s="4" t="n"/>
+      <c r="L411" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M411" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N411" s="4" t="n"/>
       <c r="O411" s="4" t="n"/>
     </row>
@@ -11240,8 +11334,16 @@
         </is>
       </c>
       <c r="K412" s="4" t="n"/>
-      <c r="L412" s="4" t="n"/>
-      <c r="M412" s="4" t="n"/>
+      <c r="L412" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M412" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N412" s="4" t="n"/>
       <c r="O412" s="4" t="n"/>
     </row>
@@ -11307,8 +11409,16 @@
         </is>
       </c>
       <c r="K415" s="4" t="n"/>
-      <c r="L415" s="4" t="n"/>
-      <c r="M415" s="4" t="n"/>
+      <c r="L415" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M415" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N415" s="4" t="n"/>
       <c r="O415" s="4" t="n"/>
     </row>
@@ -11332,8 +11442,16 @@
         </is>
       </c>
       <c r="K416" s="4" t="n"/>
-      <c r="L416" s="4" t="n"/>
-      <c r="M416" s="4" t="n"/>
+      <c r="L416" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M416" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N416" s="4" t="n"/>
       <c r="O416" s="4" t="n"/>
     </row>
@@ -11357,8 +11475,16 @@
         </is>
       </c>
       <c r="K417" s="4" t="n"/>
-      <c r="L417" s="4" t="n"/>
-      <c r="M417" s="4" t="n"/>
+      <c r="L417" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M417" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N417" s="4" t="n"/>
       <c r="O417" s="4" t="n"/>
     </row>
@@ -11382,8 +11508,16 @@
         </is>
       </c>
       <c r="K418" s="4" t="n"/>
-      <c r="L418" s="4" t="n"/>
-      <c r="M418" s="4" t="n"/>
+      <c r="L418" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M418" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N418" s="4" t="n"/>
       <c r="O418" s="4" t="n"/>
     </row>
@@ -11407,8 +11541,16 @@
         </is>
       </c>
       <c r="K419" s="4" t="n"/>
-      <c r="L419" s="4" t="n"/>
-      <c r="M419" s="4" t="n"/>
+      <c r="L419" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M419" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N419" s="4" t="n"/>
       <c r="O419" s="4" t="n"/>
     </row>
@@ -11474,8 +11616,16 @@
         </is>
       </c>
       <c r="K422" s="4" t="n"/>
-      <c r="L422" s="4" t="n"/>
-      <c r="M422" s="4" t="n"/>
+      <c r="L422" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M422" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N422" s="4" t="n"/>
       <c r="O422" s="4" t="n"/>
     </row>
@@ -11507,8 +11657,16 @@
         </is>
       </c>
       <c r="K423" s="4" t="n"/>
-      <c r="L423" s="4" t="n"/>
-      <c r="M423" s="4" t="n"/>
+      <c r="L423" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M423" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N423" s="4" t="n"/>
       <c r="O423" s="4" t="n"/>
     </row>
@@ -11540,8 +11698,16 @@
         </is>
       </c>
       <c r="K424" s="4" t="n"/>
-      <c r="L424" s="4" t="n"/>
-      <c r="M424" s="4" t="n"/>
+      <c r="L424" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M424" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N424" s="4" t="n"/>
       <c r="O424" s="4" t="n"/>
     </row>
@@ -11573,8 +11739,16 @@
         </is>
       </c>
       <c r="K425" s="4" t="n"/>
-      <c r="L425" s="4" t="n"/>
-      <c r="M425" s="4" t="n"/>
+      <c r="L425" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M425" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N425" s="4" t="n"/>
       <c r="O425" s="4" t="n"/>
     </row>
@@ -11606,8 +11780,16 @@
         </is>
       </c>
       <c r="K426" s="4" t="n"/>
-      <c r="L426" s="4" t="n"/>
-      <c r="M426" s="4" t="n"/>
+      <c r="L426" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M426" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N426" s="4" t="n"/>
       <c r="O426" s="4" t="n"/>
     </row>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8742,7 +8742,11 @@
       <c r="B333" s="4" t="n"/>
       <c r="C333" s="4" t="n"/>
       <c r="D333" s="4" t="n"/>
-      <c r="E333" s="4" t="n"/>
+      <c r="E333" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Rookie Teachers</t>
+        </is>
+      </c>
       <c r="F333" s="4" t="n"/>
       <c r="G333" s="4" t="n"/>
       <c r="H333" s="4" t="n"/>
@@ -8775,7 +8779,11 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E334" s="4" t="n"/>
+      <c r="E334" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Rookie Teachers</t>
+        </is>
+      </c>
       <c r="F334" s="4" t="n"/>
       <c r="G334" s="5" t="inlineStr">
         <is>
@@ -8820,7 +8828,11 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E335" s="4" t="n"/>
+      <c r="E335" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Rookie Teachers</t>
+        </is>
+      </c>
       <c r="F335" s="4" t="n"/>
       <c r="G335" s="5" t="inlineStr">
         <is>
@@ -9369,30 +9381,17 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="H349" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
-      <c r="I349" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
+      <c r="H349" s="4" t="n"/>
+      <c r="I349" s="4" t="n"/>
       <c r="J349" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K349" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
+      <c r="K349" s="4" t="n"/>
       <c r="L349" s="5" t="inlineStr">
         <is>
-          <t>Urban Cowboys
-Edit - Black History 2026</t>
+          <t>Edit - Black History 2026</t>
         </is>
       </c>
       <c r="M349" s="8" t="inlineStr">
@@ -9400,11 +9399,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N349" s="5" t="inlineStr">
-        <is>
-          <t>Urban Cowboys</t>
-        </is>
-      </c>
+      <c r="N349" s="4" t="n"/>
       <c r="O349" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
@@ -10963,9 +10958,21 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K401" s="4" t="n"/>
-      <c r="L401" s="4" t="n"/>
-      <c r="M401" s="4" t="n"/>
+      <c r="K401" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="L401" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M401" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N401" s="4" t="n"/>
       <c r="O401" s="4" t="n"/>
     </row>
@@ -10979,8 +10986,7 @@
       <c r="C402" s="4" t="n"/>
       <c r="D402" s="5" t="inlineStr">
         <is>
-          <t>Film - LGBTQ+
-Film - LGBTQ+</t>
+          <t>Film - LGBTQ+</t>
         </is>
       </c>
       <c r="E402" s="4" t="n"/>
@@ -10993,9 +10999,21 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K402" s="4" t="n"/>
-      <c r="L402" s="4" t="n"/>
-      <c r="M402" s="4" t="n"/>
+      <c r="K402" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="L402" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M402" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N402" s="4" t="n"/>
       <c r="O402" s="4" t="n"/>
     </row>
@@ -11007,7 +11025,11 @@
       </c>
       <c r="B403" s="4" t="n"/>
       <c r="C403" s="4" t="n"/>
-      <c r="D403" s="4" t="n"/>
+      <c r="D403" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="E403" s="4" t="n"/>
       <c r="F403" s="4" t="n"/>
       <c r="G403" s="4" t="n"/>
@@ -11018,9 +11040,21 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K403" s="4" t="n"/>
-      <c r="L403" s="4" t="n"/>
-      <c r="M403" s="4" t="n"/>
+      <c r="K403" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="L403" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M403" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N403" s="4" t="n"/>
       <c r="O403" s="4" t="n"/>
     </row>
@@ -11032,7 +11066,11 @@
       </c>
       <c r="B404" s="4" t="n"/>
       <c r="C404" s="4" t="n"/>
-      <c r="D404" s="4" t="n"/>
+      <c r="D404" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="E404" s="4" t="n"/>
       <c r="F404" s="4" t="n"/>
       <c r="G404" s="4" t="n"/>
@@ -11043,9 +11081,21 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K404" s="4" t="n"/>
-      <c r="L404" s="4" t="n"/>
-      <c r="M404" s="4" t="n"/>
+      <c r="K404" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="L404" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M404" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N404" s="4" t="n"/>
       <c r="O404" s="4" t="n"/>
     </row>
@@ -11057,7 +11107,11 @@
       </c>
       <c r="B405" s="4" t="n"/>
       <c r="C405" s="4" t="n"/>
-      <c r="D405" s="4" t="n"/>
+      <c r="D405" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="E405" s="4" t="n"/>
       <c r="F405" s="4" t="n"/>
       <c r="G405" s="9" t="inlineStr">
@@ -11076,9 +11130,21 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K405" s="4" t="n"/>
-      <c r="L405" s="4" t="n"/>
-      <c r="M405" s="4" t="n"/>
+      <c r="K405" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="L405" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M405" s="5" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N405" s="4" t="n"/>
       <c r="O405" s="4" t="n"/>
     </row>
@@ -11144,8 +11210,16 @@
         </is>
       </c>
       <c r="K408" s="4" t="n"/>
-      <c r="L408" s="4" t="n"/>
-      <c r="M408" s="4" t="n"/>
+      <c r="L408" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M408" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N408" s="4" t="n"/>
       <c r="O408" s="4" t="n"/>
     </row>
@@ -11165,8 +11239,16 @@
       <c r="I409" s="4" t="n"/>
       <c r="J409" s="4" t="n"/>
       <c r="K409" s="4" t="n"/>
-      <c r="L409" s="4" t="n"/>
-      <c r="M409" s="4" t="n"/>
+      <c r="L409" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M409" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N409" s="4" t="n"/>
       <c r="O409" s="4" t="n"/>
     </row>
@@ -11190,8 +11272,16 @@
         </is>
       </c>
       <c r="K410" s="4" t="n"/>
-      <c r="L410" s="4" t="n"/>
-      <c r="M410" s="4" t="n"/>
+      <c r="L410" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M410" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N410" s="4" t="n"/>
       <c r="O410" s="4" t="n"/>
     </row>
@@ -11215,8 +11305,16 @@
         </is>
       </c>
       <c r="K411" s="4" t="n"/>
-      <c r="L411" s="4" t="n"/>
-      <c r="M411" s="4" t="n"/>
+      <c r="L411" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M411" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N411" s="4" t="n"/>
       <c r="O411" s="4" t="n"/>
     </row>
@@ -11240,8 +11338,16 @@
         </is>
       </c>
       <c r="K412" s="4" t="n"/>
-      <c r="L412" s="4" t="n"/>
-      <c r="M412" s="4" t="n"/>
+      <c r="L412" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M412" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N412" s="4" t="n"/>
       <c r="O412" s="4" t="n"/>
     </row>
@@ -11307,8 +11413,16 @@
         </is>
       </c>
       <c r="K415" s="4" t="n"/>
-      <c r="L415" s="4" t="n"/>
-      <c r="M415" s="4" t="n"/>
+      <c r="L415" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M415" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N415" s="4" t="n"/>
       <c r="O415" s="4" t="n"/>
     </row>
@@ -11332,8 +11446,16 @@
         </is>
       </c>
       <c r="K416" s="4" t="n"/>
-      <c r="L416" s="4" t="n"/>
-      <c r="M416" s="4" t="n"/>
+      <c r="L416" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M416" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N416" s="4" t="n"/>
       <c r="O416" s="4" t="n"/>
     </row>
@@ -11357,8 +11479,16 @@
         </is>
       </c>
       <c r="K417" s="4" t="n"/>
-      <c r="L417" s="4" t="n"/>
-      <c r="M417" s="4" t="n"/>
+      <c r="L417" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M417" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N417" s="4" t="n"/>
       <c r="O417" s="4" t="n"/>
     </row>
@@ -11382,8 +11512,16 @@
         </is>
       </c>
       <c r="K418" s="4" t="n"/>
-      <c r="L418" s="4" t="n"/>
-      <c r="M418" s="4" t="n"/>
+      <c r="L418" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M418" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N418" s="4" t="n"/>
       <c r="O418" s="4" t="n"/>
     </row>
@@ -11407,8 +11545,16 @@
         </is>
       </c>
       <c r="K419" s="4" t="n"/>
-      <c r="L419" s="4" t="n"/>
-      <c r="M419" s="4" t="n"/>
+      <c r="L419" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M419" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N419" s="4" t="n"/>
       <c r="O419" s="4" t="n"/>
     </row>
@@ -11474,8 +11620,16 @@
         </is>
       </c>
       <c r="K422" s="4" t="n"/>
-      <c r="L422" s="4" t="n"/>
-      <c r="M422" s="4" t="n"/>
+      <c r="L422" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M422" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N422" s="4" t="n"/>
       <c r="O422" s="4" t="n"/>
     </row>
@@ -11507,8 +11661,16 @@
         </is>
       </c>
       <c r="K423" s="4" t="n"/>
-      <c r="L423" s="4" t="n"/>
-      <c r="M423" s="4" t="n"/>
+      <c r="L423" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M423" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N423" s="4" t="n"/>
       <c r="O423" s="4" t="n"/>
     </row>
@@ -11540,8 +11702,16 @@
         </is>
       </c>
       <c r="K424" s="4" t="n"/>
-      <c r="L424" s="4" t="n"/>
-      <c r="M424" s="4" t="n"/>
+      <c r="L424" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M424" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N424" s="4" t="n"/>
       <c r="O424" s="4" t="n"/>
     </row>
@@ -11573,8 +11743,16 @@
         </is>
       </c>
       <c r="K425" s="4" t="n"/>
-      <c r="L425" s="4" t="n"/>
-      <c r="M425" s="4" t="n"/>
+      <c r="L425" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M425" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N425" s="4" t="n"/>
       <c r="O425" s="4" t="n"/>
     </row>
@@ -11606,8 +11784,16 @@
         </is>
       </c>
       <c r="K426" s="4" t="n"/>
-      <c r="L426" s="4" t="n"/>
-      <c r="M426" s="4" t="n"/>
+      <c r="L426" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="M426" s="5" t="inlineStr">
+        <is>
+          <t>Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="N426" s="4" t="n"/>
       <c r="O426" s="4" t="n"/>
     </row>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8938,7 +8938,11 @@
         </is>
       </c>
       <c r="K338" s="4" t="n"/>
-      <c r="L338" s="4" t="n"/>
+      <c r="L338" s="5" t="inlineStr">
+        <is>
+          <t>Socials - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="M338" s="4" t="n"/>
       <c r="N338" s="4" t="n"/>
       <c r="O338" s="5" t="inlineStr">
@@ -9032,11 +9036,7 @@
         </is>
       </c>
       <c r="K340" s="4" t="n"/>
-      <c r="L340" s="5" t="inlineStr">
-        <is>
-          <t>Socials - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="L340" s="4" t="n"/>
       <c r="M340" s="4" t="n"/>
       <c r="N340" s="8" t="inlineStr">
         <is>
@@ -9073,7 +9073,11 @@
         </is>
       </c>
       <c r="K341" s="4" t="n"/>
-      <c r="L341" s="4" t="n"/>
+      <c r="L341" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Black History 2026</t>
+        </is>
+      </c>
       <c r="M341" s="4" t="n"/>
       <c r="N341" s="8" t="inlineStr">
         <is>
@@ -9114,7 +9118,11 @@
         </is>
       </c>
       <c r="K342" s="4" t="n"/>
-      <c r="L342" s="4" t="n"/>
+      <c r="L342" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Black History 2026</t>
+        </is>
+      </c>
       <c r="M342" s="4" t="n"/>
       <c r="N342" s="8" t="inlineStr">
         <is>
@@ -9139,7 +9147,11 @@
       <c r="I343" s="7" t="n"/>
       <c r="J343" s="7" t="n"/>
       <c r="K343" s="7" t="n"/>
-      <c r="L343" s="7" t="n"/>
+      <c r="L343" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Black History 2026</t>
+        </is>
+      </c>
       <c r="M343" s="7" t="n"/>
       <c r="N343" s="7" t="n"/>
       <c r="O343" s="7" t="n"/>
@@ -9160,7 +9172,11 @@
       <c r="I344" s="7" t="n"/>
       <c r="J344" s="7" t="n"/>
       <c r="K344" s="7" t="n"/>
-      <c r="L344" s="7" t="n"/>
+      <c r="L344" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Black History 2026</t>
+        </is>
+      </c>
       <c r="M344" s="7" t="n"/>
       <c r="N344" s="7" t="n"/>
       <c r="O344" s="7" t="n"/>
@@ -9291,11 +9307,7 @@
           <t>SOCIAL MEDIA CONFERENCE</t>
         </is>
       </c>
-      <c r="L347" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Black History 2026</t>
-        </is>
-      </c>
+      <c r="L347" s="4" t="n"/>
       <c r="M347" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -9340,11 +9352,7 @@
         </is>
       </c>
       <c r="K348" s="4" t="n"/>
-      <c r="L348" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Black History 2026</t>
-        </is>
-      </c>
+      <c r="L348" s="4" t="n"/>
       <c r="M348" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -9389,11 +9397,7 @@
         </is>
       </c>
       <c r="K349" s="4" t="n"/>
-      <c r="L349" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Black History 2026</t>
-        </is>
-      </c>
+      <c r="L349" s="4" t="n"/>
       <c r="M349" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9488,11 +9488,7 @@
         </is>
       </c>
       <c r="K352" s="4" t="n"/>
-      <c r="L352" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Black History 2026</t>
-        </is>
-      </c>
+      <c r="L352" s="4" t="n"/>
       <c r="M352" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9619,15 +9619,32 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K356" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L356" s="4" t="n"/>
-      <c r="M356" s="4" t="n"/>
-      <c r="N356" s="4" t="n"/>
-      <c r="O356" s="4" t="n"/>
+      <c r="K356" s="5" t="inlineStr">
+        <is>
+          <t>Film - Chepstow
+A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="L356" s="5" t="inlineStr">
+        <is>
+          <t>Film - Chepstow</t>
+        </is>
+      </c>
+      <c r="M356" s="5" t="inlineStr">
+        <is>
+          <t>Film - Chepstow</t>
+        </is>
+      </c>
+      <c r="N356" s="5" t="inlineStr">
+        <is>
+          <t>Film - Chepstow</t>
+        </is>
+      </c>
+      <c r="O356" s="5" t="inlineStr">
+        <is>
+          <t>Film - Chepstow</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="6" t="inlineStr">
@@ -9648,11 +9665,31 @@
       <c r="H357" s="7" t="n"/>
       <c r="I357" s="7" t="n"/>
       <c r="J357" s="7" t="n"/>
-      <c r="K357" s="7" t="n"/>
-      <c r="L357" s="7" t="n"/>
-      <c r="M357" s="7" t="n"/>
-      <c r="N357" s="7" t="n"/>
-      <c r="O357" s="7" t="n"/>
+      <c r="K357" s="5" t="inlineStr">
+        <is>
+          <t>Film - Chepstow</t>
+        </is>
+      </c>
+      <c r="L357" s="5" t="inlineStr">
+        <is>
+          <t>Film - Chepstow</t>
+        </is>
+      </c>
+      <c r="M357" s="5" t="inlineStr">
+        <is>
+          <t>Film - Chepstow</t>
+        </is>
+      </c>
+      <c r="N357" s="5" t="inlineStr">
+        <is>
+          <t>Film - Chepstow</t>
+        </is>
+      </c>
+      <c r="O357" s="5" t="inlineStr">
+        <is>
+          <t>Film - Chepstow</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="6" t="inlineStr">
@@ -9673,11 +9710,31 @@
       <c r="H358" s="7" t="n"/>
       <c r="I358" s="7" t="n"/>
       <c r="J358" s="7" t="n"/>
-      <c r="K358" s="7" t="n"/>
-      <c r="L358" s="7" t="n"/>
-      <c r="M358" s="7" t="n"/>
-      <c r="N358" s="7" t="n"/>
-      <c r="O358" s="7" t="n"/>
+      <c r="K358" s="5" t="inlineStr">
+        <is>
+          <t>Film - Chepstow</t>
+        </is>
+      </c>
+      <c r="L358" s="5" t="inlineStr">
+        <is>
+          <t>Film - Chepstow</t>
+        </is>
+      </c>
+      <c r="M358" s="5" t="inlineStr">
+        <is>
+          <t>Film - Chepstow</t>
+        </is>
+      </c>
+      <c r="N358" s="5" t="inlineStr">
+        <is>
+          <t>Film - Chepstow</t>
+        </is>
+      </c>
+      <c r="O358" s="5" t="inlineStr">
+        <is>
+          <t>Film - Chepstow</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="3" t="inlineStr">
@@ -9694,7 +9751,7 @@
       </c>
       <c r="E359" s="5" t="inlineStr">
         <is>
-          <t>Edit - Mabli a Ceff Ceff</t>
+          <t>Edit - Chepstow</t>
         </is>
       </c>
       <c r="F359" s="10" t="inlineStr">
@@ -9735,7 +9792,7 @@
       </c>
       <c r="E360" s="5" t="inlineStr">
         <is>
-          <t>Edit - Mabli a Ceff Ceff</t>
+          <t>Edit - Chepstow</t>
         </is>
       </c>
       <c r="F360" s="10" t="inlineStr">
@@ -9776,7 +9833,7 @@
       </c>
       <c r="E361" s="5" t="inlineStr">
         <is>
-          <t>Edit - Mabli a Ceff Ceff</t>
+          <t>Edit - Chepstow</t>
         </is>
       </c>
       <c r="F361" s="10" t="inlineStr">
@@ -9817,7 +9874,7 @@
       </c>
       <c r="E362" s="5" t="inlineStr">
         <is>
-          <t>Edit - Mabli a Ceff Ceff</t>
+          <t>Edit - Chepstow</t>
         </is>
       </c>
       <c r="F362" s="10" t="inlineStr">
@@ -9838,7 +9895,11 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L362" s="4" t="n"/>
+      <c r="L362" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Chepstow</t>
+        </is>
+      </c>
       <c r="M362" s="4" t="n"/>
       <c r="N362" s="4" t="n"/>
       <c r="O362" s="4" t="n"/>
@@ -9854,7 +9915,7 @@
       <c r="D363" s="4" t="n"/>
       <c r="E363" s="5" t="inlineStr">
         <is>
-          <t>Edit - Mabli a Ceff Ceff</t>
+          <t>Edit - Chepstow</t>
         </is>
       </c>
       <c r="F363" s="10" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9062,7 +9062,7 @@
           <t>Prep Sw Ni</t>
         </is>
       </c>
-      <c r="E341" s="4" t="n"/>
+      <c r="E341" s="5" t="inlineStr"/>
       <c r="F341" s="4" t="n"/>
       <c r="G341" s="4" t="n"/>
       <c r="H341" s="4" t="n"/>
@@ -9936,7 +9936,11 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L363" s="4" t="n"/>
+      <c r="L363" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Chepstow</t>
+        </is>
+      </c>
       <c r="M363" s="4" t="n"/>
       <c r="N363" s="4" t="n"/>
       <c r="O363" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9062,7 +9062,11 @@
           <t>Prep Sw Ni</t>
         </is>
       </c>
-      <c r="E341" s="5" t="inlineStr"/>
+      <c r="E341" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="F341" s="4" t="n"/>
       <c r="G341" s="4" t="n"/>
       <c r="H341" s="4" t="n"/>
@@ -9099,7 +9103,11 @@
           <t>Prep Sw Ni</t>
         </is>
       </c>
-      <c r="E342" s="4" t="n"/>
+      <c r="E342" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="F342" s="4" t="n"/>
       <c r="G342" s="4" t="n"/>
       <c r="H342" s="5" t="inlineStr">
@@ -9194,7 +9202,11 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E345" s="4" t="n"/>
+      <c r="E345" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="F345" s="4" t="n"/>
       <c r="G345" s="5" t="inlineStr">
         <is>
@@ -9239,7 +9251,11 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E346" s="4" t="n"/>
+      <c r="E346" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="F346" s="4" t="n"/>
       <c r="G346" s="5" t="inlineStr">
         <is>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -10032,7 +10032,11 @@
       </c>
       <c r="G366" s="4" t="n"/>
       <c r="H366" s="4" t="n"/>
-      <c r="I366" s="4" t="n"/>
+      <c r="I366" s="9" t="inlineStr">
+        <is>
+          <t>Delivery - Chepstow</t>
+        </is>
+      </c>
       <c r="J366" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
@@ -11318,7 +11322,11 @@
       <c r="G409" s="4" t="n"/>
       <c r="H409" s="4" t="n"/>
       <c r="I409" s="4" t="n"/>
-      <c r="J409" s="4" t="n"/>
+      <c r="J409" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K409" s="4" t="n"/>
       <c r="L409" s="5" t="inlineStr">
         <is>
@@ -11777,9 +11785,9 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="J424" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
+      <c r="J424" s="5" t="inlineStr">
+        <is>
+          <t>Dub - LGBTQ+</t>
         </is>
       </c>
       <c r="K424" s="4" t="n"/>
@@ -11818,9 +11826,9 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="J425" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
+      <c r="J425" s="5" t="inlineStr">
+        <is>
+          <t>Dub - LGBTQ+</t>
         </is>
       </c>
       <c r="K425" s="4" t="n"/>
@@ -11859,9 +11867,9 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="J426" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
+      <c r="J426" s="5" t="inlineStr">
+        <is>
+          <t>Dub - LGBTQ+</t>
         </is>
       </c>
       <c r="K426" s="4" t="n"/>
@@ -12307,11 +12315,7 @@
       <c r="G446" s="4" t="n"/>
       <c r="H446" s="4" t="n"/>
       <c r="I446" s="4" t="n"/>
-      <c r="J446" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J446" s="4" t="n"/>
       <c r="K446" s="4" t="n"/>
       <c r="L446" s="4" t="n"/>
       <c r="M446" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9552,32 +9552,50 @@
           <t>Wed 07 Oct 2026</t>
         </is>
       </c>
-      <c r="B354" s="4" t="n"/>
+      <c r="B354" s="5" t="inlineStr">
+        <is>
+          <t>Film - BBC Music Show</t>
+        </is>
+      </c>
       <c r="C354" s="4" t="n"/>
       <c r="D354" s="4" t="n"/>
       <c r="E354" s="5" t="inlineStr">
         <is>
-          <t>Edit - Sŵ Ni</t>
+          <t>Film - BBC Music Show
+Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="F354" s="4" t="n"/>
       <c r="G354" s="4" t="n"/>
       <c r="H354" s="4" t="n"/>
-      <c r="I354" s="4" t="n"/>
+      <c r="I354" s="5" t="inlineStr">
+        <is>
+          <t>Film - BBC Music Show</t>
+        </is>
+      </c>
       <c r="J354" s="5" t="inlineStr">
         <is>
           <t>Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="K354" s="4" t="n"/>
-      <c r="L354" s="4" t="n"/>
-      <c r="M354" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
+      <c r="L354" s="5" t="inlineStr">
+        <is>
+          <t>Film - BBC Music Show</t>
+        </is>
+      </c>
+      <c r="M354" s="5" t="inlineStr">
+        <is>
+          <t>Film - BBC Music Show
+A/L - Annual Leave</t>
         </is>
       </c>
       <c r="N354" s="4" t="n"/>
-      <c r="O354" s="4" t="n"/>
+      <c r="O354" s="5" t="inlineStr">
+        <is>
+          <t>Film - BBC Music Show</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="3" t="inlineStr">
@@ -9585,18 +9603,27 @@
           <t>Thu 08 Oct 2026</t>
         </is>
       </c>
-      <c r="B355" s="4" t="n"/>
+      <c r="B355" s="5" t="inlineStr">
+        <is>
+          <t>Film - BBC Music Show</t>
+        </is>
+      </c>
       <c r="C355" s="4" t="n"/>
       <c r="D355" s="4" t="n"/>
       <c r="E355" s="5" t="inlineStr">
         <is>
-          <t>Edit - Sŵ Ni</t>
+          <t>Film - BBC Music Show
+Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="F355" s="4" t="n"/>
       <c r="G355" s="4" t="n"/>
       <c r="H355" s="4" t="n"/>
-      <c r="I355" s="4" t="n"/>
+      <c r="I355" s="5" t="inlineStr">
+        <is>
+          <t>Film - BBC Music Show</t>
+        </is>
+      </c>
       <c r="J355" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
@@ -9607,10 +9634,22 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L355" s="4" t="n"/>
-      <c r="M355" s="4" t="n"/>
+      <c r="L355" s="5" t="inlineStr">
+        <is>
+          <t>Film - BBC Music Show</t>
+        </is>
+      </c>
+      <c r="M355" s="5" t="inlineStr">
+        <is>
+          <t>Film - BBC Music Show</t>
+        </is>
+      </c>
       <c r="N355" s="4" t="n"/>
-      <c r="O355" s="4" t="n"/>
+      <c r="O355" s="5" t="inlineStr">
+        <is>
+          <t>Film - BBC Music Show</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="3" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9155,11 +9155,7 @@
       <c r="I343" s="7" t="n"/>
       <c r="J343" s="7" t="n"/>
       <c r="K343" s="7" t="n"/>
-      <c r="L343" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Black History 2026</t>
-        </is>
-      </c>
+      <c r="L343" s="7" t="n"/>
       <c r="M343" s="7" t="n"/>
       <c r="N343" s="7" t="n"/>
       <c r="O343" s="7" t="n"/>
@@ -9180,11 +9176,7 @@
       <c r="I344" s="7" t="n"/>
       <c r="J344" s="7" t="n"/>
       <c r="K344" s="7" t="n"/>
-      <c r="L344" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Black History 2026</t>
-        </is>
-      </c>
+      <c r="L344" s="7" t="n"/>
       <c r="M344" s="7" t="n"/>
       <c r="N344" s="7" t="n"/>
       <c r="O344" s="7" t="n"/>
@@ -9323,7 +9315,11 @@
           <t>SOCIAL MEDIA CONFERENCE</t>
         </is>
       </c>
-      <c r="L347" s="4" t="n"/>
+      <c r="L347" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Black History 2026</t>
+        </is>
+      </c>
       <c r="M347" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -9368,7 +9364,11 @@
         </is>
       </c>
       <c r="K348" s="4" t="n"/>
-      <c r="L348" s="4" t="n"/>
+      <c r="L348" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Black History 2026</t>
+        </is>
+      </c>
       <c r="M348" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -10773,32 +10773,79 @@
           <t>Fri 13 Nov 2026</t>
         </is>
       </c>
-      <c r="B391" s="4" t="n"/>
-      <c r="C391" s="4" t="n"/>
-      <c r="D391" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
+      <c r="B391" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="C391" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="D391" s="5" t="inlineStr">
+        <is>
+          <t>Film
+A/L - Annual Leave</t>
         </is>
       </c>
       <c r="E391" s="5" t="inlineStr">
         <is>
-          <t>Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
-      <c r="F391" s="4" t="n"/>
-      <c r="G391" s="4" t="n"/>
-      <c r="H391" s="4" t="n"/>
-      <c r="I391" s="4" t="n"/>
-      <c r="J391" s="11" t="inlineStr">
-        <is>
-          <t>Online Edit - Sŵ Ni</t>
-        </is>
-      </c>
-      <c r="K391" s="4" t="n"/>
-      <c r="L391" s="4" t="n"/>
-      <c r="M391" s="4" t="n"/>
-      <c r="N391" s="4" t="n"/>
-      <c r="O391" s="4" t="n"/>
+          <t>Film
+Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
+      <c r="F391" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="G391" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="H391" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="I391" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="J391" s="5" t="inlineStr">
+        <is>
+          <t>Film
+Online Edit - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K391" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="L391" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="M391" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="N391" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="O391" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="6" t="inlineStr">
@@ -10806,20 +10853,76 @@
           <t>Sat 14 Nov 2026</t>
         </is>
       </c>
-      <c r="B392" s="7" t="n"/>
-      <c r="C392" s="7" t="n"/>
-      <c r="D392" s="7" t="n"/>
-      <c r="E392" s="7" t="n"/>
-      <c r="F392" s="7" t="n"/>
-      <c r="G392" s="7" t="n"/>
-      <c r="H392" s="7" t="n"/>
-      <c r="I392" s="7" t="n"/>
-      <c r="J392" s="7" t="n"/>
-      <c r="K392" s="7" t="n"/>
-      <c r="L392" s="7" t="n"/>
-      <c r="M392" s="7" t="n"/>
-      <c r="N392" s="7" t="n"/>
-      <c r="O392" s="7" t="n"/>
+      <c r="B392" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="C392" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="D392" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="E392" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="F392" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="G392" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="H392" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="I392" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="J392" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="K392" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="L392" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="M392" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="N392" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="O392" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="6" t="inlineStr">
@@ -10827,20 +10930,76 @@
           <t>Sun 15 Nov 2026</t>
         </is>
       </c>
-      <c r="B393" s="7" t="n"/>
-      <c r="C393" s="7" t="n"/>
-      <c r="D393" s="7" t="n"/>
-      <c r="E393" s="7" t="n"/>
-      <c r="F393" s="7" t="n"/>
-      <c r="G393" s="7" t="n"/>
-      <c r="H393" s="7" t="n"/>
-      <c r="I393" s="7" t="n"/>
-      <c r="J393" s="7" t="n"/>
-      <c r="K393" s="7" t="n"/>
-      <c r="L393" s="7" t="n"/>
-      <c r="M393" s="7" t="n"/>
-      <c r="N393" s="7" t="n"/>
-      <c r="O393" s="7" t="n"/>
+      <c r="B393" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="C393" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="D393" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="E393" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="F393" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="G393" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="H393" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="I393" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="J393" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="K393" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="L393" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="M393" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="N393" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="O393" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="3" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8759,7 +8759,7 @@
       <c r="K333" s="4" t="n"/>
       <c r="L333" s="5" t="inlineStr">
         <is>
-          <t>Rhwym Galon</t>
+          <t>Rhedeg Rhacs</t>
         </is>
       </c>
       <c r="M333" s="4" t="n"/>
@@ -8800,7 +8800,7 @@
       <c r="K334" s="4" t="n"/>
       <c r="L334" s="5" t="inlineStr">
         <is>
-          <t>Rhwym Galon</t>
+          <t>Socials - Rookie Teachers</t>
         </is>
       </c>
       <c r="M334" s="4" t="n"/>
@@ -8853,7 +8853,7 @@
       <c r="K335" s="4" t="n"/>
       <c r="L335" s="5" t="inlineStr">
         <is>
-          <t>Rhwym Galon</t>
+          <t>Socials - Rookie Teachers</t>
         </is>
       </c>
       <c r="M335" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9492,7 +9492,11 @@
       </c>
       <c r="F352" s="4" t="n"/>
       <c r="G352" s="4" t="n"/>
-      <c r="H352" s="4" t="n"/>
+      <c r="H352" s="5" t="inlineStr">
+        <is>
+          <t>Film - Chepstow</t>
+        </is>
+      </c>
       <c r="I352" s="9" t="inlineStr">
         <is>
           <t>Delivery - Black History 2026</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8919,11 +8919,7 @@
           <t>Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="E338" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Welsh Music Prize</t>
-        </is>
-      </c>
+      <c r="E338" s="4" t="n"/>
       <c r="F338" s="4" t="n"/>
       <c r="G338" s="5" t="inlineStr">
         <is>
@@ -9062,11 +9058,7 @@
           <t>Prep Sw Ni</t>
         </is>
       </c>
-      <c r="E341" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="E341" s="4" t="n"/>
       <c r="F341" s="4" t="n"/>
       <c r="G341" s="4" t="n"/>
       <c r="H341" s="4" t="n"/>
@@ -9105,7 +9097,7 @@
       </c>
       <c r="E342" s="5" t="inlineStr">
         <is>
-          <t>Edit - Mabli a Ceff Ceff</t>
+          <t>Edit - Welsh Music Prize</t>
         </is>
       </c>
       <c r="F342" s="4" t="n"/>
@@ -9194,11 +9186,7 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E345" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="E345" s="4" t="n"/>
       <c r="F345" s="4" t="n"/>
       <c r="G345" s="5" t="inlineStr">
         <is>
@@ -9243,11 +9231,7 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E346" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="E346" s="4" t="n"/>
       <c r="F346" s="4" t="n"/>
       <c r="G346" s="5" t="inlineStr">
         <is>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8902,7 +8902,11 @@
       <c r="J337" s="7" t="n"/>
       <c r="K337" s="7" t="n"/>
       <c r="L337" s="7" t="n"/>
-      <c r="M337" s="7" t="n"/>
+      <c r="M337" s="5" t="inlineStr">
+        <is>
+          <t>Film - Black History 2026</t>
+        </is>
+      </c>
       <c r="N337" s="7" t="n"/>
       <c r="O337" s="7" t="n"/>
     </row>
@@ -9074,7 +9078,11 @@
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="M341" s="4" t="n"/>
+      <c r="M341" s="5" t="inlineStr">
+        <is>
+          <t>Film - Black History 2026</t>
+        </is>
+      </c>
       <c r="N341" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8763,7 +8763,11 @@
         </is>
       </c>
       <c r="M333" s="4" t="n"/>
-      <c r="N333" s="4" t="n"/>
+      <c r="N333" s="5" t="inlineStr">
+        <is>
+          <t>Sick</t>
+        </is>
+      </c>
       <c r="O333" s="4" t="n"/>
     </row>
     <row r="334">
@@ -8920,7 +8924,7 @@
       <c r="C338" s="4" t="n"/>
       <c r="D338" s="5" t="inlineStr">
         <is>
-          <t>Edit - Mabli a Ceff Ceff</t>
+          <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="E338" s="4" t="n"/>
@@ -8961,7 +8965,7 @@
       <c r="C339" s="4" t="n"/>
       <c r="D339" s="5" t="inlineStr">
         <is>
-          <t>Edit - Mabli a Ceff Ceff</t>
+          <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="E339" s="5" t="inlineStr">
@@ -9010,7 +9014,7 @@
       <c r="C340" s="4" t="n"/>
       <c r="D340" s="5" t="inlineStr">
         <is>
-          <t>Edit - Mabli a Ceff Ceff</t>
+          <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="E340" s="5" t="inlineStr">
@@ -9484,11 +9488,7 @@
       </c>
       <c r="F352" s="4" t="n"/>
       <c r="G352" s="4" t="n"/>
-      <c r="H352" s="5" t="inlineStr">
-        <is>
-          <t>Film - Chepstow</t>
-        </is>
-      </c>
+      <c r="H352" s="4" t="n"/>
       <c r="I352" s="9" t="inlineStr">
         <is>
           <t>Delivery - Black History 2026</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -11113,11 +11113,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E397" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="E397" s="4" t="n"/>
       <c r="F397" s="4" t="n"/>
       <c r="G397" s="4" t="n"/>
       <c r="H397" s="4" t="n"/>
@@ -11143,11 +11139,7 @@
       <c r="B398" s="4" t="n"/>
       <c r="C398" s="4" t="n"/>
       <c r="D398" s="4" t="n"/>
-      <c r="E398" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="E398" s="4" t="n"/>
       <c r="F398" s="4" t="n"/>
       <c r="G398" s="9" t="inlineStr">
         <is>
@@ -11577,7 +11569,11 @@
       <c r="B411" s="4" t="n"/>
       <c r="C411" s="4" t="n"/>
       <c r="D411" s="4" t="n"/>
-      <c r="E411" s="4" t="n"/>
+      <c r="E411" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F411" s="4" t="n"/>
       <c r="G411" s="4" t="n"/>
       <c r="H411" s="4" t="n"/>
@@ -11610,7 +11606,11 @@
       <c r="B412" s="4" t="n"/>
       <c r="C412" s="4" t="n"/>
       <c r="D412" s="4" t="n"/>
-      <c r="E412" s="4" t="n"/>
+      <c r="E412" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F412" s="4" t="n"/>
       <c r="G412" s="4" t="n"/>
       <c r="H412" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -10354,11 +10354,7 @@
       <c r="G376" s="4" t="n"/>
       <c r="H376" s="4" t="n"/>
       <c r="I376" s="4" t="n"/>
-      <c r="J376" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J376" s="4" t="n"/>
       <c r="K376" s="4" t="n"/>
       <c r="L376" s="4" t="n"/>
       <c r="M376" s="4" t="n"/>
@@ -10383,11 +10379,7 @@
       <c r="G377" s="4" t="n"/>
       <c r="H377" s="4" t="n"/>
       <c r="I377" s="4" t="n"/>
-      <c r="J377" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J377" s="4" t="n"/>
       <c r="K377" s="4" t="n"/>
       <c r="L377" s="4" t="n"/>
       <c r="M377" s="4" t="n"/>
@@ -10458,11 +10450,7 @@
       <c r="G380" s="4" t="n"/>
       <c r="H380" s="4" t="n"/>
       <c r="I380" s="4" t="n"/>
-      <c r="J380" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J380" s="4" t="n"/>
       <c r="K380" s="4" t="n"/>
       <c r="L380" s="4" t="n"/>
       <c r="M380" s="4" t="n"/>
@@ -10487,11 +10475,7 @@
       <c r="G381" s="4" t="n"/>
       <c r="H381" s="4" t="n"/>
       <c r="I381" s="4" t="n"/>
-      <c r="J381" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J381" s="4" t="n"/>
       <c r="K381" s="4" t="n"/>
       <c r="L381" s="4" t="n"/>
       <c r="M381" s="4" t="n"/>
@@ -10516,11 +10500,7 @@
       <c r="G382" s="4" t="n"/>
       <c r="H382" s="4" t="n"/>
       <c r="I382" s="4" t="n"/>
-      <c r="J382" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J382" s="4" t="n"/>
       <c r="K382" s="4" t="n"/>
       <c r="L382" s="4" t="n"/>
       <c r="M382" s="4" t="n"/>
@@ -10545,11 +10525,7 @@
       <c r="G383" s="4" t="n"/>
       <c r="H383" s="4" t="n"/>
       <c r="I383" s="4" t="n"/>
-      <c r="J383" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J383" s="4" t="n"/>
       <c r="K383" s="4" t="n"/>
       <c r="L383" s="4" t="n"/>
       <c r="M383" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9353,7 +9353,11 @@
         </is>
       </c>
       <c r="H348" s="4" t="n"/>
-      <c r="I348" s="4" t="n"/>
+      <c r="I348" s="5" t="inlineStr">
+        <is>
+          <t>Dub - Black History 2026</t>
+        </is>
+      </c>
       <c r="J348" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
@@ -9402,7 +9406,11 @@
         </is>
       </c>
       <c r="H349" s="4" t="n"/>
-      <c r="I349" s="4" t="n"/>
+      <c r="I349" s="5" t="inlineStr">
+        <is>
+          <t>Dub - Black History 2026</t>
+        </is>
+      </c>
       <c r="J349" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8795,7 +8795,11 @@
         </is>
       </c>
       <c r="H334" s="4" t="n"/>
-      <c r="I334" s="4" t="n"/>
+      <c r="I334" s="5" t="inlineStr">
+        <is>
+          <t>Dub - Rookie Teachers</t>
+        </is>
+      </c>
       <c r="J334" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
@@ -8844,9 +8848,10 @@
         </is>
       </c>
       <c r="H335" s="4" t="n"/>
-      <c r="I335" s="9" t="inlineStr">
-        <is>
-          <t>Delivery - Sŵ Ni</t>
+      <c r="I335" s="5" t="inlineStr">
+        <is>
+          <t>Dub - Rookie Teachers
+Delivery - Sŵ Ni</t>
         </is>
       </c>
       <c r="J335" s="5" t="inlineStr">
@@ -8935,7 +8940,11 @@
         </is>
       </c>
       <c r="H338" s="4" t="n"/>
-      <c r="I338" s="4" t="n"/>
+      <c r="I338" s="5" t="inlineStr">
+        <is>
+          <t>Dub - Rookie Teachers</t>
+        </is>
+      </c>
       <c r="J338" s="5" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8993,7 +8993,11 @@
           <t>Film - Linda Wilson</t>
         </is>
       </c>
-      <c r="I339" s="4" t="n"/>
+      <c r="I339" s="5" t="inlineStr">
+        <is>
+          <t>Dub - Rookie Teachers</t>
+        </is>
+      </c>
       <c r="J339" s="5" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>
@@ -9042,7 +9046,11 @@
           <t>Ffilmio Mabli - AM</t>
         </is>
       </c>
-      <c r="I340" s="4" t="n"/>
+      <c r="I340" s="5" t="inlineStr">
+        <is>
+          <t>Dub - Rookie Teachers</t>
+        </is>
+      </c>
       <c r="J340" s="5" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9087,7 +9087,11 @@
       <c r="F341" s="4" t="n"/>
       <c r="G341" s="4" t="n"/>
       <c r="H341" s="4" t="n"/>
-      <c r="I341" s="4" t="n"/>
+      <c r="I341" s="5" t="inlineStr">
+        <is>
+          <t>Prep AS11</t>
+        </is>
+      </c>
       <c r="J341" s="5" t="inlineStr">
         <is>
           <t>Prep Sw Ni MP</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9089,7 +9089,7 @@
       <c r="H341" s="4" t="n"/>
       <c r="I341" s="5" t="inlineStr">
         <is>
-          <t>Prep AS11</t>
+          <t>Sŵ Ni</t>
         </is>
       </c>
       <c r="J341" s="5" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8797,7 +8797,8 @@
       <c r="H334" s="4" t="n"/>
       <c r="I334" s="5" t="inlineStr">
         <is>
-          <t>Dub - Rookie Teachers</t>
+          <t>Sŵ Ni
+Dub - Rookie Teachers</t>
         </is>
       </c>
       <c r="J334" s="5" t="inlineStr">
@@ -9087,11 +9088,7 @@
       <c r="F341" s="4" t="n"/>
       <c r="G341" s="4" t="n"/>
       <c r="H341" s="4" t="n"/>
-      <c r="I341" s="5" t="inlineStr">
-        <is>
-          <t>Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="I341" s="4" t="n"/>
       <c r="J341" s="5" t="inlineStr">
         <is>
           <t>Prep Sw Ni MP</t>
@@ -9427,9 +9424,10 @@
         </is>
       </c>
       <c r="H349" s="4" t="n"/>
-      <c r="I349" s="5" t="inlineStr">
-        <is>
-          <t>Dub - Black History 2026</t>
+      <c r="I349" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Black History 2026
+Dub - Black History 2026</t>
         </is>
       </c>
       <c r="J349" s="5" t="inlineStr">
@@ -9750,26 +9748,18 @@
           <t>Film - Chepstow</t>
         </is>
       </c>
-      <c r="L357" s="5" t="inlineStr">
+      <c r="L357" s="7" t="n"/>
+      <c r="M357" s="5" t="inlineStr">
         <is>
           <t>Film - Chepstow</t>
         </is>
       </c>
-      <c r="M357" s="5" t="inlineStr">
+      <c r="N357" s="5" t="inlineStr">
         <is>
           <t>Film - Chepstow</t>
         </is>
       </c>
-      <c r="N357" s="5" t="inlineStr">
-        <is>
-          <t>Film - Chepstow</t>
-        </is>
-      </c>
-      <c r="O357" s="5" t="inlineStr">
-        <is>
-          <t>Film - Chepstow</t>
-        </is>
-      </c>
+      <c r="O357" s="7" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="6" t="inlineStr">
@@ -9795,26 +9785,18 @@
           <t>Film - Chepstow</t>
         </is>
       </c>
-      <c r="L358" s="5" t="inlineStr">
+      <c r="L358" s="7" t="n"/>
+      <c r="M358" s="5" t="inlineStr">
         <is>
           <t>Film - Chepstow</t>
         </is>
       </c>
-      <c r="M358" s="5" t="inlineStr">
+      <c r="N358" s="5" t="inlineStr">
         <is>
           <t>Film - Chepstow</t>
         </is>
       </c>
-      <c r="N358" s="5" t="inlineStr">
-        <is>
-          <t>Film - Chepstow</t>
-        </is>
-      </c>
-      <c r="O358" s="5" t="inlineStr">
-        <is>
-          <t>Film - Chepstow</t>
-        </is>
-      </c>
+      <c r="O358" s="7" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="3" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -12417,11 +12417,7 @@
       <c r="G443" s="4" t="n"/>
       <c r="H443" s="4" t="n"/>
       <c r="I443" s="4" t="n"/>
-      <c r="J443" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J443" s="4" t="n"/>
       <c r="K443" s="4" t="n"/>
       <c r="L443" s="4" t="n"/>
       <c r="M443" s="4" t="n"/>
@@ -12442,11 +12438,7 @@
       <c r="G444" s="4" t="n"/>
       <c r="H444" s="4" t="n"/>
       <c r="I444" s="4" t="n"/>
-      <c r="J444" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J444" s="4" t="n"/>
       <c r="K444" s="4" t="n"/>
       <c r="L444" s="4" t="n"/>
       <c r="M444" s="4" t="n"/>
@@ -12471,11 +12463,7 @@
           <t>Delivery - LGBTQ+</t>
         </is>
       </c>
-      <c r="J445" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J445" s="4" t="n"/>
       <c r="K445" s="4" t="n"/>
       <c r="L445" s="4" t="n"/>
       <c r="M445" s="4" t="n"/>
@@ -12642,11 +12630,7 @@
       <c r="G452" s="4" t="n"/>
       <c r="H452" s="4" t="n"/>
       <c r="I452" s="4" t="n"/>
-      <c r="J452" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J452" s="4" t="n"/>
       <c r="K452" s="4" t="n"/>
       <c r="L452" s="4" t="n"/>
       <c r="M452" s="4" t="n"/>
@@ -12667,11 +12651,7 @@
       <c r="G453" s="4" t="n"/>
       <c r="H453" s="4" t="n"/>
       <c r="I453" s="4" t="n"/>
-      <c r="J453" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J453" s="4" t="n"/>
       <c r="K453" s="4" t="n"/>
       <c r="L453" s="4" t="n"/>
       <c r="M453" s="4" t="n"/>
@@ -12696,11 +12676,7 @@
           <t>Delivery - Deep Watch</t>
         </is>
       </c>
-      <c r="J454" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J454" s="4" t="n"/>
       <c r="K454" s="4" t="n"/>
       <c r="L454" s="4" t="n"/>
       <c r="M454" s="4" t="n"/>
@@ -13193,7 +13169,11 @@
       <c r="G475" s="4" t="n"/>
       <c r="H475" s="4" t="n"/>
       <c r="I475" s="4" t="n"/>
-      <c r="J475" s="4" t="n"/>
+      <c r="J475" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K475" s="4" t="n"/>
       <c r="L475" s="4" t="n"/>
       <c r="M475" s="4" t="n"/>
@@ -13260,7 +13240,11 @@
       </c>
       <c r="H478" s="4" t="n"/>
       <c r="I478" s="4" t="n"/>
-      <c r="J478" s="4" t="n"/>
+      <c r="J478" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K478" s="4" t="n"/>
       <c r="L478" s="11" t="inlineStr">
         <is>
@@ -13293,7 +13277,11 @@
       </c>
       <c r="H479" s="4" t="n"/>
       <c r="I479" s="4" t="n"/>
-      <c r="J479" s="4" t="n"/>
+      <c r="J479" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K479" s="4" t="n"/>
       <c r="L479" s="11" t="inlineStr">
         <is>
@@ -13326,7 +13314,11 @@
       </c>
       <c r="H480" s="4" t="n"/>
       <c r="I480" s="4" t="n"/>
-      <c r="J480" s="4" t="n"/>
+      <c r="J480" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K480" s="4" t="n"/>
       <c r="L480" s="11" t="inlineStr">
         <is>
@@ -13359,7 +13351,11 @@
       </c>
       <c r="H481" s="4" t="n"/>
       <c r="I481" s="4" t="n"/>
-      <c r="J481" s="4" t="n"/>
+      <c r="J481" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K481" s="4" t="n"/>
       <c r="L481" s="11" t="inlineStr">
         <is>
@@ -13396,7 +13392,11 @@
       </c>
       <c r="H482" s="4" t="n"/>
       <c r="I482" s="4" t="n"/>
-      <c r="J482" s="4" t="n"/>
+      <c r="J482" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K482" s="4" t="n"/>
       <c r="L482" s="11" t="inlineStr">
         <is>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8952,11 +8952,7 @@
         </is>
       </c>
       <c r="K338" s="4" t="n"/>
-      <c r="L338" s="5" t="inlineStr">
-        <is>
-          <t>Socials - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="L338" s="4" t="n"/>
       <c r="M338" s="4" t="n"/>
       <c r="N338" s="4" t="n"/>
       <c r="O338" s="5" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -11330,11 +11330,7 @@
       <c r="G404" s="4" t="n"/>
       <c r="H404" s="4" t="n"/>
       <c r="I404" s="4" t="n"/>
-      <c r="J404" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J404" s="4" t="n"/>
       <c r="K404" s="5" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
@@ -11379,11 +11375,7 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J405" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J405" s="4" t="n"/>
       <c r="K405" s="5" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
@@ -11458,11 +11450,7 @@
       <c r="G408" s="4" t="n"/>
       <c r="H408" s="4" t="n"/>
       <c r="I408" s="4" t="n"/>
-      <c r="J408" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J408" s="4" t="n"/>
       <c r="K408" s="4" t="n"/>
       <c r="L408" s="5" t="inlineStr">
         <is>
@@ -11491,11 +11479,7 @@
       <c r="G409" s="4" t="n"/>
       <c r="H409" s="4" t="n"/>
       <c r="I409" s="4" t="n"/>
-      <c r="J409" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J409" s="4" t="n"/>
       <c r="K409" s="4" t="n"/>
       <c r="L409" s="5" t="inlineStr">
         <is>
@@ -11739,11 +11723,7 @@
       <c r="G417" s="4" t="n"/>
       <c r="H417" s="4" t="n"/>
       <c r="I417" s="4" t="n"/>
-      <c r="J417" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J417" s="4" t="n"/>
       <c r="K417" s="4" t="n"/>
       <c r="L417" s="5" t="inlineStr">
         <is>
@@ -11772,11 +11752,7 @@
       <c r="G418" s="4" t="n"/>
       <c r="H418" s="4" t="n"/>
       <c r="I418" s="4" t="n"/>
-      <c r="J418" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J418" s="4" t="n"/>
       <c r="K418" s="4" t="n"/>
       <c r="L418" s="5" t="inlineStr">
         <is>
@@ -11805,11 +11781,7 @@
       <c r="G419" s="4" t="n"/>
       <c r="H419" s="4" t="n"/>
       <c r="I419" s="4" t="n"/>
-      <c r="J419" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J419" s="4" t="n"/>
       <c r="K419" s="4" t="n"/>
       <c r="L419" s="5" t="inlineStr">
         <is>
@@ -11880,11 +11852,7 @@
       <c r="G422" s="4" t="n"/>
       <c r="H422" s="4" t="n"/>
       <c r="I422" s="4" t="n"/>
-      <c r="J422" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J422" s="4" t="n"/>
       <c r="K422" s="4" t="n"/>
       <c r="L422" s="5" t="inlineStr">
         <is>
@@ -11921,11 +11889,7 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="J423" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J423" s="4" t="n"/>
       <c r="K423" s="4" t="n"/>
       <c r="L423" s="5" t="inlineStr">
         <is>
@@ -12934,7 +12898,11 @@
       <c r="G464" s="4" t="n"/>
       <c r="H464" s="4" t="n"/>
       <c r="I464" s="4" t="n"/>
-      <c r="J464" s="4" t="n"/>
+      <c r="J464" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K464" s="4" t="n"/>
       <c r="L464" s="4" t="n"/>
       <c r="M464" s="4" t="n"/>
@@ -12955,7 +12923,11 @@
       <c r="G465" s="4" t="n"/>
       <c r="H465" s="4" t="n"/>
       <c r="I465" s="4" t="n"/>
-      <c r="J465" s="4" t="n"/>
+      <c r="J465" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K465" s="4" t="n"/>
       <c r="L465" s="4" t="n"/>
       <c r="M465" s="4" t="n"/>
@@ -12976,7 +12948,11 @@
       <c r="G466" s="4" t="n"/>
       <c r="H466" s="4" t="n"/>
       <c r="I466" s="4" t="n"/>
-      <c r="J466" s="4" t="n"/>
+      <c r="J466" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K466" s="4" t="n"/>
       <c r="L466" s="4" t="n"/>
       <c r="M466" s="4" t="n"/>
@@ -12997,7 +12973,11 @@
       <c r="G467" s="4" t="n"/>
       <c r="H467" s="4" t="n"/>
       <c r="I467" s="4" t="n"/>
-      <c r="J467" s="4" t="n"/>
+      <c r="J467" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K467" s="4" t="n"/>
       <c r="L467" s="4" t="n"/>
       <c r="M467" s="4" t="n"/>
@@ -13018,7 +12998,11 @@
       <c r="G468" s="4" t="n"/>
       <c r="H468" s="4" t="n"/>
       <c r="I468" s="4" t="n"/>
-      <c r="J468" s="4" t="n"/>
+      <c r="J468" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K468" s="4" t="n"/>
       <c r="L468" s="4" t="n"/>
       <c r="M468" s="4" t="n"/>
@@ -13081,7 +13065,11 @@
       <c r="G471" s="4" t="n"/>
       <c r="H471" s="4" t="n"/>
       <c r="I471" s="4" t="n"/>
-      <c r="J471" s="4" t="n"/>
+      <c r="J471" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K471" s="4" t="n"/>
       <c r="L471" s="4" t="n"/>
       <c r="M471" s="4" t="n"/>
@@ -13102,7 +13090,11 @@
       <c r="G472" s="4" t="n"/>
       <c r="H472" s="4" t="n"/>
       <c r="I472" s="4" t="n"/>
-      <c r="J472" s="4" t="n"/>
+      <c r="J472" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K472" s="4" t="n"/>
       <c r="L472" s="4" t="n"/>
       <c r="M472" s="4" t="n"/>
@@ -13123,7 +13115,11 @@
       <c r="G473" s="4" t="n"/>
       <c r="H473" s="4" t="n"/>
       <c r="I473" s="4" t="n"/>
-      <c r="J473" s="4" t="n"/>
+      <c r="J473" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K473" s="4" t="n"/>
       <c r="L473" s="4" t="n"/>
       <c r="M473" s="4" t="n"/>
@@ -13144,7 +13140,11 @@
       <c r="G474" s="4" t="n"/>
       <c r="H474" s="4" t="n"/>
       <c r="I474" s="4" t="n"/>
-      <c r="J474" s="4" t="n"/>
+      <c r="J474" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K474" s="4" t="n"/>
       <c r="L474" s="4" t="n"/>
       <c r="M474" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -10557,11 +10557,7 @@
       <c r="G384" s="4" t="n"/>
       <c r="H384" s="4" t="n"/>
       <c r="I384" s="4" t="n"/>
-      <c r="J384" s="5" t="inlineStr">
-        <is>
-          <t>Dub - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J384" s="4" t="n"/>
       <c r="K384" s="4" t="n"/>
       <c r="L384" s="4" t="n"/>
       <c r="M384" s="4" t="n"/>
@@ -10636,11 +10632,7 @@
       <c r="G387" s="4" t="n"/>
       <c r="H387" s="4" t="n"/>
       <c r="I387" s="4" t="n"/>
-      <c r="J387" s="5" t="inlineStr">
-        <is>
-          <t>Dub - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J387" s="4" t="n"/>
       <c r="K387" s="4" t="n"/>
       <c r="L387" s="4" t="n"/>
       <c r="M387" s="4" t="n"/>
@@ -10669,9 +10661,9 @@
       <c r="G388" s="4" t="n"/>
       <c r="H388" s="4" t="n"/>
       <c r="I388" s="4" t="n"/>
-      <c r="J388" s="11" t="inlineStr">
-        <is>
-          <t>Online Edit - Sŵ Ni</t>
+      <c r="J388" s="5" t="inlineStr">
+        <is>
+          <t>Dub - Sŵ Ni</t>
         </is>
       </c>
       <c r="K388" s="4" t="n"/>
@@ -10796,8 +10788,7 @@
       </c>
       <c r="J391" s="5" t="inlineStr">
         <is>
-          <t>Film
-Online Edit - Sŵ Ni</t>
+          <t>Film</t>
         </is>
       </c>
       <c r="K391" s="5" t="inlineStr">
@@ -11002,12 +10993,7 @@
       <c r="G394" s="4" t="n"/>
       <c r="H394" s="4" t="n"/>
       <c r="I394" s="4" t="n"/>
-      <c r="J394" s="11" t="inlineStr">
-        <is>
-          <t>Online Edit - Mabli a Ceff Ceff
-Dub - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="J394" s="4" t="n"/>
       <c r="K394" s="4" t="n"/>
       <c r="L394" s="4" t="n"/>
       <c r="M394" s="4" t="n"/>
@@ -11036,10 +11022,9 @@
       <c r="G395" s="4" t="n"/>
       <c r="H395" s="4" t="n"/>
       <c r="I395" s="4" t="n"/>
-      <c r="J395" s="11" t="inlineStr">
-        <is>
-          <t>Online Edit - Mabli a Ceff Ceff
-Dub - Mabli a Ceff Ceff</t>
+      <c r="J395" s="5" t="inlineStr">
+        <is>
+          <t>Dub - Sŵ Ni</t>
         </is>
       </c>
       <c r="K395" s="4" t="n"/>
@@ -11073,8 +11058,7 @@
       <c r="I396" s="4" t="n"/>
       <c r="J396" s="11" t="inlineStr">
         <is>
-          <t>Online Edit - Mabli a Ceff Ceff
-Dub - Mabli a Ceff Ceff</t>
+          <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K396" s="4" t="n"/>
@@ -11101,10 +11085,9 @@
       <c r="G397" s="4" t="n"/>
       <c r="H397" s="4" t="n"/>
       <c r="I397" s="4" t="n"/>
-      <c r="J397" s="11" t="inlineStr">
-        <is>
-          <t>Online Edit - Mabli a Ceff Ceff
-Dub - Mabli a Ceff Ceff</t>
+      <c r="J397" s="5" t="inlineStr">
+        <is>
+          <t>Dub - Sŵ Ni</t>
         </is>
       </c>
       <c r="K397" s="4" t="n"/>
@@ -11135,10 +11118,9 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J398" s="5" t="inlineStr">
-        <is>
-          <t>Dub - Mabli a Ceff Ceff
-Online Edit - Mabli a Ceff Ceff</t>
+      <c r="J398" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K398" s="4" t="n"/>
@@ -11209,7 +11191,7 @@
       <c r="I401" s="4" t="n"/>
       <c r="J401" s="11" t="inlineStr">
         <is>
-          <t>Offline Edit - Sŵ Ni</t>
+          <t>Online Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="K401" s="5" t="inlineStr">
@@ -11250,7 +11232,7 @@
       <c r="I402" s="4" t="n"/>
       <c r="J402" s="11" t="inlineStr">
         <is>
-          <t>Offline Edit - Sŵ Ni</t>
+          <t>Online Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="K402" s="5" t="inlineStr">
@@ -11291,7 +11273,7 @@
       <c r="I403" s="4" t="n"/>
       <c r="J403" s="11" t="inlineStr">
         <is>
-          <t>Offline Edit - Sŵ Ni</t>
+          <t>Online Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="K403" s="5" t="inlineStr">
@@ -11330,7 +11312,11 @@
       <c r="G404" s="4" t="n"/>
       <c r="H404" s="4" t="n"/>
       <c r="I404" s="4" t="n"/>
-      <c r="J404" s="4" t="n"/>
+      <c r="J404" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="K404" s="5" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
@@ -11375,7 +11361,11 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J405" s="4" t="n"/>
+      <c r="J405" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="K405" s="5" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
@@ -11510,7 +11500,8 @@
       <c r="I410" s="4" t="n"/>
       <c r="J410" s="11" t="inlineStr">
         <is>
-          <t>Online Edit - External</t>
+          <t>Online Edit - External
+Online Edit - External</t>
         </is>
       </c>
       <c r="K410" s="4" t="n"/>
@@ -12590,7 +12581,11 @@
       <c r="G452" s="4" t="n"/>
       <c r="H452" s="4" t="n"/>
       <c r="I452" s="4" t="n"/>
-      <c r="J452" s="4" t="n"/>
+      <c r="J452" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K452" s="4" t="n"/>
       <c r="L452" s="4" t="n"/>
       <c r="M452" s="4" t="n"/>
@@ -12611,7 +12606,11 @@
       <c r="G453" s="4" t="n"/>
       <c r="H453" s="4" t="n"/>
       <c r="I453" s="4" t="n"/>
-      <c r="J453" s="4" t="n"/>
+      <c r="J453" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K453" s="4" t="n"/>
       <c r="L453" s="4" t="n"/>
       <c r="M453" s="4" t="n"/>
@@ -12636,7 +12635,11 @@
           <t>Delivery - Deep Watch</t>
         </is>
       </c>
-      <c r="J454" s="4" t="n"/>
+      <c r="J454" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K454" s="4" t="n"/>
       <c r="L454" s="4" t="n"/>
       <c r="M454" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -10557,11 +10557,7 @@
       <c r="G384" s="4" t="n"/>
       <c r="H384" s="4" t="n"/>
       <c r="I384" s="4" t="n"/>
-      <c r="J384" s="5" t="inlineStr">
-        <is>
-          <t>Dub - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J384" s="4" t="n"/>
       <c r="K384" s="4" t="n"/>
       <c r="L384" s="4" t="n"/>
       <c r="M384" s="4" t="n"/>
@@ -10636,11 +10632,7 @@
       <c r="G387" s="4" t="n"/>
       <c r="H387" s="4" t="n"/>
       <c r="I387" s="4" t="n"/>
-      <c r="J387" s="5" t="inlineStr">
-        <is>
-          <t>Dub - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J387" s="4" t="n"/>
       <c r="K387" s="4" t="n"/>
       <c r="L387" s="4" t="n"/>
       <c r="M387" s="4" t="n"/>
@@ -10669,9 +10661,9 @@
       <c r="G388" s="4" t="n"/>
       <c r="H388" s="4" t="n"/>
       <c r="I388" s="4" t="n"/>
-      <c r="J388" s="11" t="inlineStr">
-        <is>
-          <t>Online Edit - Sŵ Ni</t>
+      <c r="J388" s="5" t="inlineStr">
+        <is>
+          <t>Dub - Sŵ Ni</t>
         </is>
       </c>
       <c r="K388" s="4" t="n"/>
@@ -10794,10 +10786,10 @@
           <t>Film</t>
         </is>
       </c>
-      <c r="J391" s="5" t="inlineStr">
-        <is>
-          <t>Film
-Online Edit - Sŵ Ni</t>
+      <c r="J391" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni
+Film</t>
         </is>
       </c>
       <c r="K391" s="5" t="inlineStr">
@@ -11002,12 +10994,7 @@
       <c r="G394" s="4" t="n"/>
       <c r="H394" s="4" t="n"/>
       <c r="I394" s="4" t="n"/>
-      <c r="J394" s="11" t="inlineStr">
-        <is>
-          <t>Online Edit - Mabli a Ceff Ceff
-Dub - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="J394" s="4" t="n"/>
       <c r="K394" s="4" t="n"/>
       <c r="L394" s="4" t="n"/>
       <c r="M394" s="4" t="n"/>
@@ -11036,12 +11023,7 @@
       <c r="G395" s="4" t="n"/>
       <c r="H395" s="4" t="n"/>
       <c r="I395" s="4" t="n"/>
-      <c r="J395" s="11" t="inlineStr">
-        <is>
-          <t>Online Edit - Mabli a Ceff Ceff
-Dub - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="J395" s="4" t="n"/>
       <c r="K395" s="4" t="n"/>
       <c r="L395" s="4" t="n"/>
       <c r="M395" s="4" t="n"/>
@@ -11073,8 +11055,7 @@
       <c r="I396" s="4" t="n"/>
       <c r="J396" s="11" t="inlineStr">
         <is>
-          <t>Online Edit - Mabli a Ceff Ceff
-Dub - Mabli a Ceff Ceff</t>
+          <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K396" s="4" t="n"/>
@@ -11101,10 +11082,9 @@
       <c r="G397" s="4" t="n"/>
       <c r="H397" s="4" t="n"/>
       <c r="I397" s="4" t="n"/>
-      <c r="J397" s="11" t="inlineStr">
-        <is>
-          <t>Online Edit - Mabli a Ceff Ceff
-Dub - Mabli a Ceff Ceff</t>
+      <c r="J397" s="5" t="inlineStr">
+        <is>
+          <t>Dub - Sŵ Ni</t>
         </is>
       </c>
       <c r="K397" s="4" t="n"/>
@@ -11135,10 +11115,9 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J398" s="5" t="inlineStr">
-        <is>
-          <t>Dub - Mabli a Ceff Ceff
-Online Edit - Mabli a Ceff Ceff</t>
+      <c r="J398" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K398" s="4" t="n"/>
@@ -11209,7 +11188,7 @@
       <c r="I401" s="4" t="n"/>
       <c r="J401" s="11" t="inlineStr">
         <is>
-          <t>Offline Edit - Sŵ Ni</t>
+          <t>Online Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="K401" s="5" t="inlineStr">
@@ -11250,7 +11229,7 @@
       <c r="I402" s="4" t="n"/>
       <c r="J402" s="11" t="inlineStr">
         <is>
-          <t>Offline Edit - Sŵ Ni</t>
+          <t>Online Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="K402" s="5" t="inlineStr">
@@ -11291,7 +11270,7 @@
       <c r="I403" s="4" t="n"/>
       <c r="J403" s="11" t="inlineStr">
         <is>
-          <t>Offline Edit - Sŵ Ni</t>
+          <t>Online Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="K403" s="5" t="inlineStr">
@@ -11330,7 +11309,11 @@
       <c r="G404" s="4" t="n"/>
       <c r="H404" s="4" t="n"/>
       <c r="I404" s="4" t="n"/>
-      <c r="J404" s="4" t="n"/>
+      <c r="J404" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="K404" s="5" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
@@ -11375,7 +11358,11 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J405" s="4" t="n"/>
+      <c r="J405" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="K405" s="5" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
@@ -11510,7 +11497,8 @@
       <c r="I410" s="4" t="n"/>
       <c r="J410" s="11" t="inlineStr">
         <is>
-          <t>Online Edit - External</t>
+          <t>Online Edit - External
+Online Edit - External</t>
         </is>
       </c>
       <c r="K410" s="4" t="n"/>
@@ -12590,7 +12578,11 @@
       <c r="G452" s="4" t="n"/>
       <c r="H452" s="4" t="n"/>
       <c r="I452" s="4" t="n"/>
-      <c r="J452" s="4" t="n"/>
+      <c r="J452" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K452" s="4" t="n"/>
       <c r="L452" s="4" t="n"/>
       <c r="M452" s="4" t="n"/>
@@ -12611,7 +12603,11 @@
       <c r="G453" s="4" t="n"/>
       <c r="H453" s="4" t="n"/>
       <c r="I453" s="4" t="n"/>
-      <c r="J453" s="4" t="n"/>
+      <c r="J453" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K453" s="4" t="n"/>
       <c r="L453" s="4" t="n"/>
       <c r="M453" s="4" t="n"/>
@@ -12636,7 +12632,11 @@
           <t>Delivery - Deep Watch</t>
         </is>
       </c>
-      <c r="J454" s="4" t="n"/>
+      <c r="J454" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K454" s="4" t="n"/>
       <c r="L454" s="4" t="n"/>
       <c r="M454" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -10632,7 +10632,11 @@
       <c r="G387" s="4" t="n"/>
       <c r="H387" s="4" t="n"/>
       <c r="I387" s="4" t="n"/>
-      <c r="J387" s="4" t="n"/>
+      <c r="J387" s="5" t="inlineStr">
+        <is>
+          <t>Dub - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K387" s="4" t="n"/>
       <c r="L387" s="4" t="n"/>
       <c r="M387" s="4" t="n"/>
@@ -10661,9 +10665,9 @@
       <c r="G388" s="4" t="n"/>
       <c r="H388" s="4" t="n"/>
       <c r="I388" s="4" t="n"/>
-      <c r="J388" s="5" t="inlineStr">
-        <is>
-          <t>Dub - Sŵ Ni</t>
+      <c r="J388" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K388" s="4" t="n"/>
@@ -10694,9 +10698,9 @@
       <c r="G389" s="4" t="n"/>
       <c r="H389" s="4" t="n"/>
       <c r="I389" s="4" t="n"/>
-      <c r="J389" s="11" t="inlineStr">
-        <is>
-          <t>Online Edit - Sŵ Ni</t>
+      <c r="J389" s="5" t="inlineStr">
+        <is>
+          <t>Dub - Sŵ Ni</t>
         </is>
       </c>
       <c r="K389" s="4" t="n"/>
@@ -10727,9 +10731,9 @@
       <c r="G390" s="4" t="n"/>
       <c r="H390" s="4" t="n"/>
       <c r="I390" s="4" t="n"/>
-      <c r="J390" s="5" t="inlineStr">
-        <is>
-          <t>Dub - Sŵ Ni</t>
+      <c r="J390" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K390" s="4" t="n"/>
@@ -10786,10 +10790,10 @@
           <t>Film</t>
         </is>
       </c>
-      <c r="J391" s="11" t="inlineStr">
-        <is>
-          <t>Online Edit - Sŵ Ni
-Film</t>
+      <c r="J391" s="5" t="inlineStr">
+        <is>
+          <t>Film
+Dub - Sŵ Ni</t>
         </is>
       </c>
       <c r="K391" s="5" t="inlineStr">
@@ -10994,7 +10998,11 @@
       <c r="G394" s="4" t="n"/>
       <c r="H394" s="4" t="n"/>
       <c r="I394" s="4" t="n"/>
-      <c r="J394" s="4" t="n"/>
+      <c r="J394" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K394" s="4" t="n"/>
       <c r="L394" s="4" t="n"/>
       <c r="M394" s="4" t="n"/>
@@ -11023,7 +11031,11 @@
       <c r="G395" s="4" t="n"/>
       <c r="H395" s="4" t="n"/>
       <c r="I395" s="4" t="n"/>
-      <c r="J395" s="4" t="n"/>
+      <c r="J395" s="5" t="inlineStr">
+        <is>
+          <t>Dub - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K395" s="4" t="n"/>
       <c r="L395" s="4" t="n"/>
       <c r="M395" s="4" t="n"/>
@@ -11497,8 +11509,7 @@
       <c r="I410" s="4" t="n"/>
       <c r="J410" s="11" t="inlineStr">
         <is>
-          <t>Online Edit - External
-Online Edit - External</t>
+          <t>Online Edit - External</t>
         </is>
       </c>
       <c r="K410" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9643,11 +9643,7 @@
           <t>Film - BBC Music Show</t>
         </is>
       </c>
-      <c r="J355" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J355" s="4" t="n"/>
       <c r="K355" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -9688,11 +9684,7 @@
       <c r="G356" s="4" t="n"/>
       <c r="H356" s="4" t="n"/>
       <c r="I356" s="4" t="n"/>
-      <c r="J356" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J356" s="4" t="n"/>
       <c r="K356" s="5" t="inlineStr">
         <is>
           <t>Film - Chepstow
@@ -9820,11 +9812,7 @@
       <c r="G359" s="4" t="n"/>
       <c r="H359" s="4" t="n"/>
       <c r="I359" s="4" t="n"/>
-      <c r="J359" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J359" s="4" t="n"/>
       <c r="K359" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -9861,11 +9849,7 @@
       <c r="G360" s="4" t="n"/>
       <c r="H360" s="4" t="n"/>
       <c r="I360" s="4" t="n"/>
-      <c r="J360" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J360" s="4" t="n"/>
       <c r="K360" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -9902,11 +9886,7 @@
       <c r="G361" s="4" t="n"/>
       <c r="H361" s="4" t="n"/>
       <c r="I361" s="4" t="n"/>
-      <c r="J361" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J361" s="4" t="n"/>
       <c r="K361" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -9943,11 +9923,7 @@
       <c r="G362" s="4" t="n"/>
       <c r="H362" s="4" t="n"/>
       <c r="I362" s="4" t="n"/>
-      <c r="J362" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J362" s="4" t="n"/>
       <c r="K362" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -9984,11 +9960,7 @@
       <c r="G363" s="4" t="n"/>
       <c r="H363" s="4" t="n"/>
       <c r="I363" s="4" t="n"/>
-      <c r="J363" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J363" s="4" t="n"/>
       <c r="K363" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -10079,11 +10051,7 @@
           <t>Delivery - Chepstow</t>
         </is>
       </c>
-      <c r="J366" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J366" s="4" t="n"/>
       <c r="K366" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -10112,11 +10080,7 @@
       <c r="G367" s="4" t="n"/>
       <c r="H367" s="4" t="n"/>
       <c r="I367" s="4" t="n"/>
-      <c r="J367" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J367" s="4" t="n"/>
       <c r="K367" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -10145,11 +10109,7 @@
       <c r="G368" s="4" t="n"/>
       <c r="H368" s="4" t="n"/>
       <c r="I368" s="4" t="n"/>
-      <c r="J368" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J368" s="4" t="n"/>
       <c r="K368" s="4" t="n"/>
       <c r="L368" s="4" t="n"/>
       <c r="M368" s="4" t="n"/>
@@ -10174,11 +10134,7 @@
       <c r="G369" s="4" t="n"/>
       <c r="H369" s="4" t="n"/>
       <c r="I369" s="4" t="n"/>
-      <c r="J369" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J369" s="4" t="n"/>
       <c r="K369" s="4" t="n"/>
       <c r="L369" s="4" t="n"/>
       <c r="M369" s="4" t="n"/>
@@ -10203,11 +10159,7 @@
       <c r="G370" s="4" t="n"/>
       <c r="H370" s="4" t="n"/>
       <c r="I370" s="4" t="n"/>
-      <c r="J370" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J370" s="4" t="n"/>
       <c r="K370" s="4" t="n"/>
       <c r="L370" s="4" t="n"/>
       <c r="M370" s="4" t="n"/>
@@ -10274,11 +10226,7 @@
       <c r="G373" s="4" t="n"/>
       <c r="H373" s="4" t="n"/>
       <c r="I373" s="4" t="n"/>
-      <c r="J373" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J373" s="4" t="n"/>
       <c r="K373" s="4" t="n"/>
       <c r="L373" s="4" t="n"/>
       <c r="M373" s="4" t="n"/>
@@ -10361,7 +10309,11 @@
       <c r="G376" s="4" t="n"/>
       <c r="H376" s="4" t="n"/>
       <c r="I376" s="4" t="n"/>
-      <c r="J376" s="4" t="n"/>
+      <c r="J376" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K376" s="4" t="n"/>
       <c r="L376" s="4" t="n"/>
       <c r="M376" s="4" t="n"/>
@@ -10386,7 +10338,11 @@
       <c r="G377" s="4" t="n"/>
       <c r="H377" s="4" t="n"/>
       <c r="I377" s="4" t="n"/>
-      <c r="J377" s="4" t="n"/>
+      <c r="J377" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K377" s="4" t="n"/>
       <c r="L377" s="4" t="n"/>
       <c r="M377" s="4" t="n"/>
@@ -10457,7 +10413,11 @@
       <c r="G380" s="4" t="n"/>
       <c r="H380" s="4" t="n"/>
       <c r="I380" s="4" t="n"/>
-      <c r="J380" s="4" t="n"/>
+      <c r="J380" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K380" s="4" t="n"/>
       <c r="L380" s="4" t="n"/>
       <c r="M380" s="4" t="n"/>
@@ -10482,7 +10442,11 @@
       <c r="G381" s="4" t="n"/>
       <c r="H381" s="4" t="n"/>
       <c r="I381" s="4" t="n"/>
-      <c r="J381" s="4" t="n"/>
+      <c r="J381" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K381" s="4" t="n"/>
       <c r="L381" s="4" t="n"/>
       <c r="M381" s="4" t="n"/>
@@ -10507,7 +10471,11 @@
       <c r="G382" s="4" t="n"/>
       <c r="H382" s="4" t="n"/>
       <c r="I382" s="4" t="n"/>
-      <c r="J382" s="4" t="n"/>
+      <c r="J382" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K382" s="4" t="n"/>
       <c r="L382" s="4" t="n"/>
       <c r="M382" s="4" t="n"/>
@@ -10532,7 +10500,11 @@
       <c r="G383" s="4" t="n"/>
       <c r="H383" s="4" t="n"/>
       <c r="I383" s="4" t="n"/>
-      <c r="J383" s="4" t="n"/>
+      <c r="J383" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K383" s="4" t="n"/>
       <c r="L383" s="4" t="n"/>
       <c r="M383" s="4" t="n"/>
@@ -10557,7 +10529,11 @@
       <c r="G384" s="4" t="n"/>
       <c r="H384" s="4" t="n"/>
       <c r="I384" s="4" t="n"/>
-      <c r="J384" s="4" t="n"/>
+      <c r="J384" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K384" s="4" t="n"/>
       <c r="L384" s="4" t="n"/>
       <c r="M384" s="4" t="n"/>
@@ -11449,7 +11425,11 @@
       <c r="G408" s="4" t="n"/>
       <c r="H408" s="4" t="n"/>
       <c r="I408" s="4" t="n"/>
-      <c r="J408" s="4" t="n"/>
+      <c r="J408" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K408" s="4" t="n"/>
       <c r="L408" s="5" t="inlineStr">
         <is>
@@ -11478,7 +11458,11 @@
       <c r="G409" s="4" t="n"/>
       <c r="H409" s="4" t="n"/>
       <c r="I409" s="4" t="n"/>
-      <c r="J409" s="4" t="n"/>
+      <c r="J409" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K409" s="4" t="n"/>
       <c r="L409" s="5" t="inlineStr">
         <is>
@@ -11509,7 +11493,8 @@
       <c r="I410" s="4" t="n"/>
       <c r="J410" s="11" t="inlineStr">
         <is>
-          <t>Online Edit - External</t>
+          <t>Online Edit - External
+Offline Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K410" s="4" t="n"/>
@@ -11722,7 +11707,11 @@
       <c r="G417" s="4" t="n"/>
       <c r="H417" s="4" t="n"/>
       <c r="I417" s="4" t="n"/>
-      <c r="J417" s="4" t="n"/>
+      <c r="J417" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K417" s="4" t="n"/>
       <c r="L417" s="5" t="inlineStr">
         <is>
@@ -11751,7 +11740,11 @@
       <c r="G418" s="4" t="n"/>
       <c r="H418" s="4" t="n"/>
       <c r="I418" s="4" t="n"/>
-      <c r="J418" s="4" t="n"/>
+      <c r="J418" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K418" s="4" t="n"/>
       <c r="L418" s="5" t="inlineStr">
         <is>
@@ -11780,7 +11773,11 @@
       <c r="G419" s="4" t="n"/>
       <c r="H419" s="4" t="n"/>
       <c r="I419" s="4" t="n"/>
-      <c r="J419" s="4" t="n"/>
+      <c r="J419" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K419" s="4" t="n"/>
       <c r="L419" s="5" t="inlineStr">
         <is>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8809,13 +8809,13 @@
       <c r="K334" s="4" t="n"/>
       <c r="L334" s="5" t="inlineStr">
         <is>
-          <t>Socials - Rookie Teachers</t>
+          <t>Edit - Rhedeg Rhacs</t>
         </is>
       </c>
       <c r="M334" s="4" t="n"/>
       <c r="N334" s="5" t="inlineStr">
         <is>
-          <t>Rhodri p/up Cyfranwyr</t>
+          <t>Sick</t>
         </is>
       </c>
       <c r="O334" s="5" t="inlineStr">
@@ -8863,7 +8863,7 @@
       <c r="K335" s="4" t="n"/>
       <c r="L335" s="5" t="inlineStr">
         <is>
-          <t>Socials - Rookie Teachers</t>
+          <t>Edit - Rhedeg Rhacs</t>
         </is>
       </c>
       <c r="M335" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -12373,7 +12373,11 @@
       <c r="G443" s="4" t="n"/>
       <c r="H443" s="4" t="n"/>
       <c r="I443" s="4" t="n"/>
-      <c r="J443" s="4" t="n"/>
+      <c r="J443" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K443" s="4" t="n"/>
       <c r="L443" s="4" t="n"/>
       <c r="M443" s="4" t="n"/>
@@ -12394,7 +12398,11 @@
       <c r="G444" s="4" t="n"/>
       <c r="H444" s="4" t="n"/>
       <c r="I444" s="4" t="n"/>
-      <c r="J444" s="4" t="n"/>
+      <c r="J444" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K444" s="4" t="n"/>
       <c r="L444" s="4" t="n"/>
       <c r="M444" s="4" t="n"/>
@@ -12419,7 +12427,11 @@
           <t>Delivery - LGBTQ+</t>
         </is>
       </c>
-      <c r="J445" s="4" t="n"/>
+      <c r="J445" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K445" s="4" t="n"/>
       <c r="L445" s="4" t="n"/>
       <c r="M445" s="4" t="n"/>
@@ -13318,11 +13330,7 @@
       </c>
       <c r="H480" s="4" t="n"/>
       <c r="I480" s="4" t="n"/>
-      <c r="J480" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J480" s="4" t="n"/>
       <c r="K480" s="4" t="n"/>
       <c r="L480" s="11" t="inlineStr">
         <is>
@@ -13357,7 +13365,7 @@
       <c r="I481" s="4" t="n"/>
       <c r="J481" s="11" t="inlineStr">
         <is>
-          <t>Offline Edit - Sŵ Ni</t>
+          <t>Online Edit - Dewi Mockumentary</t>
         </is>
       </c>
       <c r="K481" s="4" t="n"/>
@@ -13398,7 +13406,7 @@
       <c r="I482" s="4" t="n"/>
       <c r="J482" s="11" t="inlineStr">
         <is>
-          <t>Offline Edit - Sŵ Ni</t>
+          <t>Online Edit - Dewi Mockumentary</t>
         </is>
       </c>
       <c r="K482" s="4" t="n"/>
@@ -13475,9 +13483,9 @@
       <c r="G485" s="4" t="n"/>
       <c r="H485" s="4" t="n"/>
       <c r="I485" s="4" t="n"/>
-      <c r="J485" s="5" t="inlineStr">
-        <is>
-          <t>Dub - Dewi Mockumentary</t>
+      <c r="J485" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Y Grŵp Chat</t>
         </is>
       </c>
       <c r="K485" s="4" t="n"/>
@@ -13502,7 +13510,7 @@
       <c r="I486" s="4" t="n"/>
       <c r="J486" s="11" t="inlineStr">
         <is>
-          <t>Online Edit - Dewi Mockumentary</t>
+          <t>Online Edit - Y Grŵp Chat</t>
         </is>
       </c>
       <c r="K486" s="4" t="n"/>
@@ -13525,11 +13533,7 @@
       <c r="G487" s="4" t="n"/>
       <c r="H487" s="4" t="n"/>
       <c r="I487" s="4" t="n"/>
-      <c r="J487" s="11" t="inlineStr">
-        <is>
-          <t>Online Edit - Dewi Mockumentary</t>
-        </is>
-      </c>
+      <c r="J487" s="4" t="n"/>
       <c r="K487" s="4" t="n"/>
       <c r="L487" s="4" t="n"/>
       <c r="M487" s="4" t="n"/>
@@ -13550,7 +13554,11 @@
       <c r="G488" s="4" t="n"/>
       <c r="H488" s="4" t="n"/>
       <c r="I488" s="4" t="n"/>
-      <c r="J488" s="4" t="n"/>
+      <c r="J488" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Hwyl Fawr Blodwen</t>
+        </is>
+      </c>
       <c r="K488" s="4" t="n"/>
       <c r="L488" s="4" t="n"/>
       <c r="M488" s="4" t="n"/>
@@ -13571,7 +13579,11 @@
       <c r="G489" s="4" t="n"/>
       <c r="H489" s="4" t="n"/>
       <c r="I489" s="4" t="n"/>
-      <c r="J489" s="4" t="n"/>
+      <c r="J489" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Hwyl Fawr Blodwen</t>
+        </is>
+      </c>
       <c r="K489" s="4" t="n"/>
       <c r="L489" s="4" t="n"/>
       <c r="M489" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -13697,7 +13697,11 @@
 Delivery - Y Grŵp Chat</t>
         </is>
       </c>
-      <c r="J494" s="4" t="n"/>
+      <c r="J494" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K494" s="4" t="n"/>
       <c r="L494" s="4" t="n"/>
       <c r="M494" s="4" t="n"/>
@@ -13718,7 +13722,11 @@
       <c r="G495" s="4" t="n"/>
       <c r="H495" s="4" t="n"/>
       <c r="I495" s="4" t="n"/>
-      <c r="J495" s="4" t="n"/>
+      <c r="J495" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K495" s="4" t="n"/>
       <c r="L495" s="4" t="n"/>
       <c r="M495" s="4" t="n"/>
@@ -13739,7 +13747,11 @@
       <c r="G496" s="4" t="n"/>
       <c r="H496" s="4" t="n"/>
       <c r="I496" s="4" t="n"/>
-      <c r="J496" s="4" t="n"/>
+      <c r="J496" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K496" s="4" t="n"/>
       <c r="L496" s="4" t="n"/>
       <c r="M496" s="4" t="n"/>
@@ -13994,9 +14006,9 @@
       <c r="G507" s="4" t="n"/>
       <c r="H507" s="4" t="n"/>
       <c r="I507" s="4" t="n"/>
-      <c r="J507" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
+      <c r="J507" s="8" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
       <c r="K507" s="4" t="n"/>
@@ -14019,9 +14031,9 @@
       <c r="G508" s="4" t="n"/>
       <c r="H508" s="4" t="n"/>
       <c r="I508" s="4" t="n"/>
-      <c r="J508" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
+      <c r="J508" s="8" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
       <c r="K508" s="4" t="n"/>
@@ -14044,9 +14056,9 @@
       <c r="G509" s="4" t="n"/>
       <c r="H509" s="4" t="n"/>
       <c r="I509" s="4" t="n"/>
-      <c r="J509" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
+      <c r="J509" s="8" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
       <c r="K509" s="4" t="n"/>
@@ -14069,7 +14081,11 @@
       <c r="G510" s="4" t="n"/>
       <c r="H510" s="4" t="n"/>
       <c r="I510" s="4" t="n"/>
-      <c r="J510" s="4" t="n"/>
+      <c r="J510" s="8" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K510" s="4" t="n"/>
       <c r="L510" s="4" t="n"/>
       <c r="M510" s="4" t="n"/>
@@ -14132,11 +14148,7 @@
       <c r="G513" s="4" t="n"/>
       <c r="H513" s="4" t="n"/>
       <c r="I513" s="4" t="n"/>
-      <c r="J513" s="8" t="inlineStr">
-        <is>
-          <t>Notes / Changes - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J513" s="4" t="n"/>
       <c r="K513" s="4" t="n"/>
       <c r="L513" s="4" t="n"/>
       <c r="M513" s="4" t="n"/>
@@ -14157,11 +14169,7 @@
       <c r="G514" s="4" t="n"/>
       <c r="H514" s="4" t="n"/>
       <c r="I514" s="4" t="n"/>
-      <c r="J514" s="8" t="inlineStr">
-        <is>
-          <t>Notes / Changes - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J514" s="4" t="n"/>
       <c r="K514" s="4" t="n"/>
       <c r="L514" s="4" t="n"/>
       <c r="M514" s="4" t="n"/>
@@ -14182,11 +14190,7 @@
       <c r="G515" s="4" t="n"/>
       <c r="H515" s="4" t="n"/>
       <c r="I515" s="4" t="n"/>
-      <c r="J515" s="8" t="inlineStr">
-        <is>
-          <t>Notes / Changes - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J515" s="4" t="n"/>
       <c r="K515" s="4" t="n"/>
       <c r="L515" s="4" t="n"/>
       <c r="M515" s="4" t="n"/>
@@ -14207,11 +14211,7 @@
       <c r="G516" s="4" t="n"/>
       <c r="H516" s="4" t="n"/>
       <c r="I516" s="4" t="n"/>
-      <c r="J516" s="8" t="inlineStr">
-        <is>
-          <t>Notes / Changes - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J516" s="4" t="n"/>
       <c r="K516" s="4" t="n"/>
       <c r="L516" s="4" t="n"/>
       <c r="M516" s="4" t="n"/>
@@ -14232,11 +14232,7 @@
       <c r="G517" s="4" t="n"/>
       <c r="H517" s="4" t="n"/>
       <c r="I517" s="4" t="n"/>
-      <c r="J517" s="8" t="inlineStr">
-        <is>
-          <t>Notes / Changes - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J517" s="4" t="n"/>
       <c r="K517" s="4" t="n"/>
       <c r="L517" s="4" t="n"/>
       <c r="M517" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -14148,7 +14148,11 @@
       <c r="G513" s="4" t="n"/>
       <c r="H513" s="4" t="n"/>
       <c r="I513" s="4" t="n"/>
-      <c r="J513" s="4" t="n"/>
+      <c r="J513" s="5" t="inlineStr">
+        <is>
+          <t>Dub - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K513" s="4" t="n"/>
       <c r="L513" s="4" t="n"/>
       <c r="M513" s="4" t="n"/>
@@ -14169,7 +14173,11 @@
       <c r="G514" s="4" t="n"/>
       <c r="H514" s="4" t="n"/>
       <c r="I514" s="4" t="n"/>
-      <c r="J514" s="4" t="n"/>
+      <c r="J514" s="5" t="inlineStr">
+        <is>
+          <t>Dub - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K514" s="4" t="n"/>
       <c r="L514" s="4" t="n"/>
       <c r="M514" s="4" t="n"/>
@@ -14190,7 +14198,11 @@
       <c r="G515" s="4" t="n"/>
       <c r="H515" s="4" t="n"/>
       <c r="I515" s="4" t="n"/>
-      <c r="J515" s="4" t="n"/>
+      <c r="J515" s="5" t="inlineStr">
+        <is>
+          <t>Dub - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K515" s="4" t="n"/>
       <c r="L515" s="4" t="n"/>
       <c r="M515" s="4" t="n"/>
@@ -14211,7 +14223,11 @@
       <c r="G516" s="4" t="n"/>
       <c r="H516" s="4" t="n"/>
       <c r="I516" s="4" t="n"/>
-      <c r="J516" s="4" t="n"/>
+      <c r="J516" s="5" t="inlineStr">
+        <is>
+          <t>Dub - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K516" s="4" t="n"/>
       <c r="L516" s="4" t="n"/>
       <c r="M516" s="4" t="n"/>
@@ -14232,7 +14248,11 @@
       <c r="G517" s="4" t="n"/>
       <c r="H517" s="4" t="n"/>
       <c r="I517" s="4" t="n"/>
-      <c r="J517" s="4" t="n"/>
+      <c r="J517" s="5" t="inlineStr">
+        <is>
+          <t>Dub - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K517" s="4" t="n"/>
       <c r="L517" s="4" t="n"/>
       <c r="M517" s="4" t="n"/>
@@ -14299,9 +14319,9 @@
       </c>
       <c r="H520" s="4" t="n"/>
       <c r="I520" s="4" t="n"/>
-      <c r="J520" s="5" t="inlineStr">
-        <is>
-          <t>Dub - Sŵ Ni</t>
+      <c r="J520" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K520" s="4" t="n"/>
@@ -14328,9 +14348,9 @@
       </c>
       <c r="H521" s="4" t="n"/>
       <c r="I521" s="4" t="n"/>
-      <c r="J521" s="5" t="inlineStr">
-        <is>
-          <t>Dub - Sŵ Ni</t>
+      <c r="J521" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K521" s="4" t="n"/>
@@ -14357,9 +14377,9 @@
       </c>
       <c r="H522" s="4" t="n"/>
       <c r="I522" s="4" t="n"/>
-      <c r="J522" s="5" t="inlineStr">
-        <is>
-          <t>Dub - Sŵ Ni</t>
+      <c r="J522" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K522" s="4" t="n"/>
@@ -14386,9 +14406,9 @@
       </c>
       <c r="H523" s="4" t="n"/>
       <c r="I523" s="4" t="n"/>
-      <c r="J523" s="5" t="inlineStr">
-        <is>
-          <t>Dub - Sŵ Ni</t>
+      <c r="J523" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K523" s="4" t="n"/>
@@ -14415,11 +14435,7 @@
       </c>
       <c r="H524" s="4" t="n"/>
       <c r="I524" s="4" t="n"/>
-      <c r="J524" s="5" t="inlineStr">
-        <is>
-          <t>Dub - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J524" s="4" t="n"/>
       <c r="K524" s="4" t="n"/>
       <c r="L524" s="4" t="n"/>
       <c r="M524" s="4" t="n"/>
@@ -14482,11 +14498,7 @@
       <c r="G527" s="4" t="n"/>
       <c r="H527" s="4" t="n"/>
       <c r="I527" s="4" t="n"/>
-      <c r="J527" s="11" t="inlineStr">
-        <is>
-          <t>Online Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J527" s="4" t="n"/>
       <c r="K527" s="4" t="n"/>
       <c r="L527" s="4" t="n"/>
       <c r="M527" s="4" t="n"/>
@@ -14507,11 +14519,7 @@
       <c r="G528" s="4" t="n"/>
       <c r="H528" s="4" t="n"/>
       <c r="I528" s="4" t="n"/>
-      <c r="J528" s="11" t="inlineStr">
-        <is>
-          <t>Online Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J528" s="4" t="n"/>
       <c r="K528" s="4" t="n"/>
       <c r="L528" s="4" t="n"/>
       <c r="M528" s="4" t="n"/>
@@ -14536,11 +14544,7 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J529" s="11" t="inlineStr">
-        <is>
-          <t>Online Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J529" s="4" t="n"/>
       <c r="K529" s="4" t="n"/>
       <c r="L529" s="4" t="n"/>
       <c r="M529" s="4" t="n"/>
@@ -14565,11 +14569,7 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J530" s="11" t="inlineStr">
-        <is>
-          <t>Online Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J530" s="4" t="n"/>
       <c r="K530" s="4" t="n"/>
       <c r="L530" s="4" t="n"/>
       <c r="M530" s="4" t="n"/>
@@ -14594,11 +14594,7 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J531" s="11" t="inlineStr">
-        <is>
-          <t>Online Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J531" s="4" t="n"/>
       <c r="K531" s="4" t="n"/>
       <c r="L531" s="4" t="n"/>
       <c r="M531" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -14435,7 +14435,11 @@
       </c>
       <c r="H524" s="4" t="n"/>
       <c r="I524" s="4" t="n"/>
-      <c r="J524" s="4" t="n"/>
+      <c r="J524" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K524" s="4" t="n"/>
       <c r="L524" s="4" t="n"/>
       <c r="M524" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -12373,11 +12373,7 @@
       <c r="G443" s="4" t="n"/>
       <c r="H443" s="4" t="n"/>
       <c r="I443" s="4" t="n"/>
-      <c r="J443" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J443" s="4" t="n"/>
       <c r="K443" s="4" t="n"/>
       <c r="L443" s="4" t="n"/>
       <c r="M443" s="4" t="n"/>
@@ -12398,11 +12394,7 @@
       <c r="G444" s="4" t="n"/>
       <c r="H444" s="4" t="n"/>
       <c r="I444" s="4" t="n"/>
-      <c r="J444" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J444" s="4" t="n"/>
       <c r="K444" s="4" t="n"/>
       <c r="L444" s="4" t="n"/>
       <c r="M444" s="4" t="n"/>
@@ -12427,11 +12419,7 @@
           <t>Delivery - LGBTQ+</t>
         </is>
       </c>
-      <c r="J445" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J445" s="4" t="n"/>
       <c r="K445" s="4" t="n"/>
       <c r="L445" s="4" t="n"/>
       <c r="M445" s="4" t="n"/>
@@ -12598,11 +12586,7 @@
       <c r="G452" s="4" t="n"/>
       <c r="H452" s="4" t="n"/>
       <c r="I452" s="4" t="n"/>
-      <c r="J452" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J452" s="4" t="n"/>
       <c r="K452" s="4" t="n"/>
       <c r="L452" s="4" t="n"/>
       <c r="M452" s="4" t="n"/>
@@ -12623,11 +12607,7 @@
       <c r="G453" s="4" t="n"/>
       <c r="H453" s="4" t="n"/>
       <c r="I453" s="4" t="n"/>
-      <c r="J453" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J453" s="4" t="n"/>
       <c r="K453" s="4" t="n"/>
       <c r="L453" s="4" t="n"/>
       <c r="M453" s="4" t="n"/>
@@ -12652,11 +12632,7 @@
           <t>Delivery - Deep Watch</t>
         </is>
       </c>
-      <c r="J454" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J454" s="4" t="n"/>
       <c r="K454" s="4" t="n"/>
       <c r="L454" s="4" t="n"/>
       <c r="M454" s="4" t="n"/>
@@ -12918,11 +12894,7 @@
       <c r="G464" s="4" t="n"/>
       <c r="H464" s="4" t="n"/>
       <c r="I464" s="4" t="n"/>
-      <c r="J464" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J464" s="4" t="n"/>
       <c r="K464" s="4" t="n"/>
       <c r="L464" s="4" t="n"/>
       <c r="M464" s="4" t="n"/>
@@ -13330,7 +13302,11 @@
       </c>
       <c r="H480" s="4" t="n"/>
       <c r="I480" s="4" t="n"/>
-      <c r="J480" s="4" t="n"/>
+      <c r="J480" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K480" s="4" t="n"/>
       <c r="L480" s="11" t="inlineStr">
         <is>
@@ -13646,7 +13622,11 @@
       <c r="G492" s="4" t="n"/>
       <c r="H492" s="4" t="n"/>
       <c r="I492" s="4" t="n"/>
-      <c r="J492" s="4" t="n"/>
+      <c r="J492" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K492" s="4" t="n"/>
       <c r="L492" s="4" t="n"/>
       <c r="M492" s="4" t="n"/>
@@ -13671,7 +13651,11 @@
           <t>Delivery - Dewi Mockumentary</t>
         </is>
       </c>
-      <c r="J493" s="4" t="n"/>
+      <c r="J493" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K493" s="4" t="n"/>
       <c r="L493" s="4" t="n"/>
       <c r="M493" s="4" t="n"/>
@@ -14006,9 +13990,9 @@
       <c r="G507" s="4" t="n"/>
       <c r="H507" s="4" t="n"/>
       <c r="I507" s="4" t="n"/>
-      <c r="J507" s="8" t="inlineStr">
-        <is>
-          <t>Notes / Changes - Sŵ Ni</t>
+      <c r="J507" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K507" s="4" t="n"/>
@@ -14031,9 +14015,9 @@
       <c r="G508" s="4" t="n"/>
       <c r="H508" s="4" t="n"/>
       <c r="I508" s="4" t="n"/>
-      <c r="J508" s="8" t="inlineStr">
-        <is>
-          <t>Notes / Changes - Sŵ Ni</t>
+      <c r="J508" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K508" s="4" t="n"/>
@@ -14056,9 +14040,9 @@
       <c r="G509" s="4" t="n"/>
       <c r="H509" s="4" t="n"/>
       <c r="I509" s="4" t="n"/>
-      <c r="J509" s="8" t="inlineStr">
-        <is>
-          <t>Notes / Changes - Sŵ Ni</t>
+      <c r="J509" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K509" s="4" t="n"/>
@@ -14081,9 +14065,9 @@
       <c r="G510" s="4" t="n"/>
       <c r="H510" s="4" t="n"/>
       <c r="I510" s="4" t="n"/>
-      <c r="J510" s="8" t="inlineStr">
-        <is>
-          <t>Notes / Changes - Sŵ Ni</t>
+      <c r="J510" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K510" s="4" t="n"/>
@@ -14148,9 +14132,9 @@
       <c r="G513" s="4" t="n"/>
       <c r="H513" s="4" t="n"/>
       <c r="I513" s="4" t="n"/>
-      <c r="J513" s="5" t="inlineStr">
-        <is>
-          <t>Dub - Sŵ Ni</t>
+      <c r="J513" s="8" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
       <c r="K513" s="4" t="n"/>
@@ -14173,9 +14157,9 @@
       <c r="G514" s="4" t="n"/>
       <c r="H514" s="4" t="n"/>
       <c r="I514" s="4" t="n"/>
-      <c r="J514" s="5" t="inlineStr">
-        <is>
-          <t>Dub - Sŵ Ni</t>
+      <c r="J514" s="8" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
       <c r="K514" s="4" t="n"/>
@@ -14198,9 +14182,9 @@
       <c r="G515" s="4" t="n"/>
       <c r="H515" s="4" t="n"/>
       <c r="I515" s="4" t="n"/>
-      <c r="J515" s="5" t="inlineStr">
-        <is>
-          <t>Dub - Sŵ Ni</t>
+      <c r="J515" s="8" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
       <c r="K515" s="4" t="n"/>
@@ -14223,9 +14207,9 @@
       <c r="G516" s="4" t="n"/>
       <c r="H516" s="4" t="n"/>
       <c r="I516" s="4" t="n"/>
-      <c r="J516" s="5" t="inlineStr">
-        <is>
-          <t>Dub - Sŵ Ni</t>
+      <c r="J516" s="8" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
       <c r="K516" s="4" t="n"/>
@@ -14248,9 +14232,9 @@
       <c r="G517" s="4" t="n"/>
       <c r="H517" s="4" t="n"/>
       <c r="I517" s="4" t="n"/>
-      <c r="J517" s="5" t="inlineStr">
-        <is>
-          <t>Dub - Sŵ Ni</t>
+      <c r="J517" s="8" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
       <c r="K517" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9140,7 +9140,7 @@
       </c>
       <c r="J342" s="5" t="inlineStr">
         <is>
-          <t>Film - Prep Sw Ni MP</t>
+          <t>Prep Sw Ni MP</t>
         </is>
       </c>
       <c r="K342" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9080,7 +9080,11 @@
           <t>Prep Sw Ni</t>
         </is>
       </c>
-      <c r="E341" s="4" t="n"/>
+      <c r="E341" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F341" s="4" t="n"/>
       <c r="G341" s="4" t="n"/>
       <c r="H341" s="4" t="n"/>
@@ -9212,7 +9216,11 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E345" s="4" t="n"/>
+      <c r="E345" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F345" s="4" t="n"/>
       <c r="G345" s="5" t="inlineStr">
         <is>
@@ -9257,7 +9265,11 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E346" s="4" t="n"/>
+      <c r="E346" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F346" s="4" t="n"/>
       <c r="G346" s="5" t="inlineStr">
         <is>
@@ -9580,8 +9592,7 @@
       <c r="D354" s="4" t="n"/>
       <c r="E354" s="5" t="inlineStr">
         <is>
-          <t>Film - BBC Music Show
-Edit - Sŵ Ni</t>
+          <t>Film - BBC Music Show</t>
         </is>
       </c>
       <c r="F354" s="4" t="n"/>
@@ -9631,8 +9642,7 @@
       <c r="D355" s="4" t="n"/>
       <c r="E355" s="5" t="inlineStr">
         <is>
-          <t>Film - BBC Music Show
-Edit - Sŵ Ni</t>
+          <t>Film - BBC Music Show</t>
         </is>
       </c>
       <c r="F355" s="4" t="n"/>
@@ -9675,11 +9685,7 @@
       <c r="B356" s="4" t="n"/>
       <c r="C356" s="4" t="n"/>
       <c r="D356" s="4" t="n"/>
-      <c r="E356" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="E356" s="4" t="n"/>
       <c r="F356" s="4" t="n"/>
       <c r="G356" s="4" t="n"/>
       <c r="H356" s="4" t="n"/>
@@ -10034,11 +10040,7 @@
       <c r="B366" s="4" t="n"/>
       <c r="C366" s="4" t="n"/>
       <c r="D366" s="4" t="n"/>
-      <c r="E366" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="E366" s="4" t="n"/>
       <c r="F366" s="10" t="inlineStr">
         <is>
           <t>OFF</t>
@@ -10071,11 +10073,7 @@
       <c r="B367" s="4" t="n"/>
       <c r="C367" s="4" t="n"/>
       <c r="D367" s="4" t="n"/>
-      <c r="E367" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="E367" s="4" t="n"/>
       <c r="F367" s="4" t="n"/>
       <c r="G367" s="4" t="n"/>
       <c r="H367" s="4" t="n"/>
@@ -10100,11 +10098,7 @@
       <c r="B368" s="4" t="n"/>
       <c r="C368" s="4" t="n"/>
       <c r="D368" s="4" t="n"/>
-      <c r="E368" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="E368" s="4" t="n"/>
       <c r="F368" s="4" t="n"/>
       <c r="G368" s="4" t="n"/>
       <c r="H368" s="4" t="n"/>
@@ -10125,11 +10119,7 @@
       <c r="B369" s="4" t="n"/>
       <c r="C369" s="4" t="n"/>
       <c r="D369" s="4" t="n"/>
-      <c r="E369" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="E369" s="4" t="n"/>
       <c r="F369" s="4" t="n"/>
       <c r="G369" s="4" t="n"/>
       <c r="H369" s="4" t="n"/>
@@ -10150,11 +10140,7 @@
       <c r="B370" s="4" t="n"/>
       <c r="C370" s="4" t="n"/>
       <c r="D370" s="4" t="n"/>
-      <c r="E370" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="E370" s="4" t="n"/>
       <c r="F370" s="4" t="n"/>
       <c r="G370" s="4" t="n"/>
       <c r="H370" s="4" t="n"/>
@@ -11169,7 +11155,11 @@
           <t>Film - LGBTQ+</t>
         </is>
       </c>
-      <c r="E401" s="4" t="n"/>
+      <c r="E401" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F401" s="4" t="n"/>
       <c r="G401" s="4" t="n"/>
       <c r="H401" s="4" t="n"/>
@@ -11210,7 +11200,11 @@
           <t>Film - LGBTQ+</t>
         </is>
       </c>
-      <c r="E402" s="4" t="n"/>
+      <c r="E402" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F402" s="4" t="n"/>
       <c r="G402" s="4" t="n"/>
       <c r="H402" s="4" t="n"/>
@@ -11251,7 +11245,11 @@
           <t>Film - LGBTQ+</t>
         </is>
       </c>
-      <c r="E403" s="4" t="n"/>
+      <c r="E403" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F403" s="4" t="n"/>
       <c r="G403" s="4" t="n"/>
       <c r="H403" s="4" t="n"/>
@@ -11292,7 +11290,11 @@
           <t>Film - LGBTQ+</t>
         </is>
       </c>
-      <c r="E404" s="4" t="n"/>
+      <c r="E404" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F404" s="4" t="n"/>
       <c r="G404" s="4" t="n"/>
       <c r="H404" s="4" t="n"/>
@@ -11333,7 +11335,11 @@
           <t>Film - LGBTQ+</t>
         </is>
       </c>
-      <c r="E405" s="4" t="n"/>
+      <c r="E405" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F405" s="4" t="n"/>
       <c r="G405" s="9" t="inlineStr">
         <is>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9001,7 +9001,11 @@
         </is>
       </c>
       <c r="K339" s="4" t="n"/>
-      <c r="L339" s="4" t="n"/>
+      <c r="L339" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Black History 2026</t>
+        </is>
+      </c>
       <c r="M339" s="4" t="n"/>
       <c r="N339" s="8" t="inlineStr">
         <is>
@@ -9054,7 +9058,11 @@
         </is>
       </c>
       <c r="K340" s="4" t="n"/>
-      <c r="L340" s="4" t="n"/>
+      <c r="L340" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Black History 2026</t>
+        </is>
+      </c>
       <c r="M340" s="4" t="n"/>
       <c r="N340" s="8" t="inlineStr">
         <is>
@@ -9337,11 +9345,7 @@
           <t>SOCIAL MEDIA CONFERENCE</t>
         </is>
       </c>
-      <c r="L347" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Black History 2026</t>
-        </is>
-      </c>
+      <c r="L347" s="4" t="n"/>
       <c r="M347" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -9390,11 +9394,7 @@
         </is>
       </c>
       <c r="K348" s="4" t="n"/>
-      <c r="L348" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Black History 2026</t>
-        </is>
-      </c>
+      <c r="L348" s="4" t="n"/>
       <c r="M348" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9345,7 +9345,11 @@
           <t>SOCIAL MEDIA CONFERENCE</t>
         </is>
       </c>
-      <c r="L347" s="4" t="n"/>
+      <c r="L347" s="8" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Black History 2026</t>
+        </is>
+      </c>
       <c r="M347" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -10462,7 +10466,11 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K382" s="4" t="n"/>
+      <c r="K382" s="5" t="inlineStr">
+        <is>
+          <t>Tac / S4C</t>
+        </is>
+      </c>
       <c r="L382" s="4" t="n"/>
       <c r="M382" s="4" t="n"/>
       <c r="N382" s="4" t="n"/>
@@ -10491,7 +10499,11 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K383" s="4" t="n"/>
+      <c r="K383" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tac / S4C </t>
+        </is>
+      </c>
       <c r="L383" s="4" t="n"/>
       <c r="M383" s="4" t="n"/>
       <c r="N383" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8955,11 +8955,7 @@
       <c r="L338" s="4" t="n"/>
       <c r="M338" s="4" t="n"/>
       <c r="N338" s="4" t="n"/>
-      <c r="O338" s="5" t="inlineStr">
-        <is>
-          <t>Hansh Socials</t>
-        </is>
-      </c>
+      <c r="O338" s="4" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="3" t="inlineStr">
@@ -9012,11 +9008,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="O339" s="5" t="inlineStr">
-        <is>
-          <t>Hansh Socials</t>
-        </is>
-      </c>
+      <c r="O339" s="4" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="3" t="inlineStr">
@@ -9069,11 +9061,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="O340" s="5" t="inlineStr">
-        <is>
-          <t>Hansh Socials</t>
-        </is>
-      </c>
+      <c r="O340" s="4" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="3" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9646,11 +9646,7 @@
         </is>
       </c>
       <c r="J355" s="4" t="n"/>
-      <c r="K355" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="K355" s="4" t="n"/>
       <c r="L355" s="5" t="inlineStr">
         <is>
           <t>Film - BBC Music Show</t>
@@ -9685,8 +9681,7 @@
       <c r="J356" s="4" t="n"/>
       <c r="K356" s="5" t="inlineStr">
         <is>
-          <t>Film - Chepstow
-A/L - Annual Leave</t>
+          <t>Film - Chepstow</t>
         </is>
       </c>
       <c r="L356" s="5" t="inlineStr">
@@ -9766,11 +9761,7 @@
       <c r="H358" s="7" t="n"/>
       <c r="I358" s="7" t="n"/>
       <c r="J358" s="7" t="n"/>
-      <c r="K358" s="5" t="inlineStr">
-        <is>
-          <t>Film - Chepstow</t>
-        </is>
-      </c>
+      <c r="K358" s="7" t="n"/>
       <c r="L358" s="7" t="n"/>
       <c r="M358" s="5" t="inlineStr">
         <is>
@@ -9811,11 +9802,7 @@
       <c r="H359" s="4" t="n"/>
       <c r="I359" s="4" t="n"/>
       <c r="J359" s="4" t="n"/>
-      <c r="K359" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="K359" s="4" t="n"/>
       <c r="L359" s="4" t="n"/>
       <c r="M359" s="4" t="n"/>
       <c r="N359" s="4" t="n"/>
@@ -9848,11 +9835,7 @@
       <c r="H360" s="4" t="n"/>
       <c r="I360" s="4" t="n"/>
       <c r="J360" s="4" t="n"/>
-      <c r="K360" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="K360" s="4" t="n"/>
       <c r="L360" s="4" t="n"/>
       <c r="M360" s="4" t="n"/>
       <c r="N360" s="4" t="n"/>
@@ -9885,11 +9868,7 @@
       <c r="H361" s="4" t="n"/>
       <c r="I361" s="4" t="n"/>
       <c r="J361" s="4" t="n"/>
-      <c r="K361" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="K361" s="4" t="n"/>
       <c r="L361" s="4" t="n"/>
       <c r="M361" s="4" t="n"/>
       <c r="N361" s="4" t="n"/>
@@ -9922,11 +9901,7 @@
       <c r="H362" s="4" t="n"/>
       <c r="I362" s="4" t="n"/>
       <c r="J362" s="4" t="n"/>
-      <c r="K362" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="K362" s="4" t="n"/>
       <c r="L362" s="5" t="inlineStr">
         <is>
           <t>Edit - Chepstow</t>
@@ -9959,11 +9934,7 @@
       <c r="H363" s="4" t="n"/>
       <c r="I363" s="4" t="n"/>
       <c r="J363" s="4" t="n"/>
-      <c r="K363" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="K363" s="4" t="n"/>
       <c r="L363" s="5" t="inlineStr">
         <is>
           <t>Edit - Chepstow</t>
@@ -10046,11 +10017,7 @@
         </is>
       </c>
       <c r="J366" s="4" t="n"/>
-      <c r="K366" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="K366" s="4" t="n"/>
       <c r="L366" s="4" t="n"/>
       <c r="M366" s="4" t="n"/>
       <c r="N366" s="4" t="n"/>
@@ -10071,11 +10038,7 @@
       <c r="H367" s="4" t="n"/>
       <c r="I367" s="4" t="n"/>
       <c r="J367" s="4" t="n"/>
-      <c r="K367" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="K367" s="4" t="n"/>
       <c r="L367" s="4" t="n"/>
       <c r="M367" s="4" t="n"/>
       <c r="N367" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9729,7 +9729,11 @@
           <t>Film - Chepstow</t>
         </is>
       </c>
-      <c r="L357" s="7" t="n"/>
+      <c r="L357" s="5" t="inlineStr">
+        <is>
+          <t>Film - Chepstow</t>
+        </is>
+      </c>
       <c r="M357" s="5" t="inlineStr">
         <is>
           <t>Film - Chepstow</t>
@@ -9762,7 +9766,11 @@
       <c r="I358" s="7" t="n"/>
       <c r="J358" s="7" t="n"/>
       <c r="K358" s="7" t="n"/>
-      <c r="L358" s="7" t="n"/>
+      <c r="L358" s="5" t="inlineStr">
+        <is>
+          <t>Film - Chepstow</t>
+        </is>
+      </c>
       <c r="M358" s="5" t="inlineStr">
         <is>
           <t>Film - Chepstow</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O535"/>
+  <dimension ref="A1:P535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -514,6 +514,7 @@
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -574,20 +575,25 @@
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
+          <t>Noa Harries</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
           <t>Osian Lewis</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Owain Jones</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Rhodri Lewis</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Wil Williams</t>
         </is>
@@ -611,12 +617,13 @@
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
       <c r="M2" s="4" t="n"/>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="N2" s="4" t="n"/>
+      <c r="O2" s="5" t="inlineStr">
         <is>
           <t>Sick - Sick</t>
         </is>
       </c>
-      <c r="O2" s="4" t="n"/>
+      <c r="P2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -636,12 +643,13 @@
       <c r="K3" s="4" t="n"/>
       <c r="L3" s="4" t="n"/>
       <c r="M3" s="4" t="n"/>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>Sick - Sick</t>
         </is>
       </c>
-      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -661,12 +669,13 @@
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
       <c r="M4" s="4" t="n"/>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>Sick - Sick</t>
         </is>
       </c>
-      <c r="O4" s="4" t="n"/>
+      <c r="P4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -686,12 +695,13 @@
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="4" t="n"/>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="5" t="inlineStr">
         <is>
           <t>Sick - Sick</t>
         </is>
       </c>
-      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -711,12 +721,13 @@
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="5" t="inlineStr">
         <is>
           <t>Sick - Sick</t>
         </is>
       </c>
-      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -738,6 +749,7 @@
       <c r="M7" s="7" t="n"/>
       <c r="N7" s="7" t="n"/>
       <c r="O7" s="7" t="n"/>
+      <c r="P7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -759,6 +771,7 @@
       <c r="M8" s="7" t="n"/>
       <c r="N8" s="7" t="n"/>
       <c r="O8" s="7" t="n"/>
+      <c r="P8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -780,6 +793,7 @@
       <c r="M9" s="4" t="n"/>
       <c r="N9" s="4" t="n"/>
       <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -801,6 +815,7 @@
       <c r="M10" s="4" t="n"/>
       <c r="N10" s="4" t="n"/>
       <c r="O10" s="4" t="n"/>
+      <c r="P10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -822,6 +837,7 @@
       <c r="M11" s="4" t="n"/>
       <c r="N11" s="4" t="n"/>
       <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -843,6 +859,7 @@
       <c r="M12" s="4" t="n"/>
       <c r="N12" s="4" t="n"/>
       <c r="O12" s="4" t="n"/>
+      <c r="P12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -864,6 +881,7 @@
       <c r="M13" s="4" t="n"/>
       <c r="N13" s="4" t="n"/>
       <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -885,6 +903,7 @@
       <c r="M14" s="7" t="n"/>
       <c r="N14" s="7" t="n"/>
       <c r="O14" s="7" t="n"/>
+      <c r="P14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -906,6 +925,7 @@
       <c r="M15" s="7" t="n"/>
       <c r="N15" s="7" t="n"/>
       <c r="O15" s="7" t="n"/>
+      <c r="P15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -927,6 +947,7 @@
       <c r="M16" s="4" t="n"/>
       <c r="N16" s="4" t="n"/>
       <c r="O16" s="4" t="n"/>
+      <c r="P16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -948,6 +969,7 @@
       <c r="M17" s="4" t="n"/>
       <c r="N17" s="4" t="n"/>
       <c r="O17" s="4" t="n"/>
+      <c r="P17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -969,6 +991,7 @@
       <c r="M18" s="4" t="n"/>
       <c r="N18" s="4" t="n"/>
       <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -990,6 +1013,7 @@
       <c r="M19" s="4" t="n"/>
       <c r="N19" s="4" t="n"/>
       <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1011,6 +1035,7 @@
       <c r="M20" s="4" t="n"/>
       <c r="N20" s="4" t="n"/>
       <c r="O20" s="4" t="n"/>
+      <c r="P20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -1032,6 +1057,7 @@
       <c r="M21" s="7" t="n"/>
       <c r="N21" s="7" t="n"/>
       <c r="O21" s="7" t="n"/>
+      <c r="P21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -1053,6 +1079,7 @@
       <c r="M22" s="7" t="n"/>
       <c r="N22" s="7" t="n"/>
       <c r="O22" s="7" t="n"/>
+      <c r="P22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1074,6 +1101,7 @@
       <c r="M23" s="4" t="n"/>
       <c r="N23" s="4" t="n"/>
       <c r="O23" s="4" t="n"/>
+      <c r="P23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1095,6 +1123,7 @@
       <c r="M24" s="4" t="n"/>
       <c r="N24" s="4" t="n"/>
       <c r="O24" s="4" t="n"/>
+      <c r="P24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1116,6 +1145,7 @@
       <c r="M25" s="4" t="n"/>
       <c r="N25" s="4" t="n"/>
       <c r="O25" s="4" t="n"/>
+      <c r="P25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1137,6 +1167,7 @@
       <c r="M26" s="4" t="n"/>
       <c r="N26" s="4" t="n"/>
       <c r="O26" s="4" t="n"/>
+      <c r="P26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1158,6 +1189,7 @@
       <c r="M27" s="4" t="n"/>
       <c r="N27" s="4" t="n"/>
       <c r="O27" s="4" t="n"/>
+      <c r="P27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -1179,6 +1211,7 @@
       <c r="M28" s="7" t="n"/>
       <c r="N28" s="7" t="n"/>
       <c r="O28" s="7" t="n"/>
+      <c r="P28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -1200,6 +1233,7 @@
       <c r="M29" s="7" t="n"/>
       <c r="N29" s="7" t="n"/>
       <c r="O29" s="7" t="n"/>
+      <c r="P29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -1221,6 +1255,7 @@
       <c r="M30" s="4" t="n"/>
       <c r="N30" s="4" t="n"/>
       <c r="O30" s="4" t="n"/>
+      <c r="P30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1242,6 +1277,7 @@
       <c r="M31" s="4" t="n"/>
       <c r="N31" s="4" t="n"/>
       <c r="O31" s="4" t="n"/>
+      <c r="P31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -1267,6 +1303,7 @@
       <c r="M32" s="4" t="n"/>
       <c r="N32" s="4" t="n"/>
       <c r="O32" s="4" t="n"/>
+      <c r="P32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -1292,6 +1329,7 @@
       <c r="M33" s="4" t="n"/>
       <c r="N33" s="4" t="n"/>
       <c r="O33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -1317,6 +1355,7 @@
       <c r="M34" s="4" t="n"/>
       <c r="N34" s="4" t="n"/>
       <c r="O34" s="4" t="n"/>
+      <c r="P34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -1338,6 +1377,7 @@
       <c r="M35" s="7" t="n"/>
       <c r="N35" s="7" t="n"/>
       <c r="O35" s="7" t="n"/>
+      <c r="P35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -1359,6 +1399,7 @@
       <c r="M36" s="7" t="n"/>
       <c r="N36" s="7" t="n"/>
       <c r="O36" s="7" t="n"/>
+      <c r="P36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1384,6 +1425,7 @@
       <c r="M37" s="4" t="n"/>
       <c r="N37" s="4" t="n"/>
       <c r="O37" s="4" t="n"/>
+      <c r="P37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -1409,6 +1451,7 @@
       <c r="M38" s="4" t="n"/>
       <c r="N38" s="4" t="n"/>
       <c r="O38" s="4" t="n"/>
+      <c r="P38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -1430,14 +1473,15 @@
       <c r="I39" s="4" t="n"/>
       <c r="J39" s="4" t="n"/>
       <c r="K39" s="4" t="n"/>
-      <c r="L39" s="5" t="inlineStr">
+      <c r="L39" s="4" t="n"/>
+      <c r="M39" s="5" t="inlineStr">
         <is>
           <t>Sick - Sick</t>
         </is>
       </c>
-      <c r="M39" s="4" t="n"/>
       <c r="N39" s="4" t="n"/>
       <c r="O39" s="4" t="n"/>
+      <c r="P39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -1455,14 +1499,15 @@
       <c r="I40" s="4" t="n"/>
       <c r="J40" s="4" t="n"/>
       <c r="K40" s="4" t="n"/>
-      <c r="L40" s="5" t="inlineStr">
+      <c r="L40" s="4" t="n"/>
+      <c r="M40" s="5" t="inlineStr">
         <is>
           <t>Sick - Sick</t>
         </is>
       </c>
-      <c r="M40" s="4" t="n"/>
       <c r="N40" s="4" t="n"/>
       <c r="O40" s="4" t="n"/>
+      <c r="P40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -1484,6 +1529,7 @@
       <c r="M41" s="4" t="n"/>
       <c r="N41" s="4" t="n"/>
       <c r="O41" s="4" t="n"/>
+      <c r="P41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -1505,6 +1551,7 @@
       <c r="M42" s="7" t="n"/>
       <c r="N42" s="7" t="n"/>
       <c r="O42" s="7" t="n"/>
+      <c r="P42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -1526,6 +1573,7 @@
       <c r="M43" s="7" t="n"/>
       <c r="N43" s="7" t="n"/>
       <c r="O43" s="7" t="n"/>
+      <c r="P43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -1547,6 +1595,7 @@
       <c r="M44" s="4" t="n"/>
       <c r="N44" s="4" t="n"/>
       <c r="O44" s="4" t="n"/>
+      <c r="P44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -1568,6 +1617,7 @@
       <c r="M45" s="4" t="n"/>
       <c r="N45" s="4" t="n"/>
       <c r="O45" s="4" t="n"/>
+      <c r="P45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -1589,6 +1639,7 @@
       <c r="M46" s="4" t="n"/>
       <c r="N46" s="4" t="n"/>
       <c r="O46" s="4" t="n"/>
+      <c r="P46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -1610,6 +1661,7 @@
       <c r="M47" s="4" t="n"/>
       <c r="N47" s="4" t="n"/>
       <c r="O47" s="4" t="n"/>
+      <c r="P47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -1631,6 +1683,7 @@
       <c r="M48" s="4" t="n"/>
       <c r="N48" s="4" t="n"/>
       <c r="O48" s="4" t="n"/>
+      <c r="P48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -1652,6 +1705,7 @@
       <c r="M49" s="7" t="n"/>
       <c r="N49" s="7" t="n"/>
       <c r="O49" s="7" t="n"/>
+      <c r="P49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -1673,6 +1727,7 @@
       <c r="M50" s="7" t="n"/>
       <c r="N50" s="7" t="n"/>
       <c r="O50" s="7" t="n"/>
+      <c r="P50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -1694,6 +1749,7 @@
       <c r="M51" s="4" t="n"/>
       <c r="N51" s="4" t="n"/>
       <c r="O51" s="4" t="n"/>
+      <c r="P51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -1715,6 +1771,7 @@
       <c r="M52" s="4" t="n"/>
       <c r="N52" s="4" t="n"/>
       <c r="O52" s="4" t="n"/>
+      <c r="P52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -1736,6 +1793,7 @@
       <c r="M53" s="4" t="n"/>
       <c r="N53" s="4" t="n"/>
       <c r="O53" s="4" t="n"/>
+      <c r="P53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -1757,6 +1815,7 @@
       <c r="M54" s="4" t="n"/>
       <c r="N54" s="4" t="n"/>
       <c r="O54" s="4" t="n"/>
+      <c r="P54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -1778,6 +1837,7 @@
       <c r="M55" s="4" t="n"/>
       <c r="N55" s="4" t="n"/>
       <c r="O55" s="4" t="n"/>
+      <c r="P55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -1799,6 +1859,7 @@
       <c r="M56" s="7" t="n"/>
       <c r="N56" s="7" t="n"/>
       <c r="O56" s="7" t="n"/>
+      <c r="P56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -1820,6 +1881,7 @@
       <c r="M57" s="7" t="n"/>
       <c r="N57" s="7" t="n"/>
       <c r="O57" s="7" t="n"/>
+      <c r="P57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -1837,14 +1899,15 @@
       <c r="I58" s="4" t="n"/>
       <c r="J58" s="4" t="n"/>
       <c r="K58" s="4" t="n"/>
-      <c r="L58" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M58" s="4" t="n"/>
+      <c r="L58" s="4" t="n"/>
+      <c r="M58" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N58" s="4" t="n"/>
       <c r="O58" s="4" t="n"/>
+      <c r="P58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -1862,14 +1925,15 @@
       <c r="I59" s="4" t="n"/>
       <c r="J59" s="4" t="n"/>
       <c r="K59" s="4" t="n"/>
-      <c r="L59" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M59" s="4" t="n"/>
+      <c r="L59" s="4" t="n"/>
+      <c r="M59" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N59" s="4" t="n"/>
       <c r="O59" s="4" t="n"/>
+      <c r="P59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -1891,6 +1955,7 @@
       <c r="M60" s="4" t="n"/>
       <c r="N60" s="4" t="n"/>
       <c r="O60" s="4" t="n"/>
+      <c r="P60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -1912,6 +1977,7 @@
       <c r="M61" s="4" t="n"/>
       <c r="N61" s="4" t="n"/>
       <c r="O61" s="4" t="n"/>
+      <c r="P61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -1933,6 +1999,7 @@
       <c r="M62" s="4" t="n"/>
       <c r="N62" s="4" t="n"/>
       <c r="O62" s="4" t="n"/>
+      <c r="P62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -1954,6 +2021,7 @@
       <c r="M63" s="7" t="n"/>
       <c r="N63" s="7" t="n"/>
       <c r="O63" s="7" t="n"/>
+      <c r="P63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
@@ -1975,6 +2043,7 @@
       <c r="M64" s="7" t="n"/>
       <c r="N64" s="7" t="n"/>
       <c r="O64" s="7" t="n"/>
+      <c r="P64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -2004,14 +2073,15 @@
         </is>
       </c>
       <c r="K65" s="4" t="n"/>
-      <c r="L65" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M65" s="4" t="n"/>
+      <c r="L65" s="4" t="n"/>
+      <c r="M65" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N65" s="4" t="n"/>
       <c r="O65" s="4" t="n"/>
+      <c r="P65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -2041,14 +2111,15 @@
         </is>
       </c>
       <c r="K66" s="4" t="n"/>
-      <c r="L66" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M66" s="4" t="n"/>
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N66" s="4" t="n"/>
       <c r="O66" s="4" t="n"/>
+      <c r="P66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -2078,14 +2149,15 @@
         </is>
       </c>
       <c r="K67" s="4" t="n"/>
-      <c r="L67" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M67" s="4" t="n"/>
+      <c r="L67" s="4" t="n"/>
+      <c r="M67" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N67" s="4" t="n"/>
       <c r="O67" s="4" t="n"/>
+      <c r="P67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -2107,6 +2179,7 @@
       <c r="M68" s="4" t="n"/>
       <c r="N68" s="4" t="n"/>
       <c r="O68" s="4" t="n"/>
+      <c r="P68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -2136,14 +2209,15 @@
         </is>
       </c>
       <c r="K69" s="4" t="n"/>
-      <c r="L69" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M69" s="4" t="n"/>
+      <c r="L69" s="4" t="n"/>
+      <c r="M69" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N69" s="4" t="n"/>
       <c r="O69" s="4" t="n"/>
+      <c r="P69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -2165,6 +2239,7 @@
       <c r="M70" s="7" t="n"/>
       <c r="N70" s="7" t="n"/>
       <c r="O70" s="7" t="n"/>
+      <c r="P70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -2186,6 +2261,7 @@
       <c r="M71" s="7" t="n"/>
       <c r="N71" s="7" t="n"/>
       <c r="O71" s="7" t="n"/>
+      <c r="P71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -2215,6 +2291,7 @@
       <c r="M72" s="4" t="n"/>
       <c r="N72" s="4" t="n"/>
       <c r="O72" s="4" t="n"/>
+      <c r="P72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -2240,14 +2317,15 @@
         </is>
       </c>
       <c r="K73" s="4" t="n"/>
-      <c r="L73" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M73" s="4" t="n"/>
+      <c r="L73" s="4" t="n"/>
+      <c r="M73" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N73" s="4" t="n"/>
       <c r="O73" s="4" t="n"/>
+      <c r="P73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -2277,6 +2355,7 @@
       <c r="M74" s="4" t="n"/>
       <c r="N74" s="4" t="n"/>
       <c r="O74" s="4" t="n"/>
+      <c r="P74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -2302,14 +2381,15 @@
         </is>
       </c>
       <c r="K75" s="4" t="n"/>
-      <c r="L75" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M75" s="4" t="n"/>
+      <c r="L75" s="4" t="n"/>
+      <c r="M75" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N75" s="4" t="n"/>
       <c r="O75" s="4" t="n"/>
+      <c r="P75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -2335,14 +2415,15 @@
         </is>
       </c>
       <c r="K76" s="4" t="n"/>
-      <c r="L76" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M76" s="4" t="n"/>
+      <c r="L76" s="4" t="n"/>
+      <c r="M76" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N76" s="4" t="n"/>
       <c r="O76" s="4" t="n"/>
+      <c r="P76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
@@ -2364,6 +2445,7 @@
       <c r="M77" s="7" t="n"/>
       <c r="N77" s="7" t="n"/>
       <c r="O77" s="7" t="n"/>
+      <c r="P77" s="7" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
@@ -2385,6 +2467,7 @@
       <c r="M78" s="7" t="n"/>
       <c r="N78" s="7" t="n"/>
       <c r="O78" s="7" t="n"/>
+      <c r="P78" s="7" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -2406,6 +2489,7 @@
       <c r="M79" s="4" t="n"/>
       <c r="N79" s="4" t="n"/>
       <c r="O79" s="4" t="n"/>
+      <c r="P79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -2427,6 +2511,7 @@
       <c r="M80" s="4" t="n"/>
       <c r="N80" s="4" t="n"/>
       <c r="O80" s="4" t="n"/>
+      <c r="P80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -2448,6 +2533,7 @@
       <c r="M81" s="4" t="n"/>
       <c r="N81" s="4" t="n"/>
       <c r="O81" s="4" t="n"/>
+      <c r="P81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -2469,6 +2555,7 @@
       <c r="M82" s="4" t="n"/>
       <c r="N82" s="4" t="n"/>
       <c r="O82" s="4" t="n"/>
+      <c r="P82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -2490,6 +2577,7 @@
       <c r="M83" s="4" t="n"/>
       <c r="N83" s="4" t="n"/>
       <c r="O83" s="4" t="n"/>
+      <c r="P83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
@@ -2511,6 +2599,7 @@
       <c r="M84" s="7" t="n"/>
       <c r="N84" s="7" t="n"/>
       <c r="O84" s="7" t="n"/>
+      <c r="P84" s="7" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
@@ -2532,6 +2621,7 @@
       <c r="M85" s="7" t="n"/>
       <c r="N85" s="7" t="n"/>
       <c r="O85" s="7" t="n"/>
+      <c r="P85" s="7" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -2551,12 +2641,13 @@
       <c r="K86" s="4" t="n"/>
       <c r="L86" s="4" t="n"/>
       <c r="M86" s="4" t="n"/>
-      <c r="N86" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O86" s="4" t="n"/>
+      <c r="N86" s="4" t="n"/>
+      <c r="O86" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -2576,12 +2667,13 @@
       <c r="K87" s="4" t="n"/>
       <c r="L87" s="4" t="n"/>
       <c r="M87" s="4" t="n"/>
-      <c r="N87" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O87" s="4" t="n"/>
+      <c r="N87" s="4" t="n"/>
+      <c r="O87" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -2601,12 +2693,13 @@
       <c r="K88" s="4" t="n"/>
       <c r="L88" s="4" t="n"/>
       <c r="M88" s="4" t="n"/>
-      <c r="N88" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O88" s="4" t="n"/>
+      <c r="N88" s="4" t="n"/>
+      <c r="O88" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -2626,12 +2719,13 @@
       <c r="K89" s="4" t="n"/>
       <c r="L89" s="4" t="n"/>
       <c r="M89" s="4" t="n"/>
-      <c r="N89" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O89" s="4" t="n"/>
+      <c r="N89" s="4" t="n"/>
+      <c r="O89" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
@@ -2651,12 +2745,13 @@
       <c r="K90" s="4" t="n"/>
       <c r="L90" s="4" t="n"/>
       <c r="M90" s="4" t="n"/>
-      <c r="N90" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O90" s="4" t="n"/>
+      <c r="N90" s="4" t="n"/>
+      <c r="O90" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
@@ -2678,6 +2773,7 @@
       <c r="M91" s="7" t="n"/>
       <c r="N91" s="7" t="n"/>
       <c r="O91" s="7" t="n"/>
+      <c r="P91" s="7" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
@@ -2699,6 +2795,7 @@
       <c r="M92" s="7" t="n"/>
       <c r="N92" s="7" t="n"/>
       <c r="O92" s="7" t="n"/>
+      <c r="P92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -2720,6 +2817,7 @@
       <c r="M93" s="4" t="n"/>
       <c r="N93" s="4" t="n"/>
       <c r="O93" s="4" t="n"/>
+      <c r="P93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -2741,6 +2839,7 @@
       <c r="M94" s="4" t="n"/>
       <c r="N94" s="4" t="n"/>
       <c r="O94" s="4" t="n"/>
+      <c r="P94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -2762,6 +2861,7 @@
       <c r="M95" s="4" t="n"/>
       <c r="N95" s="4" t="n"/>
       <c r="O95" s="4" t="n"/>
+      <c r="P95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
@@ -2783,6 +2883,7 @@
       <c r="M96" s="4" t="n"/>
       <c r="N96" s="4" t="n"/>
       <c r="O96" s="4" t="n"/>
+      <c r="P96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -2804,6 +2905,7 @@
       <c r="M97" s="4" t="n"/>
       <c r="N97" s="4" t="n"/>
       <c r="O97" s="4" t="n"/>
+      <c r="P97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
@@ -2825,6 +2927,7 @@
       <c r="M98" s="7" t="n"/>
       <c r="N98" s="7" t="n"/>
       <c r="O98" s="7" t="n"/>
+      <c r="P98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
@@ -2846,6 +2949,7 @@
       <c r="M99" s="7" t="n"/>
       <c r="N99" s="7" t="n"/>
       <c r="O99" s="7" t="n"/>
+      <c r="P99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -2867,6 +2971,7 @@
       <c r="M100" s="4" t="n"/>
       <c r="N100" s="4" t="n"/>
       <c r="O100" s="4" t="n"/>
+      <c r="P100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -2888,6 +2993,7 @@
       <c r="M101" s="4" t="n"/>
       <c r="N101" s="4" t="n"/>
       <c r="O101" s="4" t="n"/>
+      <c r="P101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -2909,6 +3015,7 @@
       <c r="M102" s="4" t="n"/>
       <c r="N102" s="4" t="n"/>
       <c r="O102" s="4" t="n"/>
+      <c r="P102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -2930,6 +3037,7 @@
       <c r="M103" s="4" t="n"/>
       <c r="N103" s="4" t="n"/>
       <c r="O103" s="4" t="n"/>
+      <c r="P103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -2951,6 +3059,7 @@
       <c r="M104" s="4" t="n"/>
       <c r="N104" s="4" t="n"/>
       <c r="O104" s="4" t="n"/>
+      <c r="P104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
@@ -2972,6 +3081,7 @@
       <c r="M105" s="7" t="n"/>
       <c r="N105" s="7" t="n"/>
       <c r="O105" s="7" t="n"/>
+      <c r="P105" s="7" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
@@ -2993,6 +3103,7 @@
       <c r="M106" s="7" t="n"/>
       <c r="N106" s="7" t="n"/>
       <c r="O106" s="7" t="n"/>
+      <c r="P106" s="7" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -3014,6 +3125,7 @@
       <c r="M107" s="4" t="n"/>
       <c r="N107" s="4" t="n"/>
       <c r="O107" s="4" t="n"/>
+      <c r="P107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -3035,6 +3147,7 @@
       <c r="M108" s="4" t="n"/>
       <c r="N108" s="4" t="n"/>
       <c r="O108" s="4" t="n"/>
+      <c r="P108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -3056,6 +3169,7 @@
       <c r="M109" s="4" t="n"/>
       <c r="N109" s="4" t="n"/>
       <c r="O109" s="4" t="n"/>
+      <c r="P109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
@@ -3077,6 +3191,7 @@
       <c r="M110" s="4" t="n"/>
       <c r="N110" s="4" t="n"/>
       <c r="O110" s="4" t="n"/>
+      <c r="P110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -3098,6 +3213,7 @@
       <c r="M111" s="4" t="n"/>
       <c r="N111" s="4" t="n"/>
       <c r="O111" s="4" t="n"/>
+      <c r="P111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
@@ -3119,6 +3235,7 @@
       <c r="M112" s="7" t="n"/>
       <c r="N112" s="7" t="n"/>
       <c r="O112" s="7" t="n"/>
+      <c r="P112" s="7" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
@@ -3140,6 +3257,7 @@
       <c r="M113" s="7" t="n"/>
       <c r="N113" s="7" t="n"/>
       <c r="O113" s="7" t="n"/>
+      <c r="P113" s="7" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -3161,6 +3279,7 @@
       <c r="M114" s="4" t="n"/>
       <c r="N114" s="4" t="n"/>
       <c r="O114" s="4" t="n"/>
+      <c r="P114" s="4" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -3182,6 +3301,7 @@
       <c r="M115" s="4" t="n"/>
       <c r="N115" s="4" t="n"/>
       <c r="O115" s="4" t="n"/>
+      <c r="P115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -3203,6 +3323,7 @@
       <c r="M116" s="4" t="n"/>
       <c r="N116" s="4" t="n"/>
       <c r="O116" s="4" t="n"/>
+      <c r="P116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -3224,6 +3345,7 @@
       <c r="M117" s="4" t="n"/>
       <c r="N117" s="4" t="n"/>
       <c r="O117" s="4" t="n"/>
+      <c r="P117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
@@ -3245,6 +3367,7 @@
       <c r="M118" s="4" t="n"/>
       <c r="N118" s="4" t="n"/>
       <c r="O118" s="4" t="n"/>
+      <c r="P118" s="4" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
@@ -3266,6 +3389,7 @@
       <c r="M119" s="7" t="n"/>
       <c r="N119" s="7" t="n"/>
       <c r="O119" s="7" t="n"/>
+      <c r="P119" s="7" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
@@ -3287,6 +3411,7 @@
       <c r="M120" s="7" t="n"/>
       <c r="N120" s="7" t="n"/>
       <c r="O120" s="7" t="n"/>
+      <c r="P120" s="7" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -3308,6 +3433,7 @@
       <c r="M121" s="4" t="n"/>
       <c r="N121" s="4" t="n"/>
       <c r="O121" s="4" t="n"/>
+      <c r="P121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -3333,6 +3459,7 @@
       <c r="M122" s="4" t="n"/>
       <c r="N122" s="4" t="n"/>
       <c r="O122" s="4" t="n"/>
+      <c r="P122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -3358,6 +3485,7 @@
       <c r="M123" s="4" t="n"/>
       <c r="N123" s="4" t="n"/>
       <c r="O123" s="4" t="n"/>
+      <c r="P123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -3379,6 +3507,7 @@
       <c r="M124" s="4" t="n"/>
       <c r="N124" s="4" t="n"/>
       <c r="O124" s="4" t="n"/>
+      <c r="P124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -3400,6 +3529,7 @@
       <c r="M125" s="4" t="n"/>
       <c r="N125" s="4" t="n"/>
       <c r="O125" s="4" t="n"/>
+      <c r="P125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
@@ -3421,6 +3551,7 @@
       <c r="M126" s="7" t="n"/>
       <c r="N126" s="7" t="n"/>
       <c r="O126" s="7" t="n"/>
+      <c r="P126" s="7" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
@@ -3442,6 +3573,7 @@
       <c r="M127" s="7" t="n"/>
       <c r="N127" s="7" t="n"/>
       <c r="O127" s="7" t="n"/>
+      <c r="P127" s="7" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
@@ -3463,6 +3595,7 @@
       <c r="M128" s="4" t="n"/>
       <c r="N128" s="4" t="n"/>
       <c r="O128" s="4" t="n"/>
+      <c r="P128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -3484,6 +3617,7 @@
       <c r="M129" s="4" t="n"/>
       <c r="N129" s="4" t="n"/>
       <c r="O129" s="4" t="n"/>
+      <c r="P129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
@@ -3505,6 +3639,7 @@
       <c r="M130" s="4" t="n"/>
       <c r="N130" s="4" t="n"/>
       <c r="O130" s="4" t="n"/>
+      <c r="P130" s="4" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
@@ -3526,6 +3661,7 @@
       <c r="M131" s="4" t="n"/>
       <c r="N131" s="4" t="n"/>
       <c r="O131" s="4" t="n"/>
+      <c r="P131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -3547,6 +3683,7 @@
       <c r="M132" s="4" t="n"/>
       <c r="N132" s="4" t="n"/>
       <c r="O132" s="4" t="n"/>
+      <c r="P132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
@@ -3568,6 +3705,7 @@
       <c r="M133" s="7" t="n"/>
       <c r="N133" s="7" t="n"/>
       <c r="O133" s="7" t="n"/>
+      <c r="P133" s="7" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
@@ -3589,6 +3727,7 @@
       <c r="M134" s="7" t="n"/>
       <c r="N134" s="7" t="n"/>
       <c r="O134" s="7" t="n"/>
+      <c r="P134" s="7" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -3610,6 +3749,7 @@
       <c r="M135" s="4" t="n"/>
       <c r="N135" s="4" t="n"/>
       <c r="O135" s="4" t="n"/>
+      <c r="P135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
@@ -3631,6 +3771,7 @@
       <c r="M136" s="4" t="n"/>
       <c r="N136" s="4" t="n"/>
       <c r="O136" s="4" t="n"/>
+      <c r="P136" s="4" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -3652,6 +3793,7 @@
       <c r="M137" s="4" t="n"/>
       <c r="N137" s="4" t="n"/>
       <c r="O137" s="4" t="n"/>
+      <c r="P137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
@@ -3671,12 +3813,13 @@
       <c r="K138" s="4" t="n"/>
       <c r="L138" s="4" t="n"/>
       <c r="M138" s="4" t="n"/>
-      <c r="N138" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O138" s="4" t="n"/>
+      <c r="N138" s="4" t="n"/>
+      <c r="O138" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P138" s="4" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
@@ -3696,12 +3839,13 @@
       <c r="K139" s="4" t="n"/>
       <c r="L139" s="4" t="n"/>
       <c r="M139" s="4" t="n"/>
-      <c r="N139" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O139" s="4" t="n"/>
+      <c r="N139" s="4" t="n"/>
+      <c r="O139" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
@@ -3723,6 +3867,7 @@
       <c r="M140" s="7" t="n"/>
       <c r="N140" s="7" t="n"/>
       <c r="O140" s="7" t="n"/>
+      <c r="P140" s="7" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
@@ -3744,6 +3889,7 @@
       <c r="M141" s="7" t="n"/>
       <c r="N141" s="7" t="n"/>
       <c r="O141" s="7" t="n"/>
+      <c r="P141" s="7" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
@@ -3763,12 +3909,13 @@
       <c r="K142" s="4" t="n"/>
       <c r="L142" s="4" t="n"/>
       <c r="M142" s="4" t="n"/>
-      <c r="N142" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O142" s="4" t="n"/>
+      <c r="N142" s="4" t="n"/>
+      <c r="O142" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P142" s="4" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -3790,6 +3937,7 @@
       <c r="M143" s="4" t="n"/>
       <c r="N143" s="4" t="n"/>
       <c r="O143" s="4" t="n"/>
+      <c r="P143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
@@ -3811,6 +3959,7 @@
       <c r="M144" s="4" t="n"/>
       <c r="N144" s="4" t="n"/>
       <c r="O144" s="4" t="n"/>
+      <c r="P144" s="4" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -3832,6 +3981,7 @@
       <c r="M145" s="4" t="n"/>
       <c r="N145" s="4" t="n"/>
       <c r="O145" s="4" t="n"/>
+      <c r="P145" s="4" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
@@ -3857,6 +4007,7 @@
       <c r="M146" s="4" t="n"/>
       <c r="N146" s="4" t="n"/>
       <c r="O146" s="4" t="n"/>
+      <c r="P146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
@@ -3878,6 +4029,7 @@
       <c r="M147" s="7" t="n"/>
       <c r="N147" s="7" t="n"/>
       <c r="O147" s="7" t="n"/>
+      <c r="P147" s="7" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
@@ -3899,6 +4051,7 @@
       <c r="M148" s="7" t="n"/>
       <c r="N148" s="7" t="n"/>
       <c r="O148" s="7" t="n"/>
+      <c r="P148" s="7" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
@@ -3924,6 +4077,7 @@
       <c r="M149" s="4" t="n"/>
       <c r="N149" s="4" t="n"/>
       <c r="O149" s="4" t="n"/>
+      <c r="P149" s="4" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
@@ -3949,6 +4103,7 @@
       <c r="M150" s="4" t="n"/>
       <c r="N150" s="4" t="n"/>
       <c r="O150" s="4" t="n"/>
+      <c r="P150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -3970,6 +4125,7 @@
       <c r="M151" s="4" t="n"/>
       <c r="N151" s="4" t="n"/>
       <c r="O151" s="4" t="n"/>
+      <c r="P151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
@@ -3991,6 +4147,7 @@
       <c r="M152" s="4" t="n"/>
       <c r="N152" s="4" t="n"/>
       <c r="O152" s="4" t="n"/>
+      <c r="P152" s="4" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -4012,6 +4169,7 @@
       <c r="M153" s="4" t="n"/>
       <c r="N153" s="4" t="n"/>
       <c r="O153" s="4" t="n"/>
+      <c r="P153" s="4" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
@@ -4033,6 +4191,7 @@
       <c r="M154" s="7" t="n"/>
       <c r="N154" s="7" t="n"/>
       <c r="O154" s="7" t="n"/>
+      <c r="P154" s="7" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
@@ -4054,6 +4213,7 @@
       <c r="M155" s="7" t="n"/>
       <c r="N155" s="7" t="n"/>
       <c r="O155" s="7" t="n"/>
+      <c r="P155" s="7" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
@@ -4075,6 +4235,7 @@
       <c r="M156" s="4" t="n"/>
       <c r="N156" s="4" t="n"/>
       <c r="O156" s="4" t="n"/>
+      <c r="P156" s="4" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
@@ -4096,6 +4257,7 @@
       <c r="M157" s="4" t="n"/>
       <c r="N157" s="4" t="n"/>
       <c r="O157" s="4" t="n"/>
+      <c r="P157" s="4" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
@@ -4117,6 +4279,7 @@
       <c r="M158" s="4" t="n"/>
       <c r="N158" s="4" t="n"/>
       <c r="O158" s="4" t="n"/>
+      <c r="P158" s="4" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -4138,6 +4301,7 @@
       <c r="M159" s="4" t="n"/>
       <c r="N159" s="4" t="n"/>
       <c r="O159" s="4" t="n"/>
+      <c r="P159" s="4" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
@@ -4159,6 +4323,7 @@
       <c r="M160" s="4" t="n"/>
       <c r="N160" s="4" t="n"/>
       <c r="O160" s="4" t="n"/>
+      <c r="P160" s="4" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
@@ -4180,6 +4345,7 @@
       <c r="M161" s="7" t="n"/>
       <c r="N161" s="7" t="n"/>
       <c r="O161" s="7" t="n"/>
+      <c r="P161" s="7" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
@@ -4201,6 +4367,7 @@
       <c r="M162" s="7" t="n"/>
       <c r="N162" s="7" t="n"/>
       <c r="O162" s="7" t="n"/>
+      <c r="P162" s="7" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -4226,6 +4393,7 @@
       <c r="M163" s="4" t="n"/>
       <c r="N163" s="4" t="n"/>
       <c r="O163" s="4" t="n"/>
+      <c r="P163" s="4" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
@@ -4247,6 +4415,7 @@
       <c r="M164" s="4" t="n"/>
       <c r="N164" s="4" t="n"/>
       <c r="O164" s="4" t="n"/>
+      <c r="P164" s="4" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -4276,6 +4445,7 @@
       <c r="M165" s="4" t="n"/>
       <c r="N165" s="4" t="n"/>
       <c r="O165" s="4" t="n"/>
+      <c r="P165" s="4" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
@@ -4305,6 +4475,7 @@
       <c r="M166" s="4" t="n"/>
       <c r="N166" s="4" t="n"/>
       <c r="O166" s="4" t="n"/>
+      <c r="P166" s="4" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
@@ -4337,7 +4508,8 @@
       <c r="L167" s="4" t="n"/>
       <c r="M167" s="4" t="n"/>
       <c r="N167" s="4" t="n"/>
-      <c r="O167" s="8" t="inlineStr">
+      <c r="O167" s="4" t="n"/>
+      <c r="P167" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -4363,6 +4535,7 @@
       <c r="M168" s="7" t="n"/>
       <c r="N168" s="7" t="n"/>
       <c r="O168" s="7" t="n"/>
+      <c r="P168" s="7" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
@@ -4384,6 +4557,7 @@
       <c r="M169" s="7" t="n"/>
       <c r="N169" s="7" t="n"/>
       <c r="O169" s="7" t="n"/>
+      <c r="P169" s="7" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
@@ -4408,7 +4582,8 @@
       <c r="L170" s="4" t="n"/>
       <c r="M170" s="4" t="n"/>
       <c r="N170" s="4" t="n"/>
-      <c r="O170" s="8" t="inlineStr">
+      <c r="O170" s="4" t="n"/>
+      <c r="P170" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -4438,6 +4613,7 @@
       <c r="M171" s="4" t="n"/>
       <c r="N171" s="4" t="n"/>
       <c r="O171" s="4" t="n"/>
+      <c r="P171" s="4" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
@@ -4463,6 +4639,7 @@
       <c r="M172" s="4" t="n"/>
       <c r="N172" s="4" t="n"/>
       <c r="O172" s="4" t="n"/>
+      <c r="P172" s="4" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -4488,6 +4665,7 @@
       <c r="M173" s="4" t="n"/>
       <c r="N173" s="4" t="n"/>
       <c r="O173" s="4" t="n"/>
+      <c r="P173" s="4" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
@@ -4513,6 +4691,7 @@
       <c r="M174" s="4" t="n"/>
       <c r="N174" s="4" t="n"/>
       <c r="O174" s="4" t="n"/>
+      <c r="P174" s="4" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
@@ -4534,6 +4713,7 @@
       <c r="M175" s="7" t="n"/>
       <c r="N175" s="7" t="n"/>
       <c r="O175" s="7" t="n"/>
+      <c r="P175" s="7" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="6" t="inlineStr">
@@ -4555,6 +4735,7 @@
       <c r="M176" s="7" t="n"/>
       <c r="N176" s="7" t="n"/>
       <c r="O176" s="7" t="n"/>
+      <c r="P176" s="7" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
@@ -4576,6 +4757,7 @@
       <c r="M177" s="4" t="n"/>
       <c r="N177" s="4" t="n"/>
       <c r="O177" s="4" t="n"/>
+      <c r="P177" s="4" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
@@ -4597,6 +4779,7 @@
       <c r="M178" s="4" t="n"/>
       <c r="N178" s="4" t="n"/>
       <c r="O178" s="4" t="n"/>
+      <c r="P178" s="4" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
@@ -4618,6 +4801,7 @@
       <c r="M179" s="4" t="n"/>
       <c r="N179" s="4" t="n"/>
       <c r="O179" s="4" t="n"/>
+      <c r="P179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
@@ -4639,6 +4823,7 @@
       <c r="M180" s="4" t="n"/>
       <c r="N180" s="4" t="n"/>
       <c r="O180" s="4" t="n"/>
+      <c r="P180" s="4" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -4660,6 +4845,7 @@
       <c r="M181" s="4" t="n"/>
       <c r="N181" s="4" t="n"/>
       <c r="O181" s="4" t="n"/>
+      <c r="P181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="6" t="inlineStr">
@@ -4681,6 +4867,7 @@
       <c r="M182" s="7" t="n"/>
       <c r="N182" s="7" t="n"/>
       <c r="O182" s="7" t="n"/>
+      <c r="P182" s="7" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
@@ -4702,6 +4889,7 @@
       <c r="M183" s="7" t="n"/>
       <c r="N183" s="7" t="n"/>
       <c r="O183" s="7" t="n"/>
+      <c r="P183" s="7" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
@@ -4723,6 +4911,7 @@
       <c r="M184" s="4" t="n"/>
       <c r="N184" s="4" t="n"/>
       <c r="O184" s="4" t="n"/>
+      <c r="P184" s="4" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -4744,6 +4933,7 @@
       <c r="M185" s="4" t="n"/>
       <c r="N185" s="4" t="n"/>
       <c r="O185" s="4" t="n"/>
+      <c r="P185" s="4" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
@@ -4765,6 +4955,7 @@
       <c r="M186" s="4" t="n"/>
       <c r="N186" s="4" t="n"/>
       <c r="O186" s="4" t="n"/>
+      <c r="P186" s="4" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -4786,6 +4977,7 @@
       <c r="M187" s="4" t="n"/>
       <c r="N187" s="4" t="n"/>
       <c r="O187" s="4" t="n"/>
+      <c r="P187" s="4" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
@@ -4807,6 +4999,7 @@
       <c r="M188" s="4" t="n"/>
       <c r="N188" s="4" t="n"/>
       <c r="O188" s="4" t="n"/>
+      <c r="P188" s="4" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
@@ -4828,6 +5021,7 @@
       <c r="M189" s="7" t="n"/>
       <c r="N189" s="7" t="n"/>
       <c r="O189" s="7" t="n"/>
+      <c r="P189" s="7" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="6" t="inlineStr">
@@ -4849,6 +5043,7 @@
       <c r="M190" s="7" t="n"/>
       <c r="N190" s="7" t="n"/>
       <c r="O190" s="7" t="n"/>
+      <c r="P190" s="7" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
@@ -4870,6 +5065,7 @@
       <c r="M191" s="4" t="n"/>
       <c r="N191" s="4" t="n"/>
       <c r="O191" s="4" t="n"/>
+      <c r="P191" s="4" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
@@ -4891,6 +5087,7 @@
       <c r="M192" s="4" t="n"/>
       <c r="N192" s="4" t="n"/>
       <c r="O192" s="4" t="n"/>
+      <c r="P192" s="4" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
@@ -4912,6 +5109,7 @@
       <c r="M193" s="4" t="n"/>
       <c r="N193" s="4" t="n"/>
       <c r="O193" s="4" t="n"/>
+      <c r="P193" s="4" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
@@ -4933,6 +5131,7 @@
       <c r="M194" s="4" t="n"/>
       <c r="N194" s="4" t="n"/>
       <c r="O194" s="4" t="n"/>
+      <c r="P194" s="4" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -4958,6 +5157,7 @@
       <c r="M195" s="4" t="n"/>
       <c r="N195" s="4" t="n"/>
       <c r="O195" s="4" t="n"/>
+      <c r="P195" s="4" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="6" t="inlineStr">
@@ -4979,6 +5179,7 @@
       <c r="M196" s="7" t="n"/>
       <c r="N196" s="7" t="n"/>
       <c r="O196" s="7" t="n"/>
+      <c r="P196" s="7" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
@@ -5000,6 +5201,7 @@
       <c r="M197" s="7" t="n"/>
       <c r="N197" s="7" t="n"/>
       <c r="O197" s="7" t="n"/>
+      <c r="P197" s="7" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
@@ -5025,6 +5227,7 @@
       <c r="M198" s="4" t="n"/>
       <c r="N198" s="4" t="n"/>
       <c r="O198" s="4" t="n"/>
+      <c r="P198" s="4" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -5050,6 +5253,7 @@
       <c r="M199" s="4" t="n"/>
       <c r="N199" s="4" t="n"/>
       <c r="O199" s="4" t="n"/>
+      <c r="P199" s="4" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
@@ -5071,6 +5275,7 @@
       <c r="M200" s="4" t="n"/>
       <c r="N200" s="4" t="n"/>
       <c r="O200" s="4" t="n"/>
+      <c r="P200" s="4" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
@@ -5092,6 +5297,7 @@
       <c r="M201" s="4" t="n"/>
       <c r="N201" s="4" t="n"/>
       <c r="O201" s="4" t="n"/>
+      <c r="P201" s="4" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
@@ -5113,6 +5319,7 @@
       <c r="M202" s="4" t="n"/>
       <c r="N202" s="4" t="n"/>
       <c r="O202" s="4" t="n"/>
+      <c r="P202" s="4" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
@@ -5134,6 +5341,7 @@
       <c r="M203" s="7" t="n"/>
       <c r="N203" s="7" t="n"/>
       <c r="O203" s="7" t="n"/>
+      <c r="P203" s="7" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="6" t="inlineStr">
@@ -5155,6 +5363,7 @@
       <c r="M204" s="7" t="n"/>
       <c r="N204" s="7" t="n"/>
       <c r="O204" s="7" t="n"/>
+      <c r="P204" s="7" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
@@ -5176,6 +5385,7 @@
       <c r="M205" s="4" t="n"/>
       <c r="N205" s="4" t="n"/>
       <c r="O205" s="4" t="n"/>
+      <c r="P205" s="4" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
@@ -5197,6 +5407,7 @@
       <c r="M206" s="4" t="n"/>
       <c r="N206" s="4" t="n"/>
       <c r="O206" s="4" t="n"/>
+      <c r="P206" s="4" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
@@ -5218,6 +5429,7 @@
       <c r="M207" s="4" t="n"/>
       <c r="N207" s="4" t="n"/>
       <c r="O207" s="4" t="n"/>
+      <c r="P207" s="4" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
@@ -5239,6 +5451,7 @@
       <c r="M208" s="4" t="n"/>
       <c r="N208" s="4" t="n"/>
       <c r="O208" s="4" t="n"/>
+      <c r="P208" s="4" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
@@ -5260,6 +5473,7 @@
       <c r="M209" s="4" t="n"/>
       <c r="N209" s="4" t="n"/>
       <c r="O209" s="4" t="n"/>
+      <c r="P209" s="4" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="6" t="inlineStr">
@@ -5281,6 +5495,7 @@
       <c r="M210" s="7" t="n"/>
       <c r="N210" s="7" t="n"/>
       <c r="O210" s="7" t="n"/>
+      <c r="P210" s="7" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
@@ -5302,6 +5517,7 @@
       <c r="M211" s="7" t="n"/>
       <c r="N211" s="7" t="n"/>
       <c r="O211" s="7" t="n"/>
+      <c r="P211" s="7" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
@@ -5323,6 +5539,7 @@
       <c r="M212" s="4" t="n"/>
       <c r="N212" s="4" t="n"/>
       <c r="O212" s="4" t="n"/>
+      <c r="P212" s="4" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
@@ -5344,6 +5561,7 @@
       <c r="M213" s="4" t="n"/>
       <c r="N213" s="4" t="n"/>
       <c r="O213" s="4" t="n"/>
+      <c r="P213" s="4" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
@@ -5365,6 +5583,7 @@
       <c r="M214" s="4" t="n"/>
       <c r="N214" s="4" t="n"/>
       <c r="O214" s="4" t="n"/>
+      <c r="P214" s="4" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
@@ -5386,6 +5605,7 @@
       <c r="M215" s="4" t="n"/>
       <c r="N215" s="4" t="n"/>
       <c r="O215" s="4" t="n"/>
+      <c r="P215" s="4" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
@@ -5407,6 +5627,7 @@
       <c r="M216" s="4" t="n"/>
       <c r="N216" s="4" t="n"/>
       <c r="O216" s="4" t="n"/>
+      <c r="P216" s="4" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
@@ -5428,6 +5649,7 @@
       <c r="M217" s="7" t="n"/>
       <c r="N217" s="7" t="n"/>
       <c r="O217" s="7" t="n"/>
+      <c r="P217" s="7" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="6" t="inlineStr">
@@ -5449,6 +5671,7 @@
       <c r="M218" s="7" t="n"/>
       <c r="N218" s="7" t="n"/>
       <c r="O218" s="7" t="n"/>
+      <c r="P218" s="7" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
@@ -5478,6 +5701,7 @@
       <c r="M219" s="4" t="n"/>
       <c r="N219" s="4" t="n"/>
       <c r="O219" s="4" t="n"/>
+      <c r="P219" s="4" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
@@ -5507,6 +5731,7 @@
       <c r="M220" s="4" t="n"/>
       <c r="N220" s="4" t="n"/>
       <c r="O220" s="4" t="n"/>
+      <c r="P220" s="4" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
@@ -5536,6 +5761,7 @@
       <c r="M221" s="4" t="n"/>
       <c r="N221" s="4" t="n"/>
       <c r="O221" s="4" t="n"/>
+      <c r="P221" s="4" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
@@ -5561,6 +5787,7 @@
       <c r="M222" s="4" t="n"/>
       <c r="N222" s="4" t="n"/>
       <c r="O222" s="4" t="n"/>
+      <c r="P222" s="4" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
@@ -5586,6 +5813,7 @@
       <c r="M223" s="4" t="n"/>
       <c r="N223" s="4" t="n"/>
       <c r="O223" s="4" t="n"/>
+      <c r="P223" s="4" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="6" t="inlineStr">
@@ -5607,6 +5835,7 @@
       <c r="M224" s="7" t="n"/>
       <c r="N224" s="7" t="n"/>
       <c r="O224" s="7" t="n"/>
+      <c r="P224" s="7" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
@@ -5628,6 +5857,7 @@
       <c r="M225" s="7" t="n"/>
       <c r="N225" s="7" t="n"/>
       <c r="O225" s="7" t="n"/>
+      <c r="P225" s="7" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
@@ -5649,6 +5879,7 @@
       <c r="M226" s="4" t="n"/>
       <c r="N226" s="4" t="n"/>
       <c r="O226" s="4" t="n"/>
+      <c r="P226" s="4" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
@@ -5670,6 +5901,7 @@
       <c r="M227" s="4" t="n"/>
       <c r="N227" s="4" t="n"/>
       <c r="O227" s="4" t="n"/>
+      <c r="P227" s="4" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
@@ -5691,14 +5923,15 @@
       </c>
       <c r="J228" s="4" t="n"/>
       <c r="K228" s="4" t="n"/>
-      <c r="L228" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M228" s="4" t="n"/>
+      <c r="L228" s="4" t="n"/>
+      <c r="M228" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N228" s="4" t="n"/>
       <c r="O228" s="4" t="n"/>
+      <c r="P228" s="4" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
@@ -5728,6 +5961,7 @@
       <c r="M229" s="4" t="n"/>
       <c r="N229" s="4" t="n"/>
       <c r="O229" s="4" t="n"/>
+      <c r="P229" s="4" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
@@ -5753,6 +5987,7 @@
       <c r="M230" s="4" t="n"/>
       <c r="N230" s="4" t="n"/>
       <c r="O230" s="4" t="n"/>
+      <c r="P230" s="4" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
@@ -5774,6 +6009,7 @@
       <c r="M231" s="7" t="n"/>
       <c r="N231" s="7" t="n"/>
       <c r="O231" s="7" t="n"/>
+      <c r="P231" s="7" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="6" t="inlineStr">
@@ -5795,6 +6031,7 @@
       <c r="M232" s="7" t="n"/>
       <c r="N232" s="7" t="n"/>
       <c r="O232" s="7" t="n"/>
+      <c r="P232" s="7" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
@@ -5820,14 +6057,15 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L233" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M233" s="4" t="n"/>
+      <c r="L233" s="4" t="n"/>
+      <c r="M233" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N233" s="4" t="n"/>
       <c r="O233" s="4" t="n"/>
+      <c r="P233" s="4" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
@@ -5849,14 +6087,15 @@
       </c>
       <c r="J234" s="4" t="n"/>
       <c r="K234" s="4" t="n"/>
-      <c r="L234" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M234" s="4" t="n"/>
+      <c r="L234" s="4" t="n"/>
+      <c r="M234" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N234" s="4" t="n"/>
       <c r="O234" s="4" t="n"/>
+      <c r="P234" s="4" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
@@ -5878,14 +6117,15 @@
       </c>
       <c r="J235" s="4" t="n"/>
       <c r="K235" s="4" t="n"/>
-      <c r="L235" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M235" s="4" t="n"/>
+      <c r="L235" s="4" t="n"/>
+      <c r="M235" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N235" s="4" t="n"/>
       <c r="O235" s="4" t="n"/>
+      <c r="P235" s="4" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
@@ -5903,14 +6143,15 @@
       <c r="I236" s="4" t="n"/>
       <c r="J236" s="4" t="n"/>
       <c r="K236" s="4" t="n"/>
-      <c r="L236" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M236" s="4" t="n"/>
+      <c r="L236" s="4" t="n"/>
+      <c r="M236" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N236" s="4" t="n"/>
       <c r="O236" s="4" t="n"/>
+      <c r="P236" s="4" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
@@ -5928,14 +6169,15 @@
       <c r="I237" s="4" t="n"/>
       <c r="J237" s="4" t="n"/>
       <c r="K237" s="4" t="n"/>
-      <c r="L237" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M237" s="4" t="n"/>
+      <c r="L237" s="4" t="n"/>
+      <c r="M237" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N237" s="4" t="n"/>
       <c r="O237" s="4" t="n"/>
+      <c r="P237" s="4" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="6" t="inlineStr">
@@ -5957,6 +6199,7 @@
       <c r="M238" s="7" t="n"/>
       <c r="N238" s="7" t="n"/>
       <c r="O238" s="7" t="n"/>
+      <c r="P238" s="7" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
@@ -5978,6 +6221,7 @@
       <c r="M239" s="7" t="n"/>
       <c r="N239" s="7" t="n"/>
       <c r="O239" s="7" t="n"/>
+      <c r="P239" s="7" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
@@ -5995,18 +6239,19 @@
       <c r="I240" s="4" t="n"/>
       <c r="J240" s="4" t="n"/>
       <c r="K240" s="4" t="n"/>
-      <c r="L240" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="L240" s="4" t="n"/>
       <c r="M240" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N240" s="4" t="n"/>
+      <c r="N240" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="O240" s="4" t="n"/>
+      <c r="P240" s="4" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
@@ -6028,18 +6273,19 @@
       </c>
       <c r="J241" s="4" t="n"/>
       <c r="K241" s="4" t="n"/>
-      <c r="L241" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="L241" s="4" t="n"/>
       <c r="M241" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N241" s="4" t="n"/>
+      <c r="N241" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="O241" s="4" t="n"/>
+      <c r="P241" s="4" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
@@ -6062,13 +6308,14 @@
       <c r="J242" s="4" t="n"/>
       <c r="K242" s="4" t="n"/>
       <c r="L242" s="4" t="n"/>
-      <c r="M242" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N242" s="4" t="n"/>
+      <c r="M242" s="4" t="n"/>
+      <c r="N242" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="O242" s="4" t="n"/>
+      <c r="P242" s="4" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
@@ -6093,7 +6340,8 @@
       <c r="L243" s="4" t="n"/>
       <c r="M243" s="4" t="n"/>
       <c r="N243" s="4" t="n"/>
-      <c r="O243" s="8" t="inlineStr">
+      <c r="O243" s="4" t="n"/>
+      <c r="P243" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6122,7 +6370,8 @@
       <c r="L244" s="4" t="n"/>
       <c r="M244" s="4" t="n"/>
       <c r="N244" s="4" t="n"/>
-      <c r="O244" s="8" t="inlineStr">
+      <c r="O244" s="4" t="n"/>
+      <c r="P244" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6148,6 +6397,7 @@
       <c r="M245" s="7" t="n"/>
       <c r="N245" s="7" t="n"/>
       <c r="O245" s="7" t="n"/>
+      <c r="P245" s="7" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="6" t="inlineStr">
@@ -6169,6 +6419,7 @@
       <c r="M246" s="7" t="n"/>
       <c r="N246" s="7" t="n"/>
       <c r="O246" s="7" t="n"/>
+      <c r="P246" s="7" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
@@ -6193,7 +6444,8 @@
       <c r="L247" s="4" t="n"/>
       <c r="M247" s="4" t="n"/>
       <c r="N247" s="4" t="n"/>
-      <c r="O247" s="8" t="inlineStr">
+      <c r="O247" s="4" t="n"/>
+      <c r="P247" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6222,7 +6474,8 @@
       <c r="L248" s="4" t="n"/>
       <c r="M248" s="4" t="n"/>
       <c r="N248" s="4" t="n"/>
-      <c r="O248" s="8" t="inlineStr">
+      <c r="O248" s="4" t="n"/>
+      <c r="P248" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6247,7 +6500,8 @@
       <c r="L249" s="4" t="n"/>
       <c r="M249" s="4" t="n"/>
       <c r="N249" s="4" t="n"/>
-      <c r="O249" s="8" t="inlineStr">
+      <c r="O249" s="4" t="n"/>
+      <c r="P249" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6273,6 +6527,7 @@
       <c r="M250" s="4" t="n"/>
       <c r="N250" s="4" t="n"/>
       <c r="O250" s="4" t="n"/>
+      <c r="P250" s="4" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
@@ -6294,6 +6549,7 @@
       <c r="M251" s="4" t="n"/>
       <c r="N251" s="4" t="n"/>
       <c r="O251" s="4" t="n"/>
+      <c r="P251" s="4" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="6" t="inlineStr">
@@ -6315,6 +6571,7 @@
       <c r="M252" s="7" t="n"/>
       <c r="N252" s="7" t="n"/>
       <c r="O252" s="7" t="n"/>
+      <c r="P252" s="7" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="6" t="inlineStr">
@@ -6336,6 +6593,7 @@
       <c r="M253" s="7" t="n"/>
       <c r="N253" s="7" t="n"/>
       <c r="O253" s="7" t="n"/>
+      <c r="P253" s="7" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
@@ -6357,6 +6615,7 @@
       <c r="M254" s="4" t="n"/>
       <c r="N254" s="4" t="n"/>
       <c r="O254" s="4" t="n"/>
+      <c r="P254" s="4" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
@@ -6378,6 +6637,7 @@
       <c r="M255" s="4" t="n"/>
       <c r="N255" s="4" t="n"/>
       <c r="O255" s="4" t="n"/>
+      <c r="P255" s="4" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
@@ -6399,6 +6659,7 @@
       <c r="M256" s="4" t="n"/>
       <c r="N256" s="4" t="n"/>
       <c r="O256" s="4" t="n"/>
+      <c r="P256" s="4" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
@@ -6416,14 +6677,15 @@
       <c r="I257" s="4" t="n"/>
       <c r="J257" s="4" t="n"/>
       <c r="K257" s="4" t="n"/>
-      <c r="L257" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M257" s="4" t="n"/>
+      <c r="L257" s="4" t="n"/>
+      <c r="M257" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N257" s="4" t="n"/>
       <c r="O257" s="4" t="n"/>
+      <c r="P257" s="4" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
@@ -6445,18 +6707,19 @@
       </c>
       <c r="J258" s="4" t="n"/>
       <c r="K258" s="4" t="n"/>
-      <c r="L258" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M258" s="4" t="n"/>
-      <c r="N258" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O258" s="4" t="n"/>
+      <c r="L258" s="4" t="n"/>
+      <c r="M258" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N258" s="4" t="n"/>
+      <c r="O258" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P258" s="4" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
@@ -6478,6 +6741,7 @@
       <c r="M259" s="7" t="n"/>
       <c r="N259" s="7" t="n"/>
       <c r="O259" s="7" t="n"/>
+      <c r="P259" s="7" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="6" t="inlineStr">
@@ -6499,6 +6763,7 @@
       <c r="M260" s="7" t="n"/>
       <c r="N260" s="7" t="n"/>
       <c r="O260" s="7" t="n"/>
+      <c r="P260" s="7" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
@@ -6520,18 +6785,19 @@
       </c>
       <c r="J261" s="4" t="n"/>
       <c r="K261" s="4" t="n"/>
-      <c r="L261" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M261" s="4" t="n"/>
-      <c r="N261" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O261" s="4" t="n"/>
+      <c r="L261" s="4" t="n"/>
+      <c r="M261" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N261" s="4" t="n"/>
+      <c r="O261" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P261" s="4" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
@@ -6549,14 +6815,15 @@
       <c r="I262" s="4" t="n"/>
       <c r="J262" s="4" t="n"/>
       <c r="K262" s="4" t="n"/>
-      <c r="L262" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M262" s="4" t="n"/>
+      <c r="L262" s="4" t="n"/>
+      <c r="M262" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N262" s="4" t="n"/>
       <c r="O262" s="4" t="n"/>
+      <c r="P262" s="4" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
@@ -6578,6 +6845,7 @@
       <c r="M263" s="4" t="n"/>
       <c r="N263" s="4" t="n"/>
       <c r="O263" s="4" t="n"/>
+      <c r="P263" s="4" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
@@ -6599,6 +6867,7 @@
       <c r="M264" s="4" t="n"/>
       <c r="N264" s="4" t="n"/>
       <c r="O264" s="4" t="n"/>
+      <c r="P264" s="4" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
@@ -6617,13 +6886,14 @@
       <c r="J265" s="4" t="n"/>
       <c r="K265" s="4" t="n"/>
       <c r="L265" s="4" t="n"/>
-      <c r="M265" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N265" s="4" t="n"/>
+      <c r="M265" s="4" t="n"/>
+      <c r="N265" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="O265" s="4" t="n"/>
+      <c r="P265" s="4" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="6" t="inlineStr">
@@ -6645,6 +6915,7 @@
       <c r="M266" s="7" t="n"/>
       <c r="N266" s="7" t="n"/>
       <c r="O266" s="7" t="n"/>
+      <c r="P266" s="7" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
@@ -6666,6 +6937,7 @@
       <c r="M267" s="7" t="n"/>
       <c r="N267" s="7" t="n"/>
       <c r="O267" s="7" t="n"/>
+      <c r="P267" s="7" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
@@ -6687,6 +6959,7 @@
       <c r="M268" s="4" t="n"/>
       <c r="N268" s="4" t="n"/>
       <c r="O268" s="4" t="n"/>
+      <c r="P268" s="4" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
@@ -6707,7 +6980,8 @@
       <c r="L269" s="4" t="n"/>
       <c r="M269" s="4" t="n"/>
       <c r="N269" s="4" t="n"/>
-      <c r="O269" s="8" t="inlineStr">
+      <c r="O269" s="4" t="n"/>
+      <c r="P269" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6736,7 +7010,8 @@
       <c r="L270" s="4" t="n"/>
       <c r="M270" s="4" t="n"/>
       <c r="N270" s="4" t="n"/>
-      <c r="O270" s="8" t="inlineStr">
+      <c r="O270" s="4" t="n"/>
+      <c r="P270" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6761,7 +7036,8 @@
       <c r="L271" s="4" t="n"/>
       <c r="M271" s="4" t="n"/>
       <c r="N271" s="4" t="n"/>
-      <c r="O271" s="8" t="inlineStr">
+      <c r="O271" s="4" t="n"/>
+      <c r="P271" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6786,7 +7062,8 @@
       <c r="L272" s="4" t="n"/>
       <c r="M272" s="4" t="n"/>
       <c r="N272" s="4" t="n"/>
-      <c r="O272" s="8" t="inlineStr">
+      <c r="O272" s="4" t="n"/>
+      <c r="P272" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6812,6 +7089,7 @@
       <c r="M273" s="7" t="n"/>
       <c r="N273" s="7" t="n"/>
       <c r="O273" s="7" t="n"/>
+      <c r="P273" s="7" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="6" t="inlineStr">
@@ -6833,6 +7111,7 @@
       <c r="M274" s="7" t="n"/>
       <c r="N274" s="7" t="n"/>
       <c r="O274" s="7" t="n"/>
+      <c r="P274" s="7" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
@@ -6856,12 +7135,13 @@
       </c>
       <c r="L275" s="4" t="n"/>
       <c r="M275" s="4" t="n"/>
-      <c r="N275" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="N275" s="4" t="n"/>
       <c r="O275" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P275" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6885,12 +7165,13 @@
       <c r="K276" s="4" t="n"/>
       <c r="L276" s="4" t="n"/>
       <c r="M276" s="4" t="n"/>
-      <c r="N276" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="N276" s="4" t="n"/>
       <c r="O276" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P276" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6914,12 +7195,13 @@
       <c r="K277" s="4" t="n"/>
       <c r="L277" s="4" t="n"/>
       <c r="M277" s="4" t="n"/>
-      <c r="N277" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="N277" s="4" t="n"/>
       <c r="O277" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P277" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6943,12 +7225,13 @@
       <c r="K278" s="4" t="n"/>
       <c r="L278" s="4" t="n"/>
       <c r="M278" s="4" t="n"/>
-      <c r="N278" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O278" s="4" t="n"/>
+      <c r="N278" s="4" t="n"/>
+      <c r="O278" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P278" s="4" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
@@ -6970,6 +7253,7 @@
       <c r="M279" s="4" t="n"/>
       <c r="N279" s="4" t="n"/>
       <c r="O279" s="4" t="n"/>
+      <c r="P279" s="4" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="6" t="inlineStr">
@@ -6991,6 +7275,7 @@
       <c r="M280" s="7" t="n"/>
       <c r="N280" s="7" t="n"/>
       <c r="O280" s="7" t="n"/>
+      <c r="P280" s="7" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
@@ -7012,6 +7297,7 @@
       <c r="M281" s="7" t="n"/>
       <c r="N281" s="7" t="n"/>
       <c r="O281" s="7" t="n"/>
+      <c r="P281" s="7" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
@@ -7037,6 +7323,7 @@
       <c r="M282" s="4" t="n"/>
       <c r="N282" s="4" t="n"/>
       <c r="O282" s="4" t="n"/>
+      <c r="P282" s="4" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
@@ -7062,6 +7349,7 @@
       <c r="M283" s="4" t="n"/>
       <c r="N283" s="4" t="n"/>
       <c r="O283" s="4" t="n"/>
+      <c r="P283" s="4" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
@@ -7087,6 +7375,7 @@
       <c r="M284" s="4" t="n"/>
       <c r="N284" s="4" t="n"/>
       <c r="O284" s="4" t="n"/>
+      <c r="P284" s="4" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
@@ -7112,6 +7401,7 @@
       <c r="M285" s="4" t="n"/>
       <c r="N285" s="4" t="n"/>
       <c r="O285" s="4" t="n"/>
+      <c r="P285" s="4" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
@@ -7133,14 +7423,15 @@
       <c r="I286" s="4" t="n"/>
       <c r="J286" s="4" t="n"/>
       <c r="K286" s="4" t="n"/>
-      <c r="L286" s="5" t="inlineStr">
+      <c r="L286" s="4" t="n"/>
+      <c r="M286" s="5" t="inlineStr">
         <is>
           <t>Sick - Sick</t>
         </is>
       </c>
-      <c r="M286" s="4" t="n"/>
       <c r="N286" s="4" t="n"/>
       <c r="O286" s="4" t="n"/>
+      <c r="P286" s="4" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="6" t="inlineStr">
@@ -7162,6 +7453,7 @@
       <c r="M287" s="7" t="n"/>
       <c r="N287" s="7" t="n"/>
       <c r="O287" s="7" t="n"/>
+      <c r="P287" s="7" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="6" t="inlineStr">
@@ -7183,6 +7475,7 @@
       <c r="M288" s="7" t="n"/>
       <c r="N288" s="7" t="n"/>
       <c r="O288" s="7" t="n"/>
+      <c r="P288" s="7" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
@@ -7220,6 +7513,7 @@
       <c r="M289" s="4" t="n"/>
       <c r="N289" s="4" t="n"/>
       <c r="O289" s="4" t="n"/>
+      <c r="P289" s="4" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
@@ -7257,6 +7551,7 @@
       <c r="M290" s="4" t="n"/>
       <c r="N290" s="4" t="n"/>
       <c r="O290" s="4" t="n"/>
+      <c r="P290" s="4" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
@@ -7286,6 +7581,7 @@
       <c r="M291" s="4" t="n"/>
       <c r="N291" s="4" t="n"/>
       <c r="O291" s="4" t="n"/>
+      <c r="P291" s="4" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
@@ -7315,6 +7611,7 @@
       <c r="M292" s="4" t="n"/>
       <c r="N292" s="4" t="n"/>
       <c r="O292" s="4" t="n"/>
+      <c r="P292" s="4" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
@@ -7348,6 +7645,7 @@
       <c r="M293" s="4" t="n"/>
       <c r="N293" s="4" t="n"/>
       <c r="O293" s="4" t="n"/>
+      <c r="P293" s="4" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="6" t="inlineStr">
@@ -7369,6 +7667,7 @@
       <c r="M294" s="7" t="n"/>
       <c r="N294" s="7" t="n"/>
       <c r="O294" s="7" t="n"/>
+      <c r="P294" s="7" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
@@ -7390,6 +7689,7 @@
       <c r="M295" s="7" t="n"/>
       <c r="N295" s="7" t="n"/>
       <c r="O295" s="7" t="n"/>
+      <c r="P295" s="7" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
@@ -7423,6 +7723,7 @@
       <c r="M296" s="4" t="n"/>
       <c r="N296" s="4" t="n"/>
       <c r="O296" s="4" t="n"/>
+      <c r="P296" s="4" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
@@ -7456,14 +7757,15 @@
         </is>
       </c>
       <c r="K297" s="4" t="n"/>
-      <c r="L297" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M297" s="4" t="n"/>
+      <c r="L297" s="4" t="n"/>
+      <c r="M297" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N297" s="4" t="n"/>
       <c r="O297" s="4" t="n"/>
+      <c r="P297" s="4" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
@@ -7493,14 +7795,15 @@
         </is>
       </c>
       <c r="K298" s="4" t="n"/>
-      <c r="L298" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M298" s="4" t="n"/>
+      <c r="L298" s="4" t="n"/>
+      <c r="M298" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N298" s="4" t="n"/>
       <c r="O298" s="4" t="n"/>
+      <c r="P298" s="4" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
@@ -7535,6 +7838,7 @@
       <c r="M299" s="4" t="n"/>
       <c r="N299" s="4" t="n"/>
       <c r="O299" s="4" t="n"/>
+      <c r="P299" s="4" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
@@ -7565,13 +7869,14 @@
       </c>
       <c r="K300" s="4" t="n"/>
       <c r="L300" s="4" t="n"/>
-      <c r="M300" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N300" s="4" t="n"/>
+      <c r="M300" s="4" t="n"/>
+      <c r="N300" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="O300" s="4" t="n"/>
+      <c r="P300" s="4" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="6" t="inlineStr">
@@ -7593,6 +7898,7 @@
       <c r="M301" s="7" t="n"/>
       <c r="N301" s="7" t="n"/>
       <c r="O301" s="7" t="n"/>
+      <c r="P301" s="7" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="6" t="inlineStr">
@@ -7614,6 +7920,7 @@
       <c r="M302" s="7" t="n"/>
       <c r="N302" s="7" t="n"/>
       <c r="O302" s="7" t="n"/>
+      <c r="P302" s="7" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
@@ -7632,13 +7939,14 @@
       <c r="J303" s="4" t="n"/>
       <c r="K303" s="4" t="n"/>
       <c r="L303" s="4" t="n"/>
-      <c r="M303" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N303" s="4" t="n"/>
+      <c r="M303" s="4" t="n"/>
+      <c r="N303" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="O303" s="4" t="n"/>
+      <c r="P303" s="4" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
@@ -7657,13 +7965,14 @@
       <c r="J304" s="4" t="n"/>
       <c r="K304" s="4" t="n"/>
       <c r="L304" s="4" t="n"/>
-      <c r="M304" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N304" s="4" t="n"/>
+      <c r="M304" s="4" t="n"/>
+      <c r="N304" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="O304" s="4" t="n"/>
+      <c r="P304" s="4" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
@@ -7682,13 +7991,14 @@
       <c r="J305" s="4" t="n"/>
       <c r="K305" s="4" t="n"/>
       <c r="L305" s="4" t="n"/>
-      <c r="M305" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N305" s="4" t="n"/>
+      <c r="M305" s="4" t="n"/>
+      <c r="N305" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="O305" s="4" t="n"/>
+      <c r="P305" s="4" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
@@ -7707,13 +8017,14 @@
       <c r="J306" s="4" t="n"/>
       <c r="K306" s="4" t="n"/>
       <c r="L306" s="4" t="n"/>
-      <c r="M306" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N306" s="4" t="n"/>
+      <c r="M306" s="4" t="n"/>
+      <c r="N306" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="O306" s="4" t="n"/>
+      <c r="P306" s="4" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
@@ -7732,17 +8043,18 @@
       <c r="J307" s="4" t="n"/>
       <c r="K307" s="4" t="n"/>
       <c r="L307" s="4" t="n"/>
-      <c r="M307" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="M307" s="4" t="n"/>
       <c r="N307" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="O307" s="4" t="n"/>
+      <c r="O307" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P307" s="4" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="6" t="inlineStr">
@@ -7764,6 +8076,7 @@
       <c r="M308" s="7" t="n"/>
       <c r="N308" s="7" t="n"/>
       <c r="O308" s="7" t="n"/>
+      <c r="P308" s="7" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="6" t="inlineStr">
@@ -7785,6 +8098,7 @@
       <c r="M309" s="7" t="n"/>
       <c r="N309" s="7" t="n"/>
       <c r="O309" s="7" t="n"/>
+      <c r="P309" s="7" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
@@ -7814,18 +8128,19 @@
           <t>Pre-Production - Mabli</t>
         </is>
       </c>
-      <c r="L310" s="5" t="inlineStr">
+      <c r="L310" s="4" t="n"/>
+      <c r="M310" s="5" t="inlineStr">
         <is>
           <t>Edit - Socials</t>
         </is>
       </c>
-      <c r="M310" s="4" t="n"/>
-      <c r="N310" s="5" t="inlineStr">
+      <c r="N310" s="4" t="n"/>
+      <c r="O310" s="5" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="O310" s="5" t="inlineStr">
+      <c r="P310" s="5" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -7867,18 +8182,19 @@
           <t>Datblygu</t>
         </is>
       </c>
-      <c r="L311" s="10" t="inlineStr">
+      <c r="L311" s="4" t="n"/>
+      <c r="M311" s="10" t="inlineStr">
         <is>
           <t>TOIL - Hansh Socials</t>
         </is>
       </c>
-      <c r="M311" s="4" t="n"/>
-      <c r="N311" s="5" t="inlineStr">
+      <c r="N311" s="4" t="n"/>
+      <c r="O311" s="5" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="O311" s="5" t="inlineStr">
+      <c r="P311" s="5" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -7920,22 +8236,23 @@
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="L312" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M312" s="5" t="inlineStr">
+      <c r="L312" s="4" t="n"/>
+      <c r="M312" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N312" s="5" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="N312" s="5" t="inlineStr">
+      <c r="O312" s="5" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="O312" s="5" t="inlineStr">
+      <c r="P312" s="5" t="inlineStr">
         <is>
           <t>Edit Annibynwyr</t>
         </is>
@@ -7981,22 +8298,23 @@
           <t>Datblygu</t>
         </is>
       </c>
-      <c r="L313" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M313" s="5" t="inlineStr">
+      <c r="L313" s="4" t="n"/>
+      <c r="M313" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N313" s="5" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="N313" s="5" t="inlineStr">
+      <c r="O313" s="5" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="O313" s="5" t="inlineStr">
+      <c r="P313" s="5" t="inlineStr">
         <is>
           <t>Edit Annibynwyr</t>
         </is>
@@ -8038,22 +8356,23 @@
           <t>Datblygu</t>
         </is>
       </c>
-      <c r="L314" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M314" s="5" t="inlineStr">
+      <c r="L314" s="4" t="n"/>
+      <c r="M314" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N314" s="5" t="inlineStr">
         <is>
           <t>Black History 2026</t>
         </is>
       </c>
-      <c r="N314" s="10" t="inlineStr">
+      <c r="O314" s="10" t="inlineStr">
         <is>
           <t>TOIL - Darts</t>
         </is>
       </c>
-      <c r="O314" s="5" t="inlineStr">
+      <c r="P314" s="5" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -8081,12 +8400,13 @@
       <c r="K315" s="7" t="n"/>
       <c r="L315" s="7" t="n"/>
       <c r="M315" s="7" t="n"/>
-      <c r="N315" s="5" t="inlineStr">
+      <c r="N315" s="7" t="n"/>
+      <c r="O315" s="5" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
       </c>
-      <c r="O315" s="5" t="inlineStr">
+      <c r="P315" s="5" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -8110,12 +8430,13 @@
       <c r="K316" s="7" t="n"/>
       <c r="L316" s="7" t="n"/>
       <c r="M316" s="7" t="n"/>
-      <c r="N316" s="5" t="inlineStr">
+      <c r="N316" s="7" t="n"/>
+      <c r="O316" s="5" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
       </c>
-      <c r="O316" s="5" t="inlineStr">
+      <c r="P316" s="5" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -8157,22 +8478,23 @@
         </is>
       </c>
       <c r="K317" s="4" t="n"/>
-      <c r="L317" s="5" t="inlineStr">
+      <c r="L317" s="4" t="n"/>
+      <c r="M317" s="5" t="inlineStr">
         <is>
           <t>Socials - Rookie Teachers</t>
         </is>
       </c>
-      <c r="M317" s="5" t="inlineStr">
+      <c r="N317" s="5" t="inlineStr">
         <is>
           <t>Film - Hansh Socials</t>
         </is>
       </c>
-      <c r="N317" s="10" t="inlineStr">
+      <c r="O317" s="10" t="inlineStr">
         <is>
           <t>TOIL - Darts 6 G</t>
         </is>
       </c>
-      <c r="O317" s="5" t="inlineStr">
+      <c r="P317" s="5" t="inlineStr">
         <is>
           <t>External - Darts 6 G</t>
         </is>
@@ -8198,22 +8520,23 @@
         </is>
       </c>
       <c r="K318" s="4" t="n"/>
-      <c r="L318" s="5" t="inlineStr">
+      <c r="L318" s="4" t="n"/>
+      <c r="M318" s="5" t="inlineStr">
         <is>
           <t>Socials - Rookie Teachers</t>
         </is>
       </c>
-      <c r="M318" s="5" t="inlineStr">
+      <c r="N318" s="5" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="N318" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O318" s="5" t="inlineStr">
+      <c r="O318" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P318" s="5" t="inlineStr">
         <is>
           <t>Edit - Hansh Socials</t>
         </is>
@@ -8239,22 +8562,23 @@
         </is>
       </c>
       <c r="K319" s="4" t="n"/>
-      <c r="L319" s="5" t="inlineStr">
+      <c r="L319" s="4" t="n"/>
+      <c r="M319" s="5" t="inlineStr">
         <is>
           <t>Socials - Rookie Teachers</t>
         </is>
       </c>
-      <c r="M319" s="5" t="inlineStr">
+      <c r="N319" s="5" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="N319" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O319" s="5" t="inlineStr">
+      <c r="O319" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P319" s="5" t="inlineStr">
         <is>
           <t>Edit - Hansh Socials</t>
         </is>
@@ -8292,22 +8616,23 @@
         </is>
       </c>
       <c r="K320" s="4" t="n"/>
-      <c r="L320" s="5" t="inlineStr">
+      <c r="L320" s="4" t="n"/>
+      <c r="M320" s="5" t="inlineStr">
         <is>
           <t>Socials - Rookie Teachers</t>
         </is>
       </c>
-      <c r="M320" s="5" t="inlineStr">
+      <c r="N320" s="5" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="N320" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O320" s="5" t="inlineStr">
+      <c r="O320" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P320" s="5" t="inlineStr">
         <is>
           <t>Film - Rhedeg Rhacs - Aberteifi</t>
         </is>
@@ -8341,22 +8666,23 @@
         </is>
       </c>
       <c r="K321" s="4" t="n"/>
-      <c r="L321" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M321" s="5" t="inlineStr">
+      <c r="L321" s="4" t="n"/>
+      <c r="M321" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N321" s="5" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="N321" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O321" s="5" t="inlineStr">
+      <c r="O321" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P321" s="5" t="inlineStr">
         <is>
           <t>Edit - Fresh From Wales</t>
         </is>
@@ -8382,6 +8708,7 @@
       <c r="M322" s="7" t="n"/>
       <c r="N322" s="7" t="n"/>
       <c r="O322" s="7" t="n"/>
+      <c r="P322" s="7" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="6" t="inlineStr">
@@ -8403,6 +8730,7 @@
       <c r="M323" s="7" t="n"/>
       <c r="N323" s="7" t="n"/>
       <c r="O323" s="7" t="n"/>
+      <c r="P323" s="7" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="3" t="inlineStr">
@@ -8424,22 +8752,23 @@
         </is>
       </c>
       <c r="K324" s="4" t="n"/>
-      <c r="L324" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M324" s="5" t="inlineStr">
+      <c r="L324" s="4" t="n"/>
+      <c r="M324" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N324" s="5" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="N324" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O324" s="4" t="n"/>
+      <c r="O324" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P324" s="4" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
@@ -8461,22 +8790,23 @@
         </is>
       </c>
       <c r="K325" s="4" t="n"/>
-      <c r="L325" s="5" t="inlineStr">
+      <c r="L325" s="4" t="n"/>
+      <c r="M325" s="5" t="inlineStr">
         <is>
           <t>Edit - Rookie Teachers</t>
         </is>
       </c>
-      <c r="M325" s="5" t="inlineStr">
+      <c r="N325" s="5" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="N325" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O325" s="4" t="n"/>
+      <c r="O325" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P325" s="4" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="3" t="inlineStr">
@@ -8498,22 +8828,23 @@
         </is>
       </c>
       <c r="K326" s="4" t="n"/>
-      <c r="L326" s="5" t="inlineStr">
+      <c r="L326" s="4" t="n"/>
+      <c r="M326" s="5" t="inlineStr">
         <is>
           <t>Edit - Rookie Teachers</t>
         </is>
       </c>
-      <c r="M326" s="5" t="inlineStr">
+      <c r="N326" s="5" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="N326" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O326" s="4" t="n"/>
+      <c r="O326" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P326" s="4" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="3" t="inlineStr">
@@ -8539,22 +8870,23 @@
         </is>
       </c>
       <c r="K327" s="4" t="n"/>
-      <c r="L327" s="5" t="inlineStr">
+      <c r="L327" s="4" t="n"/>
+      <c r="M327" s="5" t="inlineStr">
         <is>
           <t>Rookie Teachers</t>
         </is>
       </c>
-      <c r="M327" s="5" t="inlineStr">
+      <c r="N327" s="5" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="N327" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O327" s="5" t="inlineStr">
+      <c r="O327" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P327" s="5" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -8588,22 +8920,23 @@
         </is>
       </c>
       <c r="K328" s="4" t="n"/>
-      <c r="L328" s="5" t="inlineStr">
+      <c r="L328" s="4" t="n"/>
+      <c r="M328" s="5" t="inlineStr">
         <is>
           <t>Rookie Teachers</t>
         </is>
       </c>
-      <c r="M328" s="5" t="inlineStr">
+      <c r="N328" s="5" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="N328" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O328" s="5" t="inlineStr">
+      <c r="O328" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P328" s="5" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -8629,6 +8962,7 @@
       <c r="M329" s="7" t="n"/>
       <c r="N329" s="7" t="n"/>
       <c r="O329" s="7" t="n"/>
+      <c r="P329" s="7" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="6" t="inlineStr">
@@ -8650,6 +8984,7 @@
       <c r="M330" s="7" t="n"/>
       <c r="N330" s="7" t="n"/>
       <c r="O330" s="7" t="n"/>
+      <c r="P330" s="7" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="3" t="inlineStr">
@@ -8675,22 +9010,23 @@
         </is>
       </c>
       <c r="K331" s="4" t="n"/>
-      <c r="L331" s="5" t="inlineStr">
+      <c r="L331" s="4" t="n"/>
+      <c r="M331" s="5" t="inlineStr">
         <is>
           <t>Rhwym Galon</t>
         </is>
       </c>
-      <c r="M331" s="5" t="inlineStr">
+      <c r="N331" s="5" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="N331" s="5" t="inlineStr">
+      <c r="O331" s="5" t="inlineStr">
         <is>
           <t>Sick</t>
         </is>
       </c>
-      <c r="O331" s="10" t="inlineStr">
+      <c r="P331" s="10" t="inlineStr">
         <is>
           <t>TOIL - Darts 6 G</t>
         </is>
@@ -8720,18 +9056,19 @@
         </is>
       </c>
       <c r="K332" s="4" t="n"/>
-      <c r="L332" s="5" t="inlineStr">
+      <c r="L332" s="4" t="n"/>
+      <c r="M332" s="5" t="inlineStr">
         <is>
           <t>Rhedeg Rhacs</t>
         </is>
       </c>
-      <c r="M332" s="4" t="n"/>
-      <c r="N332" s="5" t="inlineStr">
+      <c r="N332" s="4" t="n"/>
+      <c r="O332" s="5" t="inlineStr">
         <is>
           <t>Sick</t>
         </is>
       </c>
-      <c r="O332" s="4" t="n"/>
+      <c r="P332" s="4" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="3" t="inlineStr">
@@ -8757,18 +9094,19 @@
         </is>
       </c>
       <c r="K333" s="4" t="n"/>
-      <c r="L333" s="5" t="inlineStr">
+      <c r="L333" s="4" t="n"/>
+      <c r="M333" s="5" t="inlineStr">
         <is>
           <t>Rhedeg Rhacs</t>
         </is>
       </c>
-      <c r="M333" s="4" t="n"/>
-      <c r="N333" s="5" t="inlineStr">
+      <c r="N333" s="4" t="n"/>
+      <c r="O333" s="5" t="inlineStr">
         <is>
           <t>Sick</t>
         </is>
       </c>
-      <c r="O333" s="4" t="n"/>
+      <c r="P333" s="4" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="3" t="inlineStr">
@@ -8807,18 +9145,19 @@
         </is>
       </c>
       <c r="K334" s="4" t="n"/>
-      <c r="L334" s="5" t="inlineStr">
+      <c r="L334" s="4" t="n"/>
+      <c r="M334" s="5" t="inlineStr">
         <is>
           <t>Edit - Rhedeg Rhacs</t>
         </is>
       </c>
-      <c r="M334" s="4" t="n"/>
-      <c r="N334" s="5" t="inlineStr">
+      <c r="N334" s="4" t="n"/>
+      <c r="O334" s="5" t="inlineStr">
         <is>
           <t>Sick</t>
         </is>
       </c>
-      <c r="O334" s="5" t="inlineStr">
+      <c r="P334" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -8861,14 +9200,15 @@
         </is>
       </c>
       <c r="K335" s="4" t="n"/>
-      <c r="L335" s="5" t="inlineStr">
+      <c r="L335" s="4" t="n"/>
+      <c r="M335" s="5" t="inlineStr">
         <is>
           <t>Edit - Rhedeg Rhacs</t>
         </is>
       </c>
-      <c r="M335" s="4" t="n"/>
       <c r="N335" s="4" t="n"/>
-      <c r="O335" s="5" t="inlineStr">
+      <c r="O335" s="4" t="n"/>
+      <c r="P335" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -8894,6 +9234,7 @@
       <c r="M336" s="7" t="n"/>
       <c r="N336" s="7" t="n"/>
       <c r="O336" s="7" t="n"/>
+      <c r="P336" s="7" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="6" t="inlineStr">
@@ -8912,13 +9253,14 @@
       <c r="J337" s="7" t="n"/>
       <c r="K337" s="7" t="n"/>
       <c r="L337" s="7" t="n"/>
-      <c r="M337" s="5" t="inlineStr">
+      <c r="M337" s="7" t="n"/>
+      <c r="N337" s="5" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="N337" s="7" t="n"/>
       <c r="O337" s="7" t="n"/>
+      <c r="P337" s="7" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="3" t="inlineStr">
@@ -8956,6 +9298,7 @@
       <c r="M338" s="4" t="n"/>
       <c r="N338" s="4" t="n"/>
       <c r="O338" s="4" t="n"/>
+      <c r="P338" s="4" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="3" t="inlineStr">
@@ -8997,18 +9340,19 @@
         </is>
       </c>
       <c r="K339" s="4" t="n"/>
-      <c r="L339" s="5" t="inlineStr">
+      <c r="L339" s="4" t="n"/>
+      <c r="M339" s="5" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="M339" s="4" t="n"/>
-      <c r="N339" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O339" s="4" t="n"/>
+      <c r="N339" s="4" t="n"/>
+      <c r="O339" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P339" s="4" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="3" t="inlineStr">
@@ -9050,18 +9394,19 @@
         </is>
       </c>
       <c r="K340" s="4" t="n"/>
-      <c r="L340" s="5" t="inlineStr">
+      <c r="L340" s="4" t="n"/>
+      <c r="M340" s="5" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="M340" s="4" t="n"/>
-      <c r="N340" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O340" s="4" t="n"/>
+      <c r="N340" s="4" t="n"/>
+      <c r="O340" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P340" s="4" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="3" t="inlineStr">
@@ -9091,22 +9436,23 @@
         </is>
       </c>
       <c r="K341" s="4" t="n"/>
-      <c r="L341" s="5" t="inlineStr">
+      <c r="L341" s="4" t="n"/>
+      <c r="M341" s="5" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="M341" s="5" t="inlineStr">
+      <c r="N341" s="5" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="N341" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O341" s="4" t="n"/>
+      <c r="O341" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P341" s="4" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="3" t="inlineStr">
@@ -9144,18 +9490,19 @@
         </is>
       </c>
       <c r="K342" s="4" t="n"/>
-      <c r="L342" s="5" t="inlineStr">
+      <c r="L342" s="4" t="n"/>
+      <c r="M342" s="5" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="M342" s="4" t="n"/>
-      <c r="N342" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O342" s="4" t="n"/>
+      <c r="N342" s="4" t="n"/>
+      <c r="O342" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P342" s="4" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="6" t="inlineStr">
@@ -9177,6 +9524,7 @@
       <c r="M343" s="7" t="n"/>
       <c r="N343" s="7" t="n"/>
       <c r="O343" s="7" t="n"/>
+      <c r="P343" s="7" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="6" t="inlineStr">
@@ -9198,6 +9546,7 @@
       <c r="M344" s="7" t="n"/>
       <c r="N344" s="7" t="n"/>
       <c r="O344" s="7" t="n"/>
+      <c r="P344" s="7" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="3" t="inlineStr">
@@ -9231,18 +9580,19 @@
         </is>
       </c>
       <c r="K345" s="4" t="n"/>
-      <c r="L345" s="5" t="inlineStr">
+      <c r="L345" s="4" t="n"/>
+      <c r="M345" s="5" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="M345" s="4" t="n"/>
-      <c r="N345" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O345" s="5" t="inlineStr">
+      <c r="N345" s="4" t="n"/>
+      <c r="O345" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P345" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -9280,18 +9630,19 @@
         </is>
       </c>
       <c r="K346" s="4" t="n"/>
-      <c r="L346" s="5" t="inlineStr">
+      <c r="L346" s="4" t="n"/>
+      <c r="M346" s="5" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="M346" s="4" t="n"/>
-      <c r="N346" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O346" s="5" t="inlineStr">
+      <c r="N346" s="4" t="n"/>
+      <c r="O346" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P346" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -9333,18 +9684,19 @@
           <t>SOCIAL MEDIA CONFERENCE</t>
         </is>
       </c>
-      <c r="L347" s="8" t="inlineStr">
+      <c r="L347" s="4" t="n"/>
+      <c r="M347" s="8" t="inlineStr">
         <is>
           <t>Notes / Changes - Black History 2026</t>
         </is>
       </c>
-      <c r="M347" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N347" s="4" t="n"/>
-      <c r="O347" s="5" t="inlineStr">
+      <c r="N347" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O347" s="4" t="n"/>
+      <c r="P347" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -9387,13 +9739,14 @@
       </c>
       <c r="K348" s="4" t="n"/>
       <c r="L348" s="4" t="n"/>
-      <c r="M348" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N348" s="4" t="n"/>
-      <c r="O348" s="5" t="inlineStr">
+      <c r="M348" s="4" t="n"/>
+      <c r="N348" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O348" s="4" t="n"/>
+      <c r="P348" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -9437,13 +9790,14 @@
       </c>
       <c r="K349" s="4" t="n"/>
       <c r="L349" s="4" t="n"/>
-      <c r="M349" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N349" s="4" t="n"/>
-      <c r="O349" s="5" t="inlineStr">
+      <c r="M349" s="4" t="n"/>
+      <c r="N349" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O349" s="4" t="n"/>
+      <c r="P349" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -9466,13 +9820,14 @@
       <c r="J350" s="7" t="n"/>
       <c r="K350" s="7" t="n"/>
       <c r="L350" s="7" t="n"/>
-      <c r="M350" s="5" t="inlineStr">
+      <c r="M350" s="7" t="n"/>
+      <c r="N350" s="5" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="N350" s="7" t="n"/>
       <c r="O350" s="7" t="n"/>
+      <c r="P350" s="7" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="6" t="inlineStr">
@@ -9491,13 +9846,14 @@
       <c r="J351" s="7" t="n"/>
       <c r="K351" s="7" t="n"/>
       <c r="L351" s="7" t="n"/>
-      <c r="M351" s="5" t="inlineStr">
+      <c r="M351" s="7" t="n"/>
+      <c r="N351" s="5" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="N351" s="7" t="n"/>
       <c r="O351" s="7" t="n"/>
+      <c r="P351" s="7" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="3" t="inlineStr">
@@ -9528,13 +9884,14 @@
       </c>
       <c r="K352" s="4" t="n"/>
       <c r="L352" s="4" t="n"/>
-      <c r="M352" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N352" s="4" t="n"/>
+      <c r="M352" s="4" t="n"/>
+      <c r="N352" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="O352" s="4" t="n"/>
+      <c r="P352" s="4" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="3" t="inlineStr">
@@ -9561,13 +9918,14 @@
       </c>
       <c r="K353" s="4" t="n"/>
       <c r="L353" s="4" t="n"/>
-      <c r="M353" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N353" s="4" t="n"/>
+      <c r="M353" s="4" t="n"/>
+      <c r="N353" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="O353" s="4" t="n"/>
+      <c r="P353" s="4" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="3" t="inlineStr">
@@ -9601,19 +9959,20 @@
         </is>
       </c>
       <c r="K354" s="4" t="n"/>
-      <c r="L354" s="5" t="inlineStr">
+      <c r="L354" s="4" t="n"/>
+      <c r="M354" s="5" t="inlineStr">
         <is>
           <t>Film - BBC Music Show</t>
         </is>
       </c>
-      <c r="M354" s="5" t="inlineStr">
+      <c r="N354" s="5" t="inlineStr">
         <is>
           <t>Film - BBC Music Show
 A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N354" s="4" t="n"/>
-      <c r="O354" s="5" t="inlineStr">
+      <c r="O354" s="4" t="n"/>
+      <c r="P354" s="5" t="inlineStr">
         <is>
           <t>Film - BBC Music Show</t>
         </is>
@@ -9647,18 +10006,19 @@
       </c>
       <c r="J355" s="4" t="n"/>
       <c r="K355" s="4" t="n"/>
-      <c r="L355" s="5" t="inlineStr">
+      <c r="L355" s="4" t="n"/>
+      <c r="M355" s="5" t="inlineStr">
         <is>
           <t>Film - BBC Music Show</t>
         </is>
       </c>
-      <c r="M355" s="5" t="inlineStr">
+      <c r="N355" s="5" t="inlineStr">
         <is>
           <t>Film - BBC Music Show</t>
         </is>
       </c>
-      <c r="N355" s="4" t="n"/>
-      <c r="O355" s="5" t="inlineStr">
+      <c r="O355" s="4" t="n"/>
+      <c r="P355" s="5" t="inlineStr">
         <is>
           <t>Film - BBC Music Show</t>
         </is>
@@ -9684,22 +10044,23 @@
           <t>Film - Chepstow</t>
         </is>
       </c>
-      <c r="L356" s="5" t="inlineStr">
+      <c r="L356" s="4" t="n"/>
+      <c r="M356" s="5" t="inlineStr">
         <is>
           <t>Film - Chepstow</t>
         </is>
       </c>
-      <c r="M356" s="5" t="inlineStr">
+      <c r="N356" s="5" t="inlineStr">
         <is>
           <t>Film - Chepstow</t>
         </is>
       </c>
-      <c r="N356" s="5" t="inlineStr">
+      <c r="O356" s="5" t="inlineStr">
         <is>
           <t>Film - Chepstow</t>
         </is>
       </c>
-      <c r="O356" s="5" t="inlineStr">
+      <c r="P356" s="5" t="inlineStr">
         <is>
           <t>Film - Chepstow</t>
         </is>
@@ -9729,22 +10090,23 @@
           <t>Film - Chepstow</t>
         </is>
       </c>
-      <c r="L357" s="5" t="inlineStr">
+      <c r="L357" s="7" t="n"/>
+      <c r="M357" s="5" t="inlineStr">
         <is>
           <t>Film - Chepstow</t>
         </is>
       </c>
-      <c r="M357" s="5" t="inlineStr">
+      <c r="N357" s="5" t="inlineStr">
         <is>
           <t>Film - Chepstow</t>
         </is>
       </c>
-      <c r="N357" s="5" t="inlineStr">
+      <c r="O357" s="5" t="inlineStr">
         <is>
           <t>Film - Chepstow</t>
         </is>
       </c>
-      <c r="O357" s="7" t="n"/>
+      <c r="P357" s="7" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="6" t="inlineStr">
@@ -9766,22 +10128,23 @@
       <c r="I358" s="7" t="n"/>
       <c r="J358" s="7" t="n"/>
       <c r="K358" s="7" t="n"/>
-      <c r="L358" s="5" t="inlineStr">
+      <c r="L358" s="7" t="n"/>
+      <c r="M358" s="5" t="inlineStr">
         <is>
           <t>Film - Chepstow</t>
         </is>
       </c>
-      <c r="M358" s="5" t="inlineStr">
+      <c r="N358" s="5" t="inlineStr">
         <is>
           <t>Film - Chepstow</t>
         </is>
       </c>
-      <c r="N358" s="5" t="inlineStr">
+      <c r="O358" s="5" t="inlineStr">
         <is>
           <t>Film - Chepstow</t>
         </is>
       </c>
-      <c r="O358" s="7" t="n"/>
+      <c r="P358" s="7" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="3" t="inlineStr">
@@ -9815,6 +10178,7 @@
       <c r="M359" s="4" t="n"/>
       <c r="N359" s="4" t="n"/>
       <c r="O359" s="4" t="n"/>
+      <c r="P359" s="4" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="3" t="inlineStr">
@@ -9848,6 +10212,7 @@
       <c r="M360" s="4" t="n"/>
       <c r="N360" s="4" t="n"/>
       <c r="O360" s="4" t="n"/>
+      <c r="P360" s="4" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="3" t="inlineStr">
@@ -9881,6 +10246,7 @@
       <c r="M361" s="4" t="n"/>
       <c r="N361" s="4" t="n"/>
       <c r="O361" s="4" t="n"/>
+      <c r="P361" s="4" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="3" t="inlineStr">
@@ -9910,14 +10276,15 @@
       <c r="I362" s="4" t="n"/>
       <c r="J362" s="4" t="n"/>
       <c r="K362" s="4" t="n"/>
-      <c r="L362" s="5" t="inlineStr">
+      <c r="L362" s="4" t="n"/>
+      <c r="M362" s="5" t="inlineStr">
         <is>
           <t>Edit - Chepstow</t>
         </is>
       </c>
-      <c r="M362" s="4" t="n"/>
       <c r="N362" s="4" t="n"/>
       <c r="O362" s="4" t="n"/>
+      <c r="P362" s="4" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="3" t="inlineStr">
@@ -9943,14 +10310,15 @@
       <c r="I363" s="4" t="n"/>
       <c r="J363" s="4" t="n"/>
       <c r="K363" s="4" t="n"/>
-      <c r="L363" s="5" t="inlineStr">
+      <c r="L363" s="4" t="n"/>
+      <c r="M363" s="5" t="inlineStr">
         <is>
           <t>Edit - Chepstow</t>
         </is>
       </c>
-      <c r="M363" s="4" t="n"/>
       <c r="N363" s="4" t="n"/>
       <c r="O363" s="4" t="n"/>
+      <c r="P363" s="4" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="6" t="inlineStr">
@@ -9976,6 +10344,7 @@
       <c r="M364" s="7" t="n"/>
       <c r="N364" s="7" t="n"/>
       <c r="O364" s="7" t="n"/>
+      <c r="P364" s="7" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="6" t="inlineStr">
@@ -10001,6 +10370,7 @@
       <c r="M365" s="7" t="n"/>
       <c r="N365" s="7" t="n"/>
       <c r="O365" s="7" t="n"/>
+      <c r="P365" s="7" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="3" t="inlineStr">
@@ -10030,6 +10400,7 @@
       <c r="M366" s="4" t="n"/>
       <c r="N366" s="4" t="n"/>
       <c r="O366" s="4" t="n"/>
+      <c r="P366" s="4" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="3" t="inlineStr">
@@ -10051,6 +10422,7 @@
       <c r="M367" s="4" t="n"/>
       <c r="N367" s="4" t="n"/>
       <c r="O367" s="4" t="n"/>
+      <c r="P367" s="4" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="3" t="inlineStr">
@@ -10072,6 +10444,7 @@
       <c r="M368" s="4" t="n"/>
       <c r="N368" s="4" t="n"/>
       <c r="O368" s="4" t="n"/>
+      <c r="P368" s="4" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="3" t="inlineStr">
@@ -10093,6 +10466,7 @@
       <c r="M369" s="4" t="n"/>
       <c r="N369" s="4" t="n"/>
       <c r="O369" s="4" t="n"/>
+      <c r="P369" s="4" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="3" t="inlineStr">
@@ -10114,6 +10488,7 @@
       <c r="M370" s="4" t="n"/>
       <c r="N370" s="4" t="n"/>
       <c r="O370" s="4" t="n"/>
+      <c r="P370" s="4" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="6" t="inlineStr">
@@ -10135,6 +10510,7 @@
       <c r="M371" s="7" t="n"/>
       <c r="N371" s="7" t="n"/>
       <c r="O371" s="7" t="n"/>
+      <c r="P371" s="7" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="6" t="inlineStr">
@@ -10156,6 +10532,7 @@
       <c r="M372" s="7" t="n"/>
       <c r="N372" s="7" t="n"/>
       <c r="O372" s="7" t="n"/>
+      <c r="P372" s="7" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="3" t="inlineStr">
@@ -10181,6 +10558,7 @@
       <c r="M373" s="4" t="n"/>
       <c r="N373" s="4" t="n"/>
       <c r="O373" s="4" t="n"/>
+      <c r="P373" s="4" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="3" t="inlineStr">
@@ -10210,6 +10588,7 @@
       <c r="M374" s="4" t="n"/>
       <c r="N374" s="4" t="n"/>
       <c r="O374" s="4" t="n"/>
+      <c r="P374" s="4" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="3" t="inlineStr">
@@ -10239,6 +10618,7 @@
       <c r="M375" s="4" t="n"/>
       <c r="N375" s="4" t="n"/>
       <c r="O375" s="4" t="n"/>
+      <c r="P375" s="4" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="3" t="inlineStr">
@@ -10268,6 +10648,7 @@
       <c r="M376" s="4" t="n"/>
       <c r="N376" s="4" t="n"/>
       <c r="O376" s="4" t="n"/>
+      <c r="P376" s="4" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="3" t="inlineStr">
@@ -10297,6 +10678,7 @@
       <c r="M377" s="4" t="n"/>
       <c r="N377" s="4" t="n"/>
       <c r="O377" s="4" t="n"/>
+      <c r="P377" s="4" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="6" t="inlineStr">
@@ -10322,6 +10704,7 @@
       <c r="M378" s="7" t="n"/>
       <c r="N378" s="7" t="n"/>
       <c r="O378" s="7" t="n"/>
+      <c r="P378" s="7" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="6" t="inlineStr">
@@ -10343,6 +10726,7 @@
       <c r="M379" s="7" t="n"/>
       <c r="N379" s="7" t="n"/>
       <c r="O379" s="7" t="n"/>
+      <c r="P379" s="7" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="3" t="inlineStr">
@@ -10372,6 +10756,7 @@
       <c r="M380" s="4" t="n"/>
       <c r="N380" s="4" t="n"/>
       <c r="O380" s="4" t="n"/>
+      <c r="P380" s="4" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="3" t="inlineStr">
@@ -10401,6 +10786,7 @@
       <c r="M381" s="4" t="n"/>
       <c r="N381" s="4" t="n"/>
       <c r="O381" s="4" t="n"/>
+      <c r="P381" s="4" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="3" t="inlineStr">
@@ -10434,6 +10820,7 @@
       <c r="M382" s="4" t="n"/>
       <c r="N382" s="4" t="n"/>
       <c r="O382" s="4" t="n"/>
+      <c r="P382" s="4" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="3" t="inlineStr">
@@ -10467,6 +10854,7 @@
       <c r="M383" s="4" t="n"/>
       <c r="N383" s="4" t="n"/>
       <c r="O383" s="4" t="n"/>
+      <c r="P383" s="4" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="3" t="inlineStr">
@@ -10494,12 +10882,13 @@
       <c r="K384" s="4" t="n"/>
       <c r="L384" s="4" t="n"/>
       <c r="M384" s="4" t="n"/>
-      <c r="N384" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O384" s="4" t="n"/>
+      <c r="N384" s="4" t="n"/>
+      <c r="O384" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P384" s="4" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="6" t="inlineStr">
@@ -10521,6 +10910,7 @@
       <c r="M385" s="7" t="n"/>
       <c r="N385" s="7" t="n"/>
       <c r="O385" s="7" t="n"/>
+      <c r="P385" s="7" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="6" t="inlineStr">
@@ -10542,6 +10932,7 @@
       <c r="M386" s="7" t="n"/>
       <c r="N386" s="7" t="n"/>
       <c r="O386" s="7" t="n"/>
+      <c r="P386" s="7" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="3" t="inlineStr">
@@ -10575,6 +10966,7 @@
       <c r="M387" s="4" t="n"/>
       <c r="N387" s="4" t="n"/>
       <c r="O387" s="4" t="n"/>
+      <c r="P387" s="4" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="3" t="inlineStr">
@@ -10608,6 +11000,7 @@
       <c r="M388" s="4" t="n"/>
       <c r="N388" s="4" t="n"/>
       <c r="O388" s="4" t="n"/>
+      <c r="P388" s="4" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="3" t="inlineStr">
@@ -10641,6 +11034,7 @@
       <c r="M389" s="4" t="n"/>
       <c r="N389" s="4" t="n"/>
       <c r="O389" s="4" t="n"/>
+      <c r="P389" s="4" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="3" t="inlineStr">
@@ -10674,6 +11068,7 @@
       <c r="M390" s="4" t="n"/>
       <c r="N390" s="4" t="n"/>
       <c r="O390" s="4" t="n"/>
+      <c r="P390" s="4" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="3" t="inlineStr">
@@ -10754,6 +11149,11 @@
           <t>Film</t>
         </is>
       </c>
+      <c r="P391" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="6" t="inlineStr">
@@ -10831,6 +11231,11 @@
           <t>Film</t>
         </is>
       </c>
+      <c r="P392" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="6" t="inlineStr">
@@ -10904,6 +11309,11 @@
         </is>
       </c>
       <c r="O393" s="5" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="P393" s="5" t="inlineStr">
         <is>
           <t>Film</t>
         </is>
@@ -10941,6 +11351,7 @@
       <c r="M394" s="4" t="n"/>
       <c r="N394" s="4" t="n"/>
       <c r="O394" s="4" t="n"/>
+      <c r="P394" s="4" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="3" t="inlineStr">
@@ -10974,6 +11385,7 @@
       <c r="M395" s="4" t="n"/>
       <c r="N395" s="4" t="n"/>
       <c r="O395" s="4" t="n"/>
+      <c r="P395" s="4" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="3" t="inlineStr">
@@ -11008,6 +11420,7 @@
       <c r="M396" s="4" t="n"/>
       <c r="N396" s="4" t="n"/>
       <c r="O396" s="4" t="n"/>
+      <c r="P396" s="4" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="3" t="inlineStr">
@@ -11037,6 +11450,7 @@
       <c r="M397" s="4" t="n"/>
       <c r="N397" s="4" t="n"/>
       <c r="O397" s="4" t="n"/>
+      <c r="P397" s="4" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="3" t="inlineStr">
@@ -11070,6 +11484,7 @@
       <c r="M398" s="4" t="n"/>
       <c r="N398" s="4" t="n"/>
       <c r="O398" s="4" t="n"/>
+      <c r="P398" s="4" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="6" t="inlineStr">
@@ -11091,6 +11506,7 @@
       <c r="M399" s="7" t="n"/>
       <c r="N399" s="7" t="n"/>
       <c r="O399" s="7" t="n"/>
+      <c r="P399" s="7" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="6" t="inlineStr">
@@ -11112,6 +11528,7 @@
       <c r="M400" s="7" t="n"/>
       <c r="N400" s="7" t="n"/>
       <c r="O400" s="7" t="n"/>
+      <c r="P400" s="7" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="3" t="inlineStr">
@@ -11145,18 +11562,19 @@
           <t>Film - LGBTQ+</t>
         </is>
       </c>
-      <c r="L401" s="5" t="inlineStr">
+      <c r="L401" s="4" t="n"/>
+      <c r="M401" s="5" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
-      <c r="M401" s="5" t="inlineStr">
+      <c r="N401" s="5" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
-      <c r="N401" s="4" t="n"/>
       <c r="O401" s="4" t="n"/>
+      <c r="P401" s="4" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="3" t="inlineStr">
@@ -11190,18 +11608,19 @@
           <t>Film - LGBTQ+</t>
         </is>
       </c>
-      <c r="L402" s="5" t="inlineStr">
+      <c r="L402" s="4" t="n"/>
+      <c r="M402" s="5" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
-      <c r="M402" s="5" t="inlineStr">
+      <c r="N402" s="5" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
-      <c r="N402" s="4" t="n"/>
       <c r="O402" s="4" t="n"/>
+      <c r="P402" s="4" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="3" t="inlineStr">
@@ -11235,18 +11654,19 @@
           <t>Film - LGBTQ+</t>
         </is>
       </c>
-      <c r="L403" s="5" t="inlineStr">
+      <c r="L403" s="4" t="n"/>
+      <c r="M403" s="5" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
-      <c r="M403" s="5" t="inlineStr">
+      <c r="N403" s="5" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
-      <c r="N403" s="4" t="n"/>
       <c r="O403" s="4" t="n"/>
+      <c r="P403" s="4" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="3" t="inlineStr">
@@ -11280,18 +11700,19 @@
           <t>Film - LGBTQ+</t>
         </is>
       </c>
-      <c r="L404" s="5" t="inlineStr">
+      <c r="L404" s="4" t="n"/>
+      <c r="M404" s="5" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
-      <c r="M404" s="5" t="inlineStr">
+      <c r="N404" s="5" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
-      <c r="N404" s="4" t="n"/>
       <c r="O404" s="4" t="n"/>
+      <c r="P404" s="4" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="3" t="inlineStr">
@@ -11333,18 +11754,19 @@
           <t>Film - LGBTQ+</t>
         </is>
       </c>
-      <c r="L405" s="5" t="inlineStr">
+      <c r="L405" s="4" t="n"/>
+      <c r="M405" s="5" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
-      <c r="M405" s="5" t="inlineStr">
+      <c r="N405" s="5" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
-      <c r="N405" s="4" t="n"/>
       <c r="O405" s="4" t="n"/>
+      <c r="P405" s="4" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="6" t="inlineStr">
@@ -11366,6 +11788,7 @@
       <c r="M406" s="7" t="n"/>
       <c r="N406" s="7" t="n"/>
       <c r="O406" s="7" t="n"/>
+      <c r="P406" s="7" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="6" t="inlineStr">
@@ -11387,6 +11810,7 @@
       <c r="M407" s="7" t="n"/>
       <c r="N407" s="7" t="n"/>
       <c r="O407" s="7" t="n"/>
+      <c r="P407" s="7" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="3" t="inlineStr">
@@ -11408,18 +11832,19 @@
         </is>
       </c>
       <c r="K408" s="4" t="n"/>
-      <c r="L408" s="5" t="inlineStr">
+      <c r="L408" s="4" t="n"/>
+      <c r="M408" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="M408" s="5" t="inlineStr">
+      <c r="N408" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="N408" s="4" t="n"/>
       <c r="O408" s="4" t="n"/>
+      <c r="P408" s="4" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="3" t="inlineStr">
@@ -11441,18 +11866,19 @@
         </is>
       </c>
       <c r="K409" s="4" t="n"/>
-      <c r="L409" s="5" t="inlineStr">
+      <c r="L409" s="4" t="n"/>
+      <c r="M409" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="M409" s="5" t="inlineStr">
+      <c r="N409" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="N409" s="4" t="n"/>
       <c r="O409" s="4" t="n"/>
+      <c r="P409" s="4" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="3" t="inlineStr">
@@ -11475,18 +11901,19 @@
         </is>
       </c>
       <c r="K410" s="4" t="n"/>
-      <c r="L410" s="5" t="inlineStr">
+      <c r="L410" s="4" t="n"/>
+      <c r="M410" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="M410" s="5" t="inlineStr">
+      <c r="N410" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="N410" s="4" t="n"/>
       <c r="O410" s="4" t="n"/>
+      <c r="P410" s="4" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="3" t="inlineStr">
@@ -11512,18 +11939,19 @@
         </is>
       </c>
       <c r="K411" s="4" t="n"/>
-      <c r="L411" s="5" t="inlineStr">
+      <c r="L411" s="4" t="n"/>
+      <c r="M411" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="M411" s="5" t="inlineStr">
+      <c r="N411" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="N411" s="4" t="n"/>
       <c r="O411" s="4" t="n"/>
+      <c r="P411" s="4" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="3" t="inlineStr">
@@ -11549,18 +11977,19 @@
         </is>
       </c>
       <c r="K412" s="4" t="n"/>
-      <c r="L412" s="5" t="inlineStr">
+      <c r="L412" s="4" t="n"/>
+      <c r="M412" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="M412" s="5" t="inlineStr">
+      <c r="N412" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="N412" s="4" t="n"/>
       <c r="O412" s="4" t="n"/>
+      <c r="P412" s="4" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="6" t="inlineStr">
@@ -11582,6 +12011,7 @@
       <c r="M413" s="7" t="n"/>
       <c r="N413" s="7" t="n"/>
       <c r="O413" s="7" t="n"/>
+      <c r="P413" s="7" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="6" t="inlineStr">
@@ -11603,6 +12033,7 @@
       <c r="M414" s="7" t="n"/>
       <c r="N414" s="7" t="n"/>
       <c r="O414" s="7" t="n"/>
+      <c r="P414" s="7" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="3" t="inlineStr">
@@ -11624,18 +12055,19 @@
         </is>
       </c>
       <c r="K415" s="4" t="n"/>
-      <c r="L415" s="5" t="inlineStr">
+      <c r="L415" s="4" t="n"/>
+      <c r="M415" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="M415" s="5" t="inlineStr">
+      <c r="N415" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="N415" s="4" t="n"/>
       <c r="O415" s="4" t="n"/>
+      <c r="P415" s="4" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="3" t="inlineStr">
@@ -11657,18 +12089,19 @@
         </is>
       </c>
       <c r="K416" s="4" t="n"/>
-      <c r="L416" s="5" t="inlineStr">
+      <c r="L416" s="4" t="n"/>
+      <c r="M416" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="M416" s="5" t="inlineStr">
+      <c r="N416" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="N416" s="4" t="n"/>
       <c r="O416" s="4" t="n"/>
+      <c r="P416" s="4" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="3" t="inlineStr">
@@ -11690,18 +12123,19 @@
         </is>
       </c>
       <c r="K417" s="4" t="n"/>
-      <c r="L417" s="5" t="inlineStr">
+      <c r="L417" s="4" t="n"/>
+      <c r="M417" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="M417" s="5" t="inlineStr">
+      <c r="N417" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="N417" s="4" t="n"/>
       <c r="O417" s="4" t="n"/>
+      <c r="P417" s="4" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="3" t="inlineStr">
@@ -11723,18 +12157,19 @@
         </is>
       </c>
       <c r="K418" s="4" t="n"/>
-      <c r="L418" s="5" t="inlineStr">
+      <c r="L418" s="4" t="n"/>
+      <c r="M418" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="M418" s="5" t="inlineStr">
+      <c r="N418" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="N418" s="4" t="n"/>
       <c r="O418" s="4" t="n"/>
+      <c r="P418" s="4" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="3" t="inlineStr">
@@ -11756,18 +12191,19 @@
         </is>
       </c>
       <c r="K419" s="4" t="n"/>
-      <c r="L419" s="5" t="inlineStr">
+      <c r="L419" s="4" t="n"/>
+      <c r="M419" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="M419" s="5" t="inlineStr">
+      <c r="N419" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="N419" s="4" t="n"/>
       <c r="O419" s="4" t="n"/>
+      <c r="P419" s="4" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="6" t="inlineStr">
@@ -11789,6 +12225,7 @@
       <c r="M420" s="7" t="n"/>
       <c r="N420" s="7" t="n"/>
       <c r="O420" s="7" t="n"/>
+      <c r="P420" s="7" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="6" t="inlineStr">
@@ -11810,6 +12247,7 @@
       <c r="M421" s="7" t="n"/>
       <c r="N421" s="7" t="n"/>
       <c r="O421" s="7" t="n"/>
+      <c r="P421" s="7" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="3" t="inlineStr">
@@ -11827,18 +12265,19 @@
       <c r="I422" s="4" t="n"/>
       <c r="J422" s="4" t="n"/>
       <c r="K422" s="4" t="n"/>
-      <c r="L422" s="5" t="inlineStr">
+      <c r="L422" s="4" t="n"/>
+      <c r="M422" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="M422" s="5" t="inlineStr">
+      <c r="N422" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="N422" s="4" t="n"/>
       <c r="O422" s="4" t="n"/>
+      <c r="P422" s="4" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="3" t="inlineStr">
@@ -11864,18 +12303,19 @@
       </c>
       <c r="J423" s="4" t="n"/>
       <c r="K423" s="4" t="n"/>
-      <c r="L423" s="5" t="inlineStr">
+      <c r="L423" s="4" t="n"/>
+      <c r="M423" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="M423" s="5" t="inlineStr">
+      <c r="N423" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="N423" s="4" t="n"/>
       <c r="O423" s="4" t="n"/>
+      <c r="P423" s="4" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="3" t="inlineStr">
@@ -11905,18 +12345,19 @@
         </is>
       </c>
       <c r="K424" s="4" t="n"/>
-      <c r="L424" s="5" t="inlineStr">
+      <c r="L424" s="4" t="n"/>
+      <c r="M424" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="M424" s="5" t="inlineStr">
+      <c r="N424" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="N424" s="4" t="n"/>
       <c r="O424" s="4" t="n"/>
+      <c r="P424" s="4" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="3" t="inlineStr">
@@ -11946,18 +12387,19 @@
         </is>
       </c>
       <c r="K425" s="4" t="n"/>
-      <c r="L425" s="5" t="inlineStr">
+      <c r="L425" s="4" t="n"/>
+      <c r="M425" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="M425" s="5" t="inlineStr">
+      <c r="N425" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="N425" s="4" t="n"/>
       <c r="O425" s="4" t="n"/>
+      <c r="P425" s="4" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="3" t="inlineStr">
@@ -11987,18 +12429,19 @@
         </is>
       </c>
       <c r="K426" s="4" t="n"/>
-      <c r="L426" s="5" t="inlineStr">
+      <c r="L426" s="4" t="n"/>
+      <c r="M426" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="M426" s="5" t="inlineStr">
+      <c r="N426" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="N426" s="4" t="n"/>
       <c r="O426" s="4" t="n"/>
+      <c r="P426" s="4" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="6" t="inlineStr">
@@ -12020,6 +12463,7 @@
       <c r="M427" s="7" t="n"/>
       <c r="N427" s="7" t="n"/>
       <c r="O427" s="7" t="n"/>
+      <c r="P427" s="7" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="6" t="inlineStr">
@@ -12041,6 +12485,7 @@
       <c r="M428" s="7" t="n"/>
       <c r="N428" s="7" t="n"/>
       <c r="O428" s="7" t="n"/>
+      <c r="P428" s="7" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="3" t="inlineStr">
@@ -12062,6 +12507,7 @@
       <c r="M429" s="4" t="n"/>
       <c r="N429" s="4" t="n"/>
       <c r="O429" s="4" t="n"/>
+      <c r="P429" s="4" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="3" t="inlineStr">
@@ -12083,6 +12529,7 @@
       <c r="M430" s="4" t="n"/>
       <c r="N430" s="4" t="n"/>
       <c r="O430" s="4" t="n"/>
+      <c r="P430" s="4" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="3" t="inlineStr">
@@ -12104,6 +12551,7 @@
       <c r="M431" s="4" t="n"/>
       <c r="N431" s="4" t="n"/>
       <c r="O431" s="4" t="n"/>
+      <c r="P431" s="4" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="3" t="inlineStr">
@@ -12125,6 +12573,7 @@
       <c r="M432" s="4" t="n"/>
       <c r="N432" s="4" t="n"/>
       <c r="O432" s="4" t="n"/>
+      <c r="P432" s="4" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="3" t="inlineStr">
@@ -12146,6 +12595,7 @@
       <c r="M433" s="4" t="n"/>
       <c r="N433" s="4" t="n"/>
       <c r="O433" s="4" t="n"/>
+      <c r="P433" s="4" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="6" t="inlineStr">
@@ -12167,6 +12617,7 @@
       <c r="M434" s="7" t="n"/>
       <c r="N434" s="7" t="n"/>
       <c r="O434" s="7" t="n"/>
+      <c r="P434" s="7" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="6" t="inlineStr">
@@ -12188,6 +12639,7 @@
       <c r="M435" s="7" t="n"/>
       <c r="N435" s="7" t="n"/>
       <c r="O435" s="7" t="n"/>
+      <c r="P435" s="7" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="3" t="inlineStr">
@@ -12209,6 +12661,7 @@
       <c r="M436" s="4" t="n"/>
       <c r="N436" s="4" t="n"/>
       <c r="O436" s="4" t="n"/>
+      <c r="P436" s="4" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="3" t="inlineStr">
@@ -12230,6 +12683,7 @@
       <c r="M437" s="4" t="n"/>
       <c r="N437" s="4" t="n"/>
       <c r="O437" s="4" t="n"/>
+      <c r="P437" s="4" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="3" t="inlineStr">
@@ -12251,6 +12705,7 @@
       <c r="M438" s="4" t="n"/>
       <c r="N438" s="4" t="n"/>
       <c r="O438" s="4" t="n"/>
+      <c r="P438" s="4" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="3" t="inlineStr">
@@ -12272,6 +12727,7 @@
       <c r="M439" s="4" t="n"/>
       <c r="N439" s="4" t="n"/>
       <c r="O439" s="4" t="n"/>
+      <c r="P439" s="4" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="3" t="inlineStr">
@@ -12293,6 +12749,7 @@
       <c r="M440" s="4" t="n"/>
       <c r="N440" s="4" t="n"/>
       <c r="O440" s="4" t="n"/>
+      <c r="P440" s="4" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="6" t="inlineStr">
@@ -12314,6 +12771,7 @@
       <c r="M441" s="7" t="n"/>
       <c r="N441" s="7" t="n"/>
       <c r="O441" s="7" t="n"/>
+      <c r="P441" s="7" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="6" t="inlineStr">
@@ -12335,6 +12793,7 @@
       <c r="M442" s="7" t="n"/>
       <c r="N442" s="7" t="n"/>
       <c r="O442" s="7" t="n"/>
+      <c r="P442" s="7" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="3" t="inlineStr">
@@ -12356,6 +12815,7 @@
       <c r="M443" s="4" t="n"/>
       <c r="N443" s="4" t="n"/>
       <c r="O443" s="4" t="n"/>
+      <c r="P443" s="4" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="3" t="inlineStr">
@@ -12377,6 +12837,7 @@
       <c r="M444" s="4" t="n"/>
       <c r="N444" s="4" t="n"/>
       <c r="O444" s="4" t="n"/>
+      <c r="P444" s="4" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="3" t="inlineStr">
@@ -12402,6 +12863,7 @@
       <c r="M445" s="4" t="n"/>
       <c r="N445" s="4" t="n"/>
       <c r="O445" s="4" t="n"/>
+      <c r="P445" s="4" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="3" t="inlineStr">
@@ -12423,6 +12885,7 @@
       <c r="M446" s="4" t="n"/>
       <c r="N446" s="4" t="n"/>
       <c r="O446" s="4" t="n"/>
+      <c r="P446" s="4" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="3" t="inlineStr">
@@ -12448,6 +12911,7 @@
       <c r="M447" s="4" t="n"/>
       <c r="N447" s="4" t="n"/>
       <c r="O447" s="4" t="n"/>
+      <c r="P447" s="4" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="6" t="inlineStr">
@@ -12469,6 +12933,7 @@
       <c r="M448" s="7" t="n"/>
       <c r="N448" s="7" t="n"/>
       <c r="O448" s="7" t="n"/>
+      <c r="P448" s="7" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="6" t="inlineStr">
@@ -12490,6 +12955,7 @@
       <c r="M449" s="7" t="n"/>
       <c r="N449" s="7" t="n"/>
       <c r="O449" s="7" t="n"/>
+      <c r="P449" s="7" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="3" t="inlineStr">
@@ -12519,6 +12985,7 @@
       <c r="M450" s="4" t="n"/>
       <c r="N450" s="4" t="n"/>
       <c r="O450" s="4" t="n"/>
+      <c r="P450" s="4" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="3" t="inlineStr">
@@ -12548,6 +13015,7 @@
       <c r="M451" s="4" t="n"/>
       <c r="N451" s="4" t="n"/>
       <c r="O451" s="4" t="n"/>
+      <c r="P451" s="4" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="3" t="inlineStr">
@@ -12569,6 +13037,7 @@
       <c r="M452" s="4" t="n"/>
       <c r="N452" s="4" t="n"/>
       <c r="O452" s="4" t="n"/>
+      <c r="P452" s="4" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="3" t="inlineStr">
@@ -12590,6 +13059,7 @@
       <c r="M453" s="4" t="n"/>
       <c r="N453" s="4" t="n"/>
       <c r="O453" s="4" t="n"/>
+      <c r="P453" s="4" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="3" t="inlineStr">
@@ -12615,6 +13085,7 @@
       <c r="M454" s="4" t="n"/>
       <c r="N454" s="4" t="n"/>
       <c r="O454" s="4" t="n"/>
+      <c r="P454" s="4" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="6" t="inlineStr">
@@ -12636,6 +13107,7 @@
       <c r="M455" s="7" t="n"/>
       <c r="N455" s="7" t="n"/>
       <c r="O455" s="7" t="n"/>
+      <c r="P455" s="7" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="6" t="inlineStr">
@@ -12657,6 +13129,7 @@
       <c r="M456" s="7" t="n"/>
       <c r="N456" s="7" t="n"/>
       <c r="O456" s="7" t="n"/>
+      <c r="P456" s="7" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="3" t="inlineStr">
@@ -12678,6 +13151,7 @@
       <c r="M457" s="4" t="n"/>
       <c r="N457" s="4" t="n"/>
       <c r="O457" s="4" t="n"/>
+      <c r="P457" s="4" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="3" t="inlineStr">
@@ -12703,6 +13177,7 @@
       <c r="M458" s="4" t="n"/>
       <c r="N458" s="4" t="n"/>
       <c r="O458" s="4" t="n"/>
+      <c r="P458" s="4" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="3" t="inlineStr">
@@ -12740,6 +13215,7 @@
       <c r="M459" s="4" t="n"/>
       <c r="N459" s="4" t="n"/>
       <c r="O459" s="4" t="n"/>
+      <c r="P459" s="4" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="3" t="inlineStr">
@@ -12777,6 +13253,7 @@
       <c r="M460" s="4" t="n"/>
       <c r="N460" s="4" t="n"/>
       <c r="O460" s="4" t="n"/>
+      <c r="P460" s="4" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="3" t="inlineStr">
@@ -12814,6 +13291,7 @@
       <c r="M461" s="4" t="n"/>
       <c r="N461" s="4" t="n"/>
       <c r="O461" s="4" t="n"/>
+      <c r="P461" s="4" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="6" t="inlineStr">
@@ -12835,6 +13313,7 @@
       <c r="M462" s="7" t="n"/>
       <c r="N462" s="7" t="n"/>
       <c r="O462" s="7" t="n"/>
+      <c r="P462" s="7" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="6" t="inlineStr">
@@ -12856,6 +13335,7 @@
       <c r="M463" s="7" t="n"/>
       <c r="N463" s="7" t="n"/>
       <c r="O463" s="7" t="n"/>
+      <c r="P463" s="7" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="3" t="inlineStr">
@@ -12877,6 +13357,7 @@
       <c r="M464" s="4" t="n"/>
       <c r="N464" s="4" t="n"/>
       <c r="O464" s="4" t="n"/>
+      <c r="P464" s="4" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="3" t="inlineStr">
@@ -12902,6 +13383,7 @@
       <c r="M465" s="4" t="n"/>
       <c r="N465" s="4" t="n"/>
       <c r="O465" s="4" t="n"/>
+      <c r="P465" s="4" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="3" t="inlineStr">
@@ -12927,6 +13409,7 @@
       <c r="M466" s="4" t="n"/>
       <c r="N466" s="4" t="n"/>
       <c r="O466" s="4" t="n"/>
+      <c r="P466" s="4" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="3" t="inlineStr">
@@ -12952,6 +13435,7 @@
       <c r="M467" s="4" t="n"/>
       <c r="N467" s="4" t="n"/>
       <c r="O467" s="4" t="n"/>
+      <c r="P467" s="4" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="3" t="inlineStr">
@@ -12977,6 +13461,7 @@
       <c r="M468" s="4" t="n"/>
       <c r="N468" s="4" t="n"/>
       <c r="O468" s="4" t="n"/>
+      <c r="P468" s="4" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="6" t="inlineStr">
@@ -12998,6 +13483,7 @@
       <c r="M469" s="7" t="n"/>
       <c r="N469" s="7" t="n"/>
       <c r="O469" s="7" t="n"/>
+      <c r="P469" s="7" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="6" t="inlineStr">
@@ -13019,6 +13505,7 @@
       <c r="M470" s="7" t="n"/>
       <c r="N470" s="7" t="n"/>
       <c r="O470" s="7" t="n"/>
+      <c r="P470" s="7" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="3" t="inlineStr">
@@ -13044,6 +13531,7 @@
       <c r="M471" s="4" t="n"/>
       <c r="N471" s="4" t="n"/>
       <c r="O471" s="4" t="n"/>
+      <c r="P471" s="4" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="3" t="inlineStr">
@@ -13069,6 +13557,7 @@
       <c r="M472" s="4" t="n"/>
       <c r="N472" s="4" t="n"/>
       <c r="O472" s="4" t="n"/>
+      <c r="P472" s="4" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="3" t="inlineStr">
@@ -13094,6 +13583,7 @@
       <c r="M473" s="4" t="n"/>
       <c r="N473" s="4" t="n"/>
       <c r="O473" s="4" t="n"/>
+      <c r="P473" s="4" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="3" t="inlineStr">
@@ -13119,6 +13609,7 @@
       <c r="M474" s="4" t="n"/>
       <c r="N474" s="4" t="n"/>
       <c r="O474" s="4" t="n"/>
+      <c r="P474" s="4" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="3" t="inlineStr">
@@ -13144,6 +13635,7 @@
       <c r="M475" s="4" t="n"/>
       <c r="N475" s="4" t="n"/>
       <c r="O475" s="4" t="n"/>
+      <c r="P475" s="4" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="6" t="inlineStr">
@@ -13165,6 +13657,7 @@
       <c r="M476" s="7" t="n"/>
       <c r="N476" s="7" t="n"/>
       <c r="O476" s="7" t="n"/>
+      <c r="P476" s="7" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="6" t="inlineStr">
@@ -13186,6 +13679,7 @@
       <c r="M477" s="7" t="n"/>
       <c r="N477" s="7" t="n"/>
       <c r="O477" s="7" t="n"/>
+      <c r="P477" s="7" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="3" t="inlineStr">
@@ -13211,18 +13705,19 @@
         </is>
       </c>
       <c r="K478" s="4" t="n"/>
-      <c r="L478" s="11" t="inlineStr">
+      <c r="L478" s="4" t="n"/>
+      <c r="M478" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Dewi Mockumentary</t>
         </is>
       </c>
-      <c r="M478" s="11" t="inlineStr">
+      <c r="N478" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Dewi Mockumentary</t>
         </is>
       </c>
-      <c r="N478" s="4" t="n"/>
       <c r="O478" s="4" t="n"/>
+      <c r="P478" s="4" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="3" t="inlineStr">
@@ -13248,18 +13743,19 @@
         </is>
       </c>
       <c r="K479" s="4" t="n"/>
-      <c r="L479" s="11" t="inlineStr">
+      <c r="L479" s="4" t="n"/>
+      <c r="M479" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Dewi Mockumentary</t>
         </is>
       </c>
-      <c r="M479" s="11" t="inlineStr">
+      <c r="N479" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Dewi Mockumentary</t>
         </is>
       </c>
-      <c r="N479" s="4" t="n"/>
       <c r="O479" s="4" t="n"/>
+      <c r="P479" s="4" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="3" t="inlineStr">
@@ -13285,18 +13781,19 @@
         </is>
       </c>
       <c r="K480" s="4" t="n"/>
-      <c r="L480" s="11" t="inlineStr">
+      <c r="L480" s="4" t="n"/>
+      <c r="M480" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Dewi Mockumentary</t>
         </is>
       </c>
-      <c r="M480" s="11" t="inlineStr">
+      <c r="N480" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Dewi Mockumentary</t>
         </is>
       </c>
-      <c r="N480" s="4" t="n"/>
       <c r="O480" s="4" t="n"/>
+      <c r="P480" s="4" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="3" t="inlineStr">
@@ -13322,22 +13819,23 @@
         </is>
       </c>
       <c r="K481" s="4" t="n"/>
-      <c r="L481" s="11" t="inlineStr">
+      <c r="L481" s="4" t="n"/>
+      <c r="M481" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Dewi Mockumentary</t>
         </is>
       </c>
-      <c r="M481" s="11" t="inlineStr">
+      <c r="N481" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Dewi Mockumentary</t>
         </is>
       </c>
-      <c r="N481" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O481" s="4" t="n"/>
+      <c r="O481" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P481" s="4" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="3" t="inlineStr">
@@ -13363,22 +13861,23 @@
         </is>
       </c>
       <c r="K482" s="4" t="n"/>
-      <c r="L482" s="11" t="inlineStr">
+      <c r="L482" s="4" t="n"/>
+      <c r="M482" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Dewi Mockumentary</t>
         </is>
       </c>
-      <c r="M482" s="11" t="inlineStr">
+      <c r="N482" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Dewi Mockumentary</t>
         </is>
       </c>
-      <c r="N482" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="O482" s="4" t="n"/>
+      <c r="O482" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="P482" s="4" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="6" t="inlineStr">
@@ -13400,6 +13899,7 @@
       <c r="M483" s="7" t="n"/>
       <c r="N483" s="7" t="n"/>
       <c r="O483" s="7" t="n"/>
+      <c r="P483" s="7" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="6" t="inlineStr">
@@ -13421,6 +13921,7 @@
       <c r="M484" s="7" t="n"/>
       <c r="N484" s="7" t="n"/>
       <c r="O484" s="7" t="n"/>
+      <c r="P484" s="7" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="3" t="inlineStr">
@@ -13446,6 +13947,7 @@
       <c r="M485" s="4" t="n"/>
       <c r="N485" s="4" t="n"/>
       <c r="O485" s="4" t="n"/>
+      <c r="P485" s="4" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="3" t="inlineStr">
@@ -13471,6 +13973,7 @@
       <c r="M486" s="4" t="n"/>
       <c r="N486" s="4" t="n"/>
       <c r="O486" s="4" t="n"/>
+      <c r="P486" s="4" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="3" t="inlineStr">
@@ -13492,6 +13995,7 @@
       <c r="M487" s="4" t="n"/>
       <c r="N487" s="4" t="n"/>
       <c r="O487" s="4" t="n"/>
+      <c r="P487" s="4" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="3" t="inlineStr">
@@ -13517,6 +14021,7 @@
       <c r="M488" s="4" t="n"/>
       <c r="N488" s="4" t="n"/>
       <c r="O488" s="4" t="n"/>
+      <c r="P488" s="4" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="3" t="inlineStr">
@@ -13542,6 +14047,7 @@
       <c r="M489" s="4" t="n"/>
       <c r="N489" s="4" t="n"/>
       <c r="O489" s="4" t="n"/>
+      <c r="P489" s="4" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="6" t="inlineStr">
@@ -13563,6 +14069,7 @@
       <c r="M490" s="7" t="n"/>
       <c r="N490" s="7" t="n"/>
       <c r="O490" s="7" t="n"/>
+      <c r="P490" s="7" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="6" t="inlineStr">
@@ -13584,6 +14091,7 @@
       <c r="M491" s="7" t="n"/>
       <c r="N491" s="7" t="n"/>
       <c r="O491" s="7" t="n"/>
+      <c r="P491" s="7" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="3" t="inlineStr">
@@ -13609,6 +14117,7 @@
       <c r="M492" s="4" t="n"/>
       <c r="N492" s="4" t="n"/>
       <c r="O492" s="4" t="n"/>
+      <c r="P492" s="4" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="3" t="inlineStr">
@@ -13638,6 +14147,7 @@
       <c r="M493" s="4" t="n"/>
       <c r="N493" s="4" t="n"/>
       <c r="O493" s="4" t="n"/>
+      <c r="P493" s="4" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="3" t="inlineStr">
@@ -13668,6 +14178,7 @@
       <c r="M494" s="4" t="n"/>
       <c r="N494" s="4" t="n"/>
       <c r="O494" s="4" t="n"/>
+      <c r="P494" s="4" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="3" t="inlineStr">
@@ -13693,6 +14204,7 @@
       <c r="M495" s="4" t="n"/>
       <c r="N495" s="4" t="n"/>
       <c r="O495" s="4" t="n"/>
+      <c r="P495" s="4" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="3" t="inlineStr">
@@ -13718,6 +14230,7 @@
       <c r="M496" s="4" t="n"/>
       <c r="N496" s="4" t="n"/>
       <c r="O496" s="4" t="n"/>
+      <c r="P496" s="4" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="6" t="inlineStr">
@@ -13739,6 +14252,7 @@
       <c r="M497" s="7" t="n"/>
       <c r="N497" s="7" t="n"/>
       <c r="O497" s="7" t="n"/>
+      <c r="P497" s="7" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="6" t="inlineStr">
@@ -13760,6 +14274,7 @@
       <c r="M498" s="7" t="n"/>
       <c r="N498" s="7" t="n"/>
       <c r="O498" s="7" t="n"/>
+      <c r="P498" s="7" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="3" t="inlineStr">
@@ -13785,6 +14300,7 @@
       <c r="M499" s="4" t="n"/>
       <c r="N499" s="4" t="n"/>
       <c r="O499" s="4" t="n"/>
+      <c r="P499" s="4" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="3" t="inlineStr">
@@ -13810,6 +14326,7 @@
       <c r="M500" s="4" t="n"/>
       <c r="N500" s="4" t="n"/>
       <c r="O500" s="4" t="n"/>
+      <c r="P500" s="4" t="n"/>
     </row>
     <row r="501">
       <c r="A501" s="3" t="inlineStr">
@@ -13835,6 +14352,7 @@
       <c r="M501" s="4" t="n"/>
       <c r="N501" s="4" t="n"/>
       <c r="O501" s="4" t="n"/>
+      <c r="P501" s="4" t="n"/>
     </row>
     <row r="502">
       <c r="A502" s="3" t="inlineStr">
@@ -13860,6 +14378,7 @@
       <c r="M502" s="4" t="n"/>
       <c r="N502" s="4" t="n"/>
       <c r="O502" s="4" t="n"/>
+      <c r="P502" s="4" t="n"/>
     </row>
     <row r="503">
       <c r="A503" s="3" t="inlineStr">
@@ -13885,6 +14404,7 @@
       <c r="M503" s="4" t="n"/>
       <c r="N503" s="4" t="n"/>
       <c r="O503" s="4" t="n"/>
+      <c r="P503" s="4" t="n"/>
     </row>
     <row r="504">
       <c r="A504" s="6" t="inlineStr">
@@ -13906,6 +14426,7 @@
       <c r="M504" s="7" t="n"/>
       <c r="N504" s="7" t="n"/>
       <c r="O504" s="7" t="n"/>
+      <c r="P504" s="7" t="n"/>
     </row>
     <row r="505">
       <c r="A505" s="6" t="inlineStr">
@@ -13927,6 +14448,7 @@
       <c r="M505" s="7" t="n"/>
       <c r="N505" s="7" t="n"/>
       <c r="O505" s="7" t="n"/>
+      <c r="P505" s="7" t="n"/>
     </row>
     <row r="506">
       <c r="A506" s="3" t="inlineStr">
@@ -13952,6 +14474,7 @@
       <c r="M506" s="4" t="n"/>
       <c r="N506" s="4" t="n"/>
       <c r="O506" s="4" t="n"/>
+      <c r="P506" s="4" t="n"/>
     </row>
     <row r="507">
       <c r="A507" s="3" t="inlineStr">
@@ -13977,6 +14500,7 @@
       <c r="M507" s="4" t="n"/>
       <c r="N507" s="4" t="n"/>
       <c r="O507" s="4" t="n"/>
+      <c r="P507" s="4" t="n"/>
     </row>
     <row r="508">
       <c r="A508" s="3" t="inlineStr">
@@ -14002,6 +14526,7 @@
       <c r="M508" s="4" t="n"/>
       <c r="N508" s="4" t="n"/>
       <c r="O508" s="4" t="n"/>
+      <c r="P508" s="4" t="n"/>
     </row>
     <row r="509">
       <c r="A509" s="3" t="inlineStr">
@@ -14027,6 +14552,7 @@
       <c r="M509" s="4" t="n"/>
       <c r="N509" s="4" t="n"/>
       <c r="O509" s="4" t="n"/>
+      <c r="P509" s="4" t="n"/>
     </row>
     <row r="510">
       <c r="A510" s="3" t="inlineStr">
@@ -14052,6 +14578,7 @@
       <c r="M510" s="4" t="n"/>
       <c r="N510" s="4" t="n"/>
       <c r="O510" s="4" t="n"/>
+      <c r="P510" s="4" t="n"/>
     </row>
     <row r="511">
       <c r="A511" s="6" t="inlineStr">
@@ -14073,6 +14600,7 @@
       <c r="M511" s="7" t="n"/>
       <c r="N511" s="7" t="n"/>
       <c r="O511" s="7" t="n"/>
+      <c r="P511" s="7" t="n"/>
     </row>
     <row r="512">
       <c r="A512" s="6" t="inlineStr">
@@ -14094,6 +14622,7 @@
       <c r="M512" s="7" t="n"/>
       <c r="N512" s="7" t="n"/>
       <c r="O512" s="7" t="n"/>
+      <c r="P512" s="7" t="n"/>
     </row>
     <row r="513">
       <c r="A513" s="3" t="inlineStr">
@@ -14119,6 +14648,7 @@
       <c r="M513" s="4" t="n"/>
       <c r="N513" s="4" t="n"/>
       <c r="O513" s="4" t="n"/>
+      <c r="P513" s="4" t="n"/>
     </row>
     <row r="514">
       <c r="A514" s="3" t="inlineStr">
@@ -14144,6 +14674,7 @@
       <c r="M514" s="4" t="n"/>
       <c r="N514" s="4" t="n"/>
       <c r="O514" s="4" t="n"/>
+      <c r="P514" s="4" t="n"/>
     </row>
     <row r="515">
       <c r="A515" s="3" t="inlineStr">
@@ -14169,6 +14700,7 @@
       <c r="M515" s="4" t="n"/>
       <c r="N515" s="4" t="n"/>
       <c r="O515" s="4" t="n"/>
+      <c r="P515" s="4" t="n"/>
     </row>
     <row r="516">
       <c r="A516" s="3" t="inlineStr">
@@ -14194,6 +14726,7 @@
       <c r="M516" s="4" t="n"/>
       <c r="N516" s="4" t="n"/>
       <c r="O516" s="4" t="n"/>
+      <c r="P516" s="4" t="n"/>
     </row>
     <row r="517">
       <c r="A517" s="3" t="inlineStr">
@@ -14219,6 +14752,7 @@
       <c r="M517" s="4" t="n"/>
       <c r="N517" s="4" t="n"/>
       <c r="O517" s="4" t="n"/>
+      <c r="P517" s="4" t="n"/>
     </row>
     <row r="518">
       <c r="A518" s="6" t="inlineStr">
@@ -14240,6 +14774,7 @@
       <c r="M518" s="7" t="n"/>
       <c r="N518" s="7" t="n"/>
       <c r="O518" s="7" t="n"/>
+      <c r="P518" s="7" t="n"/>
     </row>
     <row r="519">
       <c r="A519" s="6" t="inlineStr">
@@ -14261,6 +14796,7 @@
       <c r="M519" s="7" t="n"/>
       <c r="N519" s="7" t="n"/>
       <c r="O519" s="7" t="n"/>
+      <c r="P519" s="7" t="n"/>
     </row>
     <row r="520">
       <c r="A520" s="3" t="inlineStr">
@@ -14290,6 +14826,7 @@
       <c r="M520" s="4" t="n"/>
       <c r="N520" s="4" t="n"/>
       <c r="O520" s="4" t="n"/>
+      <c r="P520" s="4" t="n"/>
     </row>
     <row r="521">
       <c r="A521" s="3" t="inlineStr">
@@ -14319,6 +14856,7 @@
       <c r="M521" s="4" t="n"/>
       <c r="N521" s="4" t="n"/>
       <c r="O521" s="4" t="n"/>
+      <c r="P521" s="4" t="n"/>
     </row>
     <row r="522">
       <c r="A522" s="3" t="inlineStr">
@@ -14348,6 +14886,7 @@
       <c r="M522" s="4" t="n"/>
       <c r="N522" s="4" t="n"/>
       <c r="O522" s="4" t="n"/>
+      <c r="P522" s="4" t="n"/>
     </row>
     <row r="523">
       <c r="A523" s="3" t="inlineStr">
@@ -14377,6 +14916,7 @@
       <c r="M523" s="4" t="n"/>
       <c r="N523" s="4" t="n"/>
       <c r="O523" s="4" t="n"/>
+      <c r="P523" s="4" t="n"/>
     </row>
     <row r="524">
       <c r="A524" s="3" t="inlineStr">
@@ -14406,6 +14946,7 @@
       <c r="M524" s="4" t="n"/>
       <c r="N524" s="4" t="n"/>
       <c r="O524" s="4" t="n"/>
+      <c r="P524" s="4" t="n"/>
     </row>
     <row r="525">
       <c r="A525" s="6" t="inlineStr">
@@ -14427,6 +14968,7 @@
       <c r="M525" s="7" t="n"/>
       <c r="N525" s="7" t="n"/>
       <c r="O525" s="7" t="n"/>
+      <c r="P525" s="7" t="n"/>
     </row>
     <row r="526">
       <c r="A526" s="6" t="inlineStr">
@@ -14448,6 +14990,7 @@
       <c r="M526" s="7" t="n"/>
       <c r="N526" s="7" t="n"/>
       <c r="O526" s="7" t="n"/>
+      <c r="P526" s="7" t="n"/>
     </row>
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
@@ -14469,6 +15012,7 @@
       <c r="M527" s="4" t="n"/>
       <c r="N527" s="4" t="n"/>
       <c r="O527" s="4" t="n"/>
+      <c r="P527" s="4" t="n"/>
     </row>
     <row r="528">
       <c r="A528" s="3" t="inlineStr">
@@ -14490,6 +15034,7 @@
       <c r="M528" s="4" t="n"/>
       <c r="N528" s="4" t="n"/>
       <c r="O528" s="4" t="n"/>
+      <c r="P528" s="4" t="n"/>
     </row>
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
@@ -14515,6 +15060,7 @@
       <c r="M529" s="4" t="n"/>
       <c r="N529" s="4" t="n"/>
       <c r="O529" s="4" t="n"/>
+      <c r="P529" s="4" t="n"/>
     </row>
     <row r="530">
       <c r="A530" s="3" t="inlineStr">
@@ -14540,6 +15086,7 @@
       <c r="M530" s="4" t="n"/>
       <c r="N530" s="4" t="n"/>
       <c r="O530" s="4" t="n"/>
+      <c r="P530" s="4" t="n"/>
     </row>
     <row r="531">
       <c r="A531" s="3" t="inlineStr">
@@ -14565,6 +15112,7 @@
       <c r="M531" s="4" t="n"/>
       <c r="N531" s="4" t="n"/>
       <c r="O531" s="4" t="n"/>
+      <c r="P531" s="4" t="n"/>
     </row>
     <row r="532">
       <c r="A532" s="6" t="inlineStr">
@@ -14586,6 +15134,7 @@
       <c r="M532" s="7" t="n"/>
       <c r="N532" s="7" t="n"/>
       <c r="O532" s="7" t="n"/>
+      <c r="P532" s="7" t="n"/>
     </row>
     <row r="533">
       <c r="A533" s="6" t="inlineStr">
@@ -14607,6 +15156,7 @@
       <c r="M533" s="7" t="n"/>
       <c r="N533" s="7" t="n"/>
       <c r="O533" s="7" t="n"/>
+      <c r="P533" s="7" t="n"/>
     </row>
     <row r="534">
       <c r="A534" s="3" t="inlineStr">
@@ -14632,6 +15182,7 @@
       <c r="M534" s="4" t="n"/>
       <c r="N534" s="4" t="n"/>
       <c r="O534" s="4" t="n"/>
+      <c r="P534" s="4" t="n"/>
     </row>
     <row r="535">
       <c r="A535" s="3" t="inlineStr">
@@ -14657,6 +15208,7 @@
       <c r="M535" s="4" t="n"/>
       <c r="N535" s="4" t="n"/>
       <c r="O535" s="4" t="n"/>
+      <c r="P535" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9298,7 +9298,11 @@
       <c r="M338" s="4" t="n"/>
       <c r="N338" s="4" t="n"/>
       <c r="O338" s="4" t="n"/>
-      <c r="P338" s="4" t="n"/>
+      <c r="P338" s="5" t="inlineStr">
+        <is>
+          <t>Socials - Rookie Teachers</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="3" t="inlineStr">
@@ -9352,7 +9356,11 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="P339" s="4" t="n"/>
+      <c r="P339" s="5" t="inlineStr">
+        <is>
+          <t>Socials - Rookie Teachers</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="3" t="inlineStr">
@@ -9406,7 +9414,11 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="P340" s="4" t="n"/>
+      <c r="P340" s="5" t="inlineStr">
+        <is>
+          <t>Socials - Rookie Teachers</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="3" t="inlineStr">
@@ -9452,7 +9464,11 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="P341" s="4" t="n"/>
+      <c r="P341" s="5" t="inlineStr">
+        <is>
+          <t>Socials - Rookie Teachers</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="3" t="inlineStr">
@@ -9502,7 +9518,11 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="P342" s="4" t="n"/>
+      <c r="P342" s="5" t="inlineStr">
+        <is>
+          <t>Socials - Rookie Teachers</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="6" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P535"/>
+  <dimension ref="A1:P559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13393,11 +13393,7 @@
       <c r="G465" s="4" t="n"/>
       <c r="H465" s="4" t="n"/>
       <c r="I465" s="4" t="n"/>
-      <c r="J465" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J465" s="4" t="n"/>
       <c r="K465" s="4" t="n"/>
       <c r="L465" s="4" t="n"/>
       <c r="M465" s="4" t="n"/>
@@ -13419,11 +13415,7 @@
       <c r="G466" s="4" t="n"/>
       <c r="H466" s="4" t="n"/>
       <c r="I466" s="4" t="n"/>
-      <c r="J466" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J466" s="4" t="n"/>
       <c r="K466" s="4" t="n"/>
       <c r="L466" s="4" t="n"/>
       <c r="M466" s="4" t="n"/>
@@ -13445,11 +13437,7 @@
       <c r="G467" s="4" t="n"/>
       <c r="H467" s="4" t="n"/>
       <c r="I467" s="4" t="n"/>
-      <c r="J467" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J467" s="4" t="n"/>
       <c r="K467" s="4" t="n"/>
       <c r="L467" s="4" t="n"/>
       <c r="M467" s="4" t="n"/>
@@ -13471,11 +13459,7 @@
       <c r="G468" s="4" t="n"/>
       <c r="H468" s="4" t="n"/>
       <c r="I468" s="4" t="n"/>
-      <c r="J468" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J468" s="4" t="n"/>
       <c r="K468" s="4" t="n"/>
       <c r="L468" s="4" t="n"/>
       <c r="M468" s="4" t="n"/>
@@ -13541,11 +13525,7 @@
       <c r="G471" s="4" t="n"/>
       <c r="H471" s="4" t="n"/>
       <c r="I471" s="4" t="n"/>
-      <c r="J471" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J471" s="4" t="n"/>
       <c r="K471" s="4" t="n"/>
       <c r="L471" s="4" t="n"/>
       <c r="M471" s="4" t="n"/>
@@ -13567,11 +13547,7 @@
       <c r="G472" s="4" t="n"/>
       <c r="H472" s="4" t="n"/>
       <c r="I472" s="4" t="n"/>
-      <c r="J472" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J472" s="4" t="n"/>
       <c r="K472" s="4" t="n"/>
       <c r="L472" s="4" t="n"/>
       <c r="M472" s="4" t="n"/>
@@ -13593,11 +13569,7 @@
       <c r="G473" s="4" t="n"/>
       <c r="H473" s="4" t="n"/>
       <c r="I473" s="4" t="n"/>
-      <c r="J473" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J473" s="4" t="n"/>
       <c r="K473" s="4" t="n"/>
       <c r="L473" s="4" t="n"/>
       <c r="M473" s="4" t="n"/>
@@ -13619,11 +13591,7 @@
       <c r="G474" s="4" t="n"/>
       <c r="H474" s="4" t="n"/>
       <c r="I474" s="4" t="n"/>
-      <c r="J474" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J474" s="4" t="n"/>
       <c r="K474" s="4" t="n"/>
       <c r="L474" s="4" t="n"/>
       <c r="M474" s="4" t="n"/>
@@ -13645,11 +13613,7 @@
       <c r="G475" s="4" t="n"/>
       <c r="H475" s="4" t="n"/>
       <c r="I475" s="4" t="n"/>
-      <c r="J475" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J475" s="4" t="n"/>
       <c r="K475" s="4" t="n"/>
       <c r="L475" s="4" t="n"/>
       <c r="M475" s="4" t="n"/>
@@ -13719,11 +13683,7 @@
       </c>
       <c r="H478" s="4" t="n"/>
       <c r="I478" s="4" t="n"/>
-      <c r="J478" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J478" s="4" t="n"/>
       <c r="K478" s="4" t="n"/>
       <c r="L478" s="4" t="n"/>
       <c r="M478" s="11" t="inlineStr">
@@ -13757,11 +13717,7 @@
       </c>
       <c r="H479" s="4" t="n"/>
       <c r="I479" s="4" t="n"/>
-      <c r="J479" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J479" s="4" t="n"/>
       <c r="K479" s="4" t="n"/>
       <c r="L479" s="4" t="n"/>
       <c r="M479" s="11" t="inlineStr">
@@ -13795,11 +13751,7 @@
       </c>
       <c r="H480" s="4" t="n"/>
       <c r="I480" s="4" t="n"/>
-      <c r="J480" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J480" s="4" t="n"/>
       <c r="K480" s="4" t="n"/>
       <c r="L480" s="4" t="n"/>
       <c r="M480" s="11" t="inlineStr">
@@ -14127,11 +14079,7 @@
       <c r="G492" s="4" t="n"/>
       <c r="H492" s="4" t="n"/>
       <c r="I492" s="4" t="n"/>
-      <c r="J492" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J492" s="4" t="n"/>
       <c r="K492" s="4" t="n"/>
       <c r="L492" s="4" t="n"/>
       <c r="M492" s="4" t="n"/>
@@ -14157,11 +14105,7 @@
           <t>Delivery - Dewi Mockumentary</t>
         </is>
       </c>
-      <c r="J493" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J493" s="4" t="n"/>
       <c r="K493" s="4" t="n"/>
       <c r="L493" s="4" t="n"/>
       <c r="M493" s="4" t="n"/>
@@ -14188,11 +14132,7 @@
 Delivery - Y Grŵp Chat</t>
         </is>
       </c>
-      <c r="J494" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J494" s="4" t="n"/>
       <c r="K494" s="4" t="n"/>
       <c r="L494" s="4" t="n"/>
       <c r="M494" s="4" t="n"/>
@@ -14214,11 +14154,7 @@
       <c r="G495" s="4" t="n"/>
       <c r="H495" s="4" t="n"/>
       <c r="I495" s="4" t="n"/>
-      <c r="J495" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J495" s="4" t="n"/>
       <c r="K495" s="4" t="n"/>
       <c r="L495" s="4" t="n"/>
       <c r="M495" s="4" t="n"/>
@@ -14240,11 +14176,7 @@
       <c r="G496" s="4" t="n"/>
       <c r="H496" s="4" t="n"/>
       <c r="I496" s="4" t="n"/>
-      <c r="J496" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J496" s="4" t="n"/>
       <c r="K496" s="4" t="n"/>
       <c r="L496" s="4" t="n"/>
       <c r="M496" s="4" t="n"/>
@@ -14336,11 +14268,7 @@
       <c r="G500" s="4" t="n"/>
       <c r="H500" s="4" t="n"/>
       <c r="I500" s="4" t="n"/>
-      <c r="J500" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J500" s="4" t="n"/>
       <c r="K500" s="4" t="n"/>
       <c r="L500" s="4" t="n"/>
       <c r="M500" s="4" t="n"/>
@@ -14364,7 +14292,8 @@
       <c r="I501" s="4" t="n"/>
       <c r="J501" s="11" t="inlineStr">
         <is>
-          <t>Offline Edit - Sŵ Ni</t>
+          <t>Offline Edit - Sŵ Ni
+Offline Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K501" s="4" t="n"/>
@@ -14658,9 +14587,9 @@
       <c r="G513" s="4" t="n"/>
       <c r="H513" s="4" t="n"/>
       <c r="I513" s="4" t="n"/>
-      <c r="J513" s="8" t="inlineStr">
-        <is>
-          <t>Notes / Changes - Sŵ Ni</t>
+      <c r="J513" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K513" s="4" t="n"/>
@@ -14684,9 +14613,9 @@
       <c r="G514" s="4" t="n"/>
       <c r="H514" s="4" t="n"/>
       <c r="I514" s="4" t="n"/>
-      <c r="J514" s="8" t="inlineStr">
-        <is>
-          <t>Notes / Changes - Sŵ Ni</t>
+      <c r="J514" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K514" s="4" t="n"/>
@@ -14710,9 +14639,9 @@
       <c r="G515" s="4" t="n"/>
       <c r="H515" s="4" t="n"/>
       <c r="I515" s="4" t="n"/>
-      <c r="J515" s="8" t="inlineStr">
-        <is>
-          <t>Notes / Changes - Sŵ Ni</t>
+      <c r="J515" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K515" s="4" t="n"/>
@@ -14736,9 +14665,9 @@
       <c r="G516" s="4" t="n"/>
       <c r="H516" s="4" t="n"/>
       <c r="I516" s="4" t="n"/>
-      <c r="J516" s="8" t="inlineStr">
-        <is>
-          <t>Notes / Changes - Sŵ Ni</t>
+      <c r="J516" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K516" s="4" t="n"/>
@@ -14762,9 +14691,9 @@
       <c r="G517" s="4" t="n"/>
       <c r="H517" s="4" t="n"/>
       <c r="I517" s="4" t="n"/>
-      <c r="J517" s="8" t="inlineStr">
-        <is>
-          <t>Notes / Changes - Sŵ Ni</t>
+      <c r="J517" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K517" s="4" t="n"/>
@@ -14838,7 +14767,7 @@
       <c r="I520" s="4" t="n"/>
       <c r="J520" s="11" t="inlineStr">
         <is>
-          <t>Online Edit - Sŵ Ni</t>
+          <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K520" s="4" t="n"/>
@@ -14868,7 +14797,7 @@
       <c r="I521" s="4" t="n"/>
       <c r="J521" s="11" t="inlineStr">
         <is>
-          <t>Online Edit - Sŵ Ni</t>
+          <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K521" s="4" t="n"/>
@@ -14898,7 +14827,7 @@
       <c r="I522" s="4" t="n"/>
       <c r="J522" s="11" t="inlineStr">
         <is>
-          <t>Online Edit - Sŵ Ni</t>
+          <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K522" s="4" t="n"/>
@@ -14928,7 +14857,7 @@
       <c r="I523" s="4" t="n"/>
       <c r="J523" s="11" t="inlineStr">
         <is>
-          <t>Online Edit - Sŵ Ni</t>
+          <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K523" s="4" t="n"/>
@@ -14958,7 +14887,7 @@
       <c r="I524" s="4" t="n"/>
       <c r="J524" s="11" t="inlineStr">
         <is>
-          <t>Online Edit - Sŵ Ni</t>
+          <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K524" s="4" t="n"/>
@@ -15026,7 +14955,11 @@
       <c r="G527" s="4" t="n"/>
       <c r="H527" s="4" t="n"/>
       <c r="I527" s="4" t="n"/>
-      <c r="J527" s="4" t="n"/>
+      <c r="J527" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K527" s="4" t="n"/>
       <c r="L527" s="4" t="n"/>
       <c r="M527" s="4" t="n"/>
@@ -15048,7 +14981,11 @@
       <c r="G528" s="4" t="n"/>
       <c r="H528" s="4" t="n"/>
       <c r="I528" s="4" t="n"/>
-      <c r="J528" s="4" t="n"/>
+      <c r="J528" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K528" s="4" t="n"/>
       <c r="L528" s="4" t="n"/>
       <c r="M528" s="4" t="n"/>
@@ -15069,12 +15006,12 @@
       <c r="F529" s="4" t="n"/>
       <c r="G529" s="4" t="n"/>
       <c r="H529" s="4" t="n"/>
-      <c r="I529" s="9" t="inlineStr">
-        <is>
-          <t>Delivery - Sŵ Ni</t>
-        </is>
-      </c>
-      <c r="J529" s="4" t="n"/>
+      <c r="I529" s="4" t="n"/>
+      <c r="J529" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K529" s="4" t="n"/>
       <c r="L529" s="4" t="n"/>
       <c r="M529" s="4" t="n"/>
@@ -15095,12 +15032,12 @@
       <c r="F530" s="4" t="n"/>
       <c r="G530" s="4" t="n"/>
       <c r="H530" s="4" t="n"/>
-      <c r="I530" s="9" t="inlineStr">
-        <is>
-          <t>Delivery - Sŵ Ni</t>
-        </is>
-      </c>
-      <c r="J530" s="4" t="n"/>
+      <c r="I530" s="4" t="n"/>
+      <c r="J530" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K530" s="4" t="n"/>
       <c r="L530" s="4" t="n"/>
       <c r="M530" s="4" t="n"/>
@@ -15121,12 +15058,12 @@
       <c r="F531" s="4" t="n"/>
       <c r="G531" s="4" t="n"/>
       <c r="H531" s="4" t="n"/>
-      <c r="I531" s="9" t="inlineStr">
-        <is>
-          <t>Delivery - Sŵ Ni</t>
-        </is>
-      </c>
-      <c r="J531" s="4" t="n"/>
+      <c r="I531" s="4" t="n"/>
+      <c r="J531" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K531" s="4" t="n"/>
       <c r="L531" s="4" t="n"/>
       <c r="M531" s="4" t="n"/>
@@ -15191,12 +15128,12 @@
       <c r="F534" s="4" t="n"/>
       <c r="G534" s="4" t="n"/>
       <c r="H534" s="4" t="n"/>
-      <c r="I534" s="9" t="inlineStr">
-        <is>
-          <t>Delivery - Sŵ Ni</t>
-        </is>
-      </c>
-      <c r="J534" s="4" t="n"/>
+      <c r="I534" s="4" t="n"/>
+      <c r="J534" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K534" s="4" t="n"/>
       <c r="L534" s="4" t="n"/>
       <c r="M534" s="4" t="n"/>
@@ -15217,12 +15154,12 @@
       <c r="F535" s="4" t="n"/>
       <c r="G535" s="4" t="n"/>
       <c r="H535" s="4" t="n"/>
-      <c r="I535" s="9" t="inlineStr">
-        <is>
-          <t>Delivery - Sŵ Ni</t>
-        </is>
-      </c>
-      <c r="J535" s="4" t="n"/>
+      <c r="I535" s="4" t="n"/>
+      <c r="J535" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K535" s="4" t="n"/>
       <c r="L535" s="4" t="n"/>
       <c r="M535" s="4" t="n"/>
@@ -15230,6 +15167,606 @@
       <c r="O535" s="4" t="n"/>
       <c r="P535" s="4" t="n"/>
     </row>
+    <row r="536">
+      <c r="A536" s="3" t="inlineStr">
+        <is>
+          <t>Wed 07 Apr 2027</t>
+        </is>
+      </c>
+      <c r="B536" s="4" t="n"/>
+      <c r="C536" s="4" t="n"/>
+      <c r="D536" s="4" t="n"/>
+      <c r="E536" s="4" t="n"/>
+      <c r="F536" s="4" t="n"/>
+      <c r="G536" s="4" t="n"/>
+      <c r="H536" s="4" t="n"/>
+      <c r="I536" s="4" t="n"/>
+      <c r="J536" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K536" s="4" t="n"/>
+      <c r="L536" s="4" t="n"/>
+      <c r="M536" s="4" t="n"/>
+      <c r="N536" s="4" t="n"/>
+      <c r="O536" s="4" t="n"/>
+      <c r="P536" s="4" t="n"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="3" t="inlineStr">
+        <is>
+          <t>Thu 08 Apr 2027</t>
+        </is>
+      </c>
+      <c r="B537" s="4" t="n"/>
+      <c r="C537" s="4" t="n"/>
+      <c r="D537" s="4" t="n"/>
+      <c r="E537" s="4" t="n"/>
+      <c r="F537" s="4" t="n"/>
+      <c r="G537" s="4" t="n"/>
+      <c r="H537" s="4" t="n"/>
+      <c r="I537" s="4" t="n"/>
+      <c r="J537" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K537" s="4" t="n"/>
+      <c r="L537" s="4" t="n"/>
+      <c r="M537" s="4" t="n"/>
+      <c r="N537" s="4" t="n"/>
+      <c r="O537" s="4" t="n"/>
+      <c r="P537" s="4" t="n"/>
+    </row>
+    <row r="538">
+      <c r="A538" s="3" t="inlineStr">
+        <is>
+          <t>Fri 09 Apr 2027</t>
+        </is>
+      </c>
+      <c r="B538" s="4" t="n"/>
+      <c r="C538" s="4" t="n"/>
+      <c r="D538" s="4" t="n"/>
+      <c r="E538" s="4" t="n"/>
+      <c r="F538" s="4" t="n"/>
+      <c r="G538" s="4" t="n"/>
+      <c r="H538" s="4" t="n"/>
+      <c r="I538" s="4" t="n"/>
+      <c r="J538" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K538" s="4" t="n"/>
+      <c r="L538" s="4" t="n"/>
+      <c r="M538" s="4" t="n"/>
+      <c r="N538" s="4" t="n"/>
+      <c r="O538" s="4" t="n"/>
+      <c r="P538" s="4" t="n"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="6" t="inlineStr">
+        <is>
+          <t>Sat 10 Apr 2027</t>
+        </is>
+      </c>
+      <c r="B539" s="7" t="n"/>
+      <c r="C539" s="7" t="n"/>
+      <c r="D539" s="7" t="n"/>
+      <c r="E539" s="7" t="n"/>
+      <c r="F539" s="7" t="n"/>
+      <c r="G539" s="7" t="n"/>
+      <c r="H539" s="7" t="n"/>
+      <c r="I539" s="7" t="n"/>
+      <c r="J539" s="7" t="n"/>
+      <c r="K539" s="7" t="n"/>
+      <c r="L539" s="7" t="n"/>
+      <c r="M539" s="7" t="n"/>
+      <c r="N539" s="7" t="n"/>
+      <c r="O539" s="7" t="n"/>
+      <c r="P539" s="7" t="n"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="6" t="inlineStr">
+        <is>
+          <t>Sun 11 Apr 2027</t>
+        </is>
+      </c>
+      <c r="B540" s="7" t="n"/>
+      <c r="C540" s="7" t="n"/>
+      <c r="D540" s="7" t="n"/>
+      <c r="E540" s="7" t="n"/>
+      <c r="F540" s="7" t="n"/>
+      <c r="G540" s="7" t="n"/>
+      <c r="H540" s="7" t="n"/>
+      <c r="I540" s="7" t="n"/>
+      <c r="J540" s="7" t="n"/>
+      <c r="K540" s="7" t="n"/>
+      <c r="L540" s="7" t="n"/>
+      <c r="M540" s="7" t="n"/>
+      <c r="N540" s="7" t="n"/>
+      <c r="O540" s="7" t="n"/>
+      <c r="P540" s="7" t="n"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="3" t="inlineStr">
+        <is>
+          <t>Mon 12 Apr 2027</t>
+        </is>
+      </c>
+      <c r="B541" s="4" t="n"/>
+      <c r="C541" s="4" t="n"/>
+      <c r="D541" s="4" t="n"/>
+      <c r="E541" s="4" t="n"/>
+      <c r="F541" s="4" t="n"/>
+      <c r="G541" s="4" t="n"/>
+      <c r="H541" s="4" t="n"/>
+      <c r="I541" s="4" t="n"/>
+      <c r="J541" s="8" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K541" s="4" t="n"/>
+      <c r="L541" s="4" t="n"/>
+      <c r="M541" s="4" t="n"/>
+      <c r="N541" s="4" t="n"/>
+      <c r="O541" s="4" t="n"/>
+      <c r="P541" s="4" t="n"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="3" t="inlineStr">
+        <is>
+          <t>Tue 13 Apr 2027</t>
+        </is>
+      </c>
+      <c r="B542" s="4" t="n"/>
+      <c r="C542" s="4" t="n"/>
+      <c r="D542" s="4" t="n"/>
+      <c r="E542" s="4" t="n"/>
+      <c r="F542" s="4" t="n"/>
+      <c r="G542" s="4" t="n"/>
+      <c r="H542" s="4" t="n"/>
+      <c r="I542" s="4" t="n"/>
+      <c r="J542" s="8" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K542" s="4" t="n"/>
+      <c r="L542" s="4" t="n"/>
+      <c r="M542" s="4" t="n"/>
+      <c r="N542" s="4" t="n"/>
+      <c r="O542" s="4" t="n"/>
+      <c r="P542" s="4" t="n"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="3" t="inlineStr">
+        <is>
+          <t>Wed 14 Apr 2027</t>
+        </is>
+      </c>
+      <c r="B543" s="4" t="n"/>
+      <c r="C543" s="4" t="n"/>
+      <c r="D543" s="4" t="n"/>
+      <c r="E543" s="4" t="n"/>
+      <c r="F543" s="4" t="n"/>
+      <c r="G543" s="4" t="n"/>
+      <c r="H543" s="4" t="n"/>
+      <c r="I543" s="4" t="n"/>
+      <c r="J543" s="8" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K543" s="4" t="n"/>
+      <c r="L543" s="4" t="n"/>
+      <c r="M543" s="4" t="n"/>
+      <c r="N543" s="4" t="n"/>
+      <c r="O543" s="4" t="n"/>
+      <c r="P543" s="4" t="n"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="3" t="inlineStr">
+        <is>
+          <t>Thu 15 Apr 2027</t>
+        </is>
+      </c>
+      <c r="B544" s="4" t="n"/>
+      <c r="C544" s="4" t="n"/>
+      <c r="D544" s="4" t="n"/>
+      <c r="E544" s="4" t="n"/>
+      <c r="F544" s="4" t="n"/>
+      <c r="G544" s="4" t="n"/>
+      <c r="H544" s="4" t="n"/>
+      <c r="I544" s="4" t="n"/>
+      <c r="J544" s="8" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K544" s="4" t="n"/>
+      <c r="L544" s="4" t="n"/>
+      <c r="M544" s="4" t="n"/>
+      <c r="N544" s="4" t="n"/>
+      <c r="O544" s="4" t="n"/>
+      <c r="P544" s="4" t="n"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="3" t="inlineStr">
+        <is>
+          <t>Fri 16 Apr 2027</t>
+        </is>
+      </c>
+      <c r="B545" s="4" t="n"/>
+      <c r="C545" s="4" t="n"/>
+      <c r="D545" s="4" t="n"/>
+      <c r="E545" s="4" t="n"/>
+      <c r="F545" s="4" t="n"/>
+      <c r="G545" s="4" t="n"/>
+      <c r="H545" s="4" t="n"/>
+      <c r="I545" s="4" t="n"/>
+      <c r="J545" s="8" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K545" s="4" t="n"/>
+      <c r="L545" s="4" t="n"/>
+      <c r="M545" s="4" t="n"/>
+      <c r="N545" s="4" t="n"/>
+      <c r="O545" s="4" t="n"/>
+      <c r="P545" s="4" t="n"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="6" t="inlineStr">
+        <is>
+          <t>Sat 17 Apr 2027</t>
+        </is>
+      </c>
+      <c r="B546" s="7" t="n"/>
+      <c r="C546" s="7" t="n"/>
+      <c r="D546" s="7" t="n"/>
+      <c r="E546" s="7" t="n"/>
+      <c r="F546" s="7" t="n"/>
+      <c r="G546" s="7" t="n"/>
+      <c r="H546" s="7" t="n"/>
+      <c r="I546" s="7" t="n"/>
+      <c r="J546" s="7" t="n"/>
+      <c r="K546" s="7" t="n"/>
+      <c r="L546" s="7" t="n"/>
+      <c r="M546" s="7" t="n"/>
+      <c r="N546" s="7" t="n"/>
+      <c r="O546" s="7" t="n"/>
+      <c r="P546" s="7" t="n"/>
+    </row>
+    <row r="547">
+      <c r="A547" s="6" t="inlineStr">
+        <is>
+          <t>Sun 18 Apr 2027</t>
+        </is>
+      </c>
+      <c r="B547" s="7" t="n"/>
+      <c r="C547" s="7" t="n"/>
+      <c r="D547" s="7" t="n"/>
+      <c r="E547" s="7" t="n"/>
+      <c r="F547" s="7" t="n"/>
+      <c r="G547" s="7" t="n"/>
+      <c r="H547" s="7" t="n"/>
+      <c r="I547" s="7" t="n"/>
+      <c r="J547" s="7" t="n"/>
+      <c r="K547" s="7" t="n"/>
+      <c r="L547" s="7" t="n"/>
+      <c r="M547" s="7" t="n"/>
+      <c r="N547" s="7" t="n"/>
+      <c r="O547" s="7" t="n"/>
+      <c r="P547" s="7" t="n"/>
+    </row>
+    <row r="548">
+      <c r="A548" s="3" t="inlineStr">
+        <is>
+          <t>Mon 19 Apr 2027</t>
+        </is>
+      </c>
+      <c r="B548" s="4" t="n"/>
+      <c r="C548" s="4" t="n"/>
+      <c r="D548" s="4" t="n"/>
+      <c r="E548" s="4" t="n"/>
+      <c r="F548" s="4" t="n"/>
+      <c r="G548" s="4" t="n"/>
+      <c r="H548" s="4" t="n"/>
+      <c r="I548" s="4" t="n"/>
+      <c r="J548" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K548" s="4" t="n"/>
+      <c r="L548" s="4" t="n"/>
+      <c r="M548" s="4" t="n"/>
+      <c r="N548" s="4" t="n"/>
+      <c r="O548" s="4" t="n"/>
+      <c r="P548" s="4" t="n"/>
+    </row>
+    <row r="549">
+      <c r="A549" s="3" t="inlineStr">
+        <is>
+          <t>Tue 20 Apr 2027</t>
+        </is>
+      </c>
+      <c r="B549" s="4" t="n"/>
+      <c r="C549" s="4" t="n"/>
+      <c r="D549" s="4" t="n"/>
+      <c r="E549" s="4" t="n"/>
+      <c r="F549" s="4" t="n"/>
+      <c r="G549" s="4" t="n"/>
+      <c r="H549" s="4" t="n"/>
+      <c r="I549" s="4" t="n"/>
+      <c r="J549" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K549" s="4" t="n"/>
+      <c r="L549" s="4" t="n"/>
+      <c r="M549" s="4" t="n"/>
+      <c r="N549" s="4" t="n"/>
+      <c r="O549" s="4" t="n"/>
+      <c r="P549" s="4" t="n"/>
+    </row>
+    <row r="550">
+      <c r="A550" s="3" t="inlineStr">
+        <is>
+          <t>Wed 21 Apr 2027</t>
+        </is>
+      </c>
+      <c r="B550" s="4" t="n"/>
+      <c r="C550" s="4" t="n"/>
+      <c r="D550" s="4" t="n"/>
+      <c r="E550" s="4" t="n"/>
+      <c r="F550" s="4" t="n"/>
+      <c r="G550" s="4" t="n"/>
+      <c r="H550" s="4" t="n"/>
+      <c r="I550" s="4" t="n"/>
+      <c r="J550" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K550" s="4" t="n"/>
+      <c r="L550" s="4" t="n"/>
+      <c r="M550" s="4" t="n"/>
+      <c r="N550" s="4" t="n"/>
+      <c r="O550" s="4" t="n"/>
+      <c r="P550" s="4" t="n"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="3" t="inlineStr">
+        <is>
+          <t>Thu 22 Apr 2027</t>
+        </is>
+      </c>
+      <c r="B551" s="4" t="n"/>
+      <c r="C551" s="4" t="n"/>
+      <c r="D551" s="4" t="n"/>
+      <c r="E551" s="4" t="n"/>
+      <c r="F551" s="4" t="n"/>
+      <c r="G551" s="4" t="n"/>
+      <c r="H551" s="4" t="n"/>
+      <c r="I551" s="4" t="n"/>
+      <c r="J551" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K551" s="4" t="n"/>
+      <c r="L551" s="4" t="n"/>
+      <c r="M551" s="4" t="n"/>
+      <c r="N551" s="4" t="n"/>
+      <c r="O551" s="4" t="n"/>
+      <c r="P551" s="4" t="n"/>
+    </row>
+    <row r="552">
+      <c r="A552" s="3" t="inlineStr">
+        <is>
+          <t>Fri 23 Apr 2027</t>
+        </is>
+      </c>
+      <c r="B552" s="4" t="n"/>
+      <c r="C552" s="4" t="n"/>
+      <c r="D552" s="4" t="n"/>
+      <c r="E552" s="4" t="n"/>
+      <c r="F552" s="4" t="n"/>
+      <c r="G552" s="4" t="n"/>
+      <c r="H552" s="4" t="n"/>
+      <c r="I552" s="4" t="n"/>
+      <c r="J552" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K552" s="4" t="n"/>
+      <c r="L552" s="4" t="n"/>
+      <c r="M552" s="4" t="n"/>
+      <c r="N552" s="4" t="n"/>
+      <c r="O552" s="4" t="n"/>
+      <c r="P552" s="4" t="n"/>
+    </row>
+    <row r="553">
+      <c r="A553" s="6" t="inlineStr">
+        <is>
+          <t>Sat 24 Apr 2027</t>
+        </is>
+      </c>
+      <c r="B553" s="7" t="n"/>
+      <c r="C553" s="7" t="n"/>
+      <c r="D553" s="7" t="n"/>
+      <c r="E553" s="7" t="n"/>
+      <c r="F553" s="7" t="n"/>
+      <c r="G553" s="7" t="n"/>
+      <c r="H553" s="7" t="n"/>
+      <c r="I553" s="7" t="n"/>
+      <c r="J553" s="7" t="n"/>
+      <c r="K553" s="7" t="n"/>
+      <c r="L553" s="7" t="n"/>
+      <c r="M553" s="7" t="n"/>
+      <c r="N553" s="7" t="n"/>
+      <c r="O553" s="7" t="n"/>
+      <c r="P553" s="7" t="n"/>
+    </row>
+    <row r="554">
+      <c r="A554" s="6" t="inlineStr">
+        <is>
+          <t>Sun 25 Apr 2027</t>
+        </is>
+      </c>
+      <c r="B554" s="7" t="n"/>
+      <c r="C554" s="7" t="n"/>
+      <c r="D554" s="7" t="n"/>
+      <c r="E554" s="7" t="n"/>
+      <c r="F554" s="7" t="n"/>
+      <c r="G554" s="7" t="n"/>
+      <c r="H554" s="7" t="n"/>
+      <c r="I554" s="7" t="n"/>
+      <c r="J554" s="7" t="n"/>
+      <c r="K554" s="7" t="n"/>
+      <c r="L554" s="7" t="n"/>
+      <c r="M554" s="7" t="n"/>
+      <c r="N554" s="7" t="n"/>
+      <c r="O554" s="7" t="n"/>
+      <c r="P554" s="7" t="n"/>
+    </row>
+    <row r="555">
+      <c r="A555" s="3" t="inlineStr">
+        <is>
+          <t>Mon 26 Apr 2027</t>
+        </is>
+      </c>
+      <c r="B555" s="4" t="n"/>
+      <c r="C555" s="4" t="n"/>
+      <c r="D555" s="4" t="n"/>
+      <c r="E555" s="4" t="n"/>
+      <c r="F555" s="4" t="n"/>
+      <c r="G555" s="4" t="n"/>
+      <c r="H555" s="4" t="n"/>
+      <c r="I555" s="9" t="inlineStr">
+        <is>
+          <t>Delivery - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="J555" s="4" t="n"/>
+      <c r="K555" s="4" t="n"/>
+      <c r="L555" s="4" t="n"/>
+      <c r="M555" s="4" t="n"/>
+      <c r="N555" s="4" t="n"/>
+      <c r="O555" s="4" t="n"/>
+      <c r="P555" s="4" t="n"/>
+    </row>
+    <row r="556">
+      <c r="A556" s="3" t="inlineStr">
+        <is>
+          <t>Tue 27 Apr 2027</t>
+        </is>
+      </c>
+      <c r="B556" s="4" t="n"/>
+      <c r="C556" s="4" t="n"/>
+      <c r="D556" s="4" t="n"/>
+      <c r="E556" s="4" t="n"/>
+      <c r="F556" s="4" t="n"/>
+      <c r="G556" s="4" t="n"/>
+      <c r="H556" s="4" t="n"/>
+      <c r="I556" s="9" t="inlineStr">
+        <is>
+          <t>Delivery - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="J556" s="4" t="n"/>
+      <c r="K556" s="4" t="n"/>
+      <c r="L556" s="4" t="n"/>
+      <c r="M556" s="4" t="n"/>
+      <c r="N556" s="4" t="n"/>
+      <c r="O556" s="4" t="n"/>
+      <c r="P556" s="4" t="n"/>
+    </row>
+    <row r="557">
+      <c r="A557" s="3" t="inlineStr">
+        <is>
+          <t>Wed 28 Apr 2027</t>
+        </is>
+      </c>
+      <c r="B557" s="4" t="n"/>
+      <c r="C557" s="4" t="n"/>
+      <c r="D557" s="4" t="n"/>
+      <c r="E557" s="4" t="n"/>
+      <c r="F557" s="4" t="n"/>
+      <c r="G557" s="4" t="n"/>
+      <c r="H557" s="4" t="n"/>
+      <c r="I557" s="9" t="inlineStr">
+        <is>
+          <t>Delivery - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="J557" s="4" t="n"/>
+      <c r="K557" s="4" t="n"/>
+      <c r="L557" s="4" t="n"/>
+      <c r="M557" s="4" t="n"/>
+      <c r="N557" s="4" t="n"/>
+      <c r="O557" s="4" t="n"/>
+      <c r="P557" s="4" t="n"/>
+    </row>
+    <row r="558">
+      <c r="A558" s="3" t="inlineStr">
+        <is>
+          <t>Thu 29 Apr 2027</t>
+        </is>
+      </c>
+      <c r="B558" s="4" t="n"/>
+      <c r="C558" s="4" t="n"/>
+      <c r="D558" s="4" t="n"/>
+      <c r="E558" s="4" t="n"/>
+      <c r="F558" s="4" t="n"/>
+      <c r="G558" s="4" t="n"/>
+      <c r="H558" s="4" t="n"/>
+      <c r="I558" s="9" t="inlineStr">
+        <is>
+          <t>Delivery - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="J558" s="4" t="n"/>
+      <c r="K558" s="4" t="n"/>
+      <c r="L558" s="4" t="n"/>
+      <c r="M558" s="4" t="n"/>
+      <c r="N558" s="4" t="n"/>
+      <c r="O558" s="4" t="n"/>
+      <c r="P558" s="4" t="n"/>
+    </row>
+    <row r="559">
+      <c r="A559" s="3" t="inlineStr">
+        <is>
+          <t>Fri 30 Apr 2027</t>
+        </is>
+      </c>
+      <c r="B559" s="4" t="n"/>
+      <c r="C559" s="4" t="n"/>
+      <c r="D559" s="4" t="n"/>
+      <c r="E559" s="4" t="n"/>
+      <c r="F559" s="4" t="n"/>
+      <c r="G559" s="4" t="n"/>
+      <c r="H559" s="4" t="n"/>
+      <c r="I559" s="9" t="inlineStr">
+        <is>
+          <t>Delivery - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="J559" s="4" t="n"/>
+      <c r="K559" s="4" t="n"/>
+      <c r="L559" s="4" t="n"/>
+      <c r="M559" s="4" t="n"/>
+      <c r="N559" s="4" t="n"/>
+      <c r="O559" s="4" t="n"/>
+      <c r="P559" s="4" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9285,7 +9285,8 @@
       <c r="H338" s="4" t="n"/>
       <c r="I338" s="5" t="inlineStr">
         <is>
-          <t>Dub - Rookie Teachers</t>
+          <t>Ingest - Black History 2026
+Dub - Rookie Teachers</t>
         </is>
       </c>
       <c r="J338" s="5" t="inlineStr">
@@ -9433,11 +9434,7 @@
           <t>Prep Sw Ni</t>
         </is>
       </c>
-      <c r="E341" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="E341" s="4" t="n"/>
       <c r="F341" s="4" t="n"/>
       <c r="G341" s="4" t="n"/>
       <c r="H341" s="4" t="n"/>
@@ -9581,11 +9578,7 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E345" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="E345" s="4" t="n"/>
       <c r="F345" s="4" t="n"/>
       <c r="G345" s="5" t="inlineStr">
         <is>
@@ -9631,11 +9624,7 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E346" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="E346" s="4" t="n"/>
       <c r="F346" s="4" t="n"/>
       <c r="G346" s="5" t="inlineStr">
         <is>
@@ -9953,26 +9942,18 @@
           <t>Wed 07 Oct 2026</t>
         </is>
       </c>
-      <c r="B354" s="5" t="inlineStr">
-        <is>
-          <t>Film - BBC Music Show</t>
-        </is>
-      </c>
+      <c r="B354" s="4" t="n"/>
       <c r="C354" s="4" t="n"/>
       <c r="D354" s="4" t="n"/>
       <c r="E354" s="5" t="inlineStr">
         <is>
-          <t>Film - BBC Music Show</t>
+          <t>Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="F354" s="4" t="n"/>
       <c r="G354" s="4" t="n"/>
       <c r="H354" s="4" t="n"/>
-      <c r="I354" s="5" t="inlineStr">
-        <is>
-          <t>Film - BBC Music Show</t>
-        </is>
-      </c>
+      <c r="I354" s="4" t="n"/>
       <c r="J354" s="5" t="inlineStr">
         <is>
           <t>Edit - Mabli a Ceff Ceff</t>
@@ -9980,23 +9961,14 @@
       </c>
       <c r="K354" s="4" t="n"/>
       <c r="L354" s="4" t="n"/>
-      <c r="M354" s="5" t="inlineStr">
-        <is>
-          <t>Film - BBC Music Show</t>
-        </is>
-      </c>
-      <c r="N354" s="5" t="inlineStr">
-        <is>
-          <t>Film - BBC Music Show
-A/L - Annual Leave</t>
+      <c r="M354" s="4" t="n"/>
+      <c r="N354" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="O354" s="4" t="n"/>
-      <c r="P354" s="5" t="inlineStr">
-        <is>
-          <t>Film - BBC Music Show</t>
-        </is>
-      </c>
+      <c r="P354" s="4" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="3" t="inlineStr">
@@ -10004,45 +9976,25 @@
           <t>Thu 08 Oct 2026</t>
         </is>
       </c>
-      <c r="B355" s="5" t="inlineStr">
-        <is>
-          <t>Film - BBC Music Show</t>
-        </is>
-      </c>
+      <c r="B355" s="4" t="n"/>
       <c r="C355" s="4" t="n"/>
       <c r="D355" s="4" t="n"/>
       <c r="E355" s="5" t="inlineStr">
         <is>
-          <t>Film - BBC Music Show</t>
+          <t>Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="F355" s="4" t="n"/>
       <c r="G355" s="4" t="n"/>
       <c r="H355" s="4" t="n"/>
-      <c r="I355" s="5" t="inlineStr">
-        <is>
-          <t>Film - BBC Music Show</t>
-        </is>
-      </c>
+      <c r="I355" s="4" t="n"/>
       <c r="J355" s="4" t="n"/>
       <c r="K355" s="4" t="n"/>
       <c r="L355" s="4" t="n"/>
-      <c r="M355" s="5" t="inlineStr">
-        <is>
-          <t>Film - BBC Music Show</t>
-        </is>
-      </c>
-      <c r="N355" s="5" t="inlineStr">
-        <is>
-          <t>Film - BBC Music Show</t>
-        </is>
-      </c>
+      <c r="M355" s="4" t="n"/>
+      <c r="N355" s="4" t="n"/>
       <c r="O355" s="4" t="n"/>
-      <c r="P355" s="5" t="inlineStr">
-        <is>
-          <t>Film - BBC Music Show</t>
-        </is>
-      </c>
+      <c r="P355" s="4" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="3" t="inlineStr">
@@ -10053,7 +10005,11 @@
       <c r="B356" s="4" t="n"/>
       <c r="C356" s="4" t="n"/>
       <c r="D356" s="4" t="n"/>
-      <c r="E356" s="4" t="n"/>
+      <c r="E356" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F356" s="4" t="n"/>
       <c r="G356" s="4" t="n"/>
       <c r="H356" s="4" t="n"/>
@@ -10192,7 +10148,11 @@
       <c r="G359" s="4" t="n"/>
       <c r="H359" s="4" t="n"/>
       <c r="I359" s="4" t="n"/>
-      <c r="J359" s="4" t="n"/>
+      <c r="J359" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K359" s="4" t="n"/>
       <c r="L359" s="4" t="n"/>
       <c r="M359" s="4" t="n"/>
@@ -10226,7 +10186,11 @@
       <c r="G360" s="4" t="n"/>
       <c r="H360" s="4" t="n"/>
       <c r="I360" s="4" t="n"/>
-      <c r="J360" s="4" t="n"/>
+      <c r="J360" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K360" s="4" t="n"/>
       <c r="L360" s="4" t="n"/>
       <c r="M360" s="4" t="n"/>
@@ -10260,7 +10224,11 @@
       <c r="G361" s="4" t="n"/>
       <c r="H361" s="4" t="n"/>
       <c r="I361" s="4" t="n"/>
-      <c r="J361" s="4" t="n"/>
+      <c r="J361" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K361" s="4" t="n"/>
       <c r="L361" s="4" t="n"/>
       <c r="M361" s="4" t="n"/>
@@ -10294,7 +10262,11 @@
       <c r="G362" s="4" t="n"/>
       <c r="H362" s="4" t="n"/>
       <c r="I362" s="4" t="n"/>
-      <c r="J362" s="4" t="n"/>
+      <c r="J362" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K362" s="4" t="n"/>
       <c r="L362" s="4" t="n"/>
       <c r="M362" s="5" t="inlineStr">
@@ -10328,7 +10300,11 @@
       <c r="G363" s="4" t="n"/>
       <c r="H363" s="4" t="n"/>
       <c r="I363" s="4" t="n"/>
-      <c r="J363" s="4" t="n"/>
+      <c r="J363" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K363" s="4" t="n"/>
       <c r="L363" s="4" t="n"/>
       <c r="M363" s="5" t="inlineStr">
@@ -10414,7 +10390,11 @@
           <t>Delivery - Chepstow</t>
         </is>
       </c>
-      <c r="J366" s="4" t="n"/>
+      <c r="J366" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K366" s="4" t="n"/>
       <c r="L366" s="4" t="n"/>
       <c r="M366" s="4" t="n"/>
@@ -10436,7 +10416,11 @@
       <c r="G367" s="4" t="n"/>
       <c r="H367" s="4" t="n"/>
       <c r="I367" s="4" t="n"/>
-      <c r="J367" s="4" t="n"/>
+      <c r="J367" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K367" s="4" t="n"/>
       <c r="L367" s="4" t="n"/>
       <c r="M367" s="4" t="n"/>
@@ -10458,7 +10442,11 @@
       <c r="G368" s="4" t="n"/>
       <c r="H368" s="4" t="n"/>
       <c r="I368" s="4" t="n"/>
-      <c r="J368" s="4" t="n"/>
+      <c r="J368" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K368" s="4" t="n"/>
       <c r="L368" s="4" t="n"/>
       <c r="M368" s="4" t="n"/>
@@ -10480,7 +10468,11 @@
       <c r="G369" s="4" t="n"/>
       <c r="H369" s="4" t="n"/>
       <c r="I369" s="4" t="n"/>
-      <c r="J369" s="4" t="n"/>
+      <c r="J369" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K369" s="4" t="n"/>
       <c r="L369" s="4" t="n"/>
       <c r="M369" s="4" t="n"/>
@@ -10502,7 +10494,11 @@
       <c r="G370" s="4" t="n"/>
       <c r="H370" s="4" t="n"/>
       <c r="I370" s="4" t="n"/>
-      <c r="J370" s="4" t="n"/>
+      <c r="J370" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K370" s="4" t="n"/>
       <c r="L370" s="4" t="n"/>
       <c r="M370" s="4" t="n"/>
@@ -10572,7 +10568,11 @@
       <c r="G373" s="4" t="n"/>
       <c r="H373" s="4" t="n"/>
       <c r="I373" s="4" t="n"/>
-      <c r="J373" s="4" t="n"/>
+      <c r="J373" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K373" s="4" t="n"/>
       <c r="L373" s="4" t="n"/>
       <c r="M373" s="4" t="n"/>
@@ -10766,9 +10766,9 @@
       <c r="G380" s="4" t="n"/>
       <c r="H380" s="4" t="n"/>
       <c r="I380" s="4" t="n"/>
-      <c r="J380" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
+      <c r="J380" s="8" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
       <c r="K380" s="4" t="n"/>
@@ -10796,9 +10796,9 @@
       <c r="G381" s="4" t="n"/>
       <c r="H381" s="4" t="n"/>
       <c r="I381" s="4" t="n"/>
-      <c r="J381" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
+      <c r="J381" s="8" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
       <c r="K381" s="4" t="n"/>
@@ -10826,9 +10826,9 @@
       <c r="G382" s="4" t="n"/>
       <c r="H382" s="4" t="n"/>
       <c r="I382" s="4" t="n"/>
-      <c r="J382" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
+      <c r="J382" s="8" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
       <c r="K382" s="5" t="inlineStr">
@@ -10860,9 +10860,9 @@
       <c r="G383" s="4" t="n"/>
       <c r="H383" s="4" t="n"/>
       <c r="I383" s="4" t="n"/>
-      <c r="J383" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
+      <c r="J383" s="8" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
       <c r="K383" s="5" t="inlineStr">
@@ -10894,9 +10894,9 @@
       <c r="G384" s="4" t="n"/>
       <c r="H384" s="4" t="n"/>
       <c r="I384" s="4" t="n"/>
-      <c r="J384" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
+      <c r="J384" s="8" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
       <c r="K384" s="4" t="n"/>
@@ -11846,11 +11846,7 @@
       <c r="G408" s="4" t="n"/>
       <c r="H408" s="4" t="n"/>
       <c r="I408" s="4" t="n"/>
-      <c r="J408" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J408" s="4" t="n"/>
       <c r="K408" s="4" t="n"/>
       <c r="L408" s="4" t="n"/>
       <c r="M408" s="5" t="inlineStr">
@@ -11880,11 +11876,7 @@
       <c r="G409" s="4" t="n"/>
       <c r="H409" s="4" t="n"/>
       <c r="I409" s="4" t="n"/>
-      <c r="J409" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J409" s="4" t="n"/>
       <c r="K409" s="4" t="n"/>
       <c r="L409" s="4" t="n"/>
       <c r="M409" s="5" t="inlineStr">
@@ -11916,8 +11908,7 @@
       <c r="I410" s="4" t="n"/>
       <c r="J410" s="11" t="inlineStr">
         <is>
-          <t>Online Edit - External
-Offline Edit - Sŵ Ni</t>
+          <t>Online Edit - External</t>
         </is>
       </c>
       <c r="K410" s="4" t="n"/>
@@ -12137,11 +12128,7 @@
       <c r="G417" s="4" t="n"/>
       <c r="H417" s="4" t="n"/>
       <c r="I417" s="4" t="n"/>
-      <c r="J417" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J417" s="4" t="n"/>
       <c r="K417" s="4" t="n"/>
       <c r="L417" s="4" t="n"/>
       <c r="M417" s="5" t="inlineStr">
@@ -12171,11 +12158,7 @@
       <c r="G418" s="4" t="n"/>
       <c r="H418" s="4" t="n"/>
       <c r="I418" s="4" t="n"/>
-      <c r="J418" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J418" s="4" t="n"/>
       <c r="K418" s="4" t="n"/>
       <c r="L418" s="4" t="n"/>
       <c r="M418" s="5" t="inlineStr">
@@ -12205,11 +12188,7 @@
       <c r="G419" s="4" t="n"/>
       <c r="H419" s="4" t="n"/>
       <c r="I419" s="4" t="n"/>
-      <c r="J419" s="11" t="inlineStr">
-        <is>
-          <t>Offline Edit - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J419" s="4" t="n"/>
       <c r="K419" s="4" t="n"/>
       <c r="L419" s="4" t="n"/>
       <c r="M419" s="5" t="inlineStr">
@@ -12286,11 +12265,7 @@
       <c r="J422" s="4" t="n"/>
       <c r="K422" s="4" t="n"/>
       <c r="L422" s="4" t="n"/>
-      <c r="M422" s="5" t="inlineStr">
-        <is>
-          <t>Edit - LGBTQ+</t>
-        </is>
-      </c>
+      <c r="M422" s="4" t="n"/>
       <c r="N422" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
@@ -12324,11 +12299,7 @@
       <c r="J423" s="4" t="n"/>
       <c r="K423" s="4" t="n"/>
       <c r="L423" s="4" t="n"/>
-      <c r="M423" s="5" t="inlineStr">
-        <is>
-          <t>Edit - LGBTQ+</t>
-        </is>
-      </c>
+      <c r="M423" s="4" t="n"/>
       <c r="N423" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
@@ -12359,18 +12330,10 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="J424" s="5" t="inlineStr">
-        <is>
-          <t>Dub - LGBTQ+</t>
-        </is>
-      </c>
+      <c r="J424" s="4" t="n"/>
       <c r="K424" s="4" t="n"/>
       <c r="L424" s="4" t="n"/>
-      <c r="M424" s="5" t="inlineStr">
-        <is>
-          <t>Edit - LGBTQ+</t>
-        </is>
-      </c>
+      <c r="M424" s="4" t="n"/>
       <c r="N424" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
@@ -12408,11 +12371,7 @@
       </c>
       <c r="K425" s="4" t="n"/>
       <c r="L425" s="4" t="n"/>
-      <c r="M425" s="5" t="inlineStr">
-        <is>
-          <t>Edit - LGBTQ+</t>
-        </is>
-      </c>
+      <c r="M425" s="4" t="n"/>
       <c r="N425" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
@@ -12450,11 +12409,7 @@
       </c>
       <c r="K426" s="4" t="n"/>
       <c r="L426" s="4" t="n"/>
-      <c r="M426" s="5" t="inlineStr">
-        <is>
-          <t>Edit - LGBTQ+</t>
-        </is>
-      </c>
+      <c r="M426" s="4" t="n"/>
       <c r="N426" s="5" t="inlineStr">
         <is>
           <t>Edit - LGBTQ+</t>
@@ -12829,7 +12784,11 @@
       <c r="G443" s="4" t="n"/>
       <c r="H443" s="4" t="n"/>
       <c r="I443" s="4" t="n"/>
-      <c r="J443" s="4" t="n"/>
+      <c r="J443" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="K443" s="4" t="n"/>
       <c r="L443" s="4" t="n"/>
       <c r="M443" s="4" t="n"/>
@@ -12851,7 +12810,11 @@
       <c r="G444" s="4" t="n"/>
       <c r="H444" s="4" t="n"/>
       <c r="I444" s="4" t="n"/>
-      <c r="J444" s="4" t="n"/>
+      <c r="J444" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - LGBTQ+</t>
+        </is>
+      </c>
       <c r="K444" s="4" t="n"/>
       <c r="L444" s="4" t="n"/>
       <c r="M444" s="4" t="n"/>
@@ -14268,7 +14231,11 @@
       <c r="G500" s="4" t="n"/>
       <c r="H500" s="4" t="n"/>
       <c r="I500" s="4" t="n"/>
-      <c r="J500" s="4" t="n"/>
+      <c r="J500" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K500" s="4" t="n"/>
       <c r="L500" s="4" t="n"/>
       <c r="M500" s="4" t="n"/>
@@ -14292,8 +14259,7 @@
       <c r="I501" s="4" t="n"/>
       <c r="J501" s="11" t="inlineStr">
         <is>
-          <t>Offline Edit - Sŵ Ni
-Offline Edit - Sŵ Ni</t>
+          <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K501" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -10183,7 +10183,11 @@
           <t>OFF</t>
         </is>
       </c>
-      <c r="G360" s="4" t="n"/>
+      <c r="G360" s="5" t="inlineStr">
+        <is>
+          <t>Elin - Cwrs vertical drama</t>
+        </is>
+      </c>
       <c r="H360" s="4" t="n"/>
       <c r="I360" s="4" t="n"/>
       <c r="J360" s="11" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9463,7 +9463,7 @@
       </c>
       <c r="P341" s="5" t="inlineStr">
         <is>
-          <t>Socials - Rookie Teachers</t>
+          <t>Film - Black History 2026</t>
         </is>
       </c>
     </row>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -10010,7 +10010,11 @@
           <t>Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="F356" s="4" t="n"/>
+      <c r="F356" s="8" t="inlineStr">
+        <is>
+          <t>A/L</t>
+        </is>
+      </c>
       <c r="G356" s="4" t="n"/>
       <c r="H356" s="4" t="n"/>
       <c r="I356" s="4" t="n"/>
@@ -10052,11 +10056,7 @@
       <c r="C357" s="7" t="n"/>
       <c r="D357" s="7" t="n"/>
       <c r="E357" s="7" t="n"/>
-      <c r="F357" s="10" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
+      <c r="F357" s="7" t="n"/>
       <c r="G357" s="7" t="n"/>
       <c r="H357" s="7" t="n"/>
       <c r="I357" s="7" t="n"/>
@@ -10094,11 +10094,7 @@
       <c r="C358" s="7" t="n"/>
       <c r="D358" s="7" t="n"/>
       <c r="E358" s="7" t="n"/>
-      <c r="F358" s="10" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
+      <c r="F358" s="7" t="n"/>
       <c r="G358" s="7" t="n"/>
       <c r="H358" s="7" t="n"/>
       <c r="I358" s="7" t="n"/>
@@ -10140,9 +10136,9 @@
           <t>Edit - Chepstow</t>
         </is>
       </c>
-      <c r="F359" s="10" t="inlineStr">
-        <is>
-          <t>OFF</t>
+      <c r="F359" s="8" t="inlineStr">
+        <is>
+          <t>A/L</t>
         </is>
       </c>
       <c r="G359" s="4" t="n"/>
@@ -10178,9 +10174,9 @@
           <t>Edit - Chepstow</t>
         </is>
       </c>
-      <c r="F360" s="10" t="inlineStr">
-        <is>
-          <t>OFF</t>
+      <c r="F360" s="8" t="inlineStr">
+        <is>
+          <t>A/L</t>
         </is>
       </c>
       <c r="G360" s="5" t="inlineStr">
@@ -10220,9 +10216,9 @@
           <t>Edit - Chepstow</t>
         </is>
       </c>
-      <c r="F361" s="10" t="inlineStr">
-        <is>
-          <t>OFF</t>
+      <c r="F361" s="8" t="inlineStr">
+        <is>
+          <t>A/L</t>
         </is>
       </c>
       <c r="G361" s="4" t="n"/>
@@ -10258,9 +10254,9 @@
           <t>Edit - Chepstow</t>
         </is>
       </c>
-      <c r="F362" s="10" t="inlineStr">
-        <is>
-          <t>OFF</t>
+      <c r="F362" s="8" t="inlineStr">
+        <is>
+          <t>A/L</t>
         </is>
       </c>
       <c r="G362" s="4" t="n"/>
@@ -10296,9 +10292,9 @@
           <t>Edit - Chepstow</t>
         </is>
       </c>
-      <c r="F363" s="10" t="inlineStr">
-        <is>
-          <t>OFF</t>
+      <c r="F363" s="8" t="inlineStr">
+        <is>
+          <t>A/L</t>
         </is>
       </c>
       <c r="G363" s="4" t="n"/>
@@ -10330,11 +10326,7 @@
       <c r="C364" s="7" t="n"/>
       <c r="D364" s="7" t="n"/>
       <c r="E364" s="7" t="n"/>
-      <c r="F364" s="10" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
+      <c r="F364" s="7" t="n"/>
       <c r="G364" s="7" t="n"/>
       <c r="H364" s="7" t="n"/>
       <c r="I364" s="7" t="n"/>
@@ -10356,11 +10348,7 @@
       <c r="C365" s="7" t="n"/>
       <c r="D365" s="7" t="n"/>
       <c r="E365" s="7" t="n"/>
-      <c r="F365" s="10" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
+      <c r="F365" s="7" t="n"/>
       <c r="G365" s="7" t="n"/>
       <c r="H365" s="7" t="n"/>
       <c r="I365" s="7" t="n"/>
@@ -10382,9 +10370,9 @@
       <c r="C366" s="4" t="n"/>
       <c r="D366" s="4" t="n"/>
       <c r="E366" s="4" t="n"/>
-      <c r="F366" s="10" t="inlineStr">
-        <is>
-          <t>OFF</t>
+      <c r="F366" s="8" t="inlineStr">
+        <is>
+          <t>A/L</t>
         </is>
       </c>
       <c r="G366" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9463,7 +9463,8 @@
       </c>
       <c r="P341" s="5" t="inlineStr">
         <is>
-          <t>Film - Black History 2026</t>
+          <t>Film - Rookie Teachers
+Film - Black History 2026</t>
         </is>
       </c>
     </row>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8615,7 +8615,11 @@
           <t>Record VO &amp; Title Song</t>
         </is>
       </c>
-      <c r="K320" s="4" t="n"/>
+      <c r="K320" s="5" t="inlineStr">
+        <is>
+          <t>Pre-Production - Black History 2026</t>
+        </is>
+      </c>
       <c r="L320" s="4" t="n"/>
       <c r="M320" s="5" t="inlineStr">
         <is>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -10820,7 +10820,11 @@
         </is>
       </c>
       <c r="F382" s="4" t="n"/>
-      <c r="G382" s="4" t="n"/>
+      <c r="G382" s="5" t="inlineStr">
+        <is>
+          <t>TAC/S4C</t>
+        </is>
+      </c>
       <c r="H382" s="4" t="n"/>
       <c r="I382" s="4" t="n"/>
       <c r="J382" s="8" t="inlineStr">
@@ -10854,7 +10858,11 @@
         </is>
       </c>
       <c r="F383" s="4" t="n"/>
-      <c r="G383" s="4" t="n"/>
+      <c r="G383" s="5" t="inlineStr">
+        <is>
+          <t>TAC/S4C</t>
+        </is>
+      </c>
       <c r="H383" s="4" t="n"/>
       <c r="I383" s="4" t="n"/>
       <c r="J383" s="8" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9704,11 +9704,7 @@
           <t>Notes / Changes - Black History 2026</t>
         </is>
       </c>
-      <c r="N347" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="N347" s="4" t="n"/>
       <c r="O347" s="4" t="n"/>
       <c r="P347" s="5" t="inlineStr">
         <is>
@@ -9754,11 +9750,7 @@
       <c r="K348" s="4" t="n"/>
       <c r="L348" s="4" t="n"/>
       <c r="M348" s="4" t="n"/>
-      <c r="N348" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="N348" s="4" t="n"/>
       <c r="O348" s="4" t="n"/>
       <c r="P348" s="5" t="inlineStr">
         <is>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9885,7 +9885,7 @@
       </c>
       <c r="J352" s="5" t="inlineStr">
         <is>
-          <t>Edit - Mabli a Ceff Ceff</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="K352" s="4" t="n"/>
@@ -9919,7 +9919,7 @@
       <c r="I353" s="4" t="n"/>
       <c r="J353" s="5" t="inlineStr">
         <is>
-          <t>Edit - Mabli a Ceff Ceff</t>
+          <t>Sŵ Ni</t>
         </is>
       </c>
       <c r="K353" s="4" t="n"/>
@@ -9985,7 +9985,11 @@
       <c r="G355" s="4" t="n"/>
       <c r="H355" s="4" t="n"/>
       <c r="I355" s="4" t="n"/>
-      <c r="J355" s="4" t="n"/>
+      <c r="J355" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="K355" s="4" t="n"/>
       <c r="L355" s="4" t="n"/>
       <c r="M355" s="4" t="n"/>
@@ -10015,33 +10019,17 @@
       <c r="G356" s="4" t="n"/>
       <c r="H356" s="4" t="n"/>
       <c r="I356" s="4" t="n"/>
-      <c r="J356" s="4" t="n"/>
-      <c r="K356" s="5" t="inlineStr">
-        <is>
-          <t>Film - Chepstow</t>
-        </is>
-      </c>
+      <c r="J356" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
+      <c r="K356" s="4" t="n"/>
       <c r="L356" s="4" t="n"/>
-      <c r="M356" s="5" t="inlineStr">
-        <is>
-          <t>Film - Chepstow</t>
-        </is>
-      </c>
-      <c r="N356" s="5" t="inlineStr">
-        <is>
-          <t>Film - Chepstow</t>
-        </is>
-      </c>
-      <c r="O356" s="5" t="inlineStr">
-        <is>
-          <t>Film - Chepstow</t>
-        </is>
-      </c>
-      <c r="P356" s="5" t="inlineStr">
-        <is>
-          <t>Film - Chepstow</t>
-        </is>
-      </c>
+      <c r="M356" s="4" t="n"/>
+      <c r="N356" s="4" t="n"/>
+      <c r="O356" s="4" t="n"/>
+      <c r="P356" s="4" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="6" t="inlineStr">
@@ -10058,27 +10046,11 @@
       <c r="H357" s="7" t="n"/>
       <c r="I357" s="7" t="n"/>
       <c r="J357" s="7" t="n"/>
-      <c r="K357" s="5" t="inlineStr">
-        <is>
-          <t>Film - Chepstow</t>
-        </is>
-      </c>
+      <c r="K357" s="7" t="n"/>
       <c r="L357" s="7" t="n"/>
-      <c r="M357" s="5" t="inlineStr">
-        <is>
-          <t>Film - Chepstow</t>
-        </is>
-      </c>
-      <c r="N357" s="5" t="inlineStr">
-        <is>
-          <t>Film - Chepstow</t>
-        </is>
-      </c>
-      <c r="O357" s="5" t="inlineStr">
-        <is>
-          <t>Film - Chepstow</t>
-        </is>
-      </c>
+      <c r="M357" s="7" t="n"/>
+      <c r="N357" s="7" t="n"/>
+      <c r="O357" s="7" t="n"/>
       <c r="P357" s="7" t="n"/>
     </row>
     <row r="358">
@@ -10098,21 +10070,9 @@
       <c r="J358" s="7" t="n"/>
       <c r="K358" s="7" t="n"/>
       <c r="L358" s="7" t="n"/>
-      <c r="M358" s="5" t="inlineStr">
-        <is>
-          <t>Film - Chepstow</t>
-        </is>
-      </c>
-      <c r="N358" s="5" t="inlineStr">
-        <is>
-          <t>Film - Chepstow</t>
-        </is>
-      </c>
-      <c r="O358" s="5" t="inlineStr">
-        <is>
-          <t>Film - Chepstow</t>
-        </is>
-      </c>
+      <c r="M358" s="7" t="n"/>
+      <c r="N358" s="7" t="n"/>
+      <c r="O358" s="7" t="n"/>
       <c r="P358" s="7" t="n"/>
     </row>
     <row r="359">
@@ -10128,11 +10088,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E359" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Chepstow</t>
-        </is>
-      </c>
+      <c r="E359" s="4" t="n"/>
       <c r="F359" s="8" t="inlineStr">
         <is>
           <t>A/L</t>
@@ -10166,11 +10122,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E360" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Chepstow</t>
-        </is>
-      </c>
+      <c r="E360" s="4" t="n"/>
       <c r="F360" s="8" t="inlineStr">
         <is>
           <t>A/L</t>
@@ -10208,11 +10160,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E361" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Chepstow</t>
-        </is>
-      </c>
+      <c r="E361" s="4" t="n"/>
       <c r="F361" s="8" t="inlineStr">
         <is>
           <t>A/L</t>
@@ -10246,11 +10194,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E362" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Chepstow</t>
-        </is>
-      </c>
+      <c r="E362" s="4" t="n"/>
       <c r="F362" s="8" t="inlineStr">
         <is>
           <t>A/L</t>
@@ -10284,11 +10228,7 @@
       <c r="B363" s="4" t="n"/>
       <c r="C363" s="4" t="n"/>
       <c r="D363" s="4" t="n"/>
-      <c r="E363" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Chepstow</t>
-        </is>
-      </c>
+      <c r="E363" s="4" t="n"/>
       <c r="F363" s="8" t="inlineStr">
         <is>
           <t>A/L</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9704,7 +9704,11 @@
           <t>Notes / Changes - Black History 2026</t>
         </is>
       </c>
-      <c r="N347" s="4" t="n"/>
+      <c r="N347" s="10" t="inlineStr">
+        <is>
+          <t>TOIL</t>
+        </is>
+      </c>
       <c r="O347" s="4" t="n"/>
       <c r="P347" s="5" t="inlineStr">
         <is>
@@ -9750,7 +9754,11 @@
       <c r="K348" s="4" t="n"/>
       <c r="L348" s="4" t="n"/>
       <c r="M348" s="4" t="n"/>
-      <c r="N348" s="4" t="n"/>
+      <c r="N348" s="10" t="inlineStr">
+        <is>
+          <t>TOIL</t>
+        </is>
+      </c>
       <c r="O348" s="4" t="n"/>
       <c r="P348" s="5" t="inlineStr">
         <is>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9583,7 +9583,7 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E345" s="4" t="n"/>
+      <c r="E345" s="5" t="inlineStr"/>
       <c r="F345" s="4" t="n"/>
       <c r="G345" s="5" t="inlineStr">
         <is>
@@ -9675,11 +9675,7 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E347" s="5" t="inlineStr">
-        <is>
-          <t>Edit - HOYS</t>
-        </is>
-      </c>
+      <c r="E347" s="4" t="n"/>
       <c r="F347" s="4" t="n"/>
       <c r="G347" s="5" t="inlineStr">
         <is>
@@ -9729,11 +9725,7 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E348" s="5" t="inlineStr">
-        <is>
-          <t>Edit - HOYS</t>
-        </is>
-      </c>
+      <c r="E348" s="4" t="n"/>
       <c r="F348" s="4" t="n"/>
       <c r="G348" s="5" t="inlineStr">
         <is>
@@ -9779,11 +9771,7 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E349" s="5" t="inlineStr">
-        <is>
-          <t>Edit - HOYS</t>
-        </is>
-      </c>
+      <c r="E349" s="4" t="n"/>
       <c r="F349" s="4" t="n"/>
       <c r="G349" s="5" t="inlineStr">
         <is>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9583,7 +9583,11 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E345" s="5" t="inlineStr"/>
+      <c r="E345" s="10" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
       <c r="F345" s="4" t="n"/>
       <c r="G345" s="5" t="inlineStr">
         <is>
@@ -9629,7 +9633,11 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E346" s="4" t="n"/>
+      <c r="E346" s="10" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
       <c r="F346" s="4" t="n"/>
       <c r="G346" s="5" t="inlineStr">
         <is>
@@ -9675,7 +9683,11 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E347" s="4" t="n"/>
+      <c r="E347" s="10" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
       <c r="F347" s="4" t="n"/>
       <c r="G347" s="5" t="inlineStr">
         <is>
@@ -9725,7 +9737,11 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E348" s="4" t="n"/>
+      <c r="E348" s="10" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
       <c r="F348" s="4" t="n"/>
       <c r="G348" s="5" t="inlineStr">
         <is>
@@ -9771,7 +9787,11 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E349" s="4" t="n"/>
+      <c r="E349" s="10" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
       <c r="F349" s="4" t="n"/>
       <c r="G349" s="5" t="inlineStr">
         <is>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9913,7 +9913,11 @@
         </is>
       </c>
       <c r="O352" s="4" t="n"/>
-      <c r="P352" s="4" t="n"/>
+      <c r="P352" s="5" t="inlineStr">
+        <is>
+          <t>Film - WCPS Training - NEC Birmingham (1)</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="3" t="inlineStr">
@@ -9947,7 +9951,11 @@
         </is>
       </c>
       <c r="O353" s="4" t="n"/>
-      <c r="P353" s="4" t="n"/>
+      <c r="P353" s="5" t="inlineStr">
+        <is>
+          <t>Film - Tattersalls - MH Development</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="3" t="inlineStr">
@@ -10086,7 +10094,11 @@
       <c r="J358" s="7" t="n"/>
       <c r="K358" s="7" t="n"/>
       <c r="L358" s="7" t="n"/>
-      <c r="M358" s="7" t="n"/>
+      <c r="M358" s="5" t="inlineStr">
+        <is>
+          <t>Film - WCPS - Event - NEC Birmingham</t>
+        </is>
+      </c>
       <c r="N358" s="7" t="n"/>
       <c r="O358" s="7" t="n"/>
       <c r="P358" s="7" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -10342,11 +10342,7 @@
       </c>
       <c r="G366" s="4" t="n"/>
       <c r="H366" s="4" t="n"/>
-      <c r="I366" s="9" t="inlineStr">
-        <is>
-          <t>Delivery - Chepstow</t>
-        </is>
-      </c>
+      <c r="I366" s="4" t="n"/>
       <c r="J366" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9821,7 +9821,7 @@
       <c r="O349" s="4" t="n"/>
       <c r="P349" s="5" t="inlineStr">
         <is>
-          <t>Film - Sŵ Ni</t>
+          <t>Film - External</t>
         </is>
       </c>
     </row>
@@ -10053,7 +10053,11 @@
       <c r="M356" s="4" t="n"/>
       <c r="N356" s="4" t="n"/>
       <c r="O356" s="4" t="n"/>
-      <c r="P356" s="4" t="n"/>
+      <c r="P356" s="5" t="inlineStr">
+        <is>
+          <t>Film - External</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="6" t="inlineStr">
@@ -10238,14 +10242,14 @@
       </c>
       <c r="K362" s="4" t="n"/>
       <c r="L362" s="4" t="n"/>
-      <c r="M362" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Chepstow</t>
-        </is>
-      </c>
+      <c r="M362" s="4" t="n"/>
       <c r="N362" s="4" t="n"/>
       <c r="O362" s="4" t="n"/>
-      <c r="P362" s="4" t="n"/>
+      <c r="P362" s="10" t="inlineStr">
+        <is>
+          <t>TOIL - Rygbi - Digital - 17th</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="3" t="inlineStr">
@@ -10272,14 +10276,14 @@
       </c>
       <c r="K363" s="4" t="n"/>
       <c r="L363" s="4" t="n"/>
-      <c r="M363" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Chepstow</t>
-        </is>
-      </c>
+      <c r="M363" s="4" t="n"/>
       <c r="N363" s="4" t="n"/>
       <c r="O363" s="4" t="n"/>
-      <c r="P363" s="4" t="n"/>
+      <c r="P363" s="5" t="inlineStr">
+        <is>
+          <t>Film - External</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="6" t="inlineStr">
@@ -10301,7 +10305,11 @@
       <c r="M364" s="7" t="n"/>
       <c r="N364" s="7" t="n"/>
       <c r="O364" s="7" t="n"/>
-      <c r="P364" s="7" t="n"/>
+      <c r="P364" s="5" t="inlineStr">
+        <is>
+          <t>Film - External</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="6" t="inlineStr">
@@ -10531,7 +10539,11 @@
       <c r="M373" s="4" t="n"/>
       <c r="N373" s="4" t="n"/>
       <c r="O373" s="4" t="n"/>
-      <c r="P373" s="4" t="n"/>
+      <c r="P373" s="5" t="inlineStr">
+        <is>
+          <t>Film - External</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="3" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9848,7 +9848,11 @@
           <t>OFF</t>
         </is>
       </c>
-      <c r="O350" s="7" t="n"/>
+      <c r="O350" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
       <c r="P350" s="7" t="n"/>
     </row>
     <row r="351">
@@ -10078,7 +10082,11 @@
       <c r="L357" s="7" t="n"/>
       <c r="M357" s="7" t="n"/>
       <c r="N357" s="7" t="n"/>
-      <c r="O357" s="7" t="n"/>
+      <c r="O357" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
       <c r="P357" s="7" t="n"/>
     </row>
     <row r="358">
@@ -10278,7 +10286,11 @@
       <c r="L363" s="4" t="n"/>
       <c r="M363" s="4" t="n"/>
       <c r="N363" s="4" t="n"/>
-      <c r="O363" s="4" t="n"/>
+      <c r="O363" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
       <c r="P363" s="5" t="inlineStr">
         <is>
           <t>Film - External</t>
@@ -10633,7 +10645,11 @@
       <c r="M376" s="4" t="n"/>
       <c r="N376" s="4" t="n"/>
       <c r="O376" s="4" t="n"/>
-      <c r="P376" s="4" t="n"/>
+      <c r="P376" s="5" t="inlineStr">
+        <is>
+          <t>Film - External</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="3" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P559"/>
+  <dimension ref="A1:P567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9818,7 +9818,11 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="O349" s="4" t="n"/>
+      <c r="O349" s="10" t="inlineStr">
+        <is>
+          <t>TOIL</t>
+        </is>
+      </c>
       <c r="P349" s="5" t="inlineStr">
         <is>
           <t>Film - External</t>
@@ -10056,7 +10060,11 @@
       <c r="L356" s="4" t="n"/>
       <c r="M356" s="4" t="n"/>
       <c r="N356" s="4" t="n"/>
-      <c r="O356" s="4" t="n"/>
+      <c r="O356" s="10" t="inlineStr">
+        <is>
+          <t>TOIL</t>
+        </is>
+      </c>
       <c r="P356" s="5" t="inlineStr">
         <is>
           <t>Film - External</t>
@@ -11848,7 +11856,11 @@
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="O408" s="4" t="n"/>
+      <c r="O408" s="10" t="inlineStr">
+        <is>
+          <t>TOIL</t>
+        </is>
+      </c>
       <c r="P408" s="4" t="n"/>
     </row>
     <row r="409">
@@ -11878,7 +11890,11 @@
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="O409" s="4" t="n"/>
+      <c r="O409" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
       <c r="P409" s="4" t="n"/>
     </row>
     <row r="410">
@@ -11912,7 +11928,11 @@
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="O410" s="4" t="n"/>
+      <c r="O410" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
       <c r="P410" s="4" t="n"/>
     </row>
     <row r="411">
@@ -11950,7 +11970,11 @@
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="O411" s="4" t="n"/>
+      <c r="O411" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
       <c r="P411" s="4" t="n"/>
     </row>
     <row r="412">
@@ -11988,7 +12012,11 @@
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="O412" s="4" t="n"/>
+      <c r="O412" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
       <c r="P412" s="4" t="n"/>
     </row>
     <row r="413">
@@ -12010,7 +12038,11 @@
       <c r="L413" s="7" t="n"/>
       <c r="M413" s="7" t="n"/>
       <c r="N413" s="7" t="n"/>
-      <c r="O413" s="7" t="n"/>
+      <c r="O413" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
       <c r="P413" s="7" t="n"/>
     </row>
     <row r="414">
@@ -12032,7 +12064,11 @@
       <c r="L414" s="7" t="n"/>
       <c r="M414" s="7" t="n"/>
       <c r="N414" s="7" t="n"/>
-      <c r="O414" s="7" t="n"/>
+      <c r="O414" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
       <c r="P414" s="7" t="n"/>
     </row>
     <row r="415">
@@ -12066,7 +12102,11 @@
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="O415" s="4" t="n"/>
+      <c r="O415" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
       <c r="P415" s="4" t="n"/>
     </row>
     <row r="416">
@@ -12100,7 +12140,11 @@
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="O416" s="4" t="n"/>
+      <c r="O416" s="10" t="inlineStr">
+        <is>
+          <t>TOIL</t>
+        </is>
+      </c>
       <c r="P416" s="4" t="n"/>
     </row>
     <row r="417">
@@ -12130,7 +12174,11 @@
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="O417" s="4" t="n"/>
+      <c r="O417" s="10" t="inlineStr">
+        <is>
+          <t>TOIL</t>
+        </is>
+      </c>
       <c r="P417" s="4" t="n"/>
     </row>
     <row r="418">
@@ -12212,7 +12260,11 @@
       <c r="L420" s="7" t="n"/>
       <c r="M420" s="7" t="n"/>
       <c r="N420" s="7" t="n"/>
-      <c r="O420" s="7" t="n"/>
+      <c r="O420" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
       <c r="P420" s="7" t="n"/>
     </row>
     <row r="421">
@@ -12404,7 +12456,12 @@
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="O426" s="4" t="n"/>
+      <c r="O426" s="10" t="inlineStr">
+        <is>
+          <t>TOIL
+TOIL</t>
+        </is>
+      </c>
       <c r="P426" s="4" t="n"/>
     </row>
     <row r="427">
@@ -12426,7 +12483,11 @@
       <c r="L427" s="7" t="n"/>
       <c r="M427" s="7" t="n"/>
       <c r="N427" s="7" t="n"/>
-      <c r="O427" s="7" t="n"/>
+      <c r="O427" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
       <c r="P427" s="7" t="n"/>
     </row>
     <row r="428">
@@ -12580,7 +12641,11 @@
       <c r="L434" s="7" t="n"/>
       <c r="M434" s="7" t="n"/>
       <c r="N434" s="7" t="n"/>
-      <c r="O434" s="7" t="n"/>
+      <c r="O434" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
       <c r="P434" s="7" t="n"/>
     </row>
     <row r="435">
@@ -12904,7 +12969,11 @@
       <c r="L448" s="7" t="n"/>
       <c r="M448" s="7" t="n"/>
       <c r="N448" s="7" t="n"/>
-      <c r="O448" s="7" t="n"/>
+      <c r="O448" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
       <c r="P448" s="7" t="n"/>
     </row>
     <row r="449">
@@ -13056,7 +13125,11 @@
       <c r="L454" s="4" t="n"/>
       <c r="M454" s="4" t="n"/>
       <c r="N454" s="4" t="n"/>
-      <c r="O454" s="4" t="n"/>
+      <c r="O454" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
       <c r="P454" s="4" t="n"/>
     </row>
     <row r="455">
@@ -13284,7 +13357,11 @@
       <c r="L462" s="7" t="n"/>
       <c r="M462" s="7" t="n"/>
       <c r="N462" s="7" t="n"/>
-      <c r="O462" s="7" t="n"/>
+      <c r="O462" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
       <c r="P462" s="7" t="n"/>
     </row>
     <row r="463">
@@ -13438,7 +13515,11 @@
       <c r="L469" s="7" t="n"/>
       <c r="M469" s="7" t="n"/>
       <c r="N469" s="7" t="n"/>
-      <c r="O469" s="7" t="n"/>
+      <c r="O469" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
       <c r="P469" s="7" t="n"/>
     </row>
     <row r="470">
@@ -14155,7 +14236,11 @@
       <c r="L497" s="7" t="n"/>
       <c r="M497" s="7" t="n"/>
       <c r="N497" s="7" t="n"/>
-      <c r="O497" s="7" t="n"/>
+      <c r="O497" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
       <c r="P497" s="7" t="n"/>
     </row>
     <row r="498">
@@ -14871,7 +14956,11 @@
       <c r="L525" s="7" t="n"/>
       <c r="M525" s="7" t="n"/>
       <c r="N525" s="7" t="n"/>
-      <c r="O525" s="7" t="n"/>
+      <c r="O525" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
       <c r="P525" s="7" t="n"/>
     </row>
     <row r="526">
@@ -15371,7 +15460,11 @@
       <c r="L545" s="4" t="n"/>
       <c r="M545" s="4" t="n"/>
       <c r="N545" s="4" t="n"/>
-      <c r="O545" s="4" t="n"/>
+      <c r="O545" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
       <c r="P545" s="4" t="n"/>
     </row>
     <row r="546">
@@ -15722,6 +15815,186 @@
       <c r="O559" s="4" t="n"/>
       <c r="P559" s="4" t="n"/>
     </row>
+    <row r="560">
+      <c r="A560" s="6" t="inlineStr">
+        <is>
+          <t>Sat 01 May 2027</t>
+        </is>
+      </c>
+      <c r="B560" s="7" t="n"/>
+      <c r="C560" s="7" t="n"/>
+      <c r="D560" s="7" t="n"/>
+      <c r="E560" s="7" t="n"/>
+      <c r="F560" s="7" t="n"/>
+      <c r="G560" s="7" t="n"/>
+      <c r="H560" s="7" t="n"/>
+      <c r="I560" s="7" t="n"/>
+      <c r="J560" s="7" t="n"/>
+      <c r="K560" s="7" t="n"/>
+      <c r="L560" s="7" t="n"/>
+      <c r="M560" s="7" t="n"/>
+      <c r="N560" s="7" t="n"/>
+      <c r="O560" s="7" t="n"/>
+      <c r="P560" s="7" t="n"/>
+    </row>
+    <row r="561">
+      <c r="A561" s="6" t="inlineStr">
+        <is>
+          <t>Sun 02 May 2027</t>
+        </is>
+      </c>
+      <c r="B561" s="7" t="n"/>
+      <c r="C561" s="7" t="n"/>
+      <c r="D561" s="7" t="n"/>
+      <c r="E561" s="7" t="n"/>
+      <c r="F561" s="7" t="n"/>
+      <c r="G561" s="7" t="n"/>
+      <c r="H561" s="7" t="n"/>
+      <c r="I561" s="7" t="n"/>
+      <c r="J561" s="7" t="n"/>
+      <c r="K561" s="7" t="n"/>
+      <c r="L561" s="7" t="n"/>
+      <c r="M561" s="7" t="n"/>
+      <c r="N561" s="7" t="n"/>
+      <c r="O561" s="7" t="n"/>
+      <c r="P561" s="7" t="n"/>
+    </row>
+    <row r="562">
+      <c r="A562" s="3" t="inlineStr">
+        <is>
+          <t>Mon 03 May 2027</t>
+        </is>
+      </c>
+      <c r="B562" s="4" t="n"/>
+      <c r="C562" s="4" t="n"/>
+      <c r="D562" s="4" t="n"/>
+      <c r="E562" s="4" t="n"/>
+      <c r="F562" s="4" t="n"/>
+      <c r="G562" s="4" t="n"/>
+      <c r="H562" s="4" t="n"/>
+      <c r="I562" s="4" t="n"/>
+      <c r="J562" s="4" t="n"/>
+      <c r="K562" s="4" t="n"/>
+      <c r="L562" s="4" t="n"/>
+      <c r="M562" s="4" t="n"/>
+      <c r="N562" s="4" t="n"/>
+      <c r="O562" s="4" t="n"/>
+      <c r="P562" s="4" t="n"/>
+    </row>
+    <row r="563">
+      <c r="A563" s="3" t="inlineStr">
+        <is>
+          <t>Tue 04 May 2027</t>
+        </is>
+      </c>
+      <c r="B563" s="4" t="n"/>
+      <c r="C563" s="4" t="n"/>
+      <c r="D563" s="4" t="n"/>
+      <c r="E563" s="4" t="n"/>
+      <c r="F563" s="4" t="n"/>
+      <c r="G563" s="4" t="n"/>
+      <c r="H563" s="4" t="n"/>
+      <c r="I563" s="4" t="n"/>
+      <c r="J563" s="4" t="n"/>
+      <c r="K563" s="4" t="n"/>
+      <c r="L563" s="4" t="n"/>
+      <c r="M563" s="4" t="n"/>
+      <c r="N563" s="4" t="n"/>
+      <c r="O563" s="4" t="n"/>
+      <c r="P563" s="4" t="n"/>
+    </row>
+    <row r="564">
+      <c r="A564" s="3" t="inlineStr">
+        <is>
+          <t>Wed 05 May 2027</t>
+        </is>
+      </c>
+      <c r="B564" s="4" t="n"/>
+      <c r="C564" s="4" t="n"/>
+      <c r="D564" s="4" t="n"/>
+      <c r="E564" s="4" t="n"/>
+      <c r="F564" s="4" t="n"/>
+      <c r="G564" s="4" t="n"/>
+      <c r="H564" s="4" t="n"/>
+      <c r="I564" s="4" t="n"/>
+      <c r="J564" s="4" t="n"/>
+      <c r="K564" s="4" t="n"/>
+      <c r="L564" s="4" t="n"/>
+      <c r="M564" s="4" t="n"/>
+      <c r="N564" s="4" t="n"/>
+      <c r="O564" s="4" t="n"/>
+      <c r="P564" s="4" t="n"/>
+    </row>
+    <row r="565">
+      <c r="A565" s="3" t="inlineStr">
+        <is>
+          <t>Thu 06 May 2027</t>
+        </is>
+      </c>
+      <c r="B565" s="4" t="n"/>
+      <c r="C565" s="4" t="n"/>
+      <c r="D565" s="4" t="n"/>
+      <c r="E565" s="4" t="n"/>
+      <c r="F565" s="4" t="n"/>
+      <c r="G565" s="4" t="n"/>
+      <c r="H565" s="4" t="n"/>
+      <c r="I565" s="4" t="n"/>
+      <c r="J565" s="4" t="n"/>
+      <c r="K565" s="4" t="n"/>
+      <c r="L565" s="4" t="n"/>
+      <c r="M565" s="4" t="n"/>
+      <c r="N565" s="4" t="n"/>
+      <c r="O565" s="4" t="n"/>
+      <c r="P565" s="4" t="n"/>
+    </row>
+    <row r="566">
+      <c r="A566" s="3" t="inlineStr">
+        <is>
+          <t>Fri 07 May 2027</t>
+        </is>
+      </c>
+      <c r="B566" s="4" t="n"/>
+      <c r="C566" s="4" t="n"/>
+      <c r="D566" s="4" t="n"/>
+      <c r="E566" s="4" t="n"/>
+      <c r="F566" s="4" t="n"/>
+      <c r="G566" s="4" t="n"/>
+      <c r="H566" s="4" t="n"/>
+      <c r="I566" s="4" t="n"/>
+      <c r="J566" s="4" t="n"/>
+      <c r="K566" s="4" t="n"/>
+      <c r="L566" s="4" t="n"/>
+      <c r="M566" s="4" t="n"/>
+      <c r="N566" s="4" t="n"/>
+      <c r="O566" s="4" t="n"/>
+      <c r="P566" s="4" t="n"/>
+    </row>
+    <row r="567">
+      <c r="A567" s="6" t="inlineStr">
+        <is>
+          <t>Sat 08 May 2027</t>
+        </is>
+      </c>
+      <c r="B567" s="7" t="n"/>
+      <c r="C567" s="7" t="n"/>
+      <c r="D567" s="7" t="n"/>
+      <c r="E567" s="7" t="n"/>
+      <c r="F567" s="7" t="n"/>
+      <c r="G567" s="7" t="n"/>
+      <c r="H567" s="7" t="n"/>
+      <c r="I567" s="7" t="n"/>
+      <c r="J567" s="7" t="n"/>
+      <c r="K567" s="7" t="n"/>
+      <c r="L567" s="7" t="n"/>
+      <c r="M567" s="7" t="n"/>
+      <c r="N567" s="7" t="n"/>
+      <c r="O567" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="P567" s="7" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -12458,8 +12458,7 @@
       </c>
       <c r="O426" s="10" t="inlineStr">
         <is>
-          <t>TOIL
-TOIL</t>
+          <t>TOIL</t>
         </is>
       </c>
       <c r="P426" s="4" t="n"/>
@@ -12597,7 +12596,11 @@
       <c r="L432" s="4" t="n"/>
       <c r="M432" s="4" t="n"/>
       <c r="N432" s="4" t="n"/>
-      <c r="O432" s="4" t="n"/>
+      <c r="O432" s="10" t="inlineStr">
+        <is>
+          <t>TOIL</t>
+        </is>
+      </c>
       <c r="P432" s="4" t="n"/>
     </row>
     <row r="433">
@@ -12947,7 +12950,11 @@
       <c r="L447" s="4" t="n"/>
       <c r="M447" s="4" t="n"/>
       <c r="N447" s="4" t="n"/>
-      <c r="O447" s="4" t="n"/>
+      <c r="O447" s="10" t="inlineStr">
+        <is>
+          <t>TOIL</t>
+        </is>
+      </c>
       <c r="P447" s="4" t="n"/>
     </row>
     <row r="448">
@@ -13335,7 +13342,11 @@
       <c r="L461" s="4" t="n"/>
       <c r="M461" s="4" t="n"/>
       <c r="N461" s="4" t="n"/>
-      <c r="O461" s="4" t="n"/>
+      <c r="O461" s="10" t="inlineStr">
+        <is>
+          <t>TOIL</t>
+        </is>
+      </c>
       <c r="P461" s="4" t="n"/>
     </row>
     <row r="462">
@@ -13493,7 +13504,11 @@
       <c r="L468" s="4" t="n"/>
       <c r="M468" s="4" t="n"/>
       <c r="N468" s="4" t="n"/>
-      <c r="O468" s="4" t="n"/>
+      <c r="O468" s="10" t="inlineStr">
+        <is>
+          <t>TOIL</t>
+        </is>
+      </c>
       <c r="P468" s="4" t="n"/>
     </row>
     <row r="469">
@@ -14214,7 +14229,11 @@
       <c r="L496" s="4" t="n"/>
       <c r="M496" s="4" t="n"/>
       <c r="N496" s="4" t="n"/>
-      <c r="O496" s="4" t="n"/>
+      <c r="O496" s="10" t="inlineStr">
+        <is>
+          <t>TOIL</t>
+        </is>
+      </c>
       <c r="P496" s="4" t="n"/>
     </row>
     <row r="497">
@@ -14934,7 +14953,11 @@
       <c r="L524" s="4" t="n"/>
       <c r="M524" s="4" t="n"/>
       <c r="N524" s="4" t="n"/>
-      <c r="O524" s="4" t="n"/>
+      <c r="O524" s="10" t="inlineStr">
+        <is>
+          <t>TOIL</t>
+        </is>
+      </c>
       <c r="P524" s="4" t="n"/>
     </row>
     <row r="525">
@@ -15966,7 +15989,11 @@
       <c r="L566" s="4" t="n"/>
       <c r="M566" s="4" t="n"/>
       <c r="N566" s="4" t="n"/>
-      <c r="O566" s="4" t="n"/>
+      <c r="O566" s="10" t="inlineStr">
+        <is>
+          <t>TOIL</t>
+        </is>
+      </c>
       <c r="P566" s="4" t="n"/>
     </row>
     <row r="567">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9923,7 +9923,7 @@
       <c r="O352" s="4" t="n"/>
       <c r="P352" s="5" t="inlineStr">
         <is>
-          <t>Film - WCPS Training - NEC Birmingham (1)</t>
+          <t>Film - WCPS Training - NEC Birmingham</t>
         </is>
       </c>
     </row>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -11895,7 +11895,11 @@
           <t>External</t>
         </is>
       </c>
-      <c r="P409" s="4" t="n"/>
+      <c r="P409" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="3" t="inlineStr">
@@ -11933,7 +11937,11 @@
           <t>External</t>
         </is>
       </c>
-      <c r="P410" s="4" t="n"/>
+      <c r="P410" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="3" t="inlineStr">
@@ -11975,7 +11983,11 @@
           <t>External</t>
         </is>
       </c>
-      <c r="P411" s="4" t="n"/>
+      <c r="P411" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="3" t="inlineStr">
@@ -12017,7 +12029,11 @@
           <t>External</t>
         </is>
       </c>
-      <c r="P412" s="4" t="n"/>
+      <c r="P412" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="6" t="inlineStr">
@@ -12043,7 +12059,11 @@
           <t>External</t>
         </is>
       </c>
-      <c r="P413" s="7" t="n"/>
+      <c r="P413" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="6" t="inlineStr">
@@ -12102,9 +12122,9 @@
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="O415" s="5" t="inlineStr">
-        <is>
-          <t>External</t>
+      <c r="O415" s="10" t="inlineStr">
+        <is>
+          <t>TOIL</t>
         </is>
       </c>
       <c r="P415" s="4" t="n"/>
@@ -12174,11 +12194,7 @@
           <t>Edit - LGBTQ+</t>
         </is>
       </c>
-      <c r="O417" s="10" t="inlineStr">
-        <is>
-          <t>TOIL</t>
-        </is>
-      </c>
+      <c r="O417" s="4" t="n"/>
       <c r="P417" s="4" t="n"/>
     </row>
     <row r="418">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -11861,7 +11861,11 @@
           <t>TOIL</t>
         </is>
       </c>
-      <c r="P408" s="4" t="n"/>
+      <c r="P408" s="10" t="inlineStr">
+        <is>
+          <t>TOIL</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="3" t="inlineStr">
@@ -12089,7 +12093,11 @@
           <t>External</t>
         </is>
       </c>
-      <c r="P414" s="7" t="n"/>
+      <c r="P414" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="3" t="inlineStr">
@@ -12127,7 +12135,11 @@
           <t>TOIL</t>
         </is>
       </c>
-      <c r="P415" s="4" t="n"/>
+      <c r="P415" s="10" t="inlineStr">
+        <is>
+          <t>TOIL</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="3" t="inlineStr">
